--- a/artfynd/A 61327-2022 artfynd.xlsx
+++ b/artfynd/A 61327-2022 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>123834641</v>
+        <v>123831277</v>
       </c>
       <c r="B2" t="n">
-        <v>78786</v>
+        <v>57506</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,37 +691,42 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Härkämäck, Härkämäck, Dlr</t>
+          <t>Härkämäck, Dlr</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>459405</v>
+        <v>459389</v>
       </c>
       <c r="R2" t="n">
-        <v>6808172</v>
+        <v>6808070</v>
       </c>
       <c r="S2" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -751,6 +756,11 @@
       <c r="AA2" t="inlineStr">
         <is>
           <t>2025-04-07</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>Miljöbild.</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -765,22 +775,22 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123829275</v>
+        <v>123834890</v>
       </c>
       <c r="B3" t="n">
-        <v>78523</v>
+        <v>78865</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -793,34 +803,34 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>228912</v>
+        <v>864</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Lynge) Ahti</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Andljusbäcken, Andljusbäcken, Dlr</t>
+          <t>Härkämäck, Härkämäck, Dlr</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>459544</v>
+        <v>459427</v>
       </c>
       <c r="R3" t="n">
-        <v>6807989</v>
+        <v>6808130</v>
       </c>
       <c r="S3" t="n">
         <v>20</v>
@@ -879,7 +889,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123831244</v>
+        <v>123828608</v>
       </c>
       <c r="B4" t="n">
         <v>78786</v>
@@ -915,17 +925,17 @@
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Andljusbäcken, Andljusbäcken, Dlr</t>
+          <t>Härkämäck, Dlr</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>459393</v>
+        <v>459636</v>
       </c>
       <c r="R4" t="n">
-        <v>6808027</v>
+        <v>6808042</v>
       </c>
       <c r="S4" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -955,6 +965,11 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2025-04-07</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Garnlav i synfältet i en radie av ca 50 meter. Miljöbilder.</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -969,22 +984,22 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123833841</v>
+        <v>123829197</v>
       </c>
       <c r="B5" t="n">
-        <v>78786</v>
+        <v>78523</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -997,37 +1012,37 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Härkämäck, Härkämäck, Dlr</t>
+          <t>Andljusbäcken, Andljusbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>459300</v>
+        <v>459611</v>
       </c>
       <c r="R5" t="n">
-        <v>6808144</v>
+        <v>6807987</v>
       </c>
       <c r="S5" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1071,22 +1086,22 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>123828739</v>
+        <v>123828882</v>
       </c>
       <c r="B6" t="n">
-        <v>56700</v>
+        <v>78818</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1095,46 +1110,41 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100138</v>
+        <v>185</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Härkämäck, Dlr</t>
+          <t>Andljusbäcken, Andljusbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>459636</v>
+        <v>459600</v>
       </c>
       <c r="R6" t="n">
-        <v>6808042</v>
+        <v>6808030</v>
       </c>
       <c r="S6" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1178,22 +1188,22 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>123830920</v>
+        <v>123828783</v>
       </c>
       <c r="B7" t="n">
-        <v>78431</v>
+        <v>78786</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1206,21 +1216,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1230,10 +1240,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>459462</v>
+        <v>459611</v>
       </c>
       <c r="R7" t="n">
-        <v>6808078</v>
+        <v>6808048</v>
       </c>
       <c r="S7" t="n">
         <v>20</v>
@@ -1292,10 +1302,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>123828608</v>
+        <v>123830162</v>
       </c>
       <c r="B8" t="n">
-        <v>78786</v>
+        <v>78170</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1308,21 +1318,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>6437</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1332,10 +1342,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>459636</v>
+        <v>459480</v>
       </c>
       <c r="R8" t="n">
-        <v>6808042</v>
+        <v>6808013</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1372,7 +1382,7 @@
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>Garnlav i synfältet i en radie av ca 50 meter. Miljöbilder.</t>
+          <t>Miljöbild.</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1399,10 +1409,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>123831065</v>
+        <v>123834034</v>
       </c>
       <c r="B9" t="n">
-        <v>78786</v>
+        <v>57506</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1415,34 +1425,39 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Andljusbäcken, Andljusbäcken, Dlr</t>
+          <t>Andljusen, Dlr</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>459425</v>
+        <v>459325</v>
       </c>
       <c r="R9" t="n">
-        <v>6808084</v>
+        <v>6808176</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1477,6 +1492,11 @@
           <t>2025-04-07</t>
         </is>
       </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Miljöbild.</t>
+        </is>
+      </c>
       <c r="AD9" t="b">
         <v>0</v>
       </c>
@@ -1489,22 +1509,22 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>123833729</v>
+        <v>123829982</v>
       </c>
       <c r="B10" t="n">
-        <v>78523</v>
+        <v>77714</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1517,37 +1537,37 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>228912</v>
+        <v>6487</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Blågrå svartspik</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Chaenothecopsis fennica</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Laurila) Tibell</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Andljusen, Dlr</t>
+          <t>Andljusbäcken, Andljusbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>459286</v>
+        <v>459432</v>
       </c>
       <c r="R10" t="n">
-        <v>6808090</v>
+        <v>6807989</v>
       </c>
       <c r="S10" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1577,11 +1597,6 @@
       <c r="AA10" t="inlineStr">
         <is>
           <t>2025-04-07</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>Miljöbild.</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1596,19 +1611,19 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>123835135</v>
+        <v>123831067</v>
       </c>
       <c r="B11" t="n">
         <v>78786</v>
@@ -1648,10 +1663,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>459455</v>
+        <v>459439</v>
       </c>
       <c r="R11" t="n">
-        <v>6808164</v>
+        <v>6808067</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1688,7 +1703,7 @@
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>Garnlav i en radie av ca 50 meter, synfältet. Miljöbild.</t>
+          <t>Synligt i en radie av ca 50 meter. Miljöbild.</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1715,10 +1730,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>123829197</v>
+        <v>123828742</v>
       </c>
       <c r="B12" t="n">
-        <v>78523</v>
+        <v>78786</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1731,21 +1746,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1755,10 +1770,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>459611</v>
+        <v>459612</v>
       </c>
       <c r="R12" t="n">
-        <v>6807987</v>
+        <v>6808068</v>
       </c>
       <c r="S12" t="n">
         <v>20</v>
@@ -1817,10 +1832,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>123829632</v>
+        <v>123829102</v>
       </c>
       <c r="B13" t="n">
-        <v>91275</v>
+        <v>78786</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1833,37 +1848,37 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>658</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Härkämäck, Dlr</t>
+          <t>Andljusbäcken, Andljusbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>459573</v>
+        <v>459666</v>
       </c>
       <c r="R13" t="n">
-        <v>6808047</v>
+        <v>6807990</v>
       </c>
       <c r="S13" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1907,22 +1922,22 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>123829982</v>
+        <v>123834195</v>
       </c>
       <c r="B14" t="n">
-        <v>77714</v>
+        <v>78523</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1935,37 +1950,37 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6487</v>
+        <v>228912</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Blågrå svartspik</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Chaenothecopsis fennica</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Laurila) Tibell</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Andljusbäcken, Andljusbäcken, Dlr</t>
+          <t>Härkämäck, Härkämäck, Dlr</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>459432</v>
+        <v>459365</v>
       </c>
       <c r="R14" t="n">
-        <v>6807989</v>
+        <v>6808224</v>
       </c>
       <c r="S14" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2009,22 +2024,22 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>123834220</v>
+        <v>123831097</v>
       </c>
       <c r="B15" t="n">
-        <v>78786</v>
+        <v>79375</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2037,37 +2052,37 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6425</v>
+        <v>229821</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Andljusen, Dlr</t>
+          <t>Andljusbäcken, Andljusbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>459325</v>
+        <v>459402</v>
       </c>
       <c r="R15" t="n">
-        <v>6808176</v>
+        <v>6808072</v>
       </c>
       <c r="S15" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2097,11 +2112,6 @@
       <c r="AA15" t="inlineStr">
         <is>
           <t>2025-04-07</t>
-        </is>
-      </c>
-      <c r="AC15" t="inlineStr">
-        <is>
-          <t>I synfält, radie av ca 50 meter. Miljöbild.</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2116,22 +2126,22 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>123828742</v>
+        <v>123834998</v>
       </c>
       <c r="B16" t="n">
-        <v>78786</v>
+        <v>79375</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2144,34 +2154,34 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6425</v>
+        <v>229821</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Andljusbäcken, Andljusbäcken, Dlr</t>
+          <t>Härkämäck, Härkämäck, Dlr</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>459612</v>
+        <v>459437</v>
       </c>
       <c r="R16" t="n">
-        <v>6808068</v>
+        <v>6808171</v>
       </c>
       <c r="S16" t="n">
         <v>20</v>
@@ -2230,10 +2240,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>123831067</v>
+        <v>123828739</v>
       </c>
       <c r="B17" t="n">
-        <v>78786</v>
+        <v>56700</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2242,38 +2252,43 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="P17" t="inlineStr">
         <is>
           <t>Härkämäck, Dlr</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>459439</v>
+        <v>459636</v>
       </c>
       <c r="R17" t="n">
-        <v>6808067</v>
+        <v>6808042</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2306,11 +2321,6 @@
       <c r="AA17" t="inlineStr">
         <is>
           <t>2025-04-07</t>
-        </is>
-      </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>Synligt i en radie av ca 50 meter. Miljöbild.</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2337,10 +2347,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>123831578</v>
+        <v>123829310</v>
       </c>
       <c r="B18" t="n">
-        <v>74878</v>
+        <v>57506</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2353,37 +2363,42 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6440</v>
+        <v>100049</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Andljusbäcken, Andljusbäcken, Dlr</t>
+          <t>Härkämäck, Dlr</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>459287</v>
+        <v>459586</v>
       </c>
       <c r="R18" t="n">
-        <v>6808008</v>
+        <v>6807981</v>
       </c>
       <c r="S18" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2427,22 +2442,22 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>123833917</v>
+        <v>123835432</v>
       </c>
       <c r="B19" t="n">
-        <v>78523</v>
+        <v>78786</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2455,37 +2470,37 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Andljusbäcken, Andljusbäcken, Dlr</t>
+          <t>Härkämäck, Dlr</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>459292</v>
+        <v>459524</v>
       </c>
       <c r="R19" t="n">
-        <v>6808184</v>
+        <v>6808114</v>
       </c>
       <c r="S19" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2515,6 +2530,11 @@
       <c r="AA19" t="inlineStr">
         <is>
           <t>2025-04-07</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>Garnlav i alla riktningar, ca 50 meter i radie. Miljöbild.</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2529,22 +2549,22 @@
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>123834630</v>
+        <v>123830920</v>
       </c>
       <c r="B20" t="n">
-        <v>57511</v>
+        <v>78431</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2553,41 +2573,41 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>100110</v>
+        <v>353</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Gråspett</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Picus canus</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>J.F. Gmelin, 1788</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Härkämäck, Härkämäck, Dlr</t>
+          <t>Andljusbäcken, Andljusbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>459408</v>
+        <v>459462</v>
       </c>
       <c r="R20" t="n">
-        <v>6808198</v>
+        <v>6808078</v>
       </c>
       <c r="S20" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2617,11 +2637,6 @@
       <c r="AA20" t="inlineStr">
         <is>
           <t>2025-04-07</t>
-        </is>
-      </c>
-      <c r="AC20" t="inlineStr">
-        <is>
-          <t>Förbiflygande.</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2636,19 +2651,19 @@
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>123829121</v>
+        <v>123829879</v>
       </c>
       <c r="B21" t="n">
         <v>78786</v>
@@ -2684,17 +2699,17 @@
       <c r="I21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Härkämäck, Dlr</t>
+          <t>Andljusbäcken, Andljusbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>459641</v>
+        <v>459488</v>
       </c>
       <c r="R21" t="n">
-        <v>6807971</v>
+        <v>6807974</v>
       </c>
       <c r="S21" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2724,11 +2739,6 @@
       <c r="AA21" t="inlineStr">
         <is>
           <t>2025-04-07</t>
-        </is>
-      </c>
-      <c r="AC21" t="inlineStr">
-        <is>
-          <t>I synfältet i en radie av ca 40 meter. Miljöbild.</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2743,22 +2753,22 @@
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>123829310</v>
+        <v>123829712</v>
       </c>
       <c r="B22" t="n">
-        <v>57506</v>
+        <v>90988</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2771,39 +2781,34 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>100049</v>
+        <v>1202</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
-      <c r="M22" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P22" t="inlineStr">
         <is>
           <t>Härkämäck, Dlr</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>459586</v>
+        <v>459573</v>
       </c>
       <c r="R22" t="n">
-        <v>6807981</v>
+        <v>6808047</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2862,7 +2867,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>123829889</v>
+        <v>123833917</v>
       </c>
       <c r="B23" t="n">
         <v>78523</v>
@@ -2898,17 +2903,17 @@
       <c r="I23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Härkämäck, Dlr</t>
+          <t>Andljusbäcken, Andljusbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>459494</v>
+        <v>459292</v>
       </c>
       <c r="R23" t="n">
-        <v>6807997</v>
+        <v>6808184</v>
       </c>
       <c r="S23" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -2938,11 +2943,6 @@
       <c r="AA23" t="inlineStr">
         <is>
           <t>2025-04-07</t>
-        </is>
-      </c>
-      <c r="AC23" t="inlineStr">
-        <is>
-          <t>Miljöbild.</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -2957,22 +2957,22 @@
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>123834966</v>
+        <v>123829918</v>
       </c>
       <c r="B24" t="n">
-        <v>57511</v>
+        <v>78522</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -2981,46 +2981,41 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>100110</v>
+        <v>6446</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Gråspett</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Picus canus</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>J.F. Gmelin, 1788</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
-      <c r="M24" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Härkämäck, Dlr</t>
+          <t>Andljusbäcken, Andljusbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>459399</v>
+        <v>459424</v>
       </c>
       <c r="R24" t="n">
-        <v>6808189</v>
+        <v>6807998</v>
       </c>
       <c r="S24" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3050,11 +3045,6 @@
       <c r="AA24" t="inlineStr">
         <is>
           <t>2025-04-07</t>
-        </is>
-      </c>
-      <c r="AC24" t="inlineStr">
-        <is>
-          <t>Förbiflygande.</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3069,22 +3059,22 @@
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>123834890</v>
+        <v>123829889</v>
       </c>
       <c r="B25" t="n">
-        <v>78865</v>
+        <v>78523</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3097,37 +3087,37 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>864</v>
+        <v>228912</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Knottrig blåslav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Hypogymnia bitteri</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Lynge) Ahti</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Härkämäck, Härkämäck, Dlr</t>
+          <t>Härkämäck, Dlr</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>459427</v>
+        <v>459494</v>
       </c>
       <c r="R25" t="n">
-        <v>6808130</v>
+        <v>6807997</v>
       </c>
       <c r="S25" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3157,6 +3147,11 @@
       <c r="AA25" t="inlineStr">
         <is>
           <t>2025-04-07</t>
+        </is>
+      </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>Miljöbild.</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3171,19 +3166,19 @@
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>123834195</v>
+        <v>123829941</v>
       </c>
       <c r="B26" t="n">
         <v>78523</v>
@@ -3219,14 +3214,14 @@
       <c r="I26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Härkämäck, Härkämäck, Dlr</t>
+          <t>Härkämäck, Dlr</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>459365</v>
+        <v>459480</v>
       </c>
       <c r="R26" t="n">
-        <v>6808224</v>
+        <v>6808013</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3261,6 +3256,11 @@
           <t>2025-04-07</t>
         </is>
       </c>
+      <c r="AC26" t="inlineStr">
+        <is>
+          <t>Miljöbild.</t>
+        </is>
+      </c>
       <c r="AD26" t="b">
         <v>0</v>
       </c>
@@ -3273,12 +3273,12 @@
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
@@ -3387,10 +3387,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>123834006</v>
+        <v>123829394</v>
       </c>
       <c r="B28" t="n">
-        <v>78523</v>
+        <v>77714</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3403,37 +3403,37 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>228912</v>
+        <v>6487</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Blågrå svartspik</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Chaenothecopsis fennica</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Laurila) Tibell</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Härkämäck, Härkämäck, Dlr</t>
+          <t>Härkämäck, Dlr</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>459326</v>
+        <v>459586</v>
       </c>
       <c r="R28" t="n">
-        <v>6808188</v>
+        <v>6807981</v>
       </c>
       <c r="S28" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3477,22 +3477,22 @@
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>123829712</v>
+        <v>123829275</v>
       </c>
       <c r="B29" t="n">
-        <v>90988</v>
+        <v>78523</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3505,37 +3505,37 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>1202</v>
+        <v>228912</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Härkämäck, Dlr</t>
+          <t>Andljusbäcken, Andljusbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>459573</v>
+        <v>459544</v>
       </c>
       <c r="R29" t="n">
-        <v>6808047</v>
+        <v>6807989</v>
       </c>
       <c r="S29" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3579,22 +3579,22 @@
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>123829394</v>
+        <v>123834567</v>
       </c>
       <c r="B30" t="n">
-        <v>77714</v>
+        <v>79375</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3607,21 +3607,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6487</v>
+        <v>229821</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Blågrå svartspik</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Chaenothecopsis fennica</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Laurila) Tibell</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3631,10 +3631,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>459586</v>
+        <v>459399</v>
       </c>
       <c r="R30" t="n">
-        <v>6807981</v>
+        <v>6808189</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3667,6 +3667,11 @@
       <c r="AA30" t="inlineStr">
         <is>
           <t>2025-04-07</t>
+        </is>
+      </c>
+      <c r="AC30" t="inlineStr">
+        <is>
+          <t>Miljöbild.</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3693,10 +3698,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>123834998</v>
+        <v>123834966</v>
       </c>
       <c r="B31" t="n">
-        <v>79375</v>
+        <v>57511</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3705,41 +3710,46 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>229821</v>
+        <v>100110</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Gråspett</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Picus canus</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>J.F. Gmelin, 1788</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Härkämäck, Härkämäck, Dlr</t>
+          <t>Härkämäck, Dlr</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>459437</v>
+        <v>459399</v>
       </c>
       <c r="R31" t="n">
-        <v>6808171</v>
+        <v>6808189</v>
       </c>
       <c r="S31" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -3769,6 +3779,11 @@
       <c r="AA31" t="inlineStr">
         <is>
           <t>2025-04-07</t>
+        </is>
+      </c>
+      <c r="AC31" t="inlineStr">
+        <is>
+          <t>Förbiflygande.</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3783,22 +3798,22 @@
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>123834034</v>
+        <v>123831065</v>
       </c>
       <c r="B32" t="n">
-        <v>57506</v>
+        <v>78786</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -3811,39 +3826,34 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
-      <c r="M32" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Andljusen, Dlr</t>
+          <t>Andljusbäcken, Andljusbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>459325</v>
+        <v>459425</v>
       </c>
       <c r="R32" t="n">
-        <v>6808176</v>
+        <v>6808084</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3878,11 +3888,6 @@
           <t>2025-04-07</t>
         </is>
       </c>
-      <c r="AC32" t="inlineStr">
-        <is>
-          <t>Miljöbild.</t>
-        </is>
-      </c>
       <c r="AD32" t="b">
         <v>0</v>
       </c>
@@ -3895,22 +3900,22 @@
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>123830162</v>
+        <v>123831578</v>
       </c>
       <c r="B33" t="n">
-        <v>78170</v>
+        <v>74878</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -3923,37 +3928,37 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6437</v>
+        <v>6440</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Härkämäck, Dlr</t>
+          <t>Andljusbäcken, Andljusbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>459480</v>
+        <v>459287</v>
       </c>
       <c r="R33" t="n">
-        <v>6808013</v>
+        <v>6808008</v>
       </c>
       <c r="S33" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -3983,11 +3988,6 @@
       <c r="AA33" t="inlineStr">
         <is>
           <t>2025-04-07</t>
-        </is>
-      </c>
-      <c r="AC33" t="inlineStr">
-        <is>
-          <t>Miljöbild.</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4002,22 +4002,22 @@
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>123831277</v>
+        <v>123834650</v>
       </c>
       <c r="B34" t="n">
-        <v>57506</v>
+        <v>78523</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4030,39 +4030,34 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>100049</v>
+        <v>228912</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
-      <c r="M34" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P34" t="inlineStr">
         <is>
           <t>Härkämäck, Dlr</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>459389</v>
+        <v>459399</v>
       </c>
       <c r="R34" t="n">
-        <v>6808070</v>
+        <v>6808189</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4099,7 +4094,7 @@
       </c>
       <c r="AC34" t="inlineStr">
         <is>
-          <t>Miljöbild.</t>
+          <t>Miljöbild</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4126,10 +4121,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>123831097</v>
+        <v>123835135</v>
       </c>
       <c r="B35" t="n">
-        <v>79375</v>
+        <v>78786</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4142,37 +4137,37 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>229821</v>
+        <v>6425</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Andljusbäcken, Andljusbäcken, Dlr</t>
+          <t>Härkämäck, Dlr</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>459402</v>
+        <v>459455</v>
       </c>
       <c r="R35" t="n">
-        <v>6808072</v>
+        <v>6808164</v>
       </c>
       <c r="S35" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -4202,6 +4197,11 @@
       <c r="AA35" t="inlineStr">
         <is>
           <t>2025-04-07</t>
+        </is>
+      </c>
+      <c r="AC35" t="inlineStr">
+        <is>
+          <t>Garnlav i en radie av ca 50 meter, synfältet. Miljöbild.</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4216,22 +4216,22 @@
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>123830009</v>
+        <v>123834006</v>
       </c>
       <c r="B36" t="n">
-        <v>78522</v>
+        <v>78523</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4244,37 +4244,37 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6446</v>
+        <v>228912</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Härkämäck, Dlr</t>
+          <t>Härkämäck, Härkämäck, Dlr</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>459480</v>
+        <v>459326</v>
       </c>
       <c r="R36" t="n">
-        <v>6808013</v>
+        <v>6808188</v>
       </c>
       <c r="S36" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -4304,11 +4304,6 @@
       <c r="AA36" t="inlineStr">
         <is>
           <t>2025-04-07</t>
-        </is>
-      </c>
-      <c r="AC36" t="inlineStr">
-        <is>
-          <t>Miljöbild.</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4323,22 +4318,22 @@
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>123833814</v>
+        <v>123833841</v>
       </c>
       <c r="B37" t="n">
-        <v>78523</v>
+        <v>78786</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4351,21 +4346,21 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4375,10 +4370,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>459293</v>
+        <v>459300</v>
       </c>
       <c r="R37" t="n">
-        <v>6808123</v>
+        <v>6808144</v>
       </c>
       <c r="S37" t="n">
         <v>15</v>
@@ -4437,7 +4432,7 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>123828783</v>
+        <v>123829121</v>
       </c>
       <c r="B38" t="n">
         <v>78786</v>
@@ -4473,17 +4468,17 @@
       <c r="I38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
-          <t>Andljusbäcken, Andljusbäcken, Dlr</t>
+          <t>Härkämäck, Dlr</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>459611</v>
+        <v>459641</v>
       </c>
       <c r="R38" t="n">
-        <v>6808048</v>
+        <v>6807971</v>
       </c>
       <c r="S38" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -4513,6 +4508,11 @@
       <c r="AA38" t="inlineStr">
         <is>
           <t>2025-04-07</t>
+        </is>
+      </c>
+      <c r="AC38" t="inlineStr">
+        <is>
+          <t>I synfältet i en radie av ca 40 meter. Miljöbild.</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4527,22 +4527,22 @@
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>123829918</v>
+        <v>123829246</v>
       </c>
       <c r="B39" t="n">
-        <v>78522</v>
+        <v>78786</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4555,37 +4555,37 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
-          <t>Andljusbäcken, Andljusbäcken, Dlr</t>
+          <t>Härkämäck, Dlr</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>459424</v>
+        <v>459586</v>
       </c>
       <c r="R39" t="n">
-        <v>6807998</v>
+        <v>6807981</v>
       </c>
       <c r="S39" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
@@ -4615,6 +4615,11 @@
       <c r="AA39" t="inlineStr">
         <is>
           <t>2025-04-07</t>
+        </is>
+      </c>
+      <c r="AC39" t="inlineStr">
+        <is>
+          <t>Som vanligt garnlav i omgivningen. Miljöbilder.</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4629,22 +4634,22 @@
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>123828044</v>
+        <v>123829632</v>
       </c>
       <c r="B40" t="n">
-        <v>78786</v>
+        <v>91275</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -4657,21 +4662,21 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6425</v>
+        <v>658</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4681,10 +4686,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>459681</v>
+        <v>459573</v>
       </c>
       <c r="R40" t="n">
-        <v>6808072</v>
+        <v>6808047</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4717,11 +4722,6 @@
       <c r="AA40" t="inlineStr">
         <is>
           <t>2025-04-07</t>
-        </is>
-      </c>
-      <c r="AC40" t="inlineStr">
-        <is>
-          <t>Garnlav i synfältet i en radie av ca 50 meter. Miljöbild.</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4748,10 +4748,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>123827957</v>
+        <v>123833814</v>
       </c>
       <c r="B41" t="n">
-        <v>78522</v>
+        <v>78523</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -4764,37 +4764,37 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6446</v>
+        <v>228912</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
-          <t>Andljusbäcken, Andljusbäcken, Dlr</t>
+          <t>Härkämäck, Härkämäck, Dlr</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>459664</v>
+        <v>459293</v>
       </c>
       <c r="R41" t="n">
-        <v>6808079</v>
+        <v>6808123</v>
       </c>
       <c r="S41" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -4838,22 +4838,22 @@
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>123834567</v>
+        <v>123833729</v>
       </c>
       <c r="B42" t="n">
-        <v>79375</v>
+        <v>78523</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -4866,34 +4866,34 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>229821</v>
+        <v>228912</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
-          <t>Härkämäck, Dlr</t>
+          <t>Andljusen, Dlr</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>459399</v>
+        <v>459286</v>
       </c>
       <c r="R42" t="n">
-        <v>6808189</v>
+        <v>6808090</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4957,10 +4957,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>123829941</v>
+        <v>123834630</v>
       </c>
       <c r="B43" t="n">
-        <v>78523</v>
+        <v>57511</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -4969,38 +4969,38 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>228912</v>
+        <v>100110</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Gråspett</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Picus canus</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>J.F. Gmelin, 1788</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
-          <t>Härkämäck, Dlr</t>
+          <t>Härkämäck, Härkämäck, Dlr</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>459480</v>
+        <v>459408</v>
       </c>
       <c r="R43" t="n">
-        <v>6808013</v>
+        <v>6808198</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5037,7 +5037,7 @@
       </c>
       <c r="AC43" t="inlineStr">
         <is>
-          <t>Miljöbild.</t>
+          <t>Förbiflygande.</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5052,22 +5052,22 @@
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>123829205</v>
+        <v>123834641</v>
       </c>
       <c r="B44" t="n">
-        <v>78522</v>
+        <v>78786</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5080,34 +5080,34 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
-          <t>Andljusbäcken, Andljusbäcken, Dlr</t>
+          <t>Härkämäck, Härkämäck, Dlr</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>459611</v>
+        <v>459405</v>
       </c>
       <c r="R44" t="n">
-        <v>6807987</v>
+        <v>6808172</v>
       </c>
       <c r="S44" t="n">
         <v>20</v>
@@ -5166,10 +5166,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>123828882</v>
+        <v>123827957</v>
       </c>
       <c r="B45" t="n">
-        <v>78818</v>
+        <v>78522</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5182,21 +5182,21 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>185</v>
+        <v>6446</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5206,10 +5206,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>459600</v>
+        <v>459664</v>
       </c>
       <c r="R45" t="n">
-        <v>6808030</v>
+        <v>6808079</v>
       </c>
       <c r="S45" t="n">
         <v>20</v>
@@ -5268,10 +5268,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>123829246</v>
+        <v>123829205</v>
       </c>
       <c r="B46" t="n">
-        <v>78786</v>
+        <v>78522</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5284,37 +5284,37 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
-          <t>Härkämäck, Dlr</t>
+          <t>Andljusbäcken, Andljusbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>459586</v>
+        <v>459611</v>
       </c>
       <c r="R46" t="n">
-        <v>6807981</v>
+        <v>6807987</v>
       </c>
       <c r="S46" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T46" t="inlineStr">
         <is>
@@ -5344,11 +5344,6 @@
       <c r="AA46" t="inlineStr">
         <is>
           <t>2025-04-07</t>
-        </is>
-      </c>
-      <c r="AC46" t="inlineStr">
-        <is>
-          <t>Som vanligt garnlav i omgivningen. Miljöbilder.</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5363,19 +5358,19 @@
       <c r="AT46" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX46" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>123829102</v>
+        <v>123831244</v>
       </c>
       <c r="B47" t="n">
         <v>78786</v>
@@ -5415,10 +5410,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>459666</v>
+        <v>459393</v>
       </c>
       <c r="R47" t="n">
-        <v>6807990</v>
+        <v>6808027</v>
       </c>
       <c r="S47" t="n">
         <v>20</v>
@@ -5477,10 +5472,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>123835432</v>
+        <v>123831467</v>
       </c>
       <c r="B48" t="n">
-        <v>78786</v>
+        <v>79375</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -5493,34 +5488,34 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>6425</v>
+        <v>229821</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
-          <t>Härkämäck, Dlr</t>
+          <t>Härkämäck, Härkämäck, Dlr</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>459524</v>
+        <v>459290</v>
       </c>
       <c r="R48" t="n">
-        <v>6808114</v>
+        <v>6808098</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5555,11 +5550,6 @@
           <t>2025-04-07</t>
         </is>
       </c>
-      <c r="AC48" t="inlineStr">
-        <is>
-          <t>Garnlav i alla riktningar, ca 50 meter i radie. Miljöbild.</t>
-        </is>
-      </c>
       <c r="AD48" t="b">
         <v>0</v>
       </c>
@@ -5572,19 +5562,19 @@
       <c r="AT48" t="inlineStr"/>
       <c r="AW48" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Niklas Rehn</t>
         </is>
       </c>
       <c r="AX48" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Niklas Rehn</t>
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>123829879</v>
+        <v>123834220</v>
       </c>
       <c r="B49" t="n">
         <v>78786</v>
@@ -5620,17 +5610,17 @@
       <c r="I49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
-          <t>Andljusbäcken, Andljusbäcken, Dlr</t>
+          <t>Andljusen, Dlr</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>459488</v>
+        <v>459325</v>
       </c>
       <c r="R49" t="n">
-        <v>6807974</v>
+        <v>6808176</v>
       </c>
       <c r="S49" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T49" t="inlineStr">
         <is>
@@ -5660,6 +5650,11 @@
       <c r="AA49" t="inlineStr">
         <is>
           <t>2025-04-07</t>
+        </is>
+      </c>
+      <c r="AC49" t="inlineStr">
+        <is>
+          <t>I synfält, radie av ca 50 meter. Miljöbild.</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -5674,22 +5669,22 @@
       <c r="AT49" t="inlineStr"/>
       <c r="AW49" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX49" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>123833754</v>
+        <v>123828044</v>
       </c>
       <c r="B50" t="n">
-        <v>92269</v>
+        <v>78786</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -5698,41 +5693,41 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
-          <t>Härkämäck, Härkämäck, Dlr</t>
+          <t>Härkämäck, Dlr</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>459290</v>
+        <v>459681</v>
       </c>
       <c r="R50" t="n">
-        <v>6808093</v>
+        <v>6808072</v>
       </c>
       <c r="S50" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T50" t="inlineStr">
         <is>
@@ -5762,6 +5757,11 @@
       <c r="AA50" t="inlineStr">
         <is>
           <t>2025-04-07</t>
+        </is>
+      </c>
+      <c r="AC50" t="inlineStr">
+        <is>
+          <t>Garnlav i synfältet i en radie av ca 50 meter. Miljöbild.</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -5776,22 +5776,22 @@
       <c r="AT50" t="inlineStr"/>
       <c r="AW50" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX50" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>123834650</v>
+        <v>123833754</v>
       </c>
       <c r="B51" t="n">
-        <v>78523</v>
+        <v>92269</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -5800,41 +5800,41 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>228912</v>
+        <v>4364</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
-          <t>Härkämäck, Dlr</t>
+          <t>Härkämäck, Härkämäck, Dlr</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>459399</v>
+        <v>459290</v>
       </c>
       <c r="R51" t="n">
-        <v>6808189</v>
+        <v>6808093</v>
       </c>
       <c r="S51" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T51" t="inlineStr">
         <is>
@@ -5864,11 +5864,6 @@
       <c r="AA51" t="inlineStr">
         <is>
           <t>2025-04-07</t>
-        </is>
-      </c>
-      <c r="AC51" t="inlineStr">
-        <is>
-          <t>Miljöbild</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -5883,22 +5878,22 @@
       <c r="AT51" t="inlineStr"/>
       <c r="AW51" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX51" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>123831467</v>
+        <v>123830009</v>
       </c>
       <c r="B52" t="n">
-        <v>79375</v>
+        <v>78522</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -5911,34 +5906,34 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>229821</v>
+        <v>6446</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
-          <t>Härkämäck, Härkämäck, Dlr</t>
+          <t>Härkämäck, Dlr</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>459290</v>
+        <v>459480</v>
       </c>
       <c r="R52" t="n">
-        <v>6808098</v>
+        <v>6808013</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -5973,6 +5968,11 @@
           <t>2025-04-07</t>
         </is>
       </c>
+      <c r="AC52" t="inlineStr">
+        <is>
+          <t>Miljöbild.</t>
+        </is>
+      </c>
       <c r="AD52" t="b">
         <v>0</v>
       </c>
@@ -5985,12 +5985,12 @@
       <c r="AT52" t="inlineStr"/>
       <c r="AW52" t="inlineStr">
         <is>
-          <t>Niklas Rehn</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX52" t="inlineStr">
         <is>
-          <t>Niklas Rehn</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>

--- a/artfynd/A 61327-2022 artfynd.xlsx
+++ b/artfynd/A 61327-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY52"/>
+  <dimension ref="A1:AY68"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>123831277</v>
+        <v>123834183</v>
       </c>
       <c r="B2" t="n">
-        <v>57506</v>
+        <v>78788</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,42 +691,37 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Härkämäck, Dlr</t>
+          <t>Andljusbäcken, Andljusbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>459389</v>
+        <v>459373</v>
       </c>
       <c r="R2" t="n">
-        <v>6808070</v>
+        <v>6808222</v>
       </c>
       <c r="S2" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -756,11 +751,6 @@
       <c r="AA2" t="inlineStr">
         <is>
           <t>2025-04-07</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Miljöbild.</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -775,22 +765,22 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123834890</v>
+        <v>123834567</v>
       </c>
       <c r="B3" t="n">
-        <v>78865</v>
+        <v>79377</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -803,37 +793,37 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>864</v>
+        <v>229821</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Knottrig blåslav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hypogymnia bitteri</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Lynge) Ahti</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Härkämäck, Härkämäck, Dlr</t>
+          <t>Härkämäck, Dlr</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>459427</v>
+        <v>459399</v>
       </c>
       <c r="R3" t="n">
-        <v>6808130</v>
+        <v>6808189</v>
       </c>
       <c r="S3" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -863,6 +853,11 @@
       <c r="AA3" t="inlineStr">
         <is>
           <t>2025-04-07</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Miljöbild.</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -877,22 +872,22 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123828608</v>
+        <v>123831097</v>
       </c>
       <c r="B4" t="n">
-        <v>78786</v>
+        <v>79377</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -905,37 +900,37 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>229821</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Härkämäck, Dlr</t>
+          <t>Andljusbäcken, Andljusbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>459636</v>
+        <v>459402</v>
       </c>
       <c r="R4" t="n">
-        <v>6808042</v>
+        <v>6808072</v>
       </c>
       <c r="S4" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -965,11 +960,6 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2025-04-07</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Garnlav i synfältet i en radie av ca 50 meter. Miljöbilder.</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -984,22 +974,22 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123829197</v>
+        <v>123829982</v>
       </c>
       <c r="B5" t="n">
-        <v>78523</v>
+        <v>77716</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1012,21 +1002,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>228912</v>
+        <v>6487</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Blågrå svartspik</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Chaenothecopsis fennica</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Laurila) Tibell</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1036,10 +1026,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>459611</v>
+        <v>459432</v>
       </c>
       <c r="R5" t="n">
-        <v>6807987</v>
+        <v>6807989</v>
       </c>
       <c r="S5" t="n">
         <v>20</v>
@@ -1098,10 +1088,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>123828882</v>
+        <v>123833841</v>
       </c>
       <c r="B6" t="n">
-        <v>78818</v>
+        <v>78788</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1114,37 +1104,37 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Andljusbäcken, Andljusbäcken, Dlr</t>
+          <t>Härkämäck, Härkämäck, Dlr</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>459600</v>
+        <v>459300</v>
       </c>
       <c r="R6" t="n">
-        <v>6808030</v>
+        <v>6808144</v>
       </c>
       <c r="S6" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1188,22 +1178,22 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>123828783</v>
+        <v>123834650</v>
       </c>
       <c r="B7" t="n">
-        <v>78786</v>
+        <v>78525</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1216,37 +1206,37 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Andljusbäcken, Andljusbäcken, Dlr</t>
+          <t>Härkämäck, Dlr</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>459611</v>
+        <v>459399</v>
       </c>
       <c r="R7" t="n">
-        <v>6808048</v>
+        <v>6808189</v>
       </c>
       <c r="S7" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1276,6 +1266,11 @@
       <c r="AA7" t="inlineStr">
         <is>
           <t>2025-04-07</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Miljöbild</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1290,22 +1285,22 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>123830162</v>
+        <v>123829879</v>
       </c>
       <c r="B8" t="n">
-        <v>78170</v>
+        <v>78788</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1318,37 +1313,37 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6437</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Härkämäck, Dlr</t>
+          <t>Andljusbäcken, Andljusbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>459480</v>
+        <v>459488</v>
       </c>
       <c r="R8" t="n">
-        <v>6808013</v>
+        <v>6807974</v>
       </c>
       <c r="S8" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1378,11 +1373,6 @@
       <c r="AA8" t="inlineStr">
         <is>
           <t>2025-04-07</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>Miljöbild.</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1397,22 +1387,22 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>123834034</v>
+        <v>123829918</v>
       </c>
       <c r="B9" t="n">
-        <v>57506</v>
+        <v>78524</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1425,42 +1415,37 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100049</v>
+        <v>6446</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Andljusen, Dlr</t>
+          <t>Andljusbäcken, Andljusbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>459325</v>
+        <v>459424</v>
       </c>
       <c r="R9" t="n">
-        <v>6808176</v>
+        <v>6807998</v>
       </c>
       <c r="S9" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1490,11 +1475,6 @@
       <c r="AA9" t="inlineStr">
         <is>
           <t>2025-04-07</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>Miljöbild.</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1509,22 +1489,22 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>123829982</v>
+        <v>123835432</v>
       </c>
       <c r="B10" t="n">
-        <v>77714</v>
+        <v>78788</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1537,37 +1517,37 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6487</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Blågrå svartspik</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Chaenothecopsis fennica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Laurila) Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Andljusbäcken, Andljusbäcken, Dlr</t>
+          <t>Härkämäck, Dlr</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>459432</v>
+        <v>459524</v>
       </c>
       <c r="R10" t="n">
-        <v>6807989</v>
+        <v>6808114</v>
       </c>
       <c r="S10" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1597,6 +1577,11 @@
       <c r="AA10" t="inlineStr">
         <is>
           <t>2025-04-07</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Garnlav i alla riktningar, ca 50 meter i radie. Miljöbild.</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1611,22 +1596,22 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>123831067</v>
+        <v>123834195</v>
       </c>
       <c r="B11" t="n">
-        <v>78786</v>
+        <v>78525</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1639,34 +1624,34 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Härkämäck, Dlr</t>
+          <t>Härkämäck, Härkämäck, Dlr</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>459439</v>
+        <v>459365</v>
       </c>
       <c r="R11" t="n">
-        <v>6808067</v>
+        <v>6808224</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1701,11 +1686,6 @@
           <t>2025-04-07</t>
         </is>
       </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>Synligt i en radie av ca 50 meter. Miljöbild.</t>
-        </is>
-      </c>
       <c r="AD11" t="b">
         <v>0</v>
       </c>
@@ -1718,22 +1698,22 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>123828742</v>
+        <v>123828826</v>
       </c>
       <c r="B12" t="n">
-        <v>78786</v>
+        <v>56700</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1742,41 +1722,46 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Andljusbäcken, Andljusbäcken, Dlr</t>
+          <t>Härkämäck, Dlr</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>459612</v>
+        <v>459636</v>
       </c>
       <c r="R12" t="n">
-        <v>6808068</v>
+        <v>6808042</v>
       </c>
       <c r="S12" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1806,6 +1791,11 @@
       <c r="AA12" t="inlineStr">
         <is>
           <t>2025-04-07</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Garnlav i bakgrund. Miljöbild.</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1820,22 +1810,22 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>123829102</v>
+        <v>123833754</v>
       </c>
       <c r="B13" t="n">
-        <v>78786</v>
+        <v>92271</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1844,41 +1834,41 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Andljusbäcken, Andljusbäcken, Dlr</t>
+          <t>Härkämäck, Härkämäck, Dlr</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>459666</v>
+        <v>459290</v>
       </c>
       <c r="R13" t="n">
-        <v>6807990</v>
+        <v>6808093</v>
       </c>
       <c r="S13" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1922,22 +1912,22 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>123834195</v>
+        <v>123829121</v>
       </c>
       <c r="B14" t="n">
-        <v>78523</v>
+        <v>78788</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1950,34 +1940,34 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Härkämäck, Härkämäck, Dlr</t>
+          <t>Härkämäck, Dlr</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>459365</v>
+        <v>459641</v>
       </c>
       <c r="R14" t="n">
-        <v>6808224</v>
+        <v>6807971</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2012,6 +2002,11 @@
           <t>2025-04-07</t>
         </is>
       </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>I synfältet i en radie av ca 40 meter. Miljöbild.</t>
+        </is>
+      </c>
       <c r="AD14" t="b">
         <v>0</v>
       </c>
@@ -2024,22 +2019,22 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>123831097</v>
+        <v>123834034</v>
       </c>
       <c r="B15" t="n">
-        <v>79375</v>
+        <v>57507</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2052,37 +2047,42 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>229821</v>
+        <v>100049</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Andljusbäcken, Andljusbäcken, Dlr</t>
+          <t>Andljusen, Dlr</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>459402</v>
+        <v>459325</v>
       </c>
       <c r="R15" t="n">
-        <v>6808072</v>
+        <v>6808176</v>
       </c>
       <c r="S15" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2112,6 +2112,11 @@
       <c r="AA15" t="inlineStr">
         <is>
           <t>2025-04-07</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>Miljöbild.</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2126,12 +2131,12 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
@@ -2141,7 +2146,7 @@
         <v>123834998</v>
       </c>
       <c r="B16" t="n">
-        <v>79375</v>
+        <v>79377</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2240,10 +2245,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>123828739</v>
+        <v>123830009</v>
       </c>
       <c r="B17" t="n">
-        <v>56700</v>
+        <v>78524</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2252,43 +2257,38 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100138</v>
+        <v>6446</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="P17" t="inlineStr">
         <is>
           <t>Härkämäck, Dlr</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>459636</v>
+        <v>459480</v>
       </c>
       <c r="R17" t="n">
-        <v>6808042</v>
+        <v>6808013</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2321,6 +2321,11 @@
       <c r="AA17" t="inlineStr">
         <is>
           <t>2025-04-07</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>Miljöbild.</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2350,7 +2355,7 @@
         <v>123829310</v>
       </c>
       <c r="B18" t="n">
-        <v>57506</v>
+        <v>57507</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2454,10 +2459,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>123835432</v>
+        <v>123831244</v>
       </c>
       <c r="B19" t="n">
-        <v>78786</v>
+        <v>78788</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2490,17 +2495,17 @@
       <c r="I19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Härkämäck, Dlr</t>
+          <t>Andljusbäcken, Andljusbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>459524</v>
+        <v>459393</v>
       </c>
       <c r="R19" t="n">
-        <v>6808114</v>
+        <v>6808027</v>
       </c>
       <c r="S19" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2530,11 +2535,6 @@
       <c r="AA19" t="inlineStr">
         <is>
           <t>2025-04-07</t>
-        </is>
-      </c>
-      <c r="AC19" t="inlineStr">
-        <is>
-          <t>Garnlav i alla riktningar, ca 50 meter i radie. Miljöbild.</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2549,22 +2549,22 @@
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>123830920</v>
+        <v>123833814</v>
       </c>
       <c r="B20" t="n">
-        <v>78431</v>
+        <v>78525</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2577,37 +2577,37 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>353</v>
+        <v>228912</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Andljusbäcken, Andljusbäcken, Dlr</t>
+          <t>Härkämäck, Härkämäck, Dlr</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>459462</v>
+        <v>459293</v>
       </c>
       <c r="R20" t="n">
-        <v>6808078</v>
+        <v>6808123</v>
       </c>
       <c r="S20" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2651,22 +2651,22 @@
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>123829879</v>
+        <v>123827957</v>
       </c>
       <c r="B21" t="n">
-        <v>78786</v>
+        <v>78524</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2679,21 +2679,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2703,10 +2703,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>459488</v>
+        <v>459664</v>
       </c>
       <c r="R21" t="n">
-        <v>6807974</v>
+        <v>6808079</v>
       </c>
       <c r="S21" t="n">
         <v>20</v>
@@ -2765,10 +2765,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>123829712</v>
+        <v>123830162</v>
       </c>
       <c r="B22" t="n">
-        <v>90988</v>
+        <v>78172</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2781,21 +2781,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>1202</v>
+        <v>6437</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2805,10 +2805,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>459573</v>
+        <v>459480</v>
       </c>
       <c r="R22" t="n">
-        <v>6808047</v>
+        <v>6808013</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2841,6 +2841,11 @@
       <c r="AA22" t="inlineStr">
         <is>
           <t>2025-04-07</t>
+        </is>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>Miljöbild.</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2867,10 +2872,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>123833917</v>
+        <v>123828742</v>
       </c>
       <c r="B23" t="n">
-        <v>78523</v>
+        <v>78788</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2883,21 +2888,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2907,10 +2912,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>459292</v>
+        <v>459612</v>
       </c>
       <c r="R23" t="n">
-        <v>6808184</v>
+        <v>6808068</v>
       </c>
       <c r="S23" t="n">
         <v>20</v>
@@ -2969,10 +2974,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>123829918</v>
+        <v>123831277</v>
       </c>
       <c r="B24" t="n">
-        <v>78522</v>
+        <v>57507</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -2985,37 +2990,42 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6446</v>
+        <v>100049</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Andljusbäcken, Andljusbäcken, Dlr</t>
+          <t>Härkämäck, Dlr</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>459424</v>
+        <v>459389</v>
       </c>
       <c r="R24" t="n">
-        <v>6807998</v>
+        <v>6808070</v>
       </c>
       <c r="S24" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3045,6 +3055,11 @@
       <c r="AA24" t="inlineStr">
         <is>
           <t>2025-04-07</t>
+        </is>
+      </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>Miljöbild.</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3059,22 +3074,22 @@
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>123829889</v>
+        <v>123831467</v>
       </c>
       <c r="B25" t="n">
-        <v>78523</v>
+        <v>79377</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3087,34 +3102,34 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>228912</v>
+        <v>229821</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Härkämäck, Dlr</t>
+          <t>Härkämäck, Härkämäck, Dlr</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>459494</v>
+        <v>459290</v>
       </c>
       <c r="R25" t="n">
-        <v>6807997</v>
+        <v>6808098</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3149,11 +3164,6 @@
           <t>2025-04-07</t>
         </is>
       </c>
-      <c r="AC25" t="inlineStr">
-        <is>
-          <t>Miljöbild.</t>
-        </is>
-      </c>
       <c r="AD25" t="b">
         <v>0</v>
       </c>
@@ -3166,22 +3176,22 @@
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Niklas Rehn</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Niklas Rehn</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>123829941</v>
+        <v>123829246</v>
       </c>
       <c r="B26" t="n">
-        <v>78523</v>
+        <v>78788</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3194,21 +3204,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3218,10 +3228,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>459480</v>
+        <v>459586</v>
       </c>
       <c r="R26" t="n">
-        <v>6808013</v>
+        <v>6807981</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3258,7 +3268,7 @@
       </c>
       <c r="AC26" t="inlineStr">
         <is>
-          <t>Miljöbild.</t>
+          <t>Som vanligt garnlav i omgivningen. Miljöbilder.</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3285,10 +3295,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>123834183</v>
+        <v>123834220</v>
       </c>
       <c r="B27" t="n">
-        <v>78786</v>
+        <v>78788</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3321,17 +3331,17 @@
       <c r="I27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Andljusbäcken, Andljusbäcken, Dlr</t>
+          <t>Andljusen, Dlr</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>459373</v>
+        <v>459325</v>
       </c>
       <c r="R27" t="n">
-        <v>6808222</v>
+        <v>6808176</v>
       </c>
       <c r="S27" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3361,6 +3371,11 @@
       <c r="AA27" t="inlineStr">
         <is>
           <t>2025-04-07</t>
+        </is>
+      </c>
+      <c r="AC27" t="inlineStr">
+        <is>
+          <t>I synfält, radie av ca 50 meter. Miljöbild.</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3375,22 +3390,22 @@
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>123829394</v>
+        <v>123829889</v>
       </c>
       <c r="B28" t="n">
-        <v>77714</v>
+        <v>78525</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3403,21 +3418,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6487</v>
+        <v>228912</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Blågrå svartspik</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Chaenothecopsis fennica</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Laurila) Tibell</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3427,10 +3442,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>459586</v>
+        <v>459494</v>
       </c>
       <c r="R28" t="n">
-        <v>6807981</v>
+        <v>6807997</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3463,6 +3478,11 @@
       <c r="AA28" t="inlineStr">
         <is>
           <t>2025-04-07</t>
+        </is>
+      </c>
+      <c r="AC28" t="inlineStr">
+        <is>
+          <t>Miljöbild.</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3489,10 +3509,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>123829275</v>
+        <v>123829632</v>
       </c>
       <c r="B29" t="n">
-        <v>78523</v>
+        <v>91277</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3505,37 +3525,37 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>228912</v>
+        <v>658</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Andljusbäcken, Andljusbäcken, Dlr</t>
+          <t>Härkämäck, Dlr</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>459544</v>
+        <v>459573</v>
       </c>
       <c r="R29" t="n">
-        <v>6807989</v>
+        <v>6808047</v>
       </c>
       <c r="S29" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3579,22 +3599,22 @@
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>123834567</v>
+        <v>123835135</v>
       </c>
       <c r="B30" t="n">
-        <v>79375</v>
+        <v>78788</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3607,21 +3627,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>229821</v>
+        <v>6425</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3631,10 +3651,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>459399</v>
+        <v>459455</v>
       </c>
       <c r="R30" t="n">
-        <v>6808189</v>
+        <v>6808164</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3671,7 +3691,7 @@
       </c>
       <c r="AC30" t="inlineStr">
         <is>
-          <t>Miljöbild.</t>
+          <t>Garnlav i en radie av ca 50 meter, synfältet. Miljöbild.</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3698,10 +3718,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>123834966</v>
+        <v>123831578</v>
       </c>
       <c r="B31" t="n">
-        <v>57511</v>
+        <v>74879</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3710,46 +3730,41 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>100110</v>
+        <v>6440</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Gråspett</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Picus canus</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>J.F. Gmelin, 1788</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
-      <c r="M31" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Härkämäck, Dlr</t>
+          <t>Andljusbäcken, Andljusbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>459399</v>
+        <v>459287</v>
       </c>
       <c r="R31" t="n">
-        <v>6808189</v>
+        <v>6808008</v>
       </c>
       <c r="S31" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -3779,11 +3794,6 @@
       <c r="AA31" t="inlineStr">
         <is>
           <t>2025-04-07</t>
-        </is>
-      </c>
-      <c r="AC31" t="inlineStr">
-        <is>
-          <t>Förbiflygande.</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3798,22 +3808,22 @@
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>123831065</v>
+        <v>123833729</v>
       </c>
       <c r="B32" t="n">
-        <v>78786</v>
+        <v>78525</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -3826,34 +3836,34 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Andljusbäcken, Andljusbäcken, Dlr</t>
+          <t>Andljusen, Dlr</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>459425</v>
+        <v>459286</v>
       </c>
       <c r="R32" t="n">
-        <v>6808084</v>
+        <v>6808090</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3888,6 +3898,11 @@
           <t>2025-04-07</t>
         </is>
       </c>
+      <c r="AC32" t="inlineStr">
+        <is>
+          <t>Miljöbild.</t>
+        </is>
+      </c>
       <c r="AD32" t="b">
         <v>0</v>
       </c>
@@ -3900,22 +3915,22 @@
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>123831578</v>
+        <v>123831065</v>
       </c>
       <c r="B33" t="n">
-        <v>74878</v>
+        <v>78788</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -3928,21 +3943,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3952,13 +3967,13 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>459287</v>
+        <v>459425</v>
       </c>
       <c r="R33" t="n">
-        <v>6808008</v>
+        <v>6808084</v>
       </c>
       <c r="S33" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -4014,10 +4029,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>123834650</v>
+        <v>123828882</v>
       </c>
       <c r="B34" t="n">
-        <v>78523</v>
+        <v>78820</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4030,37 +4045,37 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>228912</v>
+        <v>185</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Härkämäck, Dlr</t>
+          <t>Andljusbäcken, Andljusbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>459399</v>
+        <v>459600</v>
       </c>
       <c r="R34" t="n">
-        <v>6808189</v>
+        <v>6808030</v>
       </c>
       <c r="S34" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -4090,11 +4105,6 @@
       <c r="AA34" t="inlineStr">
         <is>
           <t>2025-04-07</t>
-        </is>
-      </c>
-      <c r="AC34" t="inlineStr">
-        <is>
-          <t>Miljöbild</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4109,22 +4119,22 @@
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>123835135</v>
+        <v>123831067</v>
       </c>
       <c r="B35" t="n">
-        <v>78786</v>
+        <v>78788</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4161,10 +4171,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>459455</v>
+        <v>459439</v>
       </c>
       <c r="R35" t="n">
-        <v>6808164</v>
+        <v>6808067</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4201,7 +4211,7 @@
       </c>
       <c r="AC35" t="inlineStr">
         <is>
-          <t>Garnlav i en radie av ca 50 meter, synfältet. Miljöbild.</t>
+          <t>Synligt i en radie av ca 50 meter. Miljöbild.</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4228,10 +4238,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>123834006</v>
+        <v>123828783</v>
       </c>
       <c r="B36" t="n">
-        <v>78523</v>
+        <v>78788</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4244,37 +4254,37 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Härkämäck, Härkämäck, Dlr</t>
+          <t>Andljusbäcken, Andljusbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>459326</v>
+        <v>459611</v>
       </c>
       <c r="R36" t="n">
-        <v>6808188</v>
+        <v>6808048</v>
       </c>
       <c r="S36" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -4318,22 +4328,22 @@
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>123833841</v>
+        <v>123834966</v>
       </c>
       <c r="B37" t="n">
-        <v>78786</v>
+        <v>57512</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4342,41 +4352,46 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6425</v>
+        <v>100110</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gråspett</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picus canus</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>J.F. Gmelin, 1788</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
+      <c r="M37" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P37" t="inlineStr">
         <is>
-          <t>Härkämäck, Härkämäck, Dlr</t>
+          <t>Härkämäck, Dlr</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>459300</v>
+        <v>459399</v>
       </c>
       <c r="R37" t="n">
-        <v>6808144</v>
+        <v>6808189</v>
       </c>
       <c r="S37" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -4406,6 +4421,11 @@
       <c r="AA37" t="inlineStr">
         <is>
           <t>2025-04-07</t>
+        </is>
+      </c>
+      <c r="AC37" t="inlineStr">
+        <is>
+          <t>Förbiflygande.</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4420,22 +4440,22 @@
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>123829121</v>
+        <v>123833917</v>
       </c>
       <c r="B38" t="n">
-        <v>78786</v>
+        <v>78525</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4448,37 +4468,37 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
-          <t>Härkämäck, Dlr</t>
+          <t>Andljusbäcken, Andljusbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>459641</v>
+        <v>459292</v>
       </c>
       <c r="R38" t="n">
-        <v>6807971</v>
+        <v>6808184</v>
       </c>
       <c r="S38" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -4508,11 +4528,6 @@
       <c r="AA38" t="inlineStr">
         <is>
           <t>2025-04-07</t>
-        </is>
-      </c>
-      <c r="AC38" t="inlineStr">
-        <is>
-          <t>I synfältet i en radie av ca 40 meter. Miljöbild.</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4527,22 +4542,22 @@
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>123829246</v>
+        <v>123829197</v>
       </c>
       <c r="B39" t="n">
-        <v>78786</v>
+        <v>78525</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4555,37 +4570,37 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
-          <t>Härkämäck, Dlr</t>
+          <t>Andljusbäcken, Andljusbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>459586</v>
+        <v>459611</v>
       </c>
       <c r="R39" t="n">
-        <v>6807981</v>
+        <v>6807987</v>
       </c>
       <c r="S39" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
@@ -4615,11 +4630,6 @@
       <c r="AA39" t="inlineStr">
         <is>
           <t>2025-04-07</t>
-        </is>
-      </c>
-      <c r="AC39" t="inlineStr">
-        <is>
-          <t>Som vanligt garnlav i omgivningen. Miljöbilder.</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4634,22 +4644,22 @@
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>123829632</v>
+        <v>123828044</v>
       </c>
       <c r="B40" t="n">
-        <v>91275</v>
+        <v>78788</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -4662,21 +4672,21 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>658</v>
+        <v>6425</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4686,10 +4696,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>459573</v>
+        <v>459681</v>
       </c>
       <c r="R40" t="n">
-        <v>6808047</v>
+        <v>6808072</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4722,6 +4732,11 @@
       <c r="AA40" t="inlineStr">
         <is>
           <t>2025-04-07</t>
+        </is>
+      </c>
+      <c r="AC40" t="inlineStr">
+        <is>
+          <t>Garnlav i synfältet i en radie av ca 50 meter. Miljöbild.</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4748,10 +4763,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>123833814</v>
+        <v>123834641</v>
       </c>
       <c r="B41" t="n">
-        <v>78523</v>
+        <v>78788</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -4764,21 +4779,21 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4788,13 +4803,13 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>459293</v>
+        <v>459405</v>
       </c>
       <c r="R41" t="n">
-        <v>6808123</v>
+        <v>6808172</v>
       </c>
       <c r="S41" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -4838,22 +4853,22 @@
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>123833729</v>
+        <v>123834006</v>
       </c>
       <c r="B42" t="n">
-        <v>78523</v>
+        <v>78525</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -4886,17 +4901,17 @@
       <c r="I42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
-          <t>Andljusen, Dlr</t>
+          <t>Härkämäck, Härkämäck, Dlr</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>459286</v>
+        <v>459326</v>
       </c>
       <c r="R42" t="n">
-        <v>6808090</v>
+        <v>6808188</v>
       </c>
       <c r="S42" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -4926,11 +4941,6 @@
       <c r="AA42" t="inlineStr">
         <is>
           <t>2025-04-07</t>
-        </is>
-      </c>
-      <c r="AC42" t="inlineStr">
-        <is>
-          <t>Miljöbild.</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -4945,22 +4955,22 @@
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>123834630</v>
+        <v>123834890</v>
       </c>
       <c r="B43" t="n">
-        <v>57511</v>
+        <v>78867</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -4969,25 +4979,25 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>100110</v>
+        <v>864</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Gråspett</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Picus canus</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>J.F. Gmelin, 1788</t>
+          <t>(Lynge) Ahti</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -4997,13 +5007,13 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>459408</v>
+        <v>459427</v>
       </c>
       <c r="R43" t="n">
-        <v>6808198</v>
+        <v>6808130</v>
       </c>
       <c r="S43" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T43" t="inlineStr">
         <is>
@@ -5033,11 +5043,6 @@
       <c r="AA43" t="inlineStr">
         <is>
           <t>2025-04-07</t>
-        </is>
-      </c>
-      <c r="AC43" t="inlineStr">
-        <is>
-          <t>Förbiflygande.</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5052,22 +5057,22 @@
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>123834641</v>
+        <v>123829275</v>
       </c>
       <c r="B44" t="n">
-        <v>78786</v>
+        <v>78525</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5080,34 +5085,34 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
-          <t>Härkämäck, Härkämäck, Dlr</t>
+          <t>Andljusbäcken, Andljusbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>459405</v>
+        <v>459544</v>
       </c>
       <c r="R44" t="n">
-        <v>6808172</v>
+        <v>6807989</v>
       </c>
       <c r="S44" t="n">
         <v>20</v>
@@ -5166,10 +5171,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>123827957</v>
+        <v>123829394</v>
       </c>
       <c r="B45" t="n">
-        <v>78522</v>
+        <v>77716</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5182,37 +5187,37 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6446</v>
+        <v>6487</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Blågrå svartspik</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Chaenothecopsis fennica</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Laurila) Tibell</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
-          <t>Andljusbäcken, Andljusbäcken, Dlr</t>
+          <t>Härkämäck, Dlr</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>459664</v>
+        <v>459586</v>
       </c>
       <c r="R45" t="n">
-        <v>6808079</v>
+        <v>6807981</v>
       </c>
       <c r="S45" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T45" t="inlineStr">
         <is>
@@ -5256,22 +5261,22 @@
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>123829205</v>
+        <v>123829941</v>
       </c>
       <c r="B46" t="n">
-        <v>78522</v>
+        <v>78525</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5284,37 +5289,37 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>6446</v>
+        <v>228912</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
-          <t>Andljusbäcken, Andljusbäcken, Dlr</t>
+          <t>Härkämäck, Dlr</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>459611</v>
+        <v>459480</v>
       </c>
       <c r="R46" t="n">
-        <v>6807987</v>
+        <v>6808013</v>
       </c>
       <c r="S46" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T46" t="inlineStr">
         <is>
@@ -5344,6 +5349,11 @@
       <c r="AA46" t="inlineStr">
         <is>
           <t>2025-04-07</t>
+        </is>
+      </c>
+      <c r="AC46" t="inlineStr">
+        <is>
+          <t>Miljöbild.</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5358,22 +5368,22 @@
       <c r="AT46" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX46" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>123831244</v>
+        <v>123830920</v>
       </c>
       <c r="B47" t="n">
-        <v>78786</v>
+        <v>78433</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5386,21 +5396,21 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5410,10 +5420,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>459393</v>
+        <v>459462</v>
       </c>
       <c r="R47" t="n">
-        <v>6808027</v>
+        <v>6808078</v>
       </c>
       <c r="S47" t="n">
         <v>20</v>
@@ -5472,10 +5482,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>123831467</v>
+        <v>123829712</v>
       </c>
       <c r="B48" t="n">
-        <v>79375</v>
+        <v>90990</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -5488,34 +5498,34 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>229821</v>
+        <v>1202</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
-          <t>Härkämäck, Härkämäck, Dlr</t>
+          <t>Härkämäck, Dlr</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>459290</v>
+        <v>459573</v>
       </c>
       <c r="R48" t="n">
-        <v>6808098</v>
+        <v>6808047</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5562,22 +5572,22 @@
       <c r="AT48" t="inlineStr"/>
       <c r="AW48" t="inlineStr">
         <is>
-          <t>Niklas Rehn</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX48" t="inlineStr">
         <is>
-          <t>Niklas Rehn</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>123834220</v>
+        <v>123829205</v>
       </c>
       <c r="B49" t="n">
-        <v>78786</v>
+        <v>78524</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -5590,37 +5600,37 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
-          <t>Andljusen, Dlr</t>
+          <t>Andljusbäcken, Andljusbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>459325</v>
+        <v>459611</v>
       </c>
       <c r="R49" t="n">
-        <v>6808176</v>
+        <v>6807987</v>
       </c>
       <c r="S49" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T49" t="inlineStr">
         <is>
@@ -5650,11 +5660,6 @@
       <c r="AA49" t="inlineStr">
         <is>
           <t>2025-04-07</t>
-        </is>
-      </c>
-      <c r="AC49" t="inlineStr">
-        <is>
-          <t>I synfält, radie av ca 50 meter. Miljöbild.</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -5669,22 +5674,22 @@
       <c r="AT49" t="inlineStr"/>
       <c r="AW49" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX49" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>123828044</v>
+        <v>123828608</v>
       </c>
       <c r="B50" t="n">
-        <v>78786</v>
+        <v>78788</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -5721,10 +5726,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>459681</v>
+        <v>459636</v>
       </c>
       <c r="R50" t="n">
-        <v>6808072</v>
+        <v>6808042</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5761,7 +5766,7 @@
       </c>
       <c r="AC50" t="inlineStr">
         <is>
-          <t>Garnlav i synfältet i en radie av ca 50 meter. Miljöbild.</t>
+          <t>Garnlav i synfältet i en radie av ca 50 meter. Miljöbilder.</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -5788,10 +5793,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>123833754</v>
+        <v>123829102</v>
       </c>
       <c r="B51" t="n">
-        <v>92269</v>
+        <v>78788</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -5800,41 +5805,41 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
-          <t>Härkämäck, Härkämäck, Dlr</t>
+          <t>Andljusbäcken, Andljusbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>459290</v>
+        <v>459666</v>
       </c>
       <c r="R51" t="n">
-        <v>6808093</v>
+        <v>6807990</v>
       </c>
       <c r="S51" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T51" t="inlineStr">
         <is>
@@ -5878,22 +5883,22 @@
       <c r="AT51" t="inlineStr"/>
       <c r="AW51" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX51" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>123830009</v>
+        <v>123834630</v>
       </c>
       <c r="B52" t="n">
-        <v>78522</v>
+        <v>57512</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -5902,38 +5907,38 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>6446</v>
+        <v>100110</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Gråspett</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Picus canus</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>J.F. Gmelin, 1788</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
-          <t>Härkämäck, Dlr</t>
+          <t>Härkämäck, Härkämäck, Dlr</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>459480</v>
+        <v>459408</v>
       </c>
       <c r="R52" t="n">
-        <v>6808013</v>
+        <v>6808198</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -5970,7 +5975,7 @@
       </c>
       <c r="AC52" t="inlineStr">
         <is>
-          <t>Miljöbild.</t>
+          <t>Förbiflygande.</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -5985,15 +5990,1667 @@
       <c r="AT52" t="inlineStr"/>
       <c r="AW52" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX52" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
+    </row>
+    <row r="53">
+      <c r="A53" t="n">
+        <v>123920427</v>
+      </c>
+      <c r="B53" t="n">
+        <v>57491</v>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E53" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr"/>
+      <c r="M53" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="P53" t="inlineStr">
+        <is>
+          <t>Härkämäck, Dlr</t>
+        </is>
+      </c>
+      <c r="Q53" t="n">
+        <v>459571</v>
+      </c>
+      <c r="R53" t="n">
+        <v>6808057</v>
+      </c>
+      <c r="S53" t="n">
+        <v>10</v>
+      </c>
+      <c r="T53" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U53" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V53" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W53" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="Y53" t="inlineStr">
+        <is>
+          <t>2025-04-07</t>
+        </is>
+      </c>
+      <c r="AA53" t="inlineStr">
+        <is>
+          <t>2025-04-07</t>
+        </is>
+      </c>
+      <c r="AD53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT53" t="inlineStr"/>
+      <c r="AW53" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX53" t="inlineStr">
+        <is>
+          <t>Philipp Weiss, Anders Heggestad, Håkan Thenander, lennart karlsson, Niklas Rehn</t>
+        </is>
+      </c>
+      <c r="AY53" t="inlineStr"/>
+    </row>
+    <row r="54">
+      <c r="A54" t="n">
+        <v>123920733</v>
+      </c>
+      <c r="B54" t="n">
+        <v>78788</v>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E54" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr"/>
+      <c r="P54" t="inlineStr">
+        <is>
+          <t>Härkämäck, Dlr</t>
+        </is>
+      </c>
+      <c r="Q54" t="n">
+        <v>459589</v>
+      </c>
+      <c r="R54" t="n">
+        <v>6807980</v>
+      </c>
+      <c r="S54" t="n">
+        <v>10</v>
+      </c>
+      <c r="T54" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U54" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V54" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W54" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="Y54" t="inlineStr">
+        <is>
+          <t>2025-04-07</t>
+        </is>
+      </c>
+      <c r="AA54" t="inlineStr">
+        <is>
+          <t>2025-04-07</t>
+        </is>
+      </c>
+      <c r="AD54" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE54" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG54" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT54" t="inlineStr"/>
+      <c r="AW54" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX54" t="inlineStr">
+        <is>
+          <t>Philipp Weiss, Anders Heggestad, lennart karlsson, Håkan Thenander, Niklas Rehn</t>
+        </is>
+      </c>
+      <c r="AY54" t="inlineStr"/>
+    </row>
+    <row r="55">
+      <c r="A55" t="n">
+        <v>123920440</v>
+      </c>
+      <c r="B55" t="n">
+        <v>56700</v>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E55" t="n">
+        <v>100138</v>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>Tjäder</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>Tetrao urogallus</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr"/>
+      <c r="M55" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
+      <c r="P55" t="inlineStr">
+        <is>
+          <t>Härkämäck, Dlr</t>
+        </is>
+      </c>
+      <c r="Q55" t="n">
+        <v>459617</v>
+      </c>
+      <c r="R55" t="n">
+        <v>6808041</v>
+      </c>
+      <c r="S55" t="n">
+        <v>10</v>
+      </c>
+      <c r="T55" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U55" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V55" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W55" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="Y55" t="inlineStr">
+        <is>
+          <t>2025-04-07</t>
+        </is>
+      </c>
+      <c r="AA55" t="inlineStr">
+        <is>
+          <t>2025-04-07</t>
+        </is>
+      </c>
+      <c r="AD55" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE55" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG55" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT55" t="inlineStr"/>
+      <c r="AW55" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX55" t="inlineStr">
+        <is>
+          <t>Philipp Weiss, Anders Heggestad, Håkan Thenander, lennart karlsson, Niklas Rehn</t>
+        </is>
+      </c>
+      <c r="AY55" t="inlineStr"/>
+    </row>
+    <row r="56">
+      <c r="A56" t="n">
+        <v>123920732</v>
+      </c>
+      <c r="B56" t="n">
+        <v>78788</v>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E56" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr"/>
+      <c r="P56" t="inlineStr">
+        <is>
+          <t>Härkämäck, Dlr</t>
+        </is>
+      </c>
+      <c r="Q56" t="n">
+        <v>459616</v>
+      </c>
+      <c r="R56" t="n">
+        <v>6808044</v>
+      </c>
+      <c r="S56" t="n">
+        <v>10</v>
+      </c>
+      <c r="T56" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U56" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V56" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W56" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="Y56" t="inlineStr">
+        <is>
+          <t>2025-04-07</t>
+        </is>
+      </c>
+      <c r="AA56" t="inlineStr">
+        <is>
+          <t>2025-04-07</t>
+        </is>
+      </c>
+      <c r="AD56" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE56" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG56" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT56" t="inlineStr"/>
+      <c r="AW56" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX56" t="inlineStr">
+        <is>
+          <t>Philipp Weiss, Anders Heggestad, lennart karlsson, Håkan Thenander, Niklas Rehn</t>
+        </is>
+      </c>
+      <c r="AY56" t="inlineStr"/>
+    </row>
+    <row r="57">
+      <c r="A57" t="n">
+        <v>123920731</v>
+      </c>
+      <c r="B57" t="n">
+        <v>78788</v>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E57" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr"/>
+      <c r="P57" t="inlineStr">
+        <is>
+          <t>Härkämäck, Dlr</t>
+        </is>
+      </c>
+      <c r="Q57" t="n">
+        <v>459608</v>
+      </c>
+      <c r="R57" t="n">
+        <v>6808066</v>
+      </c>
+      <c r="S57" t="n">
+        <v>10</v>
+      </c>
+      <c r="T57" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U57" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V57" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W57" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="Y57" t="inlineStr">
+        <is>
+          <t>2025-04-07</t>
+        </is>
+      </c>
+      <c r="AA57" t="inlineStr">
+        <is>
+          <t>2025-04-07</t>
+        </is>
+      </c>
+      <c r="AD57" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE57" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG57" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT57" t="inlineStr"/>
+      <c r="AW57" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX57" t="inlineStr">
+        <is>
+          <t>Philipp Weiss, Anders Heggestad, lennart karlsson, Håkan Thenander, Niklas Rehn</t>
+        </is>
+      </c>
+      <c r="AY57" t="inlineStr"/>
+    </row>
+    <row r="58">
+      <c r="A58" t="n">
+        <v>123920734</v>
+      </c>
+      <c r="B58" t="n">
+        <v>78788</v>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E58" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr"/>
+      <c r="P58" t="inlineStr">
+        <is>
+          <t>Härkämäck, Dlr</t>
+        </is>
+      </c>
+      <c r="Q58" t="n">
+        <v>459613</v>
+      </c>
+      <c r="R58" t="n">
+        <v>6807959</v>
+      </c>
+      <c r="S58" t="n">
+        <v>10</v>
+      </c>
+      <c r="T58" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U58" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V58" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W58" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="Y58" t="inlineStr">
+        <is>
+          <t>2025-04-07</t>
+        </is>
+      </c>
+      <c r="AA58" t="inlineStr">
+        <is>
+          <t>2025-04-07</t>
+        </is>
+      </c>
+      <c r="AD58" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE58" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG58" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT58" t="inlineStr"/>
+      <c r="AW58" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX58" t="inlineStr">
+        <is>
+          <t>Philipp Weiss, Anders Heggestad, lennart karlsson, Håkan Thenander, Niklas Rehn</t>
+        </is>
+      </c>
+      <c r="AY58" t="inlineStr"/>
+    </row>
+    <row r="59">
+      <c r="A59" t="n">
+        <v>123920728</v>
+      </c>
+      <c r="B59" t="n">
+        <v>78788</v>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E59" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr"/>
+      <c r="P59" t="inlineStr">
+        <is>
+          <t>Härkämäck, Dlr</t>
+        </is>
+      </c>
+      <c r="Q59" t="n">
+        <v>459539</v>
+      </c>
+      <c r="R59" t="n">
+        <v>6808073</v>
+      </c>
+      <c r="S59" t="n">
+        <v>10</v>
+      </c>
+      <c r="T59" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U59" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V59" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W59" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="Y59" t="inlineStr">
+        <is>
+          <t>2025-04-07</t>
+        </is>
+      </c>
+      <c r="AA59" t="inlineStr">
+        <is>
+          <t>2025-04-07</t>
+        </is>
+      </c>
+      <c r="AD59" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE59" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG59" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT59" t="inlineStr"/>
+      <c r="AW59" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX59" t="inlineStr">
+        <is>
+          <t>Philipp Weiss, Anders Heggestad, lennart karlsson, Håkan Thenander, Niklas Rehn</t>
+        </is>
+      </c>
+      <c r="AY59" t="inlineStr"/>
+    </row>
+    <row r="60">
+      <c r="A60" t="n">
+        <v>123920419</v>
+      </c>
+      <c r="B60" t="n">
+        <v>90990</v>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E60" t="n">
+        <v>1202</v>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr"/>
+      <c r="P60" t="inlineStr">
+        <is>
+          <t>Härkämäck, Dlr</t>
+        </is>
+      </c>
+      <c r="Q60" t="n">
+        <v>459603</v>
+      </c>
+      <c r="R60" t="n">
+        <v>6807965</v>
+      </c>
+      <c r="S60" t="n">
+        <v>10</v>
+      </c>
+      <c r="T60" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U60" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V60" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W60" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="Y60" t="inlineStr">
+        <is>
+          <t>2025-04-07</t>
+        </is>
+      </c>
+      <c r="AA60" t="inlineStr">
+        <is>
+          <t>2025-04-07</t>
+        </is>
+      </c>
+      <c r="AD60" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE60" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG60" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT60" t="inlineStr"/>
+      <c r="AW60" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX60" t="inlineStr">
+        <is>
+          <t>Philipp Weiss, Anders Heggestad, Håkan Thenander, lennart karlsson, Niklas Rehn</t>
+        </is>
+      </c>
+      <c r="AY60" t="inlineStr"/>
+    </row>
+    <row r="61">
+      <c r="A61" t="n">
+        <v>123920540</v>
+      </c>
+      <c r="B61" t="n">
+        <v>78525</v>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E61" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr"/>
+      <c r="P61" t="inlineStr">
+        <is>
+          <t>Härkämäck, Dlr</t>
+        </is>
+      </c>
+      <c r="Q61" t="n">
+        <v>459589</v>
+      </c>
+      <c r="R61" t="n">
+        <v>6807980</v>
+      </c>
+      <c r="S61" t="n">
+        <v>10</v>
+      </c>
+      <c r="T61" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U61" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V61" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W61" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="Y61" t="inlineStr">
+        <is>
+          <t>2025-04-07</t>
+        </is>
+      </c>
+      <c r="AA61" t="inlineStr">
+        <is>
+          <t>2025-04-07</t>
+        </is>
+      </c>
+      <c r="AD61" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE61" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG61" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT61" t="inlineStr"/>
+      <c r="AW61" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX61" t="inlineStr">
+        <is>
+          <t>Philipp Weiss, Anders Heggestad, lennart karlsson, Håkan Thenander, Niklas Rehn</t>
+        </is>
+      </c>
+      <c r="AY61" t="inlineStr"/>
+    </row>
+    <row r="62">
+      <c r="A62" t="n">
+        <v>123920930</v>
+      </c>
+      <c r="B62" t="n">
+        <v>78433</v>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E62" t="n">
+        <v>353</v>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>Dvärgbägarlav</t>
+        </is>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>Cladonia parasitica</t>
+        </is>
+      </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>(Hoffm.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr"/>
+      <c r="P62" t="inlineStr">
+        <is>
+          <t>Härkämäck, Dlr</t>
+        </is>
+      </c>
+      <c r="Q62" t="n">
+        <v>459600</v>
+      </c>
+      <c r="R62" t="n">
+        <v>6807961</v>
+      </c>
+      <c r="S62" t="n">
+        <v>10</v>
+      </c>
+      <c r="T62" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U62" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V62" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W62" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="Y62" t="inlineStr">
+        <is>
+          <t>2025-04-07</t>
+        </is>
+      </c>
+      <c r="AA62" t="inlineStr">
+        <is>
+          <t>2025-04-07</t>
+        </is>
+      </c>
+      <c r="AD62" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE62" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG62" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT62" t="inlineStr"/>
+      <c r="AW62" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX62" t="inlineStr">
+        <is>
+          <t>Philipp Weiss, Anders Heggestad, lennart karlsson, Håkan Thenander, Niklas Rehn</t>
+        </is>
+      </c>
+      <c r="AY62" t="inlineStr"/>
+    </row>
+    <row r="63">
+      <c r="A63" t="n">
+        <v>123920729</v>
+      </c>
+      <c r="B63" t="n">
+        <v>78788</v>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E63" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr"/>
+      <c r="P63" t="inlineStr">
+        <is>
+          <t>Härkämäck, Dlr</t>
+        </is>
+      </c>
+      <c r="Q63" t="n">
+        <v>459566</v>
+      </c>
+      <c r="R63" t="n">
+        <v>6808068</v>
+      </c>
+      <c r="S63" t="n">
+        <v>10</v>
+      </c>
+      <c r="T63" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U63" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V63" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W63" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="Y63" t="inlineStr">
+        <is>
+          <t>2025-04-07</t>
+        </is>
+      </c>
+      <c r="AA63" t="inlineStr">
+        <is>
+          <t>2025-04-07</t>
+        </is>
+      </c>
+      <c r="AD63" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE63" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG63" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT63" t="inlineStr"/>
+      <c r="AW63" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX63" t="inlineStr">
+        <is>
+          <t>Philipp Weiss, Anders Heggestad, lennart karlsson, Håkan Thenander, Niklas Rehn</t>
+        </is>
+      </c>
+      <c r="AY63" t="inlineStr"/>
+    </row>
+    <row r="64">
+      <c r="A64" t="n">
+        <v>123920399</v>
+      </c>
+      <c r="B64" t="n">
+        <v>79377</v>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E64" t="n">
+        <v>229821</v>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>Vedflamlav</t>
+        </is>
+      </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>Ramboldia elabens</t>
+        </is>
+      </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr"/>
+      <c r="P64" t="inlineStr">
+        <is>
+          <t>Härkämäck, Dlr</t>
+        </is>
+      </c>
+      <c r="Q64" t="n">
+        <v>459591</v>
+      </c>
+      <c r="R64" t="n">
+        <v>6808065</v>
+      </c>
+      <c r="S64" t="n">
+        <v>10</v>
+      </c>
+      <c r="T64" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U64" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V64" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W64" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="Y64" t="inlineStr">
+        <is>
+          <t>2025-04-07</t>
+        </is>
+      </c>
+      <c r="AA64" t="inlineStr">
+        <is>
+          <t>2025-04-07</t>
+        </is>
+      </c>
+      <c r="AD64" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE64" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG64" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT64" t="inlineStr"/>
+      <c r="AW64" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX64" t="inlineStr">
+        <is>
+          <t>Philipp Weiss, Anders Heggestad, Håkan Thenander, lennart karlsson, Niklas Rehn</t>
+        </is>
+      </c>
+      <c r="AY64" t="inlineStr"/>
+    </row>
+    <row r="65">
+      <c r="A65" t="n">
+        <v>123920442</v>
+      </c>
+      <c r="B65" t="n">
+        <v>56700</v>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E65" t="n">
+        <v>100138</v>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>Tjäder</t>
+        </is>
+      </c>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>Tetrao urogallus</t>
+        </is>
+      </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I65" t="inlineStr"/>
+      <c r="M65" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
+      <c r="P65" t="inlineStr">
+        <is>
+          <t>Härkämäck, Dlr</t>
+        </is>
+      </c>
+      <c r="Q65" t="n">
+        <v>459593</v>
+      </c>
+      <c r="R65" t="n">
+        <v>6807978</v>
+      </c>
+      <c r="S65" t="n">
+        <v>10</v>
+      </c>
+      <c r="T65" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U65" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V65" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W65" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="Y65" t="inlineStr">
+        <is>
+          <t>2025-04-07</t>
+        </is>
+      </c>
+      <c r="AA65" t="inlineStr">
+        <is>
+          <t>2025-04-07</t>
+        </is>
+      </c>
+      <c r="AD65" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE65" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG65" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT65" t="inlineStr"/>
+      <c r="AW65" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX65" t="inlineStr">
+        <is>
+          <t>Philipp Weiss, Anders Heggestad, Håkan Thenander, lennart karlsson, Niklas Rehn</t>
+        </is>
+      </c>
+      <c r="AY65" t="inlineStr"/>
+    </row>
+    <row r="66">
+      <c r="A66" t="n">
+        <v>123920727</v>
+      </c>
+      <c r="B66" t="n">
+        <v>78788</v>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E66" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr"/>
+      <c r="P66" t="inlineStr">
+        <is>
+          <t>Härkämäck, Dlr</t>
+        </is>
+      </c>
+      <c r="Q66" t="n">
+        <v>459542</v>
+      </c>
+      <c r="R66" t="n">
+        <v>6808123</v>
+      </c>
+      <c r="S66" t="n">
+        <v>10</v>
+      </c>
+      <c r="T66" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U66" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V66" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W66" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="Y66" t="inlineStr">
+        <is>
+          <t>2025-04-07</t>
+        </is>
+      </c>
+      <c r="AA66" t="inlineStr">
+        <is>
+          <t>2025-04-07</t>
+        </is>
+      </c>
+      <c r="AD66" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE66" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG66" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT66" t="inlineStr"/>
+      <c r="AW66" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX66" t="inlineStr">
+        <is>
+          <t>Philipp Weiss, Anders Heggestad, lennart karlsson, Håkan Thenander, Niklas Rehn</t>
+        </is>
+      </c>
+      <c r="AY66" t="inlineStr"/>
+    </row>
+    <row r="67">
+      <c r="A67" t="n">
+        <v>123920730</v>
+      </c>
+      <c r="B67" t="n">
+        <v>78788</v>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E67" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I67" t="inlineStr"/>
+      <c r="P67" t="inlineStr">
+        <is>
+          <t>Härkämäck, Dlr</t>
+        </is>
+      </c>
+      <c r="Q67" t="n">
+        <v>459590</v>
+      </c>
+      <c r="R67" t="n">
+        <v>6808062</v>
+      </c>
+      <c r="S67" t="n">
+        <v>10</v>
+      </c>
+      <c r="T67" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U67" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V67" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W67" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="Y67" t="inlineStr">
+        <is>
+          <t>2025-04-07</t>
+        </is>
+      </c>
+      <c r="AA67" t="inlineStr">
+        <is>
+          <t>2025-04-07</t>
+        </is>
+      </c>
+      <c r="AD67" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE67" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG67" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT67" t="inlineStr"/>
+      <c r="AW67" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX67" t="inlineStr">
+        <is>
+          <t>Philipp Weiss, Anders Heggestad, lennart karlsson, Håkan Thenander, Niklas Rehn</t>
+        </is>
+      </c>
+      <c r="AY67" t="inlineStr"/>
+    </row>
+    <row r="68">
+      <c r="A68" t="n">
+        <v>123920441</v>
+      </c>
+      <c r="B68" t="n">
+        <v>56700</v>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E68" t="n">
+        <v>100138</v>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>Tjäder</t>
+        </is>
+      </c>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>Tetrao urogallus</t>
+        </is>
+      </c>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I68" t="inlineStr"/>
+      <c r="M68" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
+      <c r="P68" t="inlineStr">
+        <is>
+          <t>Härkämäck, Dlr</t>
+        </is>
+      </c>
+      <c r="Q68" t="n">
+        <v>459609</v>
+      </c>
+      <c r="R68" t="n">
+        <v>6807987</v>
+      </c>
+      <c r="S68" t="n">
+        <v>10</v>
+      </c>
+      <c r="T68" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U68" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V68" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W68" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="Y68" t="inlineStr">
+        <is>
+          <t>2025-04-07</t>
+        </is>
+      </c>
+      <c r="AA68" t="inlineStr">
+        <is>
+          <t>2025-04-07</t>
+        </is>
+      </c>
+      <c r="AD68" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE68" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG68" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT68" t="inlineStr"/>
+      <c r="AW68" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX68" t="inlineStr">
+        <is>
+          <t>Philipp Weiss, Anders Heggestad, Håkan Thenander, lennart karlsson, Niklas Rehn</t>
+        </is>
+      </c>
+      <c r="AY68" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 61327-2022 artfynd.xlsx
+++ b/artfynd/A 61327-2022 artfynd.xlsx
@@ -884,10 +884,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123831097</v>
+        <v>123834650</v>
       </c>
       <c r="B4" t="n">
-        <v>79377</v>
+        <v>78525</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -900,37 +900,37 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>229821</v>
+        <v>228912</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Andljusbäcken, Andljusbäcken, Dlr</t>
+          <t>Härkämäck, Dlr</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>459402</v>
+        <v>459399</v>
       </c>
       <c r="R4" t="n">
-        <v>6808072</v>
+        <v>6808189</v>
       </c>
       <c r="S4" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -960,6 +960,11 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2025-04-07</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Miljöbild</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -974,22 +979,22 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123829982</v>
+        <v>123831097</v>
       </c>
       <c r="B5" t="n">
-        <v>77716</v>
+        <v>79377</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1002,21 +1007,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6487</v>
+        <v>229821</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Blågrå svartspik</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Chaenothecopsis fennica</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Laurila) Tibell</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1026,10 +1031,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>459432</v>
+        <v>459402</v>
       </c>
       <c r="R5" t="n">
-        <v>6807989</v>
+        <v>6808072</v>
       </c>
       <c r="S5" t="n">
         <v>20</v>
@@ -1088,10 +1093,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>123833841</v>
+        <v>123829982</v>
       </c>
       <c r="B6" t="n">
-        <v>78788</v>
+        <v>77716</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1104,37 +1109,37 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>6487</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Blågrå svartspik</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenothecopsis fennica</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Laurila) Tibell</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Härkämäck, Härkämäck, Dlr</t>
+          <t>Andljusbäcken, Andljusbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>459300</v>
+        <v>459432</v>
       </c>
       <c r="R6" t="n">
-        <v>6808144</v>
+        <v>6807989</v>
       </c>
       <c r="S6" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1178,22 +1183,22 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>123834650</v>
+        <v>123833841</v>
       </c>
       <c r="B7" t="n">
-        <v>78525</v>
+        <v>78788</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1206,37 +1211,37 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Härkämäck, Dlr</t>
+          <t>Härkämäck, Härkämäck, Dlr</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>459399</v>
+        <v>459300</v>
       </c>
       <c r="R7" t="n">
-        <v>6808189</v>
+        <v>6808144</v>
       </c>
       <c r="S7" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1266,11 +1271,6 @@
       <c r="AA7" t="inlineStr">
         <is>
           <t>2025-04-07</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>Miljöbild</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1285,12 +1285,12 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
@@ -1924,10 +1924,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>123829121</v>
+        <v>123834998</v>
       </c>
       <c r="B14" t="n">
-        <v>78788</v>
+        <v>79377</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1940,37 +1940,37 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6425</v>
+        <v>229821</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Härkämäck, Dlr</t>
+          <t>Härkämäck, Härkämäck, Dlr</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>459641</v>
+        <v>459437</v>
       </c>
       <c r="R14" t="n">
-        <v>6807971</v>
+        <v>6808171</v>
       </c>
       <c r="S14" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2000,11 +2000,6 @@
       <c r="AA14" t="inlineStr">
         <is>
           <t>2025-04-07</t>
-        </is>
-      </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>I synfältet i en radie av ca 40 meter. Miljöbild.</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2019,22 +2014,22 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>123834034</v>
+        <v>123829121</v>
       </c>
       <c r="B15" t="n">
-        <v>57507</v>
+        <v>78788</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2047,39 +2042,34 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Andljusen, Dlr</t>
+          <t>Härkämäck, Dlr</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>459325</v>
+        <v>459641</v>
       </c>
       <c r="R15" t="n">
-        <v>6808176</v>
+        <v>6807971</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2116,7 +2106,7 @@
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>Miljöbild.</t>
+          <t>I synfältet i en radie av ca 40 meter. Miljöbild.</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2143,10 +2133,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>123834998</v>
+        <v>123834034</v>
       </c>
       <c r="B16" t="n">
-        <v>79377</v>
+        <v>57507</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2159,37 +2149,42 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>229821</v>
+        <v>100049</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Härkämäck, Härkämäck, Dlr</t>
+          <t>Andljusen, Dlr</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>459437</v>
+        <v>459325</v>
       </c>
       <c r="R16" t="n">
-        <v>6808171</v>
+        <v>6808176</v>
       </c>
       <c r="S16" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2219,6 +2214,11 @@
       <c r="AA16" t="inlineStr">
         <is>
           <t>2025-04-07</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>Miljöbild.</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2233,12 +2233,12 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
@@ -2459,10 +2459,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>123831244</v>
+        <v>123833814</v>
       </c>
       <c r="B19" t="n">
-        <v>78788</v>
+        <v>78525</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2475,37 +2475,37 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Andljusbäcken, Andljusbäcken, Dlr</t>
+          <t>Härkämäck, Härkämäck, Dlr</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>459393</v>
+        <v>459293</v>
       </c>
       <c r="R19" t="n">
-        <v>6808027</v>
+        <v>6808123</v>
       </c>
       <c r="S19" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2549,22 +2549,22 @@
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>123833814</v>
+        <v>123831244</v>
       </c>
       <c r="B20" t="n">
-        <v>78525</v>
+        <v>78788</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2577,37 +2577,37 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Härkämäck, Härkämäck, Dlr</t>
+          <t>Andljusbäcken, Andljusbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>459293</v>
+        <v>459393</v>
       </c>
       <c r="R20" t="n">
-        <v>6808123</v>
+        <v>6808027</v>
       </c>
       <c r="S20" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2651,12 +2651,12 @@
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
@@ -4340,10 +4340,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>123834966</v>
+        <v>123829197</v>
       </c>
       <c r="B37" t="n">
-        <v>57512</v>
+        <v>78525</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4352,46 +4352,41 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>100110</v>
+        <v>228912</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Gråspett</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Picus canus</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>J.F. Gmelin, 1788</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
-      <c r="M37" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="P37" t="inlineStr">
         <is>
-          <t>Härkämäck, Dlr</t>
+          <t>Andljusbäcken, Andljusbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>459399</v>
+        <v>459611</v>
       </c>
       <c r="R37" t="n">
-        <v>6808189</v>
+        <v>6807987</v>
       </c>
       <c r="S37" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -4421,11 +4416,6 @@
       <c r="AA37" t="inlineStr">
         <is>
           <t>2025-04-07</t>
-        </is>
-      </c>
-      <c r="AC37" t="inlineStr">
-        <is>
-          <t>Förbiflygande.</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4440,12 +4430,12 @@
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
@@ -4554,10 +4544,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>123829197</v>
+        <v>123834966</v>
       </c>
       <c r="B39" t="n">
-        <v>78525</v>
+        <v>57512</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4566,41 +4556,46 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>228912</v>
+        <v>100110</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Gråspett</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Picus canus</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>J.F. Gmelin, 1788</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P39" t="inlineStr">
         <is>
-          <t>Andljusbäcken, Andljusbäcken, Dlr</t>
+          <t>Härkämäck, Dlr</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>459611</v>
+        <v>459399</v>
       </c>
       <c r="R39" t="n">
-        <v>6807987</v>
+        <v>6808189</v>
       </c>
       <c r="S39" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
@@ -4630,6 +4625,11 @@
       <c r="AA39" t="inlineStr">
         <is>
           <t>2025-04-07</t>
+        </is>
+      </c>
+      <c r="AC39" t="inlineStr">
+        <is>
+          <t>Förbiflygande.</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4644,12 +4644,12 @@
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
@@ -4967,10 +4967,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>123834890</v>
+        <v>123829275</v>
       </c>
       <c r="B43" t="n">
-        <v>78867</v>
+        <v>78525</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -4983,34 +4983,34 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>864</v>
+        <v>228912</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Knottrig blåslav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Hypogymnia bitteri</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Lynge) Ahti</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
-          <t>Härkämäck, Härkämäck, Dlr</t>
+          <t>Andljusbäcken, Andljusbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>459427</v>
+        <v>459544</v>
       </c>
       <c r="R43" t="n">
-        <v>6808130</v>
+        <v>6807989</v>
       </c>
       <c r="S43" t="n">
         <v>20</v>
@@ -5069,10 +5069,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>123829275</v>
+        <v>123834890</v>
       </c>
       <c r="B44" t="n">
-        <v>78525</v>
+        <v>78867</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5085,34 +5085,34 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>228912</v>
+        <v>864</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Lynge) Ahti</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
-          <t>Andljusbäcken, Andljusbäcken, Dlr</t>
+          <t>Härkämäck, Härkämäck, Dlr</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>459544</v>
+        <v>459427</v>
       </c>
       <c r="R44" t="n">
-        <v>6807989</v>
+        <v>6808130</v>
       </c>
       <c r="S44" t="n">
         <v>20</v>

--- a/artfynd/A 61327-2022 artfynd.xlsx
+++ b/artfynd/A 61327-2022 artfynd.xlsx
@@ -2459,10 +2459,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>123833814</v>
+        <v>123831244</v>
       </c>
       <c r="B19" t="n">
-        <v>78525</v>
+        <v>78788</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2475,37 +2475,37 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Härkämäck, Härkämäck, Dlr</t>
+          <t>Andljusbäcken, Andljusbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>459293</v>
+        <v>459393</v>
       </c>
       <c r="R19" t="n">
-        <v>6808123</v>
+        <v>6808027</v>
       </c>
       <c r="S19" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2549,22 +2549,22 @@
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>123831244</v>
+        <v>123833814</v>
       </c>
       <c r="B20" t="n">
-        <v>78788</v>
+        <v>78525</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2577,37 +2577,37 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Andljusbäcken, Andljusbäcken, Dlr</t>
+          <t>Härkämäck, Härkämäck, Dlr</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>459393</v>
+        <v>459293</v>
       </c>
       <c r="R20" t="n">
-        <v>6808027</v>
+        <v>6808123</v>
       </c>
       <c r="S20" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2651,12 +2651,12 @@
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>

--- a/artfynd/A 61327-2022 artfynd.xlsx
+++ b/artfynd/A 61327-2022 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>123834183</v>
+        <v>123831578</v>
       </c>
       <c r="B2" t="n">
-        <v>78788</v>
+        <v>74879</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>459373</v>
+        <v>459287</v>
       </c>
       <c r="R2" t="n">
-        <v>6808222</v>
+        <v>6808008</v>
       </c>
       <c r="S2" t="n">
         <v>20</v>
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123834567</v>
+        <v>123831277</v>
       </c>
       <c r="B3" t="n">
-        <v>79377</v>
+        <v>57507</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -793,34 +793,39 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>229821</v>
+        <v>100049</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Härkämäck, Dlr</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>459399</v>
+        <v>459389</v>
       </c>
       <c r="R3" t="n">
-        <v>6808189</v>
+        <v>6808070</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -884,10 +889,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123834650</v>
+        <v>123828826</v>
       </c>
       <c r="B4" t="n">
-        <v>78525</v>
+        <v>56700</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -896,38 +901,43 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>228912</v>
+        <v>100138</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Härkämäck, Dlr</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>459399</v>
+        <v>459636</v>
       </c>
       <c r="R4" t="n">
-        <v>6808189</v>
+        <v>6808042</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -964,7 +974,7 @@
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>Miljöbild</t>
+          <t>Garnlav i bakgrund. Miljöbild.</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -991,10 +1001,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123831097</v>
+        <v>123834220</v>
       </c>
       <c r="B5" t="n">
-        <v>79377</v>
+        <v>78788</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1007,37 +1017,37 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>229821</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Andljusbäcken, Andljusbäcken, Dlr</t>
+          <t>Andljusen, Dlr</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>459402</v>
+        <v>459325</v>
       </c>
       <c r="R5" t="n">
-        <v>6808072</v>
+        <v>6808176</v>
       </c>
       <c r="S5" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1067,6 +1077,11 @@
       <c r="AA5" t="inlineStr">
         <is>
           <t>2025-04-07</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>I synfält, radie av ca 50 meter. Miljöbild.</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1081,22 +1096,22 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>123829982</v>
+        <v>123831467</v>
       </c>
       <c r="B6" t="n">
-        <v>77716</v>
+        <v>79377</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1109,37 +1124,37 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6487</v>
+        <v>229821</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Blågrå svartspik</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Chaenothecopsis fennica</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Laurila) Tibell</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Andljusbäcken, Andljusbäcken, Dlr</t>
+          <t>Härkämäck, Härkämäck, Dlr</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>459432</v>
+        <v>459290</v>
       </c>
       <c r="R6" t="n">
-        <v>6807989</v>
+        <v>6808098</v>
       </c>
       <c r="S6" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1183,22 +1198,22 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Niklas Rehn</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Niklas Rehn</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>123833841</v>
+        <v>123829632</v>
       </c>
       <c r="B7" t="n">
-        <v>78788</v>
+        <v>91277</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1211,37 +1226,37 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>658</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Härkämäck, Härkämäck, Dlr</t>
+          <t>Härkämäck, Dlr</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>459300</v>
+        <v>459573</v>
       </c>
       <c r="R7" t="n">
-        <v>6808144</v>
+        <v>6808047</v>
       </c>
       <c r="S7" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1285,22 +1300,22 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>123829879</v>
+        <v>123829197</v>
       </c>
       <c r="B8" t="n">
-        <v>78788</v>
+        <v>78525</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1313,21 +1328,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1337,10 +1352,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>459488</v>
+        <v>459611</v>
       </c>
       <c r="R8" t="n">
-        <v>6807974</v>
+        <v>6807987</v>
       </c>
       <c r="S8" t="n">
         <v>20</v>
@@ -1399,10 +1414,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>123829918</v>
+        <v>123834966</v>
       </c>
       <c r="B9" t="n">
-        <v>78524</v>
+        <v>57512</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1411,41 +1426,46 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6446</v>
+        <v>100110</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Gråspett</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Picus canus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>J.F. Gmelin, 1788</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Andljusbäcken, Andljusbäcken, Dlr</t>
+          <t>Härkämäck, Dlr</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>459424</v>
+        <v>459399</v>
       </c>
       <c r="R9" t="n">
-        <v>6807998</v>
+        <v>6808189</v>
       </c>
       <c r="S9" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1475,6 +1495,11 @@
       <c r="AA9" t="inlineStr">
         <is>
           <t>2025-04-07</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Förbiflygande.</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1489,19 +1514,19 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>123835432</v>
+        <v>123829121</v>
       </c>
       <c r="B10" t="n">
         <v>78788</v>
@@ -1541,10 +1566,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>459524</v>
+        <v>459641</v>
       </c>
       <c r="R10" t="n">
-        <v>6808114</v>
+        <v>6807971</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1581,7 +1606,7 @@
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>Garnlav i alla riktningar, ca 50 meter i radie. Miljöbild.</t>
+          <t>I synfältet i en radie av ca 40 meter. Miljöbild.</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1608,10 +1633,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>123834195</v>
+        <v>123835135</v>
       </c>
       <c r="B11" t="n">
-        <v>78525</v>
+        <v>78788</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1624,34 +1649,34 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Härkämäck, Härkämäck, Dlr</t>
+          <t>Härkämäck, Dlr</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>459365</v>
+        <v>459455</v>
       </c>
       <c r="R11" t="n">
-        <v>6808224</v>
+        <v>6808164</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1686,6 +1711,11 @@
           <t>2025-04-07</t>
         </is>
       </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Garnlav i en radie av ca 50 meter, synfältet. Miljöbild.</t>
+        </is>
+      </c>
       <c r="AD11" t="b">
         <v>0</v>
       </c>
@@ -1698,22 +1728,22 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>123828826</v>
+        <v>123829712</v>
       </c>
       <c r="B12" t="n">
-        <v>56700</v>
+        <v>90990</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1722,43 +1752,38 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100138</v>
+        <v>1202</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>Härkämäck, Dlr</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>459636</v>
+        <v>459573</v>
       </c>
       <c r="R12" t="n">
-        <v>6808042</v>
+        <v>6808047</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1791,11 +1816,6 @@
       <c r="AA12" t="inlineStr">
         <is>
           <t>2025-04-07</t>
-        </is>
-      </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>Garnlav i bakgrund. Miljöbild.</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1822,10 +1842,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>123833754</v>
+        <v>123829310</v>
       </c>
       <c r="B13" t="n">
-        <v>92271</v>
+        <v>57507</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1834,41 +1854,46 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>4364</v>
+        <v>100049</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Härkämäck, Härkämäck, Dlr</t>
+          <t>Härkämäck, Dlr</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>459290</v>
+        <v>459586</v>
       </c>
       <c r="R13" t="n">
-        <v>6808093</v>
+        <v>6807981</v>
       </c>
       <c r="S13" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1912,22 +1937,22 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>123834998</v>
+        <v>123834641</v>
       </c>
       <c r="B14" t="n">
-        <v>79377</v>
+        <v>78788</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1940,21 +1965,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>229821</v>
+        <v>6425</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1964,10 +1989,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>459437</v>
+        <v>459405</v>
       </c>
       <c r="R14" t="n">
-        <v>6808171</v>
+        <v>6808172</v>
       </c>
       <c r="S14" t="n">
         <v>20</v>
@@ -2026,7 +2051,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>123829121</v>
+        <v>123835432</v>
       </c>
       <c r="B15" t="n">
         <v>78788</v>
@@ -2066,10 +2091,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>459641</v>
+        <v>459524</v>
       </c>
       <c r="R15" t="n">
-        <v>6807971</v>
+        <v>6808114</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2106,7 +2131,7 @@
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>I synfältet i en radie av ca 40 meter. Miljöbild.</t>
+          <t>Garnlav i alla riktningar, ca 50 meter i radie. Miljöbild.</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2133,10 +2158,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>123834034</v>
+        <v>123829246</v>
       </c>
       <c r="B16" t="n">
-        <v>57507</v>
+        <v>78788</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2149,39 +2174,34 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Andljusen, Dlr</t>
+          <t>Härkämäck, Dlr</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>459325</v>
+        <v>459586</v>
       </c>
       <c r="R16" t="n">
-        <v>6808176</v>
+        <v>6807981</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2218,7 +2238,7 @@
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>Miljöbild.</t>
+          <t>Som vanligt garnlav i omgivningen. Miljöbilder.</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2245,7 +2265,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>123830009</v>
+        <v>123827957</v>
       </c>
       <c r="B17" t="n">
         <v>78524</v>
@@ -2281,17 +2301,17 @@
       <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Härkämäck, Dlr</t>
+          <t>Andljusbäcken, Andljusbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>459480</v>
+        <v>459664</v>
       </c>
       <c r="R17" t="n">
-        <v>6808013</v>
+        <v>6808079</v>
       </c>
       <c r="S17" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2321,11 +2341,6 @@
       <c r="AA17" t="inlineStr">
         <is>
           <t>2025-04-07</t>
-        </is>
-      </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>Miljöbild.</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2340,22 +2355,22 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>123829310</v>
+        <v>123828742</v>
       </c>
       <c r="B18" t="n">
-        <v>57507</v>
+        <v>78788</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2368,42 +2383,37 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Härkämäck, Dlr</t>
+          <t>Andljusbäcken, Andljusbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>459586</v>
+        <v>459612</v>
       </c>
       <c r="R18" t="n">
-        <v>6807981</v>
+        <v>6808068</v>
       </c>
       <c r="S18" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2447,19 +2457,19 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>123831244</v>
+        <v>123828783</v>
       </c>
       <c r="B19" t="n">
         <v>78788</v>
@@ -2499,10 +2509,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>459393</v>
+        <v>459611</v>
       </c>
       <c r="R19" t="n">
-        <v>6808027</v>
+        <v>6808048</v>
       </c>
       <c r="S19" t="n">
         <v>20</v>
@@ -2561,7 +2571,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>123833814</v>
+        <v>123834006</v>
       </c>
       <c r="B20" t="n">
         <v>78525</v>
@@ -2601,10 +2611,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>459293</v>
+        <v>459326</v>
       </c>
       <c r="R20" t="n">
-        <v>6808123</v>
+        <v>6808188</v>
       </c>
       <c r="S20" t="n">
         <v>15</v>
@@ -2663,10 +2673,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>123827957</v>
+        <v>123834195</v>
       </c>
       <c r="B21" t="n">
-        <v>78524</v>
+        <v>78525</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2679,37 +2689,37 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6446</v>
+        <v>228912</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Andljusbäcken, Andljusbäcken, Dlr</t>
+          <t>Härkämäck, Härkämäck, Dlr</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>459664</v>
+        <v>459365</v>
       </c>
       <c r="R21" t="n">
-        <v>6808079</v>
+        <v>6808224</v>
       </c>
       <c r="S21" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2753,22 +2763,22 @@
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>123830162</v>
+        <v>123829205</v>
       </c>
       <c r="B22" t="n">
-        <v>78172</v>
+        <v>78524</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2781,37 +2791,37 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6437</v>
+        <v>6446</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Härkämäck, Dlr</t>
+          <t>Andljusbäcken, Andljusbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>459480</v>
+        <v>459611</v>
       </c>
       <c r="R22" t="n">
-        <v>6808013</v>
+        <v>6807987</v>
       </c>
       <c r="S22" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -2841,11 +2851,6 @@
       <c r="AA22" t="inlineStr">
         <is>
           <t>2025-04-07</t>
-        </is>
-      </c>
-      <c r="AC22" t="inlineStr">
-        <is>
-          <t>Miljöbild.</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2860,22 +2865,22 @@
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>123828742</v>
+        <v>123829918</v>
       </c>
       <c r="B23" t="n">
-        <v>78788</v>
+        <v>78524</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2888,21 +2893,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2912,10 +2917,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>459612</v>
+        <v>459424</v>
       </c>
       <c r="R23" t="n">
-        <v>6808068</v>
+        <v>6807998</v>
       </c>
       <c r="S23" t="n">
         <v>20</v>
@@ -2974,10 +2979,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>123831277</v>
+        <v>123834650</v>
       </c>
       <c r="B24" t="n">
-        <v>57507</v>
+        <v>78525</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -2990,39 +2995,34 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>100049</v>
+        <v>228912</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
-      <c r="M24" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P24" t="inlineStr">
         <is>
           <t>Härkämäck, Dlr</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>459389</v>
+        <v>459399</v>
       </c>
       <c r="R24" t="n">
-        <v>6808070</v>
+        <v>6808189</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3059,7 +3059,7 @@
       </c>
       <c r="AC24" t="inlineStr">
         <is>
-          <t>Miljöbild.</t>
+          <t>Miljöbild</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3086,10 +3086,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>123831467</v>
+        <v>123829275</v>
       </c>
       <c r="B25" t="n">
-        <v>79377</v>
+        <v>78525</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3102,37 +3102,37 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>229821</v>
+        <v>228912</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Härkämäck, Härkämäck, Dlr</t>
+          <t>Andljusbäcken, Andljusbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>459290</v>
+        <v>459544</v>
       </c>
       <c r="R25" t="n">
-        <v>6808098</v>
+        <v>6807989</v>
       </c>
       <c r="S25" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3176,22 +3176,22 @@
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Niklas Rehn</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Niklas Rehn</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>123829246</v>
+        <v>123830920</v>
       </c>
       <c r="B26" t="n">
-        <v>78788</v>
+        <v>78433</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3204,37 +3204,37 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Härkämäck, Dlr</t>
+          <t>Andljusbäcken, Andljusbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>459586</v>
+        <v>459462</v>
       </c>
       <c r="R26" t="n">
-        <v>6807981</v>
+        <v>6808078</v>
       </c>
       <c r="S26" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3264,11 +3264,6 @@
       <c r="AA26" t="inlineStr">
         <is>
           <t>2025-04-07</t>
-        </is>
-      </c>
-      <c r="AC26" t="inlineStr">
-        <is>
-          <t>Som vanligt garnlav i omgivningen. Miljöbilder.</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3283,22 +3278,22 @@
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>123834220</v>
+        <v>123834890</v>
       </c>
       <c r="B27" t="n">
-        <v>78788</v>
+        <v>78867</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3311,37 +3306,37 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6425</v>
+        <v>864</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Lynge) Ahti</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Andljusen, Dlr</t>
+          <t>Härkämäck, Härkämäck, Dlr</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>459325</v>
+        <v>459427</v>
       </c>
       <c r="R27" t="n">
-        <v>6808176</v>
+        <v>6808130</v>
       </c>
       <c r="S27" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3371,11 +3366,6 @@
       <c r="AA27" t="inlineStr">
         <is>
           <t>2025-04-07</t>
-        </is>
-      </c>
-      <c r="AC27" t="inlineStr">
-        <is>
-          <t>I synfält, radie av ca 50 meter. Miljöbild.</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3390,22 +3380,22 @@
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>123829889</v>
+        <v>123831065</v>
       </c>
       <c r="B28" t="n">
-        <v>78525</v>
+        <v>78788</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3418,34 +3408,34 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Härkämäck, Dlr</t>
+          <t>Andljusbäcken, Andljusbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>459494</v>
+        <v>459425</v>
       </c>
       <c r="R28" t="n">
-        <v>6807997</v>
+        <v>6808084</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3480,11 +3470,6 @@
           <t>2025-04-07</t>
         </is>
       </c>
-      <c r="AC28" t="inlineStr">
-        <is>
-          <t>Miljöbild.</t>
-        </is>
-      </c>
       <c r="AD28" t="b">
         <v>0</v>
       </c>
@@ -3497,22 +3482,22 @@
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>123829632</v>
+        <v>123829982</v>
       </c>
       <c r="B29" t="n">
-        <v>91277</v>
+        <v>77716</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3525,37 +3510,37 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>658</v>
+        <v>6487</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Blågrå svartspik</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Chaenothecopsis fennica</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Laurila) Tibell</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Härkämäck, Dlr</t>
+          <t>Andljusbäcken, Andljusbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>459573</v>
+        <v>459432</v>
       </c>
       <c r="R29" t="n">
-        <v>6808047</v>
+        <v>6807989</v>
       </c>
       <c r="S29" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3599,22 +3584,22 @@
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>123835135</v>
+        <v>123833917</v>
       </c>
       <c r="B30" t="n">
-        <v>78788</v>
+        <v>78525</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3627,37 +3612,37 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Härkämäck, Dlr</t>
+          <t>Andljusbäcken, Andljusbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>459455</v>
+        <v>459292</v>
       </c>
       <c r="R30" t="n">
-        <v>6808164</v>
+        <v>6808184</v>
       </c>
       <c r="S30" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -3687,11 +3672,6 @@
       <c r="AA30" t="inlineStr">
         <is>
           <t>2025-04-07</t>
-        </is>
-      </c>
-      <c r="AC30" t="inlineStr">
-        <is>
-          <t>Garnlav i en radie av ca 50 meter, synfältet. Miljöbild.</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3706,22 +3686,22 @@
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>123831578</v>
+        <v>123833754</v>
       </c>
       <c r="B31" t="n">
-        <v>74879</v>
+        <v>92271</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3730,41 +3710,41 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6440</v>
+        <v>4364</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Andljusbäcken, Andljusbäcken, Dlr</t>
+          <t>Härkämäck, Härkämäck, Dlr</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>459287</v>
+        <v>459290</v>
       </c>
       <c r="R31" t="n">
-        <v>6808008</v>
+        <v>6808093</v>
       </c>
       <c r="S31" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -3808,22 +3788,22 @@
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>123833729</v>
+        <v>123831097</v>
       </c>
       <c r="B32" t="n">
-        <v>78525</v>
+        <v>79377</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -3836,37 +3816,37 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>228912</v>
+        <v>229821</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Andljusen, Dlr</t>
+          <t>Andljusbäcken, Andljusbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>459286</v>
+        <v>459402</v>
       </c>
       <c r="R32" t="n">
-        <v>6808090</v>
+        <v>6808072</v>
       </c>
       <c r="S32" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -3896,11 +3876,6 @@
       <c r="AA32" t="inlineStr">
         <is>
           <t>2025-04-07</t>
-        </is>
-      </c>
-      <c r="AC32" t="inlineStr">
-        <is>
-          <t>Miljöbild.</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -3915,22 +3890,22 @@
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>123831065</v>
+        <v>123829394</v>
       </c>
       <c r="B33" t="n">
-        <v>78788</v>
+        <v>77716</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -3943,34 +3918,34 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6425</v>
+        <v>6487</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Blågrå svartspik</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenothecopsis fennica</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Laurila) Tibell</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Andljusbäcken, Andljusbäcken, Dlr</t>
+          <t>Härkämäck, Dlr</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>459425</v>
+        <v>459586</v>
       </c>
       <c r="R33" t="n">
-        <v>6808084</v>
+        <v>6807981</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4017,22 +3992,22 @@
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>123828882</v>
+        <v>123829941</v>
       </c>
       <c r="B34" t="n">
-        <v>78820</v>
+        <v>78525</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4045,37 +4020,37 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>185</v>
+        <v>228912</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Andljusbäcken, Andljusbäcken, Dlr</t>
+          <t>Härkämäck, Dlr</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>459600</v>
+        <v>459480</v>
       </c>
       <c r="R34" t="n">
-        <v>6808030</v>
+        <v>6808013</v>
       </c>
       <c r="S34" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -4105,6 +4080,11 @@
       <c r="AA34" t="inlineStr">
         <is>
           <t>2025-04-07</t>
+        </is>
+      </c>
+      <c r="AC34" t="inlineStr">
+        <is>
+          <t>Miljöbild.</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4119,22 +4099,22 @@
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>123831067</v>
+        <v>123834567</v>
       </c>
       <c r="B35" t="n">
-        <v>78788</v>
+        <v>79377</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4147,21 +4127,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6425</v>
+        <v>229821</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4171,10 +4151,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>459439</v>
+        <v>459399</v>
       </c>
       <c r="R35" t="n">
-        <v>6808067</v>
+        <v>6808189</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4211,7 +4191,7 @@
       </c>
       <c r="AC35" t="inlineStr">
         <is>
-          <t>Synligt i en radie av ca 50 meter. Miljöbild.</t>
+          <t>Miljöbild.</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4238,10 +4218,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>123828783</v>
+        <v>123834034</v>
       </c>
       <c r="B36" t="n">
-        <v>78788</v>
+        <v>57507</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4254,37 +4234,42 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
+      <c r="M36" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Andljusbäcken, Andljusbäcken, Dlr</t>
+          <t>Andljusen, Dlr</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>459611</v>
+        <v>459325</v>
       </c>
       <c r="R36" t="n">
-        <v>6808048</v>
+        <v>6808176</v>
       </c>
       <c r="S36" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -4314,6 +4299,11 @@
       <c r="AA36" t="inlineStr">
         <is>
           <t>2025-04-07</t>
+        </is>
+      </c>
+      <c r="AC36" t="inlineStr">
+        <is>
+          <t>Miljöbild.</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4328,22 +4318,22 @@
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>123829197</v>
+        <v>123834998</v>
       </c>
       <c r="B37" t="n">
-        <v>78525</v>
+        <v>79377</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4356,34 +4346,34 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>228912</v>
+        <v>229821</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
-          <t>Andljusbäcken, Andljusbäcken, Dlr</t>
+          <t>Härkämäck, Härkämäck, Dlr</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>459611</v>
+        <v>459437</v>
       </c>
       <c r="R37" t="n">
-        <v>6807987</v>
+        <v>6808171</v>
       </c>
       <c r="S37" t="n">
         <v>20</v>
@@ -4442,10 +4432,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>123833917</v>
+        <v>123828882</v>
       </c>
       <c r="B38" t="n">
-        <v>78525</v>
+        <v>78820</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4458,21 +4448,21 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>228912</v>
+        <v>185</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4482,10 +4472,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>459292</v>
+        <v>459600</v>
       </c>
       <c r="R38" t="n">
-        <v>6808184</v>
+        <v>6808030</v>
       </c>
       <c r="S38" t="n">
         <v>20</v>
@@ -4544,10 +4534,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>123834966</v>
+        <v>123829879</v>
       </c>
       <c r="B39" t="n">
-        <v>57512</v>
+        <v>78788</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4556,46 +4546,41 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>100110</v>
+        <v>6425</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Gråspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Picus canus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>J.F. Gmelin, 1788</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
-      <c r="M39" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="P39" t="inlineStr">
         <is>
-          <t>Härkämäck, Dlr</t>
+          <t>Andljusbäcken, Andljusbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>459399</v>
+        <v>459488</v>
       </c>
       <c r="R39" t="n">
-        <v>6808189</v>
+        <v>6807974</v>
       </c>
       <c r="S39" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
@@ -4625,11 +4610,6 @@
       <c r="AA39" t="inlineStr">
         <is>
           <t>2025-04-07</t>
-        </is>
-      </c>
-      <c r="AC39" t="inlineStr">
-        <is>
-          <t>Förbiflygande.</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4644,19 +4624,19 @@
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>123828044</v>
+        <v>123828608</v>
       </c>
       <c r="B40" t="n">
         <v>78788</v>
@@ -4696,10 +4676,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>459681</v>
+        <v>459636</v>
       </c>
       <c r="R40" t="n">
-        <v>6808072</v>
+        <v>6808042</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4736,7 +4716,7 @@
       </c>
       <c r="AC40" t="inlineStr">
         <is>
-          <t>Garnlav i synfältet i en radie av ca 50 meter. Miljöbild.</t>
+          <t>Garnlav i synfältet i en radie av ca 50 meter. Miljöbilder.</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4763,7 +4743,7 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>123834641</v>
+        <v>123831067</v>
       </c>
       <c r="B41" t="n">
         <v>78788</v>
@@ -4799,17 +4779,17 @@
       <c r="I41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
-          <t>Härkämäck, Härkämäck, Dlr</t>
+          <t>Härkämäck, Dlr</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>459405</v>
+        <v>459439</v>
       </c>
       <c r="R41" t="n">
-        <v>6808172</v>
+        <v>6808067</v>
       </c>
       <c r="S41" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -4839,6 +4819,11 @@
       <c r="AA41" t="inlineStr">
         <is>
           <t>2025-04-07</t>
+        </is>
+      </c>
+      <c r="AC41" t="inlineStr">
+        <is>
+          <t>Synligt i en radie av ca 50 meter. Miljöbild.</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -4853,19 +4838,19 @@
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>123834006</v>
+        <v>123833814</v>
       </c>
       <c r="B42" t="n">
         <v>78525</v>
@@ -4905,10 +4890,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>459326</v>
+        <v>459293</v>
       </c>
       <c r="R42" t="n">
-        <v>6808188</v>
+        <v>6808123</v>
       </c>
       <c r="S42" t="n">
         <v>15</v>
@@ -4967,10 +4952,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>123829275</v>
+        <v>123834630</v>
       </c>
       <c r="B43" t="n">
-        <v>78525</v>
+        <v>57512</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -4979,41 +4964,41 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>228912</v>
+        <v>100110</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Gråspett</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Picus canus</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>J.F. Gmelin, 1788</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
-          <t>Andljusbäcken, Andljusbäcken, Dlr</t>
+          <t>Härkämäck, Härkämäck, Dlr</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>459544</v>
+        <v>459408</v>
       </c>
       <c r="R43" t="n">
-        <v>6807989</v>
+        <v>6808198</v>
       </c>
       <c r="S43" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T43" t="inlineStr">
         <is>
@@ -5043,6 +5028,11 @@
       <c r="AA43" t="inlineStr">
         <is>
           <t>2025-04-07</t>
+        </is>
+      </c>
+      <c r="AC43" t="inlineStr">
+        <is>
+          <t>Förbiflygande.</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5057,22 +5047,22 @@
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>123834890</v>
+        <v>123831244</v>
       </c>
       <c r="B44" t="n">
-        <v>78867</v>
+        <v>78788</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5085,34 +5075,34 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>864</v>
+        <v>6425</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Knottrig blåslav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Hypogymnia bitteri</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Lynge) Ahti</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
-          <t>Härkämäck, Härkämäck, Dlr</t>
+          <t>Andljusbäcken, Andljusbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>459427</v>
+        <v>459393</v>
       </c>
       <c r="R44" t="n">
-        <v>6808130</v>
+        <v>6808027</v>
       </c>
       <c r="S44" t="n">
         <v>20</v>
@@ -5171,10 +5161,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>123829394</v>
+        <v>123833841</v>
       </c>
       <c r="B45" t="n">
-        <v>77716</v>
+        <v>78788</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5187,37 +5177,37 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6487</v>
+        <v>6425</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Blågrå svartspik</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Chaenothecopsis fennica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Laurila) Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
-          <t>Härkämäck, Dlr</t>
+          <t>Härkämäck, Härkämäck, Dlr</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>459586</v>
+        <v>459300</v>
       </c>
       <c r="R45" t="n">
-        <v>6807981</v>
+        <v>6808144</v>
       </c>
       <c r="S45" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T45" t="inlineStr">
         <is>
@@ -5261,22 +5251,22 @@
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>123829941</v>
+        <v>123829102</v>
       </c>
       <c r="B46" t="n">
-        <v>78525</v>
+        <v>78788</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5289,37 +5279,37 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
-          <t>Härkämäck, Dlr</t>
+          <t>Andljusbäcken, Andljusbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>459480</v>
+        <v>459666</v>
       </c>
       <c r="R46" t="n">
-        <v>6808013</v>
+        <v>6807990</v>
       </c>
       <c r="S46" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T46" t="inlineStr">
         <is>
@@ -5349,11 +5339,6 @@
       <c r="AA46" t="inlineStr">
         <is>
           <t>2025-04-07</t>
-        </is>
-      </c>
-      <c r="AC46" t="inlineStr">
-        <is>
-          <t>Miljöbild.</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5368,22 +5353,22 @@
       <c r="AT46" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX46" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>123830920</v>
+        <v>123830162</v>
       </c>
       <c r="B47" t="n">
-        <v>78433</v>
+        <v>78172</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5396,37 +5381,37 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>353</v>
+        <v>6437</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
-          <t>Andljusbäcken, Andljusbäcken, Dlr</t>
+          <t>Härkämäck, Dlr</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>459462</v>
+        <v>459480</v>
       </c>
       <c r="R47" t="n">
-        <v>6808078</v>
+        <v>6808013</v>
       </c>
       <c r="S47" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T47" t="inlineStr">
         <is>
@@ -5456,6 +5441,11 @@
       <c r="AA47" t="inlineStr">
         <is>
           <t>2025-04-07</t>
+        </is>
+      </c>
+      <c r="AC47" t="inlineStr">
+        <is>
+          <t>Miljöbild.</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5470,22 +5460,22 @@
       <c r="AT47" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX47" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>123829712</v>
+        <v>123833729</v>
       </c>
       <c r="B48" t="n">
-        <v>90990</v>
+        <v>78525</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -5498,34 +5488,34 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>1202</v>
+        <v>228912</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
-          <t>Härkämäck, Dlr</t>
+          <t>Andljusen, Dlr</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>459573</v>
+        <v>459286</v>
       </c>
       <c r="R48" t="n">
-        <v>6808047</v>
+        <v>6808090</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5558,6 +5548,11 @@
       <c r="AA48" t="inlineStr">
         <is>
           <t>2025-04-07</t>
+        </is>
+      </c>
+      <c r="AC48" t="inlineStr">
+        <is>
+          <t>Miljöbild.</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5584,7 +5579,7 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>123829205</v>
+        <v>123830009</v>
       </c>
       <c r="B49" t="n">
         <v>78524</v>
@@ -5620,17 +5615,17 @@
       <c r="I49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
-          <t>Andljusbäcken, Andljusbäcken, Dlr</t>
+          <t>Härkämäck, Dlr</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>459611</v>
+        <v>459480</v>
       </c>
       <c r="R49" t="n">
-        <v>6807987</v>
+        <v>6808013</v>
       </c>
       <c r="S49" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T49" t="inlineStr">
         <is>
@@ -5660,6 +5655,11 @@
       <c r="AA49" t="inlineStr">
         <is>
           <t>2025-04-07</t>
+        </is>
+      </c>
+      <c r="AC49" t="inlineStr">
+        <is>
+          <t>Miljöbild.</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -5674,22 +5674,22 @@
       <c r="AT49" t="inlineStr"/>
       <c r="AW49" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX49" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>123828608</v>
+        <v>123829889</v>
       </c>
       <c r="B50" t="n">
-        <v>78788</v>
+        <v>78525</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -5702,21 +5702,21 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5726,10 +5726,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>459636</v>
+        <v>459494</v>
       </c>
       <c r="R50" t="n">
-        <v>6808042</v>
+        <v>6807997</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5766,7 +5766,7 @@
       </c>
       <c r="AC50" t="inlineStr">
         <is>
-          <t>Garnlav i synfältet i en radie av ca 50 meter. Miljöbilder.</t>
+          <t>Miljöbild.</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -5793,7 +5793,7 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>123829102</v>
+        <v>123834183</v>
       </c>
       <c r="B51" t="n">
         <v>78788</v>
@@ -5833,10 +5833,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>459666</v>
+        <v>459373</v>
       </c>
       <c r="R51" t="n">
-        <v>6807990</v>
+        <v>6808222</v>
       </c>
       <c r="S51" t="n">
         <v>20</v>
@@ -5895,10 +5895,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>123834630</v>
+        <v>123828044</v>
       </c>
       <c r="B52" t="n">
-        <v>57512</v>
+        <v>78788</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -5907,38 +5907,38 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>100110</v>
+        <v>6425</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Gråspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Picus canus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>J.F. Gmelin, 1788</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
-          <t>Härkämäck, Härkämäck, Dlr</t>
+          <t>Härkämäck, Dlr</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>459408</v>
+        <v>459681</v>
       </c>
       <c r="R52" t="n">
-        <v>6808198</v>
+        <v>6808072</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -5975,7 +5975,7 @@
       </c>
       <c r="AC52" t="inlineStr">
         <is>
-          <t>Förbiflygande.</t>
+          <t>Garnlav i synfältet i en radie av ca 50 meter. Miljöbild.</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -5990,22 +5990,22 @@
       <c r="AT52" t="inlineStr"/>
       <c r="AW52" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX52" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>123920427</v>
+        <v>123920731</v>
       </c>
       <c r="B53" t="n">
-        <v>57491</v>
+        <v>78788</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -6018,39 +6018,34 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
-      <c r="M53" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
       <c r="P53" t="inlineStr">
         <is>
           <t>Härkämäck, Dlr</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>459571</v>
+        <v>459608</v>
       </c>
       <c r="R53" t="n">
-        <v>6808057</v>
+        <v>6808066</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6102,17 +6097,17 @@
       </c>
       <c r="AX53" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Anders Heggestad, Håkan Thenander, lennart karlsson, Niklas Rehn</t>
+          <t>Philipp Weiss, Anders Heggestad, lennart karlsson, Håkan Thenander, Niklas Rehn</t>
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>123920733</v>
+        <v>123920540</v>
       </c>
       <c r="B54" t="n">
-        <v>78788</v>
+        <v>78525</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -6125,21 +6120,21 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -6211,7 +6206,7 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>123920440</v>
+        <v>123920441</v>
       </c>
       <c r="B55" t="n">
         <v>56700</v>
@@ -6256,10 +6251,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>459617</v>
+        <v>459609</v>
       </c>
       <c r="R55" t="n">
-        <v>6808041</v>
+        <v>6807987</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6318,7 +6313,7 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>123920732</v>
+        <v>123920733</v>
       </c>
       <c r="B56" t="n">
         <v>78788</v>
@@ -6358,10 +6353,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>459616</v>
+        <v>459589</v>
       </c>
       <c r="R56" t="n">
-        <v>6808044</v>
+        <v>6807980</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6420,7 +6415,7 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>123920731</v>
+        <v>123920732</v>
       </c>
       <c r="B57" t="n">
         <v>78788</v>
@@ -6460,10 +6455,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>459608</v>
+        <v>459616</v>
       </c>
       <c r="R57" t="n">
-        <v>6808066</v>
+        <v>6808044</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6522,10 +6517,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>123920734</v>
+        <v>123920419</v>
       </c>
       <c r="B58" t="n">
-        <v>78788</v>
+        <v>90990</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
@@ -6538,21 +6533,21 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -6562,10 +6557,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>459613</v>
+        <v>459603</v>
       </c>
       <c r="R58" t="n">
-        <v>6807959</v>
+        <v>6807965</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6617,7 +6612,7 @@
       </c>
       <c r="AX58" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Anders Heggestad, lennart karlsson, Håkan Thenander, Niklas Rehn</t>
+          <t>Philipp Weiss, Anders Heggestad, Håkan Thenander, lennart karlsson, Niklas Rehn</t>
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
@@ -6726,10 +6721,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>123920419</v>
+        <v>123920427</v>
       </c>
       <c r="B60" t="n">
-        <v>90990</v>
+        <v>57491</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
@@ -6742,34 +6737,39 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
+      <c r="M60" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="P60" t="inlineStr">
         <is>
           <t>Härkämäck, Dlr</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>459603</v>
+        <v>459571</v>
       </c>
       <c r="R60" t="n">
-        <v>6807965</v>
+        <v>6808057</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6828,10 +6828,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>123920540</v>
+        <v>123920729</v>
       </c>
       <c r="B61" t="n">
-        <v>78525</v>
+        <v>78788</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
@@ -6844,21 +6844,21 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -6868,10 +6868,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>459589</v>
+        <v>459566</v>
       </c>
       <c r="R61" t="n">
-        <v>6807980</v>
+        <v>6808068</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -7032,10 +7032,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>123920729</v>
+        <v>123920399</v>
       </c>
       <c r="B63" t="n">
-        <v>78788</v>
+        <v>79377</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
@@ -7048,21 +7048,21 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>6425</v>
+        <v>229821</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -7072,10 +7072,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>459566</v>
+        <v>459591</v>
       </c>
       <c r="R63" t="n">
-        <v>6808068</v>
+        <v>6808065</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -7127,17 +7127,17 @@
       </c>
       <c r="AX63" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Anders Heggestad, lennart karlsson, Håkan Thenander, Niklas Rehn</t>
+          <t>Philipp Weiss, Anders Heggestad, Håkan Thenander, lennart karlsson, Niklas Rehn</t>
         </is>
       </c>
       <c r="AY63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>123920399</v>
+        <v>123920442</v>
       </c>
       <c r="B64" t="n">
-        <v>79377</v>
+        <v>56700</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
@@ -7146,38 +7146,43 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>229821</v>
+        <v>100138</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
+      <c r="M64" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="P64" t="inlineStr">
         <is>
           <t>Härkämäck, Dlr</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>459591</v>
+        <v>459593</v>
       </c>
       <c r="R64" t="n">
-        <v>6808065</v>
+        <v>6807978</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7236,10 +7241,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>123920442</v>
+        <v>123920734</v>
       </c>
       <c r="B65" t="n">
-        <v>56700</v>
+        <v>78788</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
@@ -7248,43 +7253,38 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
-      <c r="M65" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="P65" t="inlineStr">
         <is>
           <t>Härkämäck, Dlr</t>
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>459593</v>
+        <v>459613</v>
       </c>
       <c r="R65" t="n">
-        <v>6807978</v>
+        <v>6807959</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7336,17 +7336,17 @@
       </c>
       <c r="AX65" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Anders Heggestad, Håkan Thenander, lennart karlsson, Niklas Rehn</t>
+          <t>Philipp Weiss, Anders Heggestad, lennart karlsson, Håkan Thenander, Niklas Rehn</t>
         </is>
       </c>
       <c r="AY65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>123920727</v>
+        <v>123920440</v>
       </c>
       <c r="B66" t="n">
-        <v>78788</v>
+        <v>56700</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
@@ -7355,38 +7355,43 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
+      <c r="M66" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="P66" t="inlineStr">
         <is>
           <t>Härkämäck, Dlr</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>459542</v>
+        <v>459617</v>
       </c>
       <c r="R66" t="n">
-        <v>6808123</v>
+        <v>6808041</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7438,14 +7443,14 @@
       </c>
       <c r="AX66" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Anders Heggestad, lennart karlsson, Håkan Thenander, Niklas Rehn</t>
+          <t>Philipp Weiss, Anders Heggestad, Håkan Thenander, lennart karlsson, Niklas Rehn</t>
         </is>
       </c>
       <c r="AY66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>123920730</v>
+        <v>123920727</v>
       </c>
       <c r="B67" t="n">
         <v>78788</v>
@@ -7485,10 +7490,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>459590</v>
+        <v>459542</v>
       </c>
       <c r="R67" t="n">
-        <v>6808062</v>
+        <v>6808123</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7547,10 +7552,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>123920441</v>
+        <v>123920730</v>
       </c>
       <c r="B68" t="n">
-        <v>56700</v>
+        <v>78788</v>
       </c>
       <c r="C68" t="inlineStr">
         <is>
@@ -7559,43 +7564,38 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
-      <c r="M68" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="P68" t="inlineStr">
         <is>
           <t>Härkämäck, Dlr</t>
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>459609</v>
+        <v>459590</v>
       </c>
       <c r="R68" t="n">
-        <v>6807987</v>
+        <v>6808062</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7647,7 +7647,7 @@
       </c>
       <c r="AX68" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Anders Heggestad, Håkan Thenander, lennart karlsson, Niklas Rehn</t>
+          <t>Philipp Weiss, Anders Heggestad, lennart karlsson, Håkan Thenander, Niklas Rehn</t>
         </is>
       </c>
       <c r="AY68" t="inlineStr"/>

--- a/artfynd/A 61327-2022 artfynd.xlsx
+++ b/artfynd/A 61327-2022 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>123831578</v>
+        <v>123831277</v>
       </c>
       <c r="B2" t="n">
-        <v>74879</v>
+        <v>57507</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,37 +691,42 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6440</v>
+        <v>100049</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Andljusbäcken, Andljusbäcken, Dlr</t>
+          <t>Härkämäck, Dlr</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>459287</v>
+        <v>459389</v>
       </c>
       <c r="R2" t="n">
-        <v>6808008</v>
+        <v>6808070</v>
       </c>
       <c r="S2" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -751,6 +756,11 @@
       <c r="AA2" t="inlineStr">
         <is>
           <t>2025-04-07</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>Miljöbild.</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -765,22 +775,22 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123831277</v>
+        <v>123831578</v>
       </c>
       <c r="B3" t="n">
-        <v>57507</v>
+        <v>74879</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -793,42 +803,37 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100049</v>
+        <v>6440</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Härkämäck, Dlr</t>
+          <t>Andljusbäcken, Andljusbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>459389</v>
+        <v>459287</v>
       </c>
       <c r="R3" t="n">
-        <v>6808070</v>
+        <v>6808008</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -858,11 +863,6 @@
       <c r="AA3" t="inlineStr">
         <is>
           <t>2025-04-07</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Miljöbild.</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -877,12 +877,12 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
@@ -1312,10 +1312,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>123829197</v>
+        <v>123834966</v>
       </c>
       <c r="B8" t="n">
-        <v>78525</v>
+        <v>57512</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1324,41 +1324,46 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>228912</v>
+        <v>100110</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Gråspett</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Picus canus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>J.F. Gmelin, 1788</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Andljusbäcken, Andljusbäcken, Dlr</t>
+          <t>Härkämäck, Dlr</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>459611</v>
+        <v>459399</v>
       </c>
       <c r="R8" t="n">
-        <v>6807987</v>
+        <v>6808189</v>
       </c>
       <c r="S8" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1388,6 +1393,11 @@
       <c r="AA8" t="inlineStr">
         <is>
           <t>2025-04-07</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Förbiflygande.</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1402,22 +1412,22 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>123834966</v>
+        <v>123829121</v>
       </c>
       <c r="B9" t="n">
-        <v>57512</v>
+        <v>78788</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1426,43 +1436,38 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100110</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Gråspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Picus canus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>J.F. Gmelin, 1788</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Härkämäck, Dlr</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>459399</v>
+        <v>459641</v>
       </c>
       <c r="R9" t="n">
-        <v>6808189</v>
+        <v>6807971</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1499,7 +1504,7 @@
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>Förbiflygande.</t>
+          <t>I synfältet i en radie av ca 40 meter. Miljöbild.</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1526,7 +1531,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>123829121</v>
+        <v>123835135</v>
       </c>
       <c r="B10" t="n">
         <v>78788</v>
@@ -1566,10 +1571,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>459641</v>
+        <v>459455</v>
       </c>
       <c r="R10" t="n">
-        <v>6807971</v>
+        <v>6808164</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1606,7 +1611,7 @@
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>I synfältet i en radie av ca 40 meter. Miljöbild.</t>
+          <t>Garnlav i en radie av ca 50 meter, synfältet. Miljöbild.</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1633,10 +1638,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>123835135</v>
+        <v>123829197</v>
       </c>
       <c r="B11" t="n">
-        <v>78788</v>
+        <v>78525</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1649,37 +1654,37 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Härkämäck, Dlr</t>
+          <t>Andljusbäcken, Andljusbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>459455</v>
+        <v>459611</v>
       </c>
       <c r="R11" t="n">
-        <v>6808164</v>
+        <v>6807987</v>
       </c>
       <c r="S11" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1709,11 +1714,6 @@
       <c r="AA11" t="inlineStr">
         <is>
           <t>2025-04-07</t>
-        </is>
-      </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>Garnlav i en radie av ca 50 meter, synfältet. Miljöbild.</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1728,12 +1728,12 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
@@ -3188,10 +3188,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>123830920</v>
+        <v>123833917</v>
       </c>
       <c r="B26" t="n">
-        <v>78433</v>
+        <v>78525</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3204,21 +3204,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>353</v>
+        <v>228912</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3228,10 +3228,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>459462</v>
+        <v>459292</v>
       </c>
       <c r="R26" t="n">
-        <v>6808078</v>
+        <v>6808184</v>
       </c>
       <c r="S26" t="n">
         <v>20</v>
@@ -3290,10 +3290,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>123834890</v>
+        <v>123830920</v>
       </c>
       <c r="B27" t="n">
-        <v>78867</v>
+        <v>78433</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3306,34 +3306,34 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>864</v>
+        <v>353</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Knottrig blåslav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Hypogymnia bitteri</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Lynge) Ahti</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Härkämäck, Härkämäck, Dlr</t>
+          <t>Andljusbäcken, Andljusbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>459427</v>
+        <v>459462</v>
       </c>
       <c r="R27" t="n">
-        <v>6808130</v>
+        <v>6808078</v>
       </c>
       <c r="S27" t="n">
         <v>20</v>
@@ -3392,10 +3392,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>123831065</v>
+        <v>123834890</v>
       </c>
       <c r="B28" t="n">
-        <v>78788</v>
+        <v>78867</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3408,37 +3408,37 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6425</v>
+        <v>864</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Lynge) Ahti</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Andljusbäcken, Andljusbäcken, Dlr</t>
+          <t>Härkämäck, Härkämäck, Dlr</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>459425</v>
+        <v>459427</v>
       </c>
       <c r="R28" t="n">
-        <v>6808084</v>
+        <v>6808130</v>
       </c>
       <c r="S28" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3494,10 +3494,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>123829982</v>
+        <v>123831065</v>
       </c>
       <c r="B29" t="n">
-        <v>77716</v>
+        <v>78788</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3510,21 +3510,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6487</v>
+        <v>6425</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Blågrå svartspik</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Chaenothecopsis fennica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Laurila) Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3534,13 +3534,13 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>459432</v>
+        <v>459425</v>
       </c>
       <c r="R29" t="n">
-        <v>6807989</v>
+        <v>6808084</v>
       </c>
       <c r="S29" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3596,10 +3596,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>123833917</v>
+        <v>123829982</v>
       </c>
       <c r="B30" t="n">
-        <v>78525</v>
+        <v>77716</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3612,21 +3612,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>228912</v>
+        <v>6487</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Blågrå svartspik</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Chaenothecopsis fennica</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Laurila) Tibell</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3636,10 +3636,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>459292</v>
+        <v>459432</v>
       </c>
       <c r="R30" t="n">
-        <v>6808184</v>
+        <v>6807989</v>
       </c>
       <c r="S30" t="n">
         <v>20</v>
@@ -3698,10 +3698,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>123833754</v>
+        <v>123831097</v>
       </c>
       <c r="B31" t="n">
-        <v>92271</v>
+        <v>79377</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3710,41 +3710,41 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>4364</v>
+        <v>229821</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Härkämäck, Härkämäck, Dlr</t>
+          <t>Andljusbäcken, Andljusbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>459290</v>
+        <v>459402</v>
       </c>
       <c r="R31" t="n">
-        <v>6808093</v>
+        <v>6808072</v>
       </c>
       <c r="S31" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -3788,22 +3788,22 @@
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>123831097</v>
+        <v>123833754</v>
       </c>
       <c r="B32" t="n">
-        <v>79377</v>
+        <v>92271</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -3812,41 +3812,41 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>229821</v>
+        <v>4364</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Andljusbäcken, Andljusbäcken, Dlr</t>
+          <t>Härkämäck, Härkämäck, Dlr</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>459402</v>
+        <v>459290</v>
       </c>
       <c r="R32" t="n">
-        <v>6808072</v>
+        <v>6808093</v>
       </c>
       <c r="S32" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -3890,12 +3890,12 @@
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
@@ -5686,10 +5686,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>123829889</v>
+        <v>123834183</v>
       </c>
       <c r="B50" t="n">
-        <v>78525</v>
+        <v>78788</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -5702,37 +5702,37 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
-          <t>Härkämäck, Dlr</t>
+          <t>Andljusbäcken, Andljusbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>459494</v>
+        <v>459373</v>
       </c>
       <c r="R50" t="n">
-        <v>6807997</v>
+        <v>6808222</v>
       </c>
       <c r="S50" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T50" t="inlineStr">
         <is>
@@ -5762,11 +5762,6 @@
       <c r="AA50" t="inlineStr">
         <is>
           <t>2025-04-07</t>
-        </is>
-      </c>
-      <c r="AC50" t="inlineStr">
-        <is>
-          <t>Miljöbild.</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -5781,19 +5776,19 @@
       <c r="AT50" t="inlineStr"/>
       <c r="AW50" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX50" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>123834183</v>
+        <v>123828044</v>
       </c>
       <c r="B51" t="n">
         <v>78788</v>
@@ -5829,17 +5824,17 @@
       <c r="I51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
-          <t>Andljusbäcken, Andljusbäcken, Dlr</t>
+          <t>Härkämäck, Dlr</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>459373</v>
+        <v>459681</v>
       </c>
       <c r="R51" t="n">
-        <v>6808222</v>
+        <v>6808072</v>
       </c>
       <c r="S51" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T51" t="inlineStr">
         <is>
@@ -5869,6 +5864,11 @@
       <c r="AA51" t="inlineStr">
         <is>
           <t>2025-04-07</t>
+        </is>
+      </c>
+      <c r="AC51" t="inlineStr">
+        <is>
+          <t>Garnlav i synfältet i en radie av ca 50 meter. Miljöbild.</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -5883,22 +5883,22 @@
       <c r="AT51" t="inlineStr"/>
       <c r="AW51" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX51" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>123828044</v>
+        <v>123829889</v>
       </c>
       <c r="B52" t="n">
-        <v>78788</v>
+        <v>78525</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -5911,21 +5911,21 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -5935,10 +5935,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>459681</v>
+        <v>459494</v>
       </c>
       <c r="R52" t="n">
-        <v>6808072</v>
+        <v>6807997</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -5975,7 +5975,7 @@
       </c>
       <c r="AC52" t="inlineStr">
         <is>
-          <t>Garnlav i synfältet i en radie av ca 50 meter. Miljöbild.</t>
+          <t>Miljöbild.</t>
         </is>
       </c>
       <c r="AD52" t="b">

--- a/artfynd/A 61327-2022 artfynd.xlsx
+++ b/artfynd/A 61327-2022 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>123831277</v>
+        <v>123828882</v>
       </c>
       <c r="B2" t="n">
-        <v>57507</v>
+        <v>78820</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,42 +691,37 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100049</v>
+        <v>185</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Härkämäck, Dlr</t>
+          <t>Andljusbäcken, Andljusbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>459389</v>
+        <v>459600</v>
       </c>
       <c r="R2" t="n">
-        <v>6808070</v>
+        <v>6808030</v>
       </c>
       <c r="S2" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -756,11 +751,6 @@
       <c r="AA2" t="inlineStr">
         <is>
           <t>2025-04-07</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Miljöbild.</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -775,22 +765,22 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123831578</v>
+        <v>123834034</v>
       </c>
       <c r="B3" t="n">
-        <v>74879</v>
+        <v>57507</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -803,37 +793,42 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6440</v>
+        <v>100049</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Andljusbäcken, Andljusbäcken, Dlr</t>
+          <t>Andljusen, Dlr</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>459287</v>
+        <v>459325</v>
       </c>
       <c r="R3" t="n">
-        <v>6808008</v>
+        <v>6808176</v>
       </c>
       <c r="S3" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -863,6 +858,11 @@
       <c r="AA3" t="inlineStr">
         <is>
           <t>2025-04-07</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Miljöbild.</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -877,22 +877,22 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123828826</v>
+        <v>123828783</v>
       </c>
       <c r="B4" t="n">
-        <v>56700</v>
+        <v>78788</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -901,46 +901,41 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Härkämäck, Dlr</t>
+          <t>Andljusbäcken, Andljusbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>459636</v>
+        <v>459611</v>
       </c>
       <c r="R4" t="n">
-        <v>6808042</v>
+        <v>6808048</v>
       </c>
       <c r="S4" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -970,11 +965,6 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2025-04-07</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Garnlav i bakgrund. Miljöbild.</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -989,22 +979,22 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123834220</v>
+        <v>123834650</v>
       </c>
       <c r="B5" t="n">
-        <v>78788</v>
+        <v>78525</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1017,34 +1007,34 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Andljusen, Dlr</t>
+          <t>Härkämäck, Dlr</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>459325</v>
+        <v>459399</v>
       </c>
       <c r="R5" t="n">
-        <v>6808176</v>
+        <v>6808189</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1081,7 +1071,7 @@
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>I synfält, radie av ca 50 meter. Miljöbild.</t>
+          <t>Miljöbild</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1108,10 +1098,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>123831467</v>
+        <v>123829275</v>
       </c>
       <c r="B6" t="n">
-        <v>79377</v>
+        <v>78525</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1124,37 +1114,37 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>229821</v>
+        <v>228912</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Härkämäck, Härkämäck, Dlr</t>
+          <t>Andljusbäcken, Andljusbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>459290</v>
+        <v>459544</v>
       </c>
       <c r="R6" t="n">
-        <v>6808098</v>
+        <v>6807989</v>
       </c>
       <c r="S6" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1198,22 +1188,22 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Niklas Rehn</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Niklas Rehn</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>123829632</v>
+        <v>123828044</v>
       </c>
       <c r="B7" t="n">
-        <v>91277</v>
+        <v>78788</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1226,21 +1216,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>658</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1250,10 +1240,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>459573</v>
+        <v>459681</v>
       </c>
       <c r="R7" t="n">
-        <v>6808047</v>
+        <v>6808072</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1286,6 +1276,11 @@
       <c r="AA7" t="inlineStr">
         <is>
           <t>2025-04-07</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Garnlav i synfältet i en radie av ca 50 meter. Miljöbild.</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1312,10 +1307,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>123834966</v>
+        <v>123835135</v>
       </c>
       <c r="B8" t="n">
-        <v>57512</v>
+        <v>78788</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1324,43 +1319,38 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100110</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Gråspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Picus canus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>J.F. Gmelin, 1788</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Härkämäck, Dlr</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>459399</v>
+        <v>459455</v>
       </c>
       <c r="R8" t="n">
-        <v>6808189</v>
+        <v>6808164</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1397,7 +1387,7 @@
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>Förbiflygande.</t>
+          <t>Garnlav i en radie av ca 50 meter, synfältet. Miljöbild.</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1424,7 +1414,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>123829121</v>
+        <v>123833841</v>
       </c>
       <c r="B9" t="n">
         <v>78788</v>
@@ -1460,17 +1450,17 @@
       <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Härkämäck, Dlr</t>
+          <t>Härkämäck, Härkämäck, Dlr</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>459641</v>
+        <v>459300</v>
       </c>
       <c r="R9" t="n">
-        <v>6807971</v>
+        <v>6808144</v>
       </c>
       <c r="S9" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1500,11 +1490,6 @@
       <c r="AA9" t="inlineStr">
         <is>
           <t>2025-04-07</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>I synfältet i en radie av ca 40 meter. Miljöbild.</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1519,22 +1504,22 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>123835135</v>
+        <v>123831277</v>
       </c>
       <c r="B10" t="n">
-        <v>78788</v>
+        <v>57507</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1547,34 +1532,39 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Härkämäck, Dlr</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>459455</v>
+        <v>459389</v>
       </c>
       <c r="R10" t="n">
-        <v>6808164</v>
+        <v>6808070</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1611,7 +1601,7 @@
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>Garnlav i en radie av ca 50 meter, synfältet. Miljöbild.</t>
+          <t>Miljöbild.</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1638,10 +1628,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>123829197</v>
+        <v>123833754</v>
       </c>
       <c r="B11" t="n">
-        <v>78525</v>
+        <v>92271</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1650,41 +1640,41 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>228912</v>
+        <v>4364</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Andljusbäcken, Andljusbäcken, Dlr</t>
+          <t>Härkämäck, Härkämäck, Dlr</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>459611</v>
+        <v>459290</v>
       </c>
       <c r="R11" t="n">
-        <v>6807987</v>
+        <v>6808093</v>
       </c>
       <c r="S11" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1728,22 +1718,22 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>123829712</v>
+        <v>123833917</v>
       </c>
       <c r="B12" t="n">
-        <v>90990</v>
+        <v>78525</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1756,37 +1746,37 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>1202</v>
+        <v>228912</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Härkämäck, Dlr</t>
+          <t>Andljusbäcken, Andljusbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>459573</v>
+        <v>459292</v>
       </c>
       <c r="R12" t="n">
-        <v>6808047</v>
+        <v>6808184</v>
       </c>
       <c r="S12" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1830,22 +1820,22 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>123829310</v>
+        <v>123834006</v>
       </c>
       <c r="B13" t="n">
-        <v>57507</v>
+        <v>78525</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1858,42 +1848,37 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100049</v>
+        <v>228912</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Härkämäck, Dlr</t>
+          <t>Härkämäck, Härkämäck, Dlr</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>459586</v>
+        <v>459326</v>
       </c>
       <c r="R13" t="n">
-        <v>6807981</v>
+        <v>6808188</v>
       </c>
       <c r="S13" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1937,22 +1922,22 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>123834641</v>
+        <v>123834567</v>
       </c>
       <c r="B14" t="n">
-        <v>78788</v>
+        <v>79377</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1965,37 +1950,37 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6425</v>
+        <v>229821</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Härkämäck, Härkämäck, Dlr</t>
+          <t>Härkämäck, Dlr</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>459405</v>
+        <v>459399</v>
       </c>
       <c r="R14" t="n">
-        <v>6808172</v>
+        <v>6808189</v>
       </c>
       <c r="S14" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2025,6 +2010,11 @@
       <c r="AA14" t="inlineStr">
         <is>
           <t>2025-04-07</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>Miljöbild.</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2039,22 +2029,22 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>123835432</v>
+        <v>123831467</v>
       </c>
       <c r="B15" t="n">
-        <v>78788</v>
+        <v>79377</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2067,34 +2057,34 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6425</v>
+        <v>229821</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Härkämäck, Dlr</t>
+          <t>Härkämäck, Härkämäck, Dlr</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>459524</v>
+        <v>459290</v>
       </c>
       <c r="R15" t="n">
-        <v>6808114</v>
+        <v>6808098</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2129,11 +2119,6 @@
           <t>2025-04-07</t>
         </is>
       </c>
-      <c r="AC15" t="inlineStr">
-        <is>
-          <t>Garnlav i alla riktningar, ca 50 meter i radie. Miljöbild.</t>
-        </is>
-      </c>
       <c r="AD15" t="b">
         <v>0</v>
       </c>
@@ -2146,22 +2131,22 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Niklas Rehn</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Niklas Rehn</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>123829246</v>
+        <v>123834998</v>
       </c>
       <c r="B16" t="n">
-        <v>78788</v>
+        <v>79377</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2174,37 +2159,37 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6425</v>
+        <v>229821</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Härkämäck, Dlr</t>
+          <t>Härkämäck, Härkämäck, Dlr</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>459586</v>
+        <v>459437</v>
       </c>
       <c r="R16" t="n">
-        <v>6807981</v>
+        <v>6808171</v>
       </c>
       <c r="S16" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2234,11 +2219,6 @@
       <c r="AA16" t="inlineStr">
         <is>
           <t>2025-04-07</t>
-        </is>
-      </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>Som vanligt garnlav i omgivningen. Miljöbilder.</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2253,12 +2233,12 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
@@ -2367,10 +2347,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>123828742</v>
+        <v>123828739</v>
       </c>
       <c r="B18" t="n">
-        <v>78788</v>
+        <v>56700</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2379,41 +2359,46 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Andljusbäcken, Andljusbäcken, Dlr</t>
+          <t>Härkämäck, Dlr</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>459612</v>
+        <v>459636</v>
       </c>
       <c r="R18" t="n">
-        <v>6808068</v>
+        <v>6808042</v>
       </c>
       <c r="S18" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2457,19 +2442,19 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>123828783</v>
+        <v>123829879</v>
       </c>
       <c r="B19" t="n">
         <v>78788</v>
@@ -2509,10 +2494,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>459611</v>
+        <v>459488</v>
       </c>
       <c r="R19" t="n">
-        <v>6808048</v>
+        <v>6807974</v>
       </c>
       <c r="S19" t="n">
         <v>20</v>
@@ -2571,10 +2556,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>123834006</v>
+        <v>123829205</v>
       </c>
       <c r="B20" t="n">
-        <v>78525</v>
+        <v>78524</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2587,37 +2572,37 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>228912</v>
+        <v>6446</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Härkämäck, Härkämäck, Dlr</t>
+          <t>Andljusbäcken, Andljusbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>459326</v>
+        <v>459611</v>
       </c>
       <c r="R20" t="n">
-        <v>6808188</v>
+        <v>6807987</v>
       </c>
       <c r="S20" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2661,22 +2646,22 @@
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>123834195</v>
+        <v>123831578</v>
       </c>
       <c r="B21" t="n">
-        <v>78525</v>
+        <v>74879</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2689,37 +2674,37 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>228912</v>
+        <v>6440</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Härkämäck, Härkämäck, Dlr</t>
+          <t>Andljusbäcken, Andljusbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>459365</v>
+        <v>459287</v>
       </c>
       <c r="R21" t="n">
-        <v>6808224</v>
+        <v>6808008</v>
       </c>
       <c r="S21" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2763,22 +2748,22 @@
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>123829205</v>
+        <v>123829982</v>
       </c>
       <c r="B22" t="n">
-        <v>78524</v>
+        <v>77716</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2791,21 +2776,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6446</v>
+        <v>6487</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Blågrå svartspik</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Chaenothecopsis fennica</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Laurila) Tibell</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2815,10 +2800,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>459611</v>
+        <v>459432</v>
       </c>
       <c r="R22" t="n">
-        <v>6807987</v>
+        <v>6807989</v>
       </c>
       <c r="S22" t="n">
         <v>20</v>
@@ -2877,10 +2862,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>123829918</v>
+        <v>123829941</v>
       </c>
       <c r="B23" t="n">
-        <v>78524</v>
+        <v>78525</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2893,37 +2878,37 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6446</v>
+        <v>228912</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Andljusbäcken, Andljusbäcken, Dlr</t>
+          <t>Härkämäck, Dlr</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>459424</v>
+        <v>459480</v>
       </c>
       <c r="R23" t="n">
-        <v>6807998</v>
+        <v>6808013</v>
       </c>
       <c r="S23" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -2953,6 +2938,11 @@
       <c r="AA23" t="inlineStr">
         <is>
           <t>2025-04-07</t>
+        </is>
+      </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>Miljöbild.</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -2967,22 +2957,22 @@
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>123834650</v>
+        <v>123829918</v>
       </c>
       <c r="B24" t="n">
-        <v>78525</v>
+        <v>78524</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -2995,37 +2985,37 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>228912</v>
+        <v>6446</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Härkämäck, Dlr</t>
+          <t>Andljusbäcken, Andljusbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>459399</v>
+        <v>459424</v>
       </c>
       <c r="R24" t="n">
-        <v>6808189</v>
+        <v>6807998</v>
       </c>
       <c r="S24" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3055,11 +3045,6 @@
       <c r="AA24" t="inlineStr">
         <is>
           <t>2025-04-07</t>
-        </is>
-      </c>
-      <c r="AC24" t="inlineStr">
-        <is>
-          <t>Miljöbild</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3074,22 +3059,22 @@
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>123829275</v>
+        <v>123830162</v>
       </c>
       <c r="B25" t="n">
-        <v>78525</v>
+        <v>78172</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3102,37 +3087,37 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>228912</v>
+        <v>6437</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Andljusbäcken, Andljusbäcken, Dlr</t>
+          <t>Härkämäck, Dlr</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>459544</v>
+        <v>459480</v>
       </c>
       <c r="R25" t="n">
-        <v>6807989</v>
+        <v>6808013</v>
       </c>
       <c r="S25" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3162,6 +3147,11 @@
       <c r="AA25" t="inlineStr">
         <is>
           <t>2025-04-07</t>
+        </is>
+      </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>Miljöbild.</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3176,22 +3166,22 @@
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>123833917</v>
+        <v>123834890</v>
       </c>
       <c r="B26" t="n">
-        <v>78525</v>
+        <v>78867</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3204,34 +3194,34 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>228912</v>
+        <v>864</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Lynge) Ahti</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Andljusbäcken, Andljusbäcken, Dlr</t>
+          <t>Härkämäck, Härkämäck, Dlr</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>459292</v>
+        <v>459427</v>
       </c>
       <c r="R26" t="n">
-        <v>6808184</v>
+        <v>6808130</v>
       </c>
       <c r="S26" t="n">
         <v>20</v>
@@ -3290,10 +3280,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>123830920</v>
+        <v>123829889</v>
       </c>
       <c r="B27" t="n">
-        <v>78433</v>
+        <v>78525</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3306,37 +3296,37 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>353</v>
+        <v>228912</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Andljusbäcken, Andljusbäcken, Dlr</t>
+          <t>Härkämäck, Dlr</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>459462</v>
+        <v>459494</v>
       </c>
       <c r="R27" t="n">
-        <v>6808078</v>
+        <v>6807997</v>
       </c>
       <c r="S27" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3366,6 +3356,11 @@
       <c r="AA27" t="inlineStr">
         <is>
           <t>2025-04-07</t>
+        </is>
+      </c>
+      <c r="AC27" t="inlineStr">
+        <is>
+          <t>Miljöbild.</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3380,22 +3375,22 @@
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>123834890</v>
+        <v>123831067</v>
       </c>
       <c r="B28" t="n">
-        <v>78867</v>
+        <v>78788</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3408,37 +3403,37 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>864</v>
+        <v>6425</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Knottrig blåslav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Hypogymnia bitteri</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Lynge) Ahti</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Härkämäck, Härkämäck, Dlr</t>
+          <t>Härkämäck, Dlr</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>459427</v>
+        <v>459439</v>
       </c>
       <c r="R28" t="n">
-        <v>6808130</v>
+        <v>6808067</v>
       </c>
       <c r="S28" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3468,6 +3463,11 @@
       <c r="AA28" t="inlineStr">
         <is>
           <t>2025-04-07</t>
+        </is>
+      </c>
+      <c r="AC28" t="inlineStr">
+        <is>
+          <t>Synligt i en radie av ca 50 meter. Miljöbild.</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3482,19 +3482,19 @@
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>123831065</v>
+        <v>123829121</v>
       </c>
       <c r="B29" t="n">
         <v>78788</v>
@@ -3530,14 +3530,14 @@
       <c r="I29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Andljusbäcken, Andljusbäcken, Dlr</t>
+          <t>Härkämäck, Dlr</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>459425</v>
+        <v>459641</v>
       </c>
       <c r="R29" t="n">
-        <v>6808084</v>
+        <v>6807971</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3572,6 +3572,11 @@
           <t>2025-04-07</t>
         </is>
       </c>
+      <c r="AC29" t="inlineStr">
+        <is>
+          <t>I synfältet i en radie av ca 40 meter. Miljöbild.</t>
+        </is>
+      </c>
       <c r="AD29" t="b">
         <v>0</v>
       </c>
@@ -3584,22 +3589,22 @@
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>123829982</v>
+        <v>123834220</v>
       </c>
       <c r="B30" t="n">
-        <v>77716</v>
+        <v>78788</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3612,37 +3617,37 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6487</v>
+        <v>6425</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Blågrå svartspik</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Chaenothecopsis fennica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Laurila) Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Andljusbäcken, Andljusbäcken, Dlr</t>
+          <t>Andljusen, Dlr</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>459432</v>
+        <v>459325</v>
       </c>
       <c r="R30" t="n">
-        <v>6807989</v>
+        <v>6808176</v>
       </c>
       <c r="S30" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -3672,6 +3677,11 @@
       <c r="AA30" t="inlineStr">
         <is>
           <t>2025-04-07</t>
+        </is>
+      </c>
+      <c r="AC30" t="inlineStr">
+        <is>
+          <t>I synfält, radie av ca 50 meter. Miljöbild.</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3686,22 +3696,22 @@
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>123831097</v>
+        <v>123831065</v>
       </c>
       <c r="B31" t="n">
-        <v>79377</v>
+        <v>78788</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3714,21 +3724,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>229821</v>
+        <v>6425</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3738,13 +3748,13 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>459402</v>
+        <v>459425</v>
       </c>
       <c r="R31" t="n">
-        <v>6808072</v>
+        <v>6808084</v>
       </c>
       <c r="S31" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -3800,10 +3810,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>123833754</v>
+        <v>123829712</v>
       </c>
       <c r="B32" t="n">
-        <v>92271</v>
+        <v>90990</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -3812,41 +3822,41 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>4364</v>
+        <v>1202</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Härkämäck, Härkämäck, Dlr</t>
+          <t>Härkämäck, Dlr</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>459290</v>
+        <v>459573</v>
       </c>
       <c r="R32" t="n">
-        <v>6808093</v>
+        <v>6808047</v>
       </c>
       <c r="S32" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -3890,22 +3900,22 @@
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>123829394</v>
+        <v>123833729</v>
       </c>
       <c r="B33" t="n">
-        <v>77716</v>
+        <v>78525</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -3918,34 +3928,34 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6487</v>
+        <v>228912</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Blågrå svartspik</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Chaenothecopsis fennica</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Laurila) Tibell</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Härkämäck, Dlr</t>
+          <t>Andljusen, Dlr</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>459586</v>
+        <v>459286</v>
       </c>
       <c r="R33" t="n">
-        <v>6807981</v>
+        <v>6808090</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3978,6 +3988,11 @@
       <c r="AA33" t="inlineStr">
         <is>
           <t>2025-04-07</t>
+        </is>
+      </c>
+      <c r="AC33" t="inlineStr">
+        <is>
+          <t>Miljöbild.</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4004,10 +4019,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>123829941</v>
+        <v>123834641</v>
       </c>
       <c r="B34" t="n">
-        <v>78525</v>
+        <v>78788</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4020,37 +4035,37 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Härkämäck, Dlr</t>
+          <t>Härkämäck, Härkämäck, Dlr</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>459480</v>
+        <v>459405</v>
       </c>
       <c r="R34" t="n">
-        <v>6808013</v>
+        <v>6808172</v>
       </c>
       <c r="S34" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -4080,11 +4095,6 @@
       <c r="AA34" t="inlineStr">
         <is>
           <t>2025-04-07</t>
-        </is>
-      </c>
-      <c r="AC34" t="inlineStr">
-        <is>
-          <t>Miljöbild.</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4099,22 +4109,22 @@
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>123834567</v>
+        <v>123831244</v>
       </c>
       <c r="B35" t="n">
-        <v>79377</v>
+        <v>78788</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4127,37 +4137,37 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>229821</v>
+        <v>6425</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Härkämäck, Dlr</t>
+          <t>Andljusbäcken, Andljusbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>459399</v>
+        <v>459393</v>
       </c>
       <c r="R35" t="n">
-        <v>6808189</v>
+        <v>6808027</v>
       </c>
       <c r="S35" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -4187,11 +4197,6 @@
       <c r="AA35" t="inlineStr">
         <is>
           <t>2025-04-07</t>
-        </is>
-      </c>
-      <c r="AC35" t="inlineStr">
-        <is>
-          <t>Miljöbild.</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4206,22 +4211,22 @@
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>123834034</v>
+        <v>123833814</v>
       </c>
       <c r="B36" t="n">
-        <v>57507</v>
+        <v>78525</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4234,42 +4239,37 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>100049</v>
+        <v>228912</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
-      <c r="M36" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Andljusen, Dlr</t>
+          <t>Härkämäck, Härkämäck, Dlr</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>459325</v>
+        <v>459293</v>
       </c>
       <c r="R36" t="n">
-        <v>6808176</v>
+        <v>6808123</v>
       </c>
       <c r="S36" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -4299,11 +4299,6 @@
       <c r="AA36" t="inlineStr">
         <is>
           <t>2025-04-07</t>
-        </is>
-      </c>
-      <c r="AC36" t="inlineStr">
-        <is>
-          <t>Miljöbild.</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4318,19 +4313,19 @@
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>123834998</v>
+        <v>123831097</v>
       </c>
       <c r="B37" t="n">
         <v>79377</v>
@@ -4366,14 +4361,14 @@
       <c r="I37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
-          <t>Härkämäck, Härkämäck, Dlr</t>
+          <t>Andljusbäcken, Andljusbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>459437</v>
+        <v>459402</v>
       </c>
       <c r="R37" t="n">
-        <v>6808171</v>
+        <v>6808072</v>
       </c>
       <c r="S37" t="n">
         <v>20</v>
@@ -4432,10 +4427,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>123828882</v>
+        <v>123829632</v>
       </c>
       <c r="B38" t="n">
-        <v>78820</v>
+        <v>91277</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4448,37 +4443,37 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>185</v>
+        <v>658</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
-          <t>Andljusbäcken, Andljusbäcken, Dlr</t>
+          <t>Härkämäck, Dlr</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>459600</v>
+        <v>459573</v>
       </c>
       <c r="R38" t="n">
-        <v>6808030</v>
+        <v>6808047</v>
       </c>
       <c r="S38" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -4522,19 +4517,19 @@
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>123829879</v>
+        <v>123835432</v>
       </c>
       <c r="B39" t="n">
         <v>78788</v>
@@ -4570,17 +4565,17 @@
       <c r="I39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
-          <t>Andljusbäcken, Andljusbäcken, Dlr</t>
+          <t>Härkämäck, Dlr</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>459488</v>
+        <v>459524</v>
       </c>
       <c r="R39" t="n">
-        <v>6807974</v>
+        <v>6808114</v>
       </c>
       <c r="S39" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
@@ -4610,6 +4605,11 @@
       <c r="AA39" t="inlineStr">
         <is>
           <t>2025-04-07</t>
+        </is>
+      </c>
+      <c r="AC39" t="inlineStr">
+        <is>
+          <t>Garnlav i alla riktningar, ca 50 meter i radie. Miljöbild.</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4624,19 +4624,19 @@
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>123828608</v>
+        <v>123828742</v>
       </c>
       <c r="B40" t="n">
         <v>78788</v>
@@ -4672,17 +4672,17 @@
       <c r="I40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
-          <t>Härkämäck, Dlr</t>
+          <t>Andljusbäcken, Andljusbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>459636</v>
+        <v>459612</v>
       </c>
       <c r="R40" t="n">
-        <v>6808042</v>
+        <v>6808068</v>
       </c>
       <c r="S40" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T40" t="inlineStr">
         <is>
@@ -4712,11 +4712,6 @@
       <c r="AA40" t="inlineStr">
         <is>
           <t>2025-04-07</t>
-        </is>
-      </c>
-      <c r="AC40" t="inlineStr">
-        <is>
-          <t>Garnlav i synfältet i en radie av ca 50 meter. Miljöbilder.</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4731,19 +4726,19 @@
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>123831067</v>
+        <v>123828608</v>
       </c>
       <c r="B41" t="n">
         <v>78788</v>
@@ -4783,10 +4778,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>459439</v>
+        <v>459636</v>
       </c>
       <c r="R41" t="n">
-        <v>6808067</v>
+        <v>6808042</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4823,7 +4818,7 @@
       </c>
       <c r="AC41" t="inlineStr">
         <is>
-          <t>Synligt i en radie av ca 50 meter. Miljöbild.</t>
+          <t>Garnlav i synfältet i en radie av ca 50 meter. Miljöbilder.</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -4850,10 +4845,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>123833814</v>
+        <v>123830009</v>
       </c>
       <c r="B42" t="n">
-        <v>78525</v>
+        <v>78524</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -4866,37 +4861,37 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>228912</v>
+        <v>6446</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
-          <t>Härkämäck, Härkämäck, Dlr</t>
+          <t>Härkämäck, Dlr</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>459293</v>
+        <v>459480</v>
       </c>
       <c r="R42" t="n">
-        <v>6808123</v>
+        <v>6808013</v>
       </c>
       <c r="S42" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -4926,6 +4921,11 @@
       <c r="AA42" t="inlineStr">
         <is>
           <t>2025-04-07</t>
+        </is>
+      </c>
+      <c r="AC42" t="inlineStr">
+        <is>
+          <t>Miljöbild.</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -4940,22 +4940,22 @@
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>123834630</v>
+        <v>123830920</v>
       </c>
       <c r="B43" t="n">
-        <v>57512</v>
+        <v>78433</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -4964,41 +4964,41 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>100110</v>
+        <v>353</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Gråspett</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Picus canus</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>J.F. Gmelin, 1788</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
-          <t>Härkämäck, Härkämäck, Dlr</t>
+          <t>Andljusbäcken, Andljusbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>459408</v>
+        <v>459462</v>
       </c>
       <c r="R43" t="n">
-        <v>6808198</v>
+        <v>6808078</v>
       </c>
       <c r="S43" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T43" t="inlineStr">
         <is>
@@ -5028,11 +5028,6 @@
       <c r="AA43" t="inlineStr">
         <is>
           <t>2025-04-07</t>
-        </is>
-      </c>
-      <c r="AC43" t="inlineStr">
-        <is>
-          <t>Förbiflygande.</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5047,19 +5042,19 @@
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>123831244</v>
+        <v>123829246</v>
       </c>
       <c r="B44" t="n">
         <v>78788</v>
@@ -5095,17 +5090,17 @@
       <c r="I44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
-          <t>Andljusbäcken, Andljusbäcken, Dlr</t>
+          <t>Härkämäck, Dlr</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>459393</v>
+        <v>459586</v>
       </c>
       <c r="R44" t="n">
-        <v>6808027</v>
+        <v>6807981</v>
       </c>
       <c r="S44" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T44" t="inlineStr">
         <is>
@@ -5135,6 +5130,11 @@
       <c r="AA44" t="inlineStr">
         <is>
           <t>2025-04-07</t>
+        </is>
+      </c>
+      <c r="AC44" t="inlineStr">
+        <is>
+          <t>Som vanligt garnlav i omgivningen. Miljöbilder.</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5149,19 +5149,19 @@
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>123833841</v>
+        <v>123829102</v>
       </c>
       <c r="B45" t="n">
         <v>78788</v>
@@ -5197,17 +5197,17 @@
       <c r="I45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
-          <t>Härkämäck, Härkämäck, Dlr</t>
+          <t>Andljusbäcken, Andljusbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>459300</v>
+        <v>459666</v>
       </c>
       <c r="R45" t="n">
-        <v>6808144</v>
+        <v>6807990</v>
       </c>
       <c r="S45" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T45" t="inlineStr">
         <is>
@@ -5251,22 +5251,22 @@
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>123829102</v>
+        <v>123834195</v>
       </c>
       <c r="B46" t="n">
-        <v>78788</v>
+        <v>78525</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5279,37 +5279,37 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
-          <t>Andljusbäcken, Andljusbäcken, Dlr</t>
+          <t>Härkämäck, Härkämäck, Dlr</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>459666</v>
+        <v>459365</v>
       </c>
       <c r="R46" t="n">
-        <v>6807990</v>
+        <v>6808224</v>
       </c>
       <c r="S46" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T46" t="inlineStr">
         <is>
@@ -5353,22 +5353,22 @@
       <c r="AT46" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX46" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>123830162</v>
+        <v>123829197</v>
       </c>
       <c r="B47" t="n">
-        <v>78172</v>
+        <v>78525</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5381,37 +5381,37 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>6437</v>
+        <v>228912</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
-          <t>Härkämäck, Dlr</t>
+          <t>Andljusbäcken, Andljusbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>459480</v>
+        <v>459611</v>
       </c>
       <c r="R47" t="n">
-        <v>6808013</v>
+        <v>6807987</v>
       </c>
       <c r="S47" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T47" t="inlineStr">
         <is>
@@ -5441,11 +5441,6 @@
       <c r="AA47" t="inlineStr">
         <is>
           <t>2025-04-07</t>
-        </is>
-      </c>
-      <c r="AC47" t="inlineStr">
-        <is>
-          <t>Miljöbild.</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5460,22 +5455,22 @@
       <c r="AT47" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX47" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>123833729</v>
+        <v>123834183</v>
       </c>
       <c r="B48" t="n">
-        <v>78525</v>
+        <v>78788</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -5488,37 +5483,37 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
-          <t>Andljusen, Dlr</t>
+          <t>Andljusbäcken, Andljusbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>459286</v>
+        <v>459373</v>
       </c>
       <c r="R48" t="n">
-        <v>6808090</v>
+        <v>6808222</v>
       </c>
       <c r="S48" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T48" t="inlineStr">
         <is>
@@ -5548,11 +5543,6 @@
       <c r="AA48" t="inlineStr">
         <is>
           <t>2025-04-07</t>
-        </is>
-      </c>
-      <c r="AC48" t="inlineStr">
-        <is>
-          <t>Miljöbild.</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5567,22 +5557,22 @@
       <c r="AT48" t="inlineStr"/>
       <c r="AW48" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX48" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>123830009</v>
+        <v>123829394</v>
       </c>
       <c r="B49" t="n">
-        <v>78524</v>
+        <v>77716</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -5595,21 +5585,21 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>6446</v>
+        <v>6487</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Blågrå svartspik</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Chaenothecopsis fennica</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Laurila) Tibell</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5619,10 +5609,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>459480</v>
+        <v>459586</v>
       </c>
       <c r="R49" t="n">
-        <v>6808013</v>
+        <v>6807981</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5655,11 +5645,6 @@
       <c r="AA49" t="inlineStr">
         <is>
           <t>2025-04-07</t>
-        </is>
-      </c>
-      <c r="AC49" t="inlineStr">
-        <is>
-          <t>Miljöbild.</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -5686,10 +5671,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>123834183</v>
+        <v>123829310</v>
       </c>
       <c r="B50" t="n">
-        <v>78788</v>
+        <v>57507</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -5702,37 +5687,42 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
+      <c r="M50" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P50" t="inlineStr">
         <is>
-          <t>Andljusbäcken, Andljusbäcken, Dlr</t>
+          <t>Härkämäck, Dlr</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>459373</v>
+        <v>459586</v>
       </c>
       <c r="R50" t="n">
-        <v>6808222</v>
+        <v>6807981</v>
       </c>
       <c r="S50" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T50" t="inlineStr">
         <is>
@@ -5776,22 +5766,22 @@
       <c r="AT50" t="inlineStr"/>
       <c r="AW50" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX50" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>123828044</v>
+        <v>123834630</v>
       </c>
       <c r="B51" t="n">
-        <v>78788</v>
+        <v>57512</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -5800,38 +5790,38 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>6425</v>
+        <v>100110</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gråspett</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picus canus</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>J.F. Gmelin, 1788</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
-          <t>Härkämäck, Dlr</t>
+          <t>Härkämäck, Härkämäck, Dlr</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>459681</v>
+        <v>459408</v>
       </c>
       <c r="R51" t="n">
-        <v>6808072</v>
+        <v>6808198</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5868,7 +5858,7 @@
       </c>
       <c r="AC51" t="inlineStr">
         <is>
-          <t>Garnlav i synfältet i en radie av ca 50 meter. Miljöbild.</t>
+          <t>Förbiflygande.</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -5883,22 +5873,22 @@
       <c r="AT51" t="inlineStr"/>
       <c r="AW51" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX51" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>123829889</v>
+        <v>123834966</v>
       </c>
       <c r="B52" t="n">
-        <v>78525</v>
+        <v>57512</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -5907,38 +5897,43 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>228912</v>
+        <v>100110</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Gråspett</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Picus canus</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>J.F. Gmelin, 1788</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
+      <c r="M52" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P52" t="inlineStr">
         <is>
           <t>Härkämäck, Dlr</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>459494</v>
+        <v>459399</v>
       </c>
       <c r="R52" t="n">
-        <v>6807997</v>
+        <v>6808189</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -5975,7 +5970,7 @@
       </c>
       <c r="AC52" t="inlineStr">
         <is>
-          <t>Miljöbild.</t>
+          <t>Förbiflygande.</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6002,10 +5997,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>123920731</v>
+        <v>123920441</v>
       </c>
       <c r="B53" t="n">
-        <v>78788</v>
+        <v>56700</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -6014,38 +6009,43 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
+      <c r="M53" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="P53" t="inlineStr">
         <is>
           <t>Härkämäck, Dlr</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>459608</v>
+        <v>459609</v>
       </c>
       <c r="R53" t="n">
-        <v>6808066</v>
+        <v>6807987</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6097,17 +6097,17 @@
       </c>
       <c r="AX53" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Anders Heggestad, lennart karlsson, Håkan Thenander, Niklas Rehn</t>
+          <t>Philipp Weiss, Anders Heggestad, Håkan Thenander, lennart karlsson, Niklas Rehn</t>
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>123920540</v>
+        <v>123920730</v>
       </c>
       <c r="B54" t="n">
-        <v>78525</v>
+        <v>78788</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -6120,21 +6120,21 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -6144,10 +6144,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>459589</v>
+        <v>459590</v>
       </c>
       <c r="R54" t="n">
-        <v>6807980</v>
+        <v>6808062</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6206,10 +6206,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>123920441</v>
+        <v>123920540</v>
       </c>
       <c r="B55" t="n">
-        <v>56700</v>
+        <v>78525</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -6218,43 +6218,38 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>100138</v>
+        <v>228912</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
-      <c r="M55" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="P55" t="inlineStr">
         <is>
           <t>Härkämäck, Dlr</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>459609</v>
+        <v>459589</v>
       </c>
       <c r="R55" t="n">
-        <v>6807987</v>
+        <v>6807980</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6306,14 +6301,14 @@
       </c>
       <c r="AX55" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Anders Heggestad, Håkan Thenander, lennart karlsson, Niklas Rehn</t>
+          <t>Philipp Weiss, Anders Heggestad, lennart karlsson, Håkan Thenander, Niklas Rehn</t>
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>123920733</v>
+        <v>123920731</v>
       </c>
       <c r="B56" t="n">
         <v>78788</v>
@@ -6353,10 +6348,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>459589</v>
+        <v>459608</v>
       </c>
       <c r="R56" t="n">
-        <v>6807980</v>
+        <v>6808066</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6415,10 +6410,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>123920732</v>
+        <v>123920419</v>
       </c>
       <c r="B57" t="n">
-        <v>78788</v>
+        <v>90990</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -6431,21 +6426,21 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6455,10 +6450,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>459616</v>
+        <v>459603</v>
       </c>
       <c r="R57" t="n">
-        <v>6808044</v>
+        <v>6807965</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6510,17 +6505,17 @@
       </c>
       <c r="AX57" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Anders Heggestad, lennart karlsson, Håkan Thenander, Niklas Rehn</t>
+          <t>Philipp Weiss, Anders Heggestad, Håkan Thenander, lennart karlsson, Niklas Rehn</t>
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>123920419</v>
+        <v>123920427</v>
       </c>
       <c r="B58" t="n">
-        <v>90990</v>
+        <v>57491</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
@@ -6533,34 +6528,39 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
+      <c r="M58" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="P58" t="inlineStr">
         <is>
           <t>Härkämäck, Dlr</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>459603</v>
+        <v>459571</v>
       </c>
       <c r="R58" t="n">
-        <v>6807965</v>
+        <v>6808057</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6619,7 +6619,7 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>123920728</v>
+        <v>123920734</v>
       </c>
       <c r="B59" t="n">
         <v>78788</v>
@@ -6659,10 +6659,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>459539</v>
+        <v>459613</v>
       </c>
       <c r="R59" t="n">
-        <v>6808073</v>
+        <v>6807959</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6721,10 +6721,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>123920427</v>
+        <v>123920729</v>
       </c>
       <c r="B60" t="n">
-        <v>57491</v>
+        <v>78788</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
@@ -6737,39 +6737,34 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
-      <c r="M60" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
       <c r="P60" t="inlineStr">
         <is>
           <t>Härkämäck, Dlr</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>459571</v>
+        <v>459566</v>
       </c>
       <c r="R60" t="n">
-        <v>6808057</v>
+        <v>6808068</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6821,14 +6816,14 @@
       </c>
       <c r="AX60" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Anders Heggestad, Håkan Thenander, lennart karlsson, Niklas Rehn</t>
+          <t>Philipp Weiss, Anders Heggestad, lennart karlsson, Håkan Thenander, Niklas Rehn</t>
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>123920729</v>
+        <v>123920728</v>
       </c>
       <c r="B61" t="n">
         <v>78788</v>
@@ -6868,10 +6863,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>459566</v>
+        <v>459539</v>
       </c>
       <c r="R61" t="n">
-        <v>6808068</v>
+        <v>6808073</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -6930,10 +6925,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>123920930</v>
+        <v>123920442</v>
       </c>
       <c r="B62" t="n">
-        <v>78433</v>
+        <v>56700</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
@@ -6942,38 +6937,43 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>353</v>
+        <v>100138</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
+      <c r="M62" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="P62" t="inlineStr">
         <is>
           <t>Härkämäck, Dlr</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>459600</v>
+        <v>459593</v>
       </c>
       <c r="R62" t="n">
-        <v>6807961</v>
+        <v>6807978</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -7025,17 +7025,17 @@
       </c>
       <c r="AX62" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Anders Heggestad, lennart karlsson, Håkan Thenander, Niklas Rehn</t>
+          <t>Philipp Weiss, Anders Heggestad, Håkan Thenander, lennart karlsson, Niklas Rehn</t>
         </is>
       </c>
       <c r="AY62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>123920399</v>
+        <v>123920727</v>
       </c>
       <c r="B63" t="n">
-        <v>79377</v>
+        <v>78788</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
@@ -7048,21 +7048,21 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>229821</v>
+        <v>6425</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -7072,10 +7072,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>459591</v>
+        <v>459542</v>
       </c>
       <c r="R63" t="n">
-        <v>6808065</v>
+        <v>6808123</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -7127,17 +7127,17 @@
       </c>
       <c r="AX63" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Anders Heggestad, Håkan Thenander, lennart karlsson, Niklas Rehn</t>
+          <t>Philipp Weiss, Anders Heggestad, lennart karlsson, Håkan Thenander, Niklas Rehn</t>
         </is>
       </c>
       <c r="AY63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>123920442</v>
+        <v>123920930</v>
       </c>
       <c r="B64" t="n">
-        <v>56700</v>
+        <v>78433</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
@@ -7146,43 +7146,38 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>100138</v>
+        <v>353</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
-      <c r="M64" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="P64" t="inlineStr">
         <is>
           <t>Härkämäck, Dlr</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>459593</v>
+        <v>459600</v>
       </c>
       <c r="R64" t="n">
-        <v>6807978</v>
+        <v>6807961</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7234,17 +7229,17 @@
       </c>
       <c r="AX64" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Anders Heggestad, Håkan Thenander, lennart karlsson, Niklas Rehn</t>
+          <t>Philipp Weiss, Anders Heggestad, lennart karlsson, Håkan Thenander, Niklas Rehn</t>
         </is>
       </c>
       <c r="AY64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>123920734</v>
+        <v>123920399</v>
       </c>
       <c r="B65" t="n">
-        <v>78788</v>
+        <v>79377</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
@@ -7257,21 +7252,21 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>6425</v>
+        <v>229821</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -7281,10 +7276,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>459613</v>
+        <v>459591</v>
       </c>
       <c r="R65" t="n">
-        <v>6807959</v>
+        <v>6808065</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7336,17 +7331,17 @@
       </c>
       <c r="AX65" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Anders Heggestad, lennart karlsson, Håkan Thenander, Niklas Rehn</t>
+          <t>Philipp Weiss, Anders Heggestad, Håkan Thenander, lennart karlsson, Niklas Rehn</t>
         </is>
       </c>
       <c r="AY65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>123920440</v>
+        <v>123920732</v>
       </c>
       <c r="B66" t="n">
-        <v>56700</v>
+        <v>78788</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
@@ -7355,43 +7350,38 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
-      <c r="M66" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="P66" t="inlineStr">
         <is>
           <t>Härkämäck, Dlr</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>459617</v>
+        <v>459616</v>
       </c>
       <c r="R66" t="n">
-        <v>6808041</v>
+        <v>6808044</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7443,14 +7433,14 @@
       </c>
       <c r="AX66" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Anders Heggestad, Håkan Thenander, lennart karlsson, Niklas Rehn</t>
+          <t>Philipp Weiss, Anders Heggestad, lennart karlsson, Håkan Thenander, Niklas Rehn</t>
         </is>
       </c>
       <c r="AY66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>123920727</v>
+        <v>123920733</v>
       </c>
       <c r="B67" t="n">
         <v>78788</v>
@@ -7490,10 +7480,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>459542</v>
+        <v>459589</v>
       </c>
       <c r="R67" t="n">
-        <v>6808123</v>
+        <v>6807980</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7552,10 +7542,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>123920730</v>
+        <v>123920440</v>
       </c>
       <c r="B68" t="n">
-        <v>78788</v>
+        <v>56700</v>
       </c>
       <c r="C68" t="inlineStr">
         <is>
@@ -7564,38 +7554,43 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
+      <c r="M68" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="P68" t="inlineStr">
         <is>
           <t>Härkämäck, Dlr</t>
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>459590</v>
+        <v>459617</v>
       </c>
       <c r="R68" t="n">
-        <v>6808062</v>
+        <v>6808041</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7647,7 +7642,7 @@
       </c>
       <c r="AX68" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Anders Heggestad, lennart karlsson, Håkan Thenander, Niklas Rehn</t>
+          <t>Philipp Weiss, Anders Heggestad, Håkan Thenander, lennart karlsson, Niklas Rehn</t>
         </is>
       </c>
       <c r="AY68" t="inlineStr"/>

--- a/artfynd/A 61327-2022 artfynd.xlsx
+++ b/artfynd/A 61327-2022 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>123828882</v>
+        <v>123829941</v>
       </c>
       <c r="B2" t="n">
-        <v>78820</v>
+        <v>78525</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,37 +691,37 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>185</v>
+        <v>228912</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Andljusbäcken, Andljusbäcken, Dlr</t>
+          <t>Härkämäck, Dlr</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>459600</v>
+        <v>459480</v>
       </c>
       <c r="R2" t="n">
-        <v>6808030</v>
+        <v>6808013</v>
       </c>
       <c r="S2" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -751,6 +751,11 @@
       <c r="AA2" t="inlineStr">
         <is>
           <t>2025-04-07</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>Miljöbild.</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -765,22 +770,22 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123834034</v>
+        <v>123834195</v>
       </c>
       <c r="B3" t="n">
-        <v>57507</v>
+        <v>78525</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -793,39 +798,34 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100049</v>
+        <v>228912</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Andljusen, Dlr</t>
+          <t>Härkämäck, Härkämäck, Dlr</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>459325</v>
+        <v>459365</v>
       </c>
       <c r="R3" t="n">
-        <v>6808176</v>
+        <v>6808224</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -860,11 +860,6 @@
           <t>2025-04-07</t>
         </is>
       </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Miljöbild.</t>
-        </is>
-      </c>
       <c r="AD3" t="b">
         <v>0</v>
       </c>
@@ -877,22 +872,22 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123828783</v>
+        <v>123827957</v>
       </c>
       <c r="B4" t="n">
-        <v>78788</v>
+        <v>78524</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -905,21 +900,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -929,10 +924,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>459611</v>
+        <v>459664</v>
       </c>
       <c r="R4" t="n">
-        <v>6808048</v>
+        <v>6808079</v>
       </c>
       <c r="S4" t="n">
         <v>20</v>
@@ -991,10 +986,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123834650</v>
+        <v>123828882</v>
       </c>
       <c r="B5" t="n">
-        <v>78525</v>
+        <v>78820</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1007,37 +1002,37 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>228912</v>
+        <v>185</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Härkämäck, Dlr</t>
+          <t>Andljusbäcken, Andljusbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>459399</v>
+        <v>459600</v>
       </c>
       <c r="R5" t="n">
-        <v>6808189</v>
+        <v>6808030</v>
       </c>
       <c r="S5" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1067,11 +1062,6 @@
       <c r="AA5" t="inlineStr">
         <is>
           <t>2025-04-07</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Miljöbild</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1086,22 +1076,22 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>123829275</v>
+        <v>123829310</v>
       </c>
       <c r="B6" t="n">
-        <v>78525</v>
+        <v>57507</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1114,37 +1104,42 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>228912</v>
+        <v>100049</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Andljusbäcken, Andljusbäcken, Dlr</t>
+          <t>Härkämäck, Dlr</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>459544</v>
+        <v>459586</v>
       </c>
       <c r="R6" t="n">
-        <v>6807989</v>
+        <v>6807981</v>
       </c>
       <c r="S6" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1188,22 +1183,22 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>123828044</v>
+        <v>123834966</v>
       </c>
       <c r="B7" t="n">
-        <v>78788</v>
+        <v>57512</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1212,38 +1207,43 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>100110</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gråspett</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picus canus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>J.F. Gmelin, 1788</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Härkämäck, Dlr</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>459681</v>
+        <v>459399</v>
       </c>
       <c r="R7" t="n">
-        <v>6808072</v>
+        <v>6808189</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1280,7 +1280,7 @@
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>Garnlav i synfältet i en radie av ca 50 meter. Miljöbild.</t>
+          <t>Förbiflygande.</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1307,10 +1307,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>123835135</v>
+        <v>123834650</v>
       </c>
       <c r="B8" t="n">
-        <v>78788</v>
+        <v>78525</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1323,21 +1323,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1347,10 +1347,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>459455</v>
+        <v>459399</v>
       </c>
       <c r="R8" t="n">
-        <v>6808164</v>
+        <v>6808189</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1387,7 +1387,7 @@
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>Garnlav i en radie av ca 50 meter, synfältet. Miljöbild.</t>
+          <t>Miljöbild</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1414,10 +1414,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>123833841</v>
+        <v>123831097</v>
       </c>
       <c r="B9" t="n">
-        <v>78788</v>
+        <v>79377</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1430,37 +1430,37 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>229821</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Härkämäck, Härkämäck, Dlr</t>
+          <t>Andljusbäcken, Andljusbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>459300</v>
+        <v>459402</v>
       </c>
       <c r="R9" t="n">
-        <v>6808144</v>
+        <v>6808072</v>
       </c>
       <c r="S9" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1504,22 +1504,22 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>123831277</v>
+        <v>123829879</v>
       </c>
       <c r="B10" t="n">
-        <v>57507</v>
+        <v>78788</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1532,42 +1532,37 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Härkämäck, Dlr</t>
+          <t>Andljusbäcken, Andljusbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>459389</v>
+        <v>459488</v>
       </c>
       <c r="R10" t="n">
-        <v>6808070</v>
+        <v>6807974</v>
       </c>
       <c r="S10" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1597,11 +1592,6 @@
       <c r="AA10" t="inlineStr">
         <is>
           <t>2025-04-07</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>Miljöbild.</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1616,22 +1606,22 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>123833754</v>
+        <v>123834630</v>
       </c>
       <c r="B11" t="n">
-        <v>92271</v>
+        <v>57512</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1644,21 +1634,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>4364</v>
+        <v>100110</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Gråspett</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Picus canus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>J.F. Gmelin, 1788</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1668,13 +1658,13 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>459290</v>
+        <v>459408</v>
       </c>
       <c r="R11" t="n">
-        <v>6808093</v>
+        <v>6808198</v>
       </c>
       <c r="S11" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1704,6 +1694,11 @@
       <c r="AA11" t="inlineStr">
         <is>
           <t>2025-04-07</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Förbiflygande.</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1730,10 +1725,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>123833917</v>
+        <v>123829246</v>
       </c>
       <c r="B12" t="n">
-        <v>78525</v>
+        <v>78788</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1746,37 +1741,37 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Andljusbäcken, Andljusbäcken, Dlr</t>
+          <t>Härkämäck, Dlr</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>459292</v>
+        <v>459586</v>
       </c>
       <c r="R12" t="n">
-        <v>6808184</v>
+        <v>6807981</v>
       </c>
       <c r="S12" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1806,6 +1801,11 @@
       <c r="AA12" t="inlineStr">
         <is>
           <t>2025-04-07</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Som vanligt garnlav i omgivningen. Miljöbilder.</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1820,22 +1820,22 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>123834006</v>
+        <v>123830920</v>
       </c>
       <c r="B13" t="n">
-        <v>78525</v>
+        <v>78433</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1848,37 +1848,37 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>228912</v>
+        <v>353</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Härkämäck, Härkämäck, Dlr</t>
+          <t>Andljusbäcken, Andljusbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>459326</v>
+        <v>459462</v>
       </c>
       <c r="R13" t="n">
-        <v>6808188</v>
+        <v>6808078</v>
       </c>
       <c r="S13" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1922,22 +1922,22 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>123834567</v>
+        <v>123834034</v>
       </c>
       <c r="B14" t="n">
-        <v>79377</v>
+        <v>57507</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1950,34 +1950,39 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>229821</v>
+        <v>100049</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Härkämäck, Dlr</t>
+          <t>Andljusen, Dlr</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>459399</v>
+        <v>459325</v>
       </c>
       <c r="R14" t="n">
-        <v>6808189</v>
+        <v>6808176</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2041,10 +2046,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>123831467</v>
+        <v>123831578</v>
       </c>
       <c r="B15" t="n">
-        <v>79377</v>
+        <v>74879</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2057,37 +2062,37 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>229821</v>
+        <v>6440</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Härkämäck, Härkämäck, Dlr</t>
+          <t>Andljusbäcken, Andljusbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>459290</v>
+        <v>459287</v>
       </c>
       <c r="R15" t="n">
-        <v>6808098</v>
+        <v>6808008</v>
       </c>
       <c r="S15" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2131,22 +2136,22 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Niklas Rehn</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Niklas Rehn</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>123834998</v>
+        <v>123829102</v>
       </c>
       <c r="B16" t="n">
-        <v>79377</v>
+        <v>78788</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2159,34 +2164,34 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>229821</v>
+        <v>6425</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Härkämäck, Härkämäck, Dlr</t>
+          <t>Andljusbäcken, Andljusbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>459437</v>
+        <v>459666</v>
       </c>
       <c r="R16" t="n">
-        <v>6808171</v>
+        <v>6807990</v>
       </c>
       <c r="S16" t="n">
         <v>20</v>
@@ -2245,10 +2250,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>123827957</v>
+        <v>123835432</v>
       </c>
       <c r="B17" t="n">
-        <v>78524</v>
+        <v>78788</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2261,37 +2266,37 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Andljusbäcken, Andljusbäcken, Dlr</t>
+          <t>Härkämäck, Dlr</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>459664</v>
+        <v>459524</v>
       </c>
       <c r="R17" t="n">
-        <v>6808079</v>
+        <v>6808114</v>
       </c>
       <c r="S17" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2321,6 +2326,11 @@
       <c r="AA17" t="inlineStr">
         <is>
           <t>2025-04-07</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>Garnlav i alla riktningar, ca 50 meter i radie. Miljöbild.</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2335,22 +2345,22 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>123828739</v>
+        <v>123828044</v>
       </c>
       <c r="B18" t="n">
-        <v>56700</v>
+        <v>78788</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2359,43 +2369,38 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="P18" t="inlineStr">
         <is>
           <t>Härkämäck, Dlr</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>459636</v>
+        <v>459681</v>
       </c>
       <c r="R18" t="n">
-        <v>6808042</v>
+        <v>6808072</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2428,6 +2433,11 @@
       <c r="AA18" t="inlineStr">
         <is>
           <t>2025-04-07</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>Garnlav i synfältet i en radie av ca 50 meter. Miljöbild.</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2454,7 +2464,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>123829879</v>
+        <v>123831067</v>
       </c>
       <c r="B19" t="n">
         <v>78788</v>
@@ -2490,17 +2500,17 @@
       <c r="I19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Andljusbäcken, Andljusbäcken, Dlr</t>
+          <t>Härkämäck, Dlr</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>459488</v>
+        <v>459439</v>
       </c>
       <c r="R19" t="n">
-        <v>6807974</v>
+        <v>6808067</v>
       </c>
       <c r="S19" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2530,6 +2540,11 @@
       <c r="AA19" t="inlineStr">
         <is>
           <t>2025-04-07</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>Synligt i en radie av ca 50 meter. Miljöbild.</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2544,22 +2559,22 @@
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>123829205</v>
+        <v>123831244</v>
       </c>
       <c r="B20" t="n">
-        <v>78524</v>
+        <v>78788</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2572,21 +2587,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2596,10 +2611,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>459611</v>
+        <v>459393</v>
       </c>
       <c r="R20" t="n">
-        <v>6807987</v>
+        <v>6808027</v>
       </c>
       <c r="S20" t="n">
         <v>20</v>
@@ -2658,10 +2673,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>123831578</v>
+        <v>123829712</v>
       </c>
       <c r="B21" t="n">
-        <v>74879</v>
+        <v>90990</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2674,37 +2689,37 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6440</v>
+        <v>1202</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Andljusbäcken, Andljusbäcken, Dlr</t>
+          <t>Härkämäck, Dlr</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>459287</v>
+        <v>459573</v>
       </c>
       <c r="R21" t="n">
-        <v>6808008</v>
+        <v>6808047</v>
       </c>
       <c r="S21" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2748,22 +2763,22 @@
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>123829982</v>
+        <v>123834006</v>
       </c>
       <c r="B22" t="n">
-        <v>77716</v>
+        <v>78525</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2776,37 +2791,37 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6487</v>
+        <v>228912</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Blågrå svartspik</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Chaenothecopsis fennica</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Laurila) Tibell</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Andljusbäcken, Andljusbäcken, Dlr</t>
+          <t>Härkämäck, Härkämäck, Dlr</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>459432</v>
+        <v>459326</v>
       </c>
       <c r="R22" t="n">
-        <v>6807989</v>
+        <v>6808188</v>
       </c>
       <c r="S22" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -2850,22 +2865,22 @@
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>123829941</v>
+        <v>123833841</v>
       </c>
       <c r="B23" t="n">
-        <v>78525</v>
+        <v>78788</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2878,37 +2893,37 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Härkämäck, Dlr</t>
+          <t>Härkämäck, Härkämäck, Dlr</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>459480</v>
+        <v>459300</v>
       </c>
       <c r="R23" t="n">
-        <v>6808013</v>
+        <v>6808144</v>
       </c>
       <c r="S23" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -2938,11 +2953,6 @@
       <c r="AA23" t="inlineStr">
         <is>
           <t>2025-04-07</t>
-        </is>
-      </c>
-      <c r="AC23" t="inlineStr">
-        <is>
-          <t>Miljöbild.</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -2957,22 +2967,22 @@
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>123829918</v>
+        <v>123828783</v>
       </c>
       <c r="B24" t="n">
-        <v>78524</v>
+        <v>78788</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -2985,21 +2995,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3009,10 +3019,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>459424</v>
+        <v>459611</v>
       </c>
       <c r="R24" t="n">
-        <v>6807998</v>
+        <v>6808048</v>
       </c>
       <c r="S24" t="n">
         <v>20</v>
@@ -3071,10 +3081,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>123830162</v>
+        <v>123833814</v>
       </c>
       <c r="B25" t="n">
-        <v>78172</v>
+        <v>78525</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3087,37 +3097,37 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6437</v>
+        <v>228912</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Härkämäck, Dlr</t>
+          <t>Härkämäck, Härkämäck, Dlr</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>459480</v>
+        <v>459293</v>
       </c>
       <c r="R25" t="n">
-        <v>6808013</v>
+        <v>6808123</v>
       </c>
       <c r="S25" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3147,11 +3157,6 @@
       <c r="AA25" t="inlineStr">
         <is>
           <t>2025-04-07</t>
-        </is>
-      </c>
-      <c r="AC25" t="inlineStr">
-        <is>
-          <t>Miljöbild.</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3166,22 +3171,22 @@
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>123834890</v>
+        <v>123833729</v>
       </c>
       <c r="B26" t="n">
-        <v>78867</v>
+        <v>78525</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3194,37 +3199,37 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>864</v>
+        <v>228912</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Knottrig blåslav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Hypogymnia bitteri</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Lynge) Ahti</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Härkämäck, Härkämäck, Dlr</t>
+          <t>Andljusen, Dlr</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>459427</v>
+        <v>459286</v>
       </c>
       <c r="R26" t="n">
-        <v>6808130</v>
+        <v>6808090</v>
       </c>
       <c r="S26" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3254,6 +3259,11 @@
       <c r="AA26" t="inlineStr">
         <is>
           <t>2025-04-07</t>
+        </is>
+      </c>
+      <c r="AC26" t="inlineStr">
+        <is>
+          <t>Miljöbild.</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3268,12 +3278,12 @@
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
@@ -3387,10 +3397,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>123831067</v>
+        <v>123829982</v>
       </c>
       <c r="B28" t="n">
-        <v>78788</v>
+        <v>77716</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3403,37 +3413,37 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6425</v>
+        <v>6487</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Blågrå svartspik</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenothecopsis fennica</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Laurila) Tibell</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Härkämäck, Dlr</t>
+          <t>Andljusbäcken, Andljusbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>459439</v>
+        <v>459432</v>
       </c>
       <c r="R28" t="n">
-        <v>6808067</v>
+        <v>6807989</v>
       </c>
       <c r="S28" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3463,11 +3473,6 @@
       <c r="AA28" t="inlineStr">
         <is>
           <t>2025-04-07</t>
-        </is>
-      </c>
-      <c r="AC28" t="inlineStr">
-        <is>
-          <t>Synligt i en radie av ca 50 meter. Miljöbild.</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3482,22 +3487,22 @@
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>123829121</v>
+        <v>123828826</v>
       </c>
       <c r="B29" t="n">
-        <v>78788</v>
+        <v>56700</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3506,38 +3511,43 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="P29" t="inlineStr">
         <is>
           <t>Härkämäck, Dlr</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>459641</v>
+        <v>459636</v>
       </c>
       <c r="R29" t="n">
-        <v>6807971</v>
+        <v>6808042</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3574,7 +3584,7 @@
       </c>
       <c r="AC29" t="inlineStr">
         <is>
-          <t>I synfältet i en radie av ca 40 meter. Miljöbild.</t>
+          <t>Garnlav i bakgrund. Miljöbild.</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3601,10 +3611,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>123834220</v>
+        <v>123829632</v>
       </c>
       <c r="B30" t="n">
-        <v>78788</v>
+        <v>91277</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3617,34 +3627,34 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6425</v>
+        <v>658</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Andljusen, Dlr</t>
+          <t>Härkämäck, Dlr</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>459325</v>
+        <v>459573</v>
       </c>
       <c r="R30" t="n">
-        <v>6808176</v>
+        <v>6808047</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3677,11 +3687,6 @@
       <c r="AA30" t="inlineStr">
         <is>
           <t>2025-04-07</t>
-        </is>
-      </c>
-      <c r="AC30" t="inlineStr">
-        <is>
-          <t>I synfält, radie av ca 50 meter. Miljöbild.</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3708,10 +3713,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>123831065</v>
+        <v>123829197</v>
       </c>
       <c r="B31" t="n">
-        <v>78788</v>
+        <v>78525</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3724,21 +3729,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3748,13 +3753,13 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>459425</v>
+        <v>459611</v>
       </c>
       <c r="R31" t="n">
-        <v>6808084</v>
+        <v>6807987</v>
       </c>
       <c r="S31" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -3810,10 +3815,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>123829712</v>
+        <v>123834567</v>
       </c>
       <c r="B32" t="n">
-        <v>90990</v>
+        <v>79377</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -3826,21 +3831,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>1202</v>
+        <v>229821</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3850,10 +3855,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>459573</v>
+        <v>459399</v>
       </c>
       <c r="R32" t="n">
-        <v>6808047</v>
+        <v>6808189</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3886,6 +3891,11 @@
       <c r="AA32" t="inlineStr">
         <is>
           <t>2025-04-07</t>
+        </is>
+      </c>
+      <c r="AC32" t="inlineStr">
+        <is>
+          <t>Miljöbild.</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -3912,10 +3922,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>123833729</v>
+        <v>123834641</v>
       </c>
       <c r="B33" t="n">
-        <v>78525</v>
+        <v>78788</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -3928,37 +3938,37 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Andljusen, Dlr</t>
+          <t>Härkämäck, Härkämäck, Dlr</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>459286</v>
+        <v>459405</v>
       </c>
       <c r="R33" t="n">
-        <v>6808090</v>
+        <v>6808172</v>
       </c>
       <c r="S33" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -3988,11 +3998,6 @@
       <c r="AA33" t="inlineStr">
         <is>
           <t>2025-04-07</t>
-        </is>
-      </c>
-      <c r="AC33" t="inlineStr">
-        <is>
-          <t>Miljöbild.</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4007,22 +4012,22 @@
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>123834641</v>
+        <v>123831277</v>
       </c>
       <c r="B34" t="n">
-        <v>78788</v>
+        <v>57507</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4035,37 +4040,42 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Härkämäck, Härkämäck, Dlr</t>
+          <t>Härkämäck, Dlr</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>459405</v>
+        <v>459389</v>
       </c>
       <c r="R34" t="n">
-        <v>6808172</v>
+        <v>6808070</v>
       </c>
       <c r="S34" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -4095,6 +4105,11 @@
       <c r="AA34" t="inlineStr">
         <is>
           <t>2025-04-07</t>
+        </is>
+      </c>
+      <c r="AC34" t="inlineStr">
+        <is>
+          <t>Miljöbild.</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4109,22 +4124,22 @@
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>123831244</v>
+        <v>123833917</v>
       </c>
       <c r="B35" t="n">
-        <v>78788</v>
+        <v>78525</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4137,21 +4152,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4161,10 +4176,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>459393</v>
+        <v>459292</v>
       </c>
       <c r="R35" t="n">
-        <v>6808027</v>
+        <v>6808184</v>
       </c>
       <c r="S35" t="n">
         <v>20</v>
@@ -4223,10 +4238,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>123833814</v>
+        <v>123834890</v>
       </c>
       <c r="B36" t="n">
-        <v>78525</v>
+        <v>78867</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4239,21 +4254,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>228912</v>
+        <v>864</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Lynge) Ahti</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4263,13 +4278,13 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>459293</v>
+        <v>459427</v>
       </c>
       <c r="R36" t="n">
-        <v>6808123</v>
+        <v>6808130</v>
       </c>
       <c r="S36" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -4313,22 +4328,22 @@
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>123831097</v>
+        <v>123834183</v>
       </c>
       <c r="B37" t="n">
-        <v>79377</v>
+        <v>78788</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4341,21 +4356,21 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>229821</v>
+        <v>6425</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4365,10 +4380,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>459402</v>
+        <v>459373</v>
       </c>
       <c r="R37" t="n">
-        <v>6808072</v>
+        <v>6808222</v>
       </c>
       <c r="S37" t="n">
         <v>20</v>
@@ -4427,10 +4442,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>123829632</v>
+        <v>123833754</v>
       </c>
       <c r="B38" t="n">
-        <v>91277</v>
+        <v>92271</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4439,41 +4454,41 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>658</v>
+        <v>4364</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
-          <t>Härkämäck, Dlr</t>
+          <t>Härkämäck, Härkämäck, Dlr</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>459573</v>
+        <v>459290</v>
       </c>
       <c r="R38" t="n">
-        <v>6808047</v>
+        <v>6808093</v>
       </c>
       <c r="S38" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -4517,19 +4532,19 @@
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>123835432</v>
+        <v>123834220</v>
       </c>
       <c r="B39" t="n">
         <v>78788</v>
@@ -4565,14 +4580,14 @@
       <c r="I39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
-          <t>Härkämäck, Dlr</t>
+          <t>Andljusen, Dlr</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>459524</v>
+        <v>459325</v>
       </c>
       <c r="R39" t="n">
-        <v>6808114</v>
+        <v>6808176</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4609,7 +4624,7 @@
       </c>
       <c r="AC39" t="inlineStr">
         <is>
-          <t>Garnlav i alla riktningar, ca 50 meter i radie. Miljöbild.</t>
+          <t>I synfält, radie av ca 50 meter. Miljöbild.</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4636,7 +4651,7 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>123828742</v>
+        <v>123829121</v>
       </c>
       <c r="B40" t="n">
         <v>78788</v>
@@ -4672,17 +4687,17 @@
       <c r="I40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
-          <t>Andljusbäcken, Andljusbäcken, Dlr</t>
+          <t>Härkämäck, Dlr</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>459612</v>
+        <v>459641</v>
       </c>
       <c r="R40" t="n">
-        <v>6808068</v>
+        <v>6807971</v>
       </c>
       <c r="S40" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T40" t="inlineStr">
         <is>
@@ -4712,6 +4727,11 @@
       <c r="AA40" t="inlineStr">
         <is>
           <t>2025-04-07</t>
+        </is>
+      </c>
+      <c r="AC40" t="inlineStr">
+        <is>
+          <t>I synfältet i en radie av ca 40 meter. Miljöbild.</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4726,12 +4746,12 @@
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
@@ -4952,10 +4972,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>123830920</v>
+        <v>123830162</v>
       </c>
       <c r="B43" t="n">
-        <v>78433</v>
+        <v>78172</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -4968,37 +4988,37 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>353</v>
+        <v>6437</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
-          <t>Andljusbäcken, Andljusbäcken, Dlr</t>
+          <t>Härkämäck, Dlr</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>459462</v>
+        <v>459480</v>
       </c>
       <c r="R43" t="n">
-        <v>6808078</v>
+        <v>6808013</v>
       </c>
       <c r="S43" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T43" t="inlineStr">
         <is>
@@ -5028,6 +5048,11 @@
       <c r="AA43" t="inlineStr">
         <is>
           <t>2025-04-07</t>
+        </is>
+      </c>
+      <c r="AC43" t="inlineStr">
+        <is>
+          <t>Miljöbild.</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5042,19 +5067,19 @@
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>123829246</v>
+        <v>123828742</v>
       </c>
       <c r="B44" t="n">
         <v>78788</v>
@@ -5090,17 +5115,17 @@
       <c r="I44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
-          <t>Härkämäck, Dlr</t>
+          <t>Andljusbäcken, Andljusbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>459586</v>
+        <v>459612</v>
       </c>
       <c r="R44" t="n">
-        <v>6807981</v>
+        <v>6808068</v>
       </c>
       <c r="S44" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T44" t="inlineStr">
         <is>
@@ -5130,11 +5155,6 @@
       <c r="AA44" t="inlineStr">
         <is>
           <t>2025-04-07</t>
-        </is>
-      </c>
-      <c r="AC44" t="inlineStr">
-        <is>
-          <t>Som vanligt garnlav i omgivningen. Miljöbilder.</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5149,22 +5169,22 @@
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>123829102</v>
+        <v>123831467</v>
       </c>
       <c r="B45" t="n">
-        <v>78788</v>
+        <v>79377</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5177,37 +5197,37 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6425</v>
+        <v>229821</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
-          <t>Andljusbäcken, Andljusbäcken, Dlr</t>
+          <t>Härkämäck, Härkämäck, Dlr</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>459666</v>
+        <v>459290</v>
       </c>
       <c r="R45" t="n">
-        <v>6807990</v>
+        <v>6808098</v>
       </c>
       <c r="S45" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T45" t="inlineStr">
         <is>
@@ -5251,22 +5271,22 @@
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Niklas Rehn</t>
         </is>
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Niklas Rehn</t>
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>123834195</v>
+        <v>123829205</v>
       </c>
       <c r="B46" t="n">
-        <v>78525</v>
+        <v>78524</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5279,37 +5299,37 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>228912</v>
+        <v>6446</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
-          <t>Härkämäck, Härkämäck, Dlr</t>
+          <t>Andljusbäcken, Andljusbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>459365</v>
+        <v>459611</v>
       </c>
       <c r="R46" t="n">
-        <v>6808224</v>
+        <v>6807987</v>
       </c>
       <c r="S46" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T46" t="inlineStr">
         <is>
@@ -5353,22 +5373,22 @@
       <c r="AT46" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX46" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>123829197</v>
+        <v>123834998</v>
       </c>
       <c r="B47" t="n">
-        <v>78525</v>
+        <v>79377</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5381,34 +5401,34 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>228912</v>
+        <v>229821</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
-          <t>Andljusbäcken, Andljusbäcken, Dlr</t>
+          <t>Härkämäck, Härkämäck, Dlr</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>459611</v>
+        <v>459437</v>
       </c>
       <c r="R47" t="n">
-        <v>6807987</v>
+        <v>6808171</v>
       </c>
       <c r="S47" t="n">
         <v>20</v>
@@ -5467,10 +5487,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>123834183</v>
+        <v>123829275</v>
       </c>
       <c r="B48" t="n">
-        <v>78788</v>
+        <v>78525</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -5483,21 +5503,21 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5507,10 +5527,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>459373</v>
+        <v>459544</v>
       </c>
       <c r="R48" t="n">
-        <v>6808222</v>
+        <v>6807989</v>
       </c>
       <c r="S48" t="n">
         <v>20</v>
@@ -5569,10 +5589,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>123829394</v>
+        <v>123831065</v>
       </c>
       <c r="B49" t="n">
-        <v>77716</v>
+        <v>78788</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -5585,34 +5605,34 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>6487</v>
+        <v>6425</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Blågrå svartspik</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Chaenothecopsis fennica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Laurila) Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
-          <t>Härkämäck, Dlr</t>
+          <t>Andljusbäcken, Andljusbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>459586</v>
+        <v>459425</v>
       </c>
       <c r="R49" t="n">
-        <v>6807981</v>
+        <v>6808084</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5659,22 +5679,22 @@
       <c r="AT49" t="inlineStr"/>
       <c r="AW49" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX49" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>123829310</v>
+        <v>123829918</v>
       </c>
       <c r="B50" t="n">
-        <v>57507</v>
+        <v>78524</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -5687,42 +5707,37 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>100049</v>
+        <v>6446</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
-      <c r="M50" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P50" t="inlineStr">
         <is>
-          <t>Härkämäck, Dlr</t>
+          <t>Andljusbäcken, Andljusbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>459586</v>
+        <v>459424</v>
       </c>
       <c r="R50" t="n">
-        <v>6807981</v>
+        <v>6807998</v>
       </c>
       <c r="S50" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T50" t="inlineStr">
         <is>
@@ -5766,22 +5781,22 @@
       <c r="AT50" t="inlineStr"/>
       <c r="AW50" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX50" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>123834630</v>
+        <v>123829394</v>
       </c>
       <c r="B51" t="n">
-        <v>57512</v>
+        <v>77716</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -5790,38 +5805,38 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>100110</v>
+        <v>6487</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Gråspett</t>
+          <t>Blågrå svartspik</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Picus canus</t>
+          <t>Chaenothecopsis fennica</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>J.F. Gmelin, 1788</t>
+          <t>(Laurila) Tibell</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
-          <t>Härkämäck, Härkämäck, Dlr</t>
+          <t>Härkämäck, Dlr</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>459408</v>
+        <v>459586</v>
       </c>
       <c r="R51" t="n">
-        <v>6808198</v>
+        <v>6807981</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5856,11 +5871,6 @@
           <t>2025-04-07</t>
         </is>
       </c>
-      <c r="AC51" t="inlineStr">
-        <is>
-          <t>Förbiflygande.</t>
-        </is>
-      </c>
       <c r="AD51" t="b">
         <v>0</v>
       </c>
@@ -5873,22 +5883,22 @@
       <c r="AT51" t="inlineStr"/>
       <c r="AW51" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX51" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>123834966</v>
+        <v>123835135</v>
       </c>
       <c r="B52" t="n">
-        <v>57512</v>
+        <v>78788</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -5897,43 +5907,38 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>100110</v>
+        <v>6425</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Gråspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Picus canus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>J.F. Gmelin, 1788</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
-      <c r="M52" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="P52" t="inlineStr">
         <is>
           <t>Härkämäck, Dlr</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>459399</v>
+        <v>459455</v>
       </c>
       <c r="R52" t="n">
-        <v>6808189</v>
+        <v>6808164</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -5970,7 +5975,7 @@
       </c>
       <c r="AC52" t="inlineStr">
         <is>
-          <t>Förbiflygande.</t>
+          <t>Garnlav i en radie av ca 50 meter, synfältet. Miljöbild.</t>
         </is>
       </c>
       <c r="AD52" t="b">

--- a/artfynd/A 61327-2022 artfynd.xlsx
+++ b/artfynd/A 61327-2022 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>123829941</v>
+        <v>123829121</v>
       </c>
       <c r="B2" t="n">
-        <v>78525</v>
+        <v>78788</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>459480</v>
+        <v>459641</v>
       </c>
       <c r="R2" t="n">
-        <v>6808013</v>
+        <v>6807971</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -755,7 +755,7 @@
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>Miljöbild.</t>
+          <t>I synfältet i en radie av ca 40 meter. Miljöbild.</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -782,10 +782,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123834195</v>
+        <v>123828044</v>
       </c>
       <c r="B3" t="n">
-        <v>78525</v>
+        <v>78788</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -798,34 +798,34 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Härkämäck, Härkämäck, Dlr</t>
+          <t>Härkämäck, Dlr</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>459365</v>
+        <v>459681</v>
       </c>
       <c r="R3" t="n">
-        <v>6808224</v>
+        <v>6808072</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -860,6 +860,11 @@
           <t>2025-04-07</t>
         </is>
       </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Garnlav i synfältet i en radie av ca 50 meter. Miljöbild.</t>
+        </is>
+      </c>
       <c r="AD3" t="b">
         <v>0</v>
       </c>
@@ -872,22 +877,22 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123827957</v>
+        <v>123828742</v>
       </c>
       <c r="B4" t="n">
-        <v>78524</v>
+        <v>78788</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -900,21 +905,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -924,10 +929,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>459664</v>
+        <v>459612</v>
       </c>
       <c r="R4" t="n">
-        <v>6808079</v>
+        <v>6808068</v>
       </c>
       <c r="S4" t="n">
         <v>20</v>
@@ -986,10 +991,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123828882</v>
+        <v>123834183</v>
       </c>
       <c r="B5" t="n">
-        <v>78820</v>
+        <v>78788</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1002,21 +1007,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1026,10 +1031,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>459600</v>
+        <v>459373</v>
       </c>
       <c r="R5" t="n">
-        <v>6808030</v>
+        <v>6808222</v>
       </c>
       <c r="S5" t="n">
         <v>20</v>
@@ -1088,10 +1093,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>123829310</v>
+        <v>123833729</v>
       </c>
       <c r="B6" t="n">
-        <v>57507</v>
+        <v>78525</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1104,39 +1109,34 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100049</v>
+        <v>228912</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Härkämäck, Dlr</t>
+          <t>Andljusen, Dlr</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>459586</v>
+        <v>459286</v>
       </c>
       <c r="R6" t="n">
-        <v>6807981</v>
+        <v>6808090</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1169,6 +1169,11 @@
       <c r="AA6" t="inlineStr">
         <is>
           <t>2025-04-07</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Miljöbild.</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1195,10 +1200,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>123834966</v>
+        <v>123829197</v>
       </c>
       <c r="B7" t="n">
-        <v>57512</v>
+        <v>78525</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1207,46 +1212,41 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100110</v>
+        <v>228912</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Gråspett</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Picus canus</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>J.F. Gmelin, 1788</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Härkämäck, Dlr</t>
+          <t>Andljusbäcken, Andljusbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>459399</v>
+        <v>459611</v>
       </c>
       <c r="R7" t="n">
-        <v>6808189</v>
+        <v>6807987</v>
       </c>
       <c r="S7" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1276,11 +1276,6 @@
       <c r="AA7" t="inlineStr">
         <is>
           <t>2025-04-07</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>Förbiflygande.</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1295,22 +1290,22 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>123834650</v>
+        <v>123831067</v>
       </c>
       <c r="B8" t="n">
-        <v>78525</v>
+        <v>78788</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1323,21 +1318,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1347,10 +1342,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>459399</v>
+        <v>459439</v>
       </c>
       <c r="R8" t="n">
-        <v>6808189</v>
+        <v>6808067</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1387,7 +1382,7 @@
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>Miljöbild</t>
+          <t>Synligt i en radie av ca 50 meter. Miljöbild.</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1414,10 +1409,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>123831097</v>
+        <v>123834641</v>
       </c>
       <c r="B9" t="n">
-        <v>79377</v>
+        <v>78788</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1430,34 +1425,34 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>229821</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Andljusbäcken, Andljusbäcken, Dlr</t>
+          <t>Härkämäck, Härkämäck, Dlr</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>459402</v>
+        <v>459405</v>
       </c>
       <c r="R9" t="n">
-        <v>6808072</v>
+        <v>6808172</v>
       </c>
       <c r="S9" t="n">
         <v>20</v>
@@ -1516,10 +1511,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>123829879</v>
+        <v>123830920</v>
       </c>
       <c r="B10" t="n">
-        <v>78788</v>
+        <v>78433</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1532,21 +1527,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1556,10 +1551,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>459488</v>
+        <v>459462</v>
       </c>
       <c r="R10" t="n">
-        <v>6807974</v>
+        <v>6808078</v>
       </c>
       <c r="S10" t="n">
         <v>20</v>
@@ -1618,10 +1613,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>123834630</v>
+        <v>123834650</v>
       </c>
       <c r="B11" t="n">
-        <v>57512</v>
+        <v>78525</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1630,38 +1625,38 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100110</v>
+        <v>228912</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Gråspett</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Picus canus</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>J.F. Gmelin, 1788</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Härkämäck, Härkämäck, Dlr</t>
+          <t>Härkämäck, Dlr</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>459408</v>
+        <v>459399</v>
       </c>
       <c r="R11" t="n">
-        <v>6808198</v>
+        <v>6808189</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1698,7 +1693,7 @@
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>Förbiflygande.</t>
+          <t>Miljöbild</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1713,22 +1708,22 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>123829246</v>
+        <v>123831467</v>
       </c>
       <c r="B12" t="n">
-        <v>78788</v>
+        <v>79377</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1741,34 +1736,34 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6425</v>
+        <v>229821</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Härkämäck, Dlr</t>
+          <t>Härkämäck, Härkämäck, Dlr</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>459586</v>
+        <v>459290</v>
       </c>
       <c r="R12" t="n">
-        <v>6807981</v>
+        <v>6808098</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1803,11 +1798,6 @@
           <t>2025-04-07</t>
         </is>
       </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>Som vanligt garnlav i omgivningen. Miljöbilder.</t>
-        </is>
-      </c>
       <c r="AD12" t="b">
         <v>0</v>
       </c>
@@ -1820,22 +1810,22 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Niklas Rehn</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Niklas Rehn</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>123830920</v>
+        <v>123834998</v>
       </c>
       <c r="B13" t="n">
-        <v>78433</v>
+        <v>79377</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1848,34 +1838,34 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>353</v>
+        <v>229821</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Andljusbäcken, Andljusbäcken, Dlr</t>
+          <t>Härkämäck, Härkämäck, Dlr</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>459462</v>
+        <v>459437</v>
       </c>
       <c r="R13" t="n">
-        <v>6808078</v>
+        <v>6808171</v>
       </c>
       <c r="S13" t="n">
         <v>20</v>
@@ -1934,10 +1924,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>123834034</v>
+        <v>123829246</v>
       </c>
       <c r="B14" t="n">
-        <v>57507</v>
+        <v>78788</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1950,39 +1940,34 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Andljusen, Dlr</t>
+          <t>Härkämäck, Dlr</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>459325</v>
+        <v>459586</v>
       </c>
       <c r="R14" t="n">
-        <v>6808176</v>
+        <v>6807981</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2019,7 +2004,7 @@
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>Miljöbild.</t>
+          <t>Som vanligt garnlav i omgivningen. Miljöbilder.</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2046,10 +2031,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>123831578</v>
+        <v>123831244</v>
       </c>
       <c r="B15" t="n">
-        <v>74879</v>
+        <v>78788</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2062,21 +2047,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2086,10 +2071,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>459287</v>
+        <v>459393</v>
       </c>
       <c r="R15" t="n">
-        <v>6808008</v>
+        <v>6808027</v>
       </c>
       <c r="S15" t="n">
         <v>20</v>
@@ -2148,10 +2133,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>123829102</v>
+        <v>123829275</v>
       </c>
       <c r="B16" t="n">
-        <v>78788</v>
+        <v>78525</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2164,21 +2149,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2188,10 +2173,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>459666</v>
+        <v>459544</v>
       </c>
       <c r="R16" t="n">
-        <v>6807990</v>
+        <v>6807989</v>
       </c>
       <c r="S16" t="n">
         <v>20</v>
@@ -2250,10 +2235,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>123835432</v>
+        <v>123834966</v>
       </c>
       <c r="B17" t="n">
-        <v>78788</v>
+        <v>57512</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2262,38 +2247,43 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6425</v>
+        <v>100110</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gråspett</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picus canus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>J.F. Gmelin, 1788</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P17" t="inlineStr">
         <is>
           <t>Härkämäck, Dlr</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>459524</v>
+        <v>459399</v>
       </c>
       <c r="R17" t="n">
-        <v>6808114</v>
+        <v>6808189</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2330,7 +2320,7 @@
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>Garnlav i alla riktningar, ca 50 meter i radie. Miljöbild.</t>
+          <t>Förbiflygande.</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2357,10 +2347,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>123828044</v>
+        <v>123833814</v>
       </c>
       <c r="B18" t="n">
-        <v>78788</v>
+        <v>78525</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2373,37 +2363,37 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Härkämäck, Dlr</t>
+          <t>Härkämäck, Härkämäck, Dlr</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>459681</v>
+        <v>459293</v>
       </c>
       <c r="R18" t="n">
-        <v>6808072</v>
+        <v>6808123</v>
       </c>
       <c r="S18" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2433,11 +2423,6 @@
       <c r="AA18" t="inlineStr">
         <is>
           <t>2025-04-07</t>
-        </is>
-      </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>Garnlav i synfältet i en radie av ca 50 meter. Miljöbild.</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2452,22 +2437,22 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>123831067</v>
+        <v>123829712</v>
       </c>
       <c r="B19" t="n">
-        <v>78788</v>
+        <v>90990</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2480,21 +2465,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2504,10 +2489,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>459439</v>
+        <v>459573</v>
       </c>
       <c r="R19" t="n">
-        <v>6808067</v>
+        <v>6808047</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2540,11 +2525,6 @@
       <c r="AA19" t="inlineStr">
         <is>
           <t>2025-04-07</t>
-        </is>
-      </c>
-      <c r="AC19" t="inlineStr">
-        <is>
-          <t>Synligt i en radie av ca 50 meter. Miljöbild.</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2571,10 +2551,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>123831244</v>
+        <v>123831578</v>
       </c>
       <c r="B20" t="n">
-        <v>78788</v>
+        <v>74879</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2587,21 +2567,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2611,10 +2591,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>459393</v>
+        <v>459287</v>
       </c>
       <c r="R20" t="n">
-        <v>6808027</v>
+        <v>6808008</v>
       </c>
       <c r="S20" t="n">
         <v>20</v>
@@ -2673,10 +2653,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>123829712</v>
+        <v>123829941</v>
       </c>
       <c r="B21" t="n">
-        <v>90990</v>
+        <v>78525</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2689,21 +2669,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>1202</v>
+        <v>228912</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2713,10 +2693,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>459573</v>
+        <v>459480</v>
       </c>
       <c r="R21" t="n">
-        <v>6808047</v>
+        <v>6808013</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2749,6 +2729,11 @@
       <c r="AA21" t="inlineStr">
         <is>
           <t>2025-04-07</t>
+        </is>
+      </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>Miljöbild.</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2775,10 +2760,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>123834006</v>
+        <v>123834630</v>
       </c>
       <c r="B22" t="n">
-        <v>78525</v>
+        <v>57512</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2787,25 +2772,25 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>228912</v>
+        <v>100110</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Gråspett</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Picus canus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>J.F. Gmelin, 1788</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2815,13 +2800,13 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>459326</v>
+        <v>459408</v>
       </c>
       <c r="R22" t="n">
-        <v>6808188</v>
+        <v>6808198</v>
       </c>
       <c r="S22" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -2851,6 +2836,11 @@
       <c r="AA22" t="inlineStr">
         <is>
           <t>2025-04-07</t>
+        </is>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>Förbiflygande.</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2877,10 +2867,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>123833841</v>
+        <v>123834034</v>
       </c>
       <c r="B23" t="n">
-        <v>78788</v>
+        <v>57507</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2893,37 +2883,42 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Härkämäck, Härkämäck, Dlr</t>
+          <t>Andljusen, Dlr</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>459300</v>
+        <v>459325</v>
       </c>
       <c r="R23" t="n">
-        <v>6808144</v>
+        <v>6808176</v>
       </c>
       <c r="S23" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -2953,6 +2948,11 @@
       <c r="AA23" t="inlineStr">
         <is>
           <t>2025-04-07</t>
+        </is>
+      </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>Miljöbild.</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -2967,19 +2967,19 @@
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>123828783</v>
+        <v>123829879</v>
       </c>
       <c r="B24" t="n">
         <v>78788</v>
@@ -3019,10 +3019,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>459611</v>
+        <v>459488</v>
       </c>
       <c r="R24" t="n">
-        <v>6808048</v>
+        <v>6807974</v>
       </c>
       <c r="S24" t="n">
         <v>20</v>
@@ -3081,7 +3081,7 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>123833814</v>
+        <v>123833917</v>
       </c>
       <c r="B25" t="n">
         <v>78525</v>
@@ -3117,17 +3117,17 @@
       <c r="I25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Härkämäck, Härkämäck, Dlr</t>
+          <t>Andljusbäcken, Andljusbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>459293</v>
+        <v>459292</v>
       </c>
       <c r="R25" t="n">
-        <v>6808123</v>
+        <v>6808184</v>
       </c>
       <c r="S25" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3171,19 +3171,19 @@
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>123833729</v>
+        <v>123829889</v>
       </c>
       <c r="B26" t="n">
         <v>78525</v>
@@ -3219,14 +3219,14 @@
       <c r="I26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Andljusen, Dlr</t>
+          <t>Härkämäck, Dlr</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>459286</v>
+        <v>459494</v>
       </c>
       <c r="R26" t="n">
-        <v>6808090</v>
+        <v>6807997</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3290,10 +3290,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>123829889</v>
+        <v>123829632</v>
       </c>
       <c r="B27" t="n">
-        <v>78525</v>
+        <v>91277</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3306,21 +3306,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>228912</v>
+        <v>658</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3330,10 +3330,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>459494</v>
+        <v>459573</v>
       </c>
       <c r="R27" t="n">
-        <v>6807997</v>
+        <v>6808047</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3366,11 +3366,6 @@
       <c r="AA27" t="inlineStr">
         <is>
           <t>2025-04-07</t>
-        </is>
-      </c>
-      <c r="AC27" t="inlineStr">
-        <is>
-          <t>Miljöbild.</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3397,10 +3392,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>123829982</v>
+        <v>123831065</v>
       </c>
       <c r="B28" t="n">
-        <v>77716</v>
+        <v>78788</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3413,21 +3408,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6487</v>
+        <v>6425</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Blågrå svartspik</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Chaenothecopsis fennica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Laurila) Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3437,13 +3432,13 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>459432</v>
+        <v>459425</v>
       </c>
       <c r="R28" t="n">
-        <v>6807989</v>
+        <v>6808084</v>
       </c>
       <c r="S28" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3499,10 +3494,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>123828826</v>
+        <v>123834890</v>
       </c>
       <c r="B29" t="n">
-        <v>56700</v>
+        <v>78867</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3511,46 +3506,41 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>100138</v>
+        <v>864</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Lynge) Ahti</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
-      <c r="M29" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Härkämäck, Dlr</t>
+          <t>Härkämäck, Härkämäck, Dlr</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>459636</v>
+        <v>459427</v>
       </c>
       <c r="R29" t="n">
-        <v>6808042</v>
+        <v>6808130</v>
       </c>
       <c r="S29" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3580,11 +3570,6 @@
       <c r="AA29" t="inlineStr">
         <is>
           <t>2025-04-07</t>
-        </is>
-      </c>
-      <c r="AC29" t="inlineStr">
-        <is>
-          <t>Garnlav i bakgrund. Miljöbild.</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3599,22 +3584,22 @@
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>123829632</v>
+        <v>123835432</v>
       </c>
       <c r="B30" t="n">
-        <v>91277</v>
+        <v>78788</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3627,21 +3612,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>658</v>
+        <v>6425</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3651,10 +3636,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>459573</v>
+        <v>459524</v>
       </c>
       <c r="R30" t="n">
-        <v>6808047</v>
+        <v>6808114</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3687,6 +3672,11 @@
       <c r="AA30" t="inlineStr">
         <is>
           <t>2025-04-07</t>
+        </is>
+      </c>
+      <c r="AC30" t="inlineStr">
+        <is>
+          <t>Garnlav i alla riktningar, ca 50 meter i radie. Miljöbild.</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3713,10 +3703,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>123829197</v>
+        <v>123830162</v>
       </c>
       <c r="B31" t="n">
-        <v>78525</v>
+        <v>78172</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3729,37 +3719,37 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>228912</v>
+        <v>6437</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Andljusbäcken, Andljusbäcken, Dlr</t>
+          <t>Härkämäck, Dlr</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>459611</v>
+        <v>459480</v>
       </c>
       <c r="R31" t="n">
-        <v>6807987</v>
+        <v>6808013</v>
       </c>
       <c r="S31" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -3789,6 +3779,11 @@
       <c r="AA31" t="inlineStr">
         <is>
           <t>2025-04-07</t>
+        </is>
+      </c>
+      <c r="AC31" t="inlineStr">
+        <is>
+          <t>Miljöbild.</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3803,22 +3798,22 @@
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>123834567</v>
+        <v>123827957</v>
       </c>
       <c r="B32" t="n">
-        <v>79377</v>
+        <v>78524</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -3831,37 +3826,37 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>229821</v>
+        <v>6446</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Härkämäck, Dlr</t>
+          <t>Andljusbäcken, Andljusbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>459399</v>
+        <v>459664</v>
       </c>
       <c r="R32" t="n">
-        <v>6808189</v>
+        <v>6808079</v>
       </c>
       <c r="S32" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -3891,11 +3886,6 @@
       <c r="AA32" t="inlineStr">
         <is>
           <t>2025-04-07</t>
-        </is>
-      </c>
-      <c r="AC32" t="inlineStr">
-        <is>
-          <t>Miljöbild.</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -3910,22 +3900,22 @@
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>123834641</v>
+        <v>123834006</v>
       </c>
       <c r="B33" t="n">
-        <v>78788</v>
+        <v>78525</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -3938,21 +3928,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3962,13 +3952,13 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>459405</v>
+        <v>459326</v>
       </c>
       <c r="R33" t="n">
-        <v>6808172</v>
+        <v>6808188</v>
       </c>
       <c r="S33" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -4012,22 +4002,22 @@
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>123831277</v>
+        <v>123834195</v>
       </c>
       <c r="B34" t="n">
-        <v>57507</v>
+        <v>78525</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4040,39 +4030,34 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>100049</v>
+        <v>228912</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
-      <c r="M34" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Härkämäck, Dlr</t>
+          <t>Härkämäck, Härkämäck, Dlr</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>459389</v>
+        <v>459365</v>
       </c>
       <c r="R34" t="n">
-        <v>6808070</v>
+        <v>6808224</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4107,11 +4092,6 @@
           <t>2025-04-07</t>
         </is>
       </c>
-      <c r="AC34" t="inlineStr">
-        <is>
-          <t>Miljöbild.</t>
-        </is>
-      </c>
       <c r="AD34" t="b">
         <v>0</v>
       </c>
@@ -4124,22 +4104,22 @@
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>123833917</v>
+        <v>123831097</v>
       </c>
       <c r="B35" t="n">
-        <v>78525</v>
+        <v>79377</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4152,21 +4132,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>228912</v>
+        <v>229821</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4176,10 +4156,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>459292</v>
+        <v>459402</v>
       </c>
       <c r="R35" t="n">
-        <v>6808184</v>
+        <v>6808072</v>
       </c>
       <c r="S35" t="n">
         <v>20</v>
@@ -4238,10 +4218,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>123834890</v>
+        <v>123828783</v>
       </c>
       <c r="B36" t="n">
-        <v>78867</v>
+        <v>78788</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4254,34 +4234,34 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>864</v>
+        <v>6425</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Knottrig blåslav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Hypogymnia bitteri</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Lynge) Ahti</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Härkämäck, Härkämäck, Dlr</t>
+          <t>Andljusbäcken, Andljusbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>459427</v>
+        <v>459611</v>
       </c>
       <c r="R36" t="n">
-        <v>6808130</v>
+        <v>6808048</v>
       </c>
       <c r="S36" t="n">
         <v>20</v>
@@ -4340,10 +4320,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>123834183</v>
+        <v>123828882</v>
       </c>
       <c r="B37" t="n">
-        <v>78788</v>
+        <v>78820</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4356,21 +4336,21 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4380,10 +4360,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>459373</v>
+        <v>459600</v>
       </c>
       <c r="R37" t="n">
-        <v>6808222</v>
+        <v>6808030</v>
       </c>
       <c r="S37" t="n">
         <v>20</v>
@@ -4442,10 +4422,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>123833754</v>
+        <v>123834567</v>
       </c>
       <c r="B38" t="n">
-        <v>92271</v>
+        <v>79377</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4454,41 +4434,41 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>4364</v>
+        <v>229821</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
-          <t>Härkämäck, Härkämäck, Dlr</t>
+          <t>Härkämäck, Dlr</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>459290</v>
+        <v>459399</v>
       </c>
       <c r="R38" t="n">
-        <v>6808093</v>
+        <v>6808189</v>
       </c>
       <c r="S38" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -4518,6 +4498,11 @@
       <c r="AA38" t="inlineStr">
         <is>
           <t>2025-04-07</t>
+        </is>
+      </c>
+      <c r="AC38" t="inlineStr">
+        <is>
+          <t>Miljöbild.</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4532,22 +4517,22 @@
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>123834220</v>
+        <v>123829205</v>
       </c>
       <c r="B39" t="n">
-        <v>78788</v>
+        <v>78524</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4560,37 +4545,37 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
-          <t>Andljusen, Dlr</t>
+          <t>Andljusbäcken, Andljusbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>459325</v>
+        <v>459611</v>
       </c>
       <c r="R39" t="n">
-        <v>6808176</v>
+        <v>6807987</v>
       </c>
       <c r="S39" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
@@ -4620,11 +4605,6 @@
       <c r="AA39" t="inlineStr">
         <is>
           <t>2025-04-07</t>
-        </is>
-      </c>
-      <c r="AC39" t="inlineStr">
-        <is>
-          <t>I synfält, radie av ca 50 meter. Miljöbild.</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4639,22 +4619,22 @@
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>123829121</v>
+        <v>123829394</v>
       </c>
       <c r="B40" t="n">
-        <v>78788</v>
+        <v>77716</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -4667,21 +4647,21 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6425</v>
+        <v>6487</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Blågrå svartspik</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenothecopsis fennica</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Laurila) Tibell</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4691,10 +4671,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>459641</v>
+        <v>459586</v>
       </c>
       <c r="R40" t="n">
-        <v>6807971</v>
+        <v>6807981</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4727,11 +4707,6 @@
       <c r="AA40" t="inlineStr">
         <is>
           <t>2025-04-07</t>
-        </is>
-      </c>
-      <c r="AC40" t="inlineStr">
-        <is>
-          <t>I synfältet i en radie av ca 40 meter. Miljöbild.</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4758,7 +4733,7 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>123828608</v>
+        <v>123829102</v>
       </c>
       <c r="B41" t="n">
         <v>78788</v>
@@ -4794,17 +4769,17 @@
       <c r="I41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
-          <t>Härkämäck, Dlr</t>
+          <t>Andljusbäcken, Andljusbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>459636</v>
+        <v>459666</v>
       </c>
       <c r="R41" t="n">
-        <v>6808042</v>
+        <v>6807990</v>
       </c>
       <c r="S41" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -4834,11 +4809,6 @@
       <c r="AA41" t="inlineStr">
         <is>
           <t>2025-04-07</t>
-        </is>
-      </c>
-      <c r="AC41" t="inlineStr">
-        <is>
-          <t>Garnlav i synfältet i en radie av ca 50 meter. Miljöbilder.</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -4853,22 +4823,22 @@
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>123830009</v>
+        <v>123835135</v>
       </c>
       <c r="B42" t="n">
-        <v>78524</v>
+        <v>78788</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -4881,21 +4851,21 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4905,10 +4875,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>459480</v>
+        <v>459455</v>
       </c>
       <c r="R42" t="n">
-        <v>6808013</v>
+        <v>6808164</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4945,7 +4915,7 @@
       </c>
       <c r="AC42" t="inlineStr">
         <is>
-          <t>Miljöbild.</t>
+          <t>Garnlav i en radie av ca 50 meter, synfältet. Miljöbild.</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -4972,10 +4942,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>123830162</v>
+        <v>123831277</v>
       </c>
       <c r="B43" t="n">
-        <v>78172</v>
+        <v>57507</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -4988,34 +4958,39 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6437</v>
+        <v>100049</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P43" t="inlineStr">
         <is>
           <t>Härkämäck, Dlr</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>459480</v>
+        <v>459389</v>
       </c>
       <c r="R43" t="n">
-        <v>6808013</v>
+        <v>6808070</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5079,10 +5054,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>123828742</v>
+        <v>123829982</v>
       </c>
       <c r="B44" t="n">
-        <v>78788</v>
+        <v>77716</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5095,21 +5070,21 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6425</v>
+        <v>6487</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Blågrå svartspik</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenothecopsis fennica</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Laurila) Tibell</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5119,10 +5094,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>459612</v>
+        <v>459432</v>
       </c>
       <c r="R44" t="n">
-        <v>6808068</v>
+        <v>6807989</v>
       </c>
       <c r="S44" t="n">
         <v>20</v>
@@ -5181,10 +5156,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>123831467</v>
+        <v>123829918</v>
       </c>
       <c r="B45" t="n">
-        <v>79377</v>
+        <v>78524</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5197,37 +5172,37 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>229821</v>
+        <v>6446</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
-          <t>Härkämäck, Härkämäck, Dlr</t>
+          <t>Andljusbäcken, Andljusbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>459290</v>
+        <v>459424</v>
       </c>
       <c r="R45" t="n">
-        <v>6808098</v>
+        <v>6807998</v>
       </c>
       <c r="S45" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T45" t="inlineStr">
         <is>
@@ -5271,22 +5246,22 @@
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
         <is>
-          <t>Niklas Rehn</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>Niklas Rehn</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>123829205</v>
+        <v>123834220</v>
       </c>
       <c r="B46" t="n">
-        <v>78524</v>
+        <v>78788</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5299,37 +5274,37 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
-          <t>Andljusbäcken, Andljusbäcken, Dlr</t>
+          <t>Andljusen, Dlr</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>459611</v>
+        <v>459325</v>
       </c>
       <c r="R46" t="n">
-        <v>6807987</v>
+        <v>6808176</v>
       </c>
       <c r="S46" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T46" t="inlineStr">
         <is>
@@ -5359,6 +5334,11 @@
       <c r="AA46" t="inlineStr">
         <is>
           <t>2025-04-07</t>
+        </is>
+      </c>
+      <c r="AC46" t="inlineStr">
+        <is>
+          <t>I synfält, radie av ca 50 meter. Miljöbild.</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5373,22 +5353,22 @@
       <c r="AT46" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX46" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>123834998</v>
+        <v>123829310</v>
       </c>
       <c r="B47" t="n">
-        <v>79377</v>
+        <v>57507</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5401,37 +5381,42 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>229821</v>
+        <v>100049</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
+      <c r="M47" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P47" t="inlineStr">
         <is>
-          <t>Härkämäck, Härkämäck, Dlr</t>
+          <t>Härkämäck, Dlr</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>459437</v>
+        <v>459586</v>
       </c>
       <c r="R47" t="n">
-        <v>6808171</v>
+        <v>6807981</v>
       </c>
       <c r="S47" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T47" t="inlineStr">
         <is>
@@ -5475,22 +5460,22 @@
       <c r="AT47" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX47" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>123829275</v>
+        <v>123828826</v>
       </c>
       <c r="B48" t="n">
-        <v>78525</v>
+        <v>56700</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -5499,41 +5484,46 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>228912</v>
+        <v>100138</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
+      <c r="M48" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="P48" t="inlineStr">
         <is>
-          <t>Andljusbäcken, Andljusbäcken, Dlr</t>
+          <t>Härkämäck, Dlr</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>459544</v>
+        <v>459636</v>
       </c>
       <c r="R48" t="n">
-        <v>6807989</v>
+        <v>6808042</v>
       </c>
       <c r="S48" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T48" t="inlineStr">
         <is>
@@ -5563,6 +5553,11 @@
       <c r="AA48" t="inlineStr">
         <is>
           <t>2025-04-07</t>
+        </is>
+      </c>
+      <c r="AC48" t="inlineStr">
+        <is>
+          <t>Garnlav i bakgrund. Miljöbild.</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5577,19 +5572,19 @@
       <c r="AT48" t="inlineStr"/>
       <c r="AW48" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX48" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>123831065</v>
+        <v>123833841</v>
       </c>
       <c r="B49" t="n">
         <v>78788</v>
@@ -5625,17 +5620,17 @@
       <c r="I49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
-          <t>Andljusbäcken, Andljusbäcken, Dlr</t>
+          <t>Härkämäck, Härkämäck, Dlr</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>459425</v>
+        <v>459300</v>
       </c>
       <c r="R49" t="n">
-        <v>6808084</v>
+        <v>6808144</v>
       </c>
       <c r="S49" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T49" t="inlineStr">
         <is>
@@ -5679,22 +5674,22 @@
       <c r="AT49" t="inlineStr"/>
       <c r="AW49" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX49" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>123829918</v>
+        <v>123833754</v>
       </c>
       <c r="B50" t="n">
-        <v>78524</v>
+        <v>92271</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -5703,41 +5698,41 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>6446</v>
+        <v>4364</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
-          <t>Andljusbäcken, Andljusbäcken, Dlr</t>
+          <t>Härkämäck, Härkämäck, Dlr</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>459424</v>
+        <v>459290</v>
       </c>
       <c r="R50" t="n">
-        <v>6807998</v>
+        <v>6808093</v>
       </c>
       <c r="S50" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T50" t="inlineStr">
         <is>
@@ -5781,22 +5776,22 @@
       <c r="AT50" t="inlineStr"/>
       <c r="AW50" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX50" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>123829394</v>
+        <v>123828608</v>
       </c>
       <c r="B51" t="n">
-        <v>77716</v>
+        <v>78788</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -5809,21 +5804,21 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>6487</v>
+        <v>6425</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Blågrå svartspik</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Chaenothecopsis fennica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Laurila) Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -5833,10 +5828,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>459586</v>
+        <v>459636</v>
       </c>
       <c r="R51" t="n">
-        <v>6807981</v>
+        <v>6808042</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5869,6 +5864,11 @@
       <c r="AA51" t="inlineStr">
         <is>
           <t>2025-04-07</t>
+        </is>
+      </c>
+      <c r="AC51" t="inlineStr">
+        <is>
+          <t>Garnlav i synfältet i en radie av ca 50 meter. Miljöbilder.</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -5895,10 +5895,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>123835135</v>
+        <v>123830009</v>
       </c>
       <c r="B52" t="n">
-        <v>78788</v>
+        <v>78524</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -5911,21 +5911,21 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -5935,10 +5935,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>459455</v>
+        <v>459480</v>
       </c>
       <c r="R52" t="n">
-        <v>6808164</v>
+        <v>6808013</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -5975,7 +5975,7 @@
       </c>
       <c r="AC52" t="inlineStr">
         <is>
-          <t>Garnlav i en radie av ca 50 meter, synfältet. Miljöbild.</t>
+          <t>Miljöbild.</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6002,10 +6002,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>123920441</v>
+        <v>123920732</v>
       </c>
       <c r="B53" t="n">
-        <v>56700</v>
+        <v>78788</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -6014,43 +6014,38 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
-      <c r="M53" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="P53" t="inlineStr">
         <is>
           <t>Härkämäck, Dlr</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>459609</v>
+        <v>459616</v>
       </c>
       <c r="R53" t="n">
-        <v>6807987</v>
+        <v>6808044</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6102,14 +6097,14 @@
       </c>
       <c r="AX53" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Anders Heggestad, Håkan Thenander, lennart karlsson, Niklas Rehn</t>
+          <t>Philipp Weiss, Anders Heggestad, lennart karlsson, Håkan Thenander, Niklas Rehn</t>
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>123920730</v>
+        <v>123920727</v>
       </c>
       <c r="B54" t="n">
         <v>78788</v>
@@ -6149,10 +6144,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>459590</v>
+        <v>459542</v>
       </c>
       <c r="R54" t="n">
-        <v>6808062</v>
+        <v>6808123</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6211,10 +6206,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>123920540</v>
+        <v>123920728</v>
       </c>
       <c r="B55" t="n">
-        <v>78525</v>
+        <v>78788</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -6227,21 +6222,21 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -6251,10 +6246,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>459589</v>
+        <v>459539</v>
       </c>
       <c r="R55" t="n">
-        <v>6807980</v>
+        <v>6808073</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6313,10 +6308,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>123920731</v>
+        <v>123920540</v>
       </c>
       <c r="B56" t="n">
-        <v>78788</v>
+        <v>78525</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -6329,21 +6324,21 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6353,10 +6348,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>459608</v>
+        <v>459589</v>
       </c>
       <c r="R56" t="n">
-        <v>6808066</v>
+        <v>6807980</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6415,10 +6410,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>123920419</v>
+        <v>123920442</v>
       </c>
       <c r="B57" t="n">
-        <v>90990</v>
+        <v>56700</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -6427,38 +6422,43 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>1202</v>
+        <v>100138</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
+      <c r="M57" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="P57" t="inlineStr">
         <is>
           <t>Härkämäck, Dlr</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>459603</v>
+        <v>459593</v>
       </c>
       <c r="R57" t="n">
-        <v>6807965</v>
+        <v>6807978</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6517,10 +6517,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>123920427</v>
+        <v>123920729</v>
       </c>
       <c r="B58" t="n">
-        <v>57491</v>
+        <v>78788</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
@@ -6533,39 +6533,34 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
-      <c r="M58" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
       <c r="P58" t="inlineStr">
         <is>
           <t>Härkämäck, Dlr</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>459571</v>
+        <v>459566</v>
       </c>
       <c r="R58" t="n">
-        <v>6808057</v>
+        <v>6808068</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6617,17 +6612,17 @@
       </c>
       <c r="AX58" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Anders Heggestad, Håkan Thenander, lennart karlsson, Niklas Rehn</t>
+          <t>Philipp Weiss, Anders Heggestad, lennart karlsson, Håkan Thenander, Niklas Rehn</t>
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>123920734</v>
+        <v>123920419</v>
       </c>
       <c r="B59" t="n">
-        <v>78788</v>
+        <v>90990</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
@@ -6640,21 +6635,21 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -6664,10 +6659,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>459613</v>
+        <v>459603</v>
       </c>
       <c r="R59" t="n">
-        <v>6807959</v>
+        <v>6807965</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6719,14 +6714,14 @@
       </c>
       <c r="AX59" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Anders Heggestad, lennart karlsson, Håkan Thenander, Niklas Rehn</t>
+          <t>Philipp Weiss, Anders Heggestad, Håkan Thenander, lennart karlsson, Niklas Rehn</t>
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>123920729</v>
+        <v>123920733</v>
       </c>
       <c r="B60" t="n">
         <v>78788</v>
@@ -6766,10 +6761,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>459566</v>
+        <v>459589</v>
       </c>
       <c r="R60" t="n">
-        <v>6808068</v>
+        <v>6807980</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6828,10 +6823,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>123920728</v>
+        <v>123920399</v>
       </c>
       <c r="B61" t="n">
-        <v>78788</v>
+        <v>79377</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
@@ -6844,21 +6839,21 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>6425</v>
+        <v>229821</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -6868,10 +6863,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>459539</v>
+        <v>459591</v>
       </c>
       <c r="R61" t="n">
-        <v>6808073</v>
+        <v>6808065</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -6923,17 +6918,17 @@
       </c>
       <c r="AX61" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Anders Heggestad, lennart karlsson, Håkan Thenander, Niklas Rehn</t>
+          <t>Philipp Weiss, Anders Heggestad, Håkan Thenander, lennart karlsson, Niklas Rehn</t>
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>123920442</v>
+        <v>123920731</v>
       </c>
       <c r="B62" t="n">
-        <v>56700</v>
+        <v>78788</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
@@ -6942,43 +6937,38 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
-      <c r="M62" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="P62" t="inlineStr">
         <is>
           <t>Härkämäck, Dlr</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>459593</v>
+        <v>459608</v>
       </c>
       <c r="R62" t="n">
-        <v>6807978</v>
+        <v>6808066</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -7030,17 +7020,17 @@
       </c>
       <c r="AX62" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Anders Heggestad, Håkan Thenander, lennart karlsson, Niklas Rehn</t>
+          <t>Philipp Weiss, Anders Heggestad, lennart karlsson, Håkan Thenander, Niklas Rehn</t>
         </is>
       </c>
       <c r="AY62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>123920727</v>
+        <v>123920441</v>
       </c>
       <c r="B63" t="n">
-        <v>78788</v>
+        <v>56700</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
@@ -7049,38 +7039,43 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
+      <c r="M63" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="P63" t="inlineStr">
         <is>
           <t>Härkämäck, Dlr</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>459542</v>
+        <v>459609</v>
       </c>
       <c r="R63" t="n">
-        <v>6808123</v>
+        <v>6807987</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -7132,7 +7127,7 @@
       </c>
       <c r="AX63" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Anders Heggestad, lennart karlsson, Håkan Thenander, Niklas Rehn</t>
+          <t>Philipp Weiss, Anders Heggestad, Håkan Thenander, lennart karlsson, Niklas Rehn</t>
         </is>
       </c>
       <c r="AY63" t="inlineStr"/>
@@ -7241,10 +7236,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>123920399</v>
+        <v>123920427</v>
       </c>
       <c r="B65" t="n">
-        <v>79377</v>
+        <v>57491</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
@@ -7257,34 +7252,39 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>229821</v>
+        <v>100109</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
+      <c r="M65" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="P65" t="inlineStr">
         <is>
           <t>Härkämäck, Dlr</t>
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>459591</v>
+        <v>459571</v>
       </c>
       <c r="R65" t="n">
-        <v>6808065</v>
+        <v>6808057</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7343,7 +7343,7 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>123920732</v>
+        <v>123920734</v>
       </c>
       <c r="B66" t="n">
         <v>78788</v>
@@ -7383,10 +7383,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>459616</v>
+        <v>459613</v>
       </c>
       <c r="R66" t="n">
-        <v>6808044</v>
+        <v>6807959</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7445,7 +7445,7 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>123920733</v>
+        <v>123920730</v>
       </c>
       <c r="B67" t="n">
         <v>78788</v>
@@ -7485,10 +7485,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>459589</v>
+        <v>459590</v>
       </c>
       <c r="R67" t="n">
-        <v>6807980</v>
+        <v>6808062</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>

--- a/artfynd/A 61327-2022 artfynd.xlsx
+++ b/artfynd/A 61327-2022 artfynd.xlsx
@@ -3392,10 +3392,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>123831065</v>
+        <v>123834890</v>
       </c>
       <c r="B28" t="n">
-        <v>78788</v>
+        <v>78867</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3408,37 +3408,37 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6425</v>
+        <v>864</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Lynge) Ahti</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Andljusbäcken, Andljusbäcken, Dlr</t>
+          <t>Härkämäck, Härkämäck, Dlr</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>459425</v>
+        <v>459427</v>
       </c>
       <c r="R28" t="n">
-        <v>6808084</v>
+        <v>6808130</v>
       </c>
       <c r="S28" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3494,10 +3494,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>123834890</v>
+        <v>123831065</v>
       </c>
       <c r="B29" t="n">
-        <v>78867</v>
+        <v>78788</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3510,37 +3510,37 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>864</v>
+        <v>6425</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Knottrig blåslav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Hypogymnia bitteri</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Lynge) Ahti</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Härkämäck, Härkämäck, Dlr</t>
+          <t>Andljusbäcken, Andljusbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>459427</v>
+        <v>459425</v>
       </c>
       <c r="R29" t="n">
-        <v>6808130</v>
+        <v>6808084</v>
       </c>
       <c r="S29" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -4218,10 +4218,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>123828783</v>
+        <v>123828882</v>
       </c>
       <c r="B36" t="n">
-        <v>78788</v>
+        <v>78820</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4234,21 +4234,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4258,10 +4258,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>459611</v>
+        <v>459600</v>
       </c>
       <c r="R36" t="n">
-        <v>6808048</v>
+        <v>6808030</v>
       </c>
       <c r="S36" t="n">
         <v>20</v>
@@ -4320,10 +4320,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>123828882</v>
+        <v>123828783</v>
       </c>
       <c r="B37" t="n">
-        <v>78820</v>
+        <v>78788</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4336,21 +4336,21 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4360,10 +4360,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>459600</v>
+        <v>459611</v>
       </c>
       <c r="R37" t="n">
-        <v>6808030</v>
+        <v>6808048</v>
       </c>
       <c r="S37" t="n">
         <v>20</v>
@@ -4942,7 +4942,7 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>123831277</v>
+        <v>123829310</v>
       </c>
       <c r="B43" t="n">
         <v>57507</v>
@@ -4978,7 +4978,7 @@
       <c r="I43" t="inlineStr"/>
       <c r="M43" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P43" t="inlineStr">
@@ -4987,10 +4987,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>459389</v>
+        <v>459586</v>
       </c>
       <c r="R43" t="n">
-        <v>6808070</v>
+        <v>6807981</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5023,11 +5023,6 @@
       <c r="AA43" t="inlineStr">
         <is>
           <t>2025-04-07</t>
-        </is>
-      </c>
-      <c r="AC43" t="inlineStr">
-        <is>
-          <t>Miljöbild.</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5054,10 +5049,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>123829982</v>
+        <v>123831277</v>
       </c>
       <c r="B44" t="n">
-        <v>77716</v>
+        <v>57507</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5070,37 +5065,42 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6487</v>
+        <v>100049</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Blågrå svartspik</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Chaenothecopsis fennica</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Laurila) Tibell</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P44" t="inlineStr">
         <is>
-          <t>Andljusbäcken, Andljusbäcken, Dlr</t>
+          <t>Härkämäck, Dlr</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>459432</v>
+        <v>459389</v>
       </c>
       <c r="R44" t="n">
-        <v>6807989</v>
+        <v>6808070</v>
       </c>
       <c r="S44" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T44" t="inlineStr">
         <is>
@@ -5130,6 +5130,11 @@
       <c r="AA44" t="inlineStr">
         <is>
           <t>2025-04-07</t>
+        </is>
+      </c>
+      <c r="AC44" t="inlineStr">
+        <is>
+          <t>Miljöbild.</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5144,22 +5149,22 @@
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>123829918</v>
+        <v>123829982</v>
       </c>
       <c r="B45" t="n">
-        <v>78524</v>
+        <v>77716</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5172,21 +5177,21 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6446</v>
+        <v>6487</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Blågrå svartspik</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Chaenothecopsis fennica</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Laurila) Tibell</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5196,10 +5201,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>459424</v>
+        <v>459432</v>
       </c>
       <c r="R45" t="n">
-        <v>6807998</v>
+        <v>6807989</v>
       </c>
       <c r="S45" t="n">
         <v>20</v>
@@ -5258,10 +5263,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>123834220</v>
+        <v>123829918</v>
       </c>
       <c r="B46" t="n">
-        <v>78788</v>
+        <v>78524</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5274,37 +5279,37 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
-          <t>Andljusen, Dlr</t>
+          <t>Andljusbäcken, Andljusbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>459325</v>
+        <v>459424</v>
       </c>
       <c r="R46" t="n">
-        <v>6808176</v>
+        <v>6807998</v>
       </c>
       <c r="S46" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T46" t="inlineStr">
         <is>
@@ -5334,11 +5339,6 @@
       <c r="AA46" t="inlineStr">
         <is>
           <t>2025-04-07</t>
-        </is>
-      </c>
-      <c r="AC46" t="inlineStr">
-        <is>
-          <t>I synfält, radie av ca 50 meter. Miljöbild.</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5353,22 +5353,22 @@
       <c r="AT46" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX46" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>123829310</v>
+        <v>123834220</v>
       </c>
       <c r="B47" t="n">
-        <v>57507</v>
+        <v>78788</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5381,39 +5381,34 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
-      <c r="M47" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P47" t="inlineStr">
         <is>
-          <t>Härkämäck, Dlr</t>
+          <t>Andljusen, Dlr</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>459586</v>
+        <v>459325</v>
       </c>
       <c r="R47" t="n">
-        <v>6807981</v>
+        <v>6808176</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5446,6 +5441,11 @@
       <c r="AA47" t="inlineStr">
         <is>
           <t>2025-04-07</t>
+        </is>
+      </c>
+      <c r="AC47" t="inlineStr">
+        <is>
+          <t>I synfält, radie av ca 50 meter. Miljöbild.</t>
         </is>
       </c>
       <c r="AD47" t="b">

--- a/artfynd/A 61327-2022 artfynd.xlsx
+++ b/artfynd/A 61327-2022 artfynd.xlsx
@@ -782,10 +782,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123828044</v>
+        <v>123830009</v>
       </c>
       <c r="B3" t="n">
-        <v>78788</v>
+        <v>78524</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -798,21 +798,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -822,10 +822,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>459681</v>
+        <v>459480</v>
       </c>
       <c r="R3" t="n">
-        <v>6808072</v>
+        <v>6808013</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -862,7 +862,7 @@
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>Garnlav i synfältet i en radie av ca 50 meter. Miljöbild.</t>
+          <t>Miljöbild.</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -889,7 +889,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123828742</v>
+        <v>123835135</v>
       </c>
       <c r="B4" t="n">
         <v>78788</v>
@@ -925,17 +925,17 @@
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Andljusbäcken, Andljusbäcken, Dlr</t>
+          <t>Härkämäck, Dlr</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>459612</v>
+        <v>459455</v>
       </c>
       <c r="R4" t="n">
-        <v>6808068</v>
+        <v>6808164</v>
       </c>
       <c r="S4" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -965,6 +965,11 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2025-04-07</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Garnlav i en radie av ca 50 meter, synfältet. Miljöbild.</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -979,22 +984,22 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123834183</v>
+        <v>123829394</v>
       </c>
       <c r="B5" t="n">
-        <v>78788</v>
+        <v>77716</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1007,37 +1012,37 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>6487</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Blågrå svartspik</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenothecopsis fennica</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Laurila) Tibell</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Andljusbäcken, Andljusbäcken, Dlr</t>
+          <t>Härkämäck, Dlr</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>459373</v>
+        <v>459586</v>
       </c>
       <c r="R5" t="n">
-        <v>6808222</v>
+        <v>6807981</v>
       </c>
       <c r="S5" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1081,22 +1086,22 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>123833729</v>
+        <v>123831244</v>
       </c>
       <c r="B6" t="n">
-        <v>78525</v>
+        <v>78788</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1109,37 +1114,37 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Andljusen, Dlr</t>
+          <t>Andljusbäcken, Andljusbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>459286</v>
+        <v>459393</v>
       </c>
       <c r="R6" t="n">
-        <v>6808090</v>
+        <v>6808027</v>
       </c>
       <c r="S6" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1169,11 +1174,6 @@
       <c r="AA6" t="inlineStr">
         <is>
           <t>2025-04-07</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>Miljöbild.</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1188,22 +1188,22 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>123829197</v>
+        <v>123834966</v>
       </c>
       <c r="B7" t="n">
-        <v>78525</v>
+        <v>57512</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1212,41 +1212,46 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>228912</v>
+        <v>100110</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Gråspett</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Picus canus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>J.F. Gmelin, 1788</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Andljusbäcken, Andljusbäcken, Dlr</t>
+          <t>Härkämäck, Dlr</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>459611</v>
+        <v>459399</v>
       </c>
       <c r="R7" t="n">
-        <v>6807987</v>
+        <v>6808189</v>
       </c>
       <c r="S7" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1276,6 +1281,11 @@
       <c r="AA7" t="inlineStr">
         <is>
           <t>2025-04-07</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Förbiflygande.</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1290,19 +1300,19 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>123831067</v>
+        <v>123833841</v>
       </c>
       <c r="B8" t="n">
         <v>78788</v>
@@ -1338,17 +1348,17 @@
       <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Härkämäck, Dlr</t>
+          <t>Härkämäck, Härkämäck, Dlr</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>459439</v>
+        <v>459300</v>
       </c>
       <c r="R8" t="n">
-        <v>6808067</v>
+        <v>6808144</v>
       </c>
       <c r="S8" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1378,11 +1388,6 @@
       <c r="AA8" t="inlineStr">
         <is>
           <t>2025-04-07</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>Synligt i en radie av ca 50 meter. Miljöbild.</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1397,22 +1402,22 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>123834641</v>
+        <v>123827957</v>
       </c>
       <c r="B9" t="n">
-        <v>78788</v>
+        <v>78524</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1425,34 +1430,34 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Härkämäck, Härkämäck, Dlr</t>
+          <t>Andljusbäcken, Andljusbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>459405</v>
+        <v>459664</v>
       </c>
       <c r="R9" t="n">
-        <v>6808172</v>
+        <v>6808079</v>
       </c>
       <c r="S9" t="n">
         <v>20</v>
@@ -1511,10 +1516,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>123830920</v>
+        <v>123834890</v>
       </c>
       <c r="B10" t="n">
-        <v>78433</v>
+        <v>78867</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1527,34 +1532,34 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>353</v>
+        <v>864</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Lynge) Ahti</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Andljusbäcken, Andljusbäcken, Dlr</t>
+          <t>Härkämäck, Härkämäck, Dlr</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>459462</v>
+        <v>459427</v>
       </c>
       <c r="R10" t="n">
-        <v>6808078</v>
+        <v>6808130</v>
       </c>
       <c r="S10" t="n">
         <v>20</v>
@@ -1613,10 +1618,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>123834650</v>
+        <v>123834630</v>
       </c>
       <c r="B11" t="n">
-        <v>78525</v>
+        <v>57512</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1625,38 +1630,38 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>228912</v>
+        <v>100110</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Gråspett</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Picus canus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>J.F. Gmelin, 1788</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Härkämäck, Dlr</t>
+          <t>Härkämäck, Härkämäck, Dlr</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>459399</v>
+        <v>459408</v>
       </c>
       <c r="R11" t="n">
-        <v>6808189</v>
+        <v>6808198</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1693,7 +1698,7 @@
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>Miljöbild</t>
+          <t>Förbiflygande.</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1708,22 +1713,22 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>123831467</v>
+        <v>123829941</v>
       </c>
       <c r="B12" t="n">
-        <v>79377</v>
+        <v>78525</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1736,34 +1741,34 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>229821</v>
+        <v>228912</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Härkämäck, Härkämäck, Dlr</t>
+          <t>Härkämäck, Dlr</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>459290</v>
+        <v>459480</v>
       </c>
       <c r="R12" t="n">
-        <v>6808098</v>
+        <v>6808013</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1798,6 +1803,11 @@
           <t>2025-04-07</t>
         </is>
       </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Miljöbild.</t>
+        </is>
+      </c>
       <c r="AD12" t="b">
         <v>0</v>
       </c>
@@ -1810,22 +1820,22 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Niklas Rehn</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Niklas Rehn</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>123834998</v>
+        <v>123829275</v>
       </c>
       <c r="B13" t="n">
-        <v>79377</v>
+        <v>78525</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1838,34 +1848,34 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>229821</v>
+        <v>228912</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Härkämäck, Härkämäck, Dlr</t>
+          <t>Andljusbäcken, Andljusbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>459437</v>
+        <v>459544</v>
       </c>
       <c r="R13" t="n">
-        <v>6808171</v>
+        <v>6807989</v>
       </c>
       <c r="S13" t="n">
         <v>20</v>
@@ -1924,10 +1934,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>123829246</v>
+        <v>123833754</v>
       </c>
       <c r="B14" t="n">
-        <v>78788</v>
+        <v>92271</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1936,41 +1946,41 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Härkämäck, Dlr</t>
+          <t>Härkämäck, Härkämäck, Dlr</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>459586</v>
+        <v>459290</v>
       </c>
       <c r="R14" t="n">
-        <v>6807981</v>
+        <v>6808093</v>
       </c>
       <c r="S14" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2000,11 +2010,6 @@
       <c r="AA14" t="inlineStr">
         <is>
           <t>2025-04-07</t>
-        </is>
-      </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>Som vanligt garnlav i omgivningen. Miljöbilder.</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2019,19 +2024,19 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>123831244</v>
+        <v>123828742</v>
       </c>
       <c r="B15" t="n">
         <v>78788</v>
@@ -2071,10 +2076,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>459393</v>
+        <v>459612</v>
       </c>
       <c r="R15" t="n">
-        <v>6808027</v>
+        <v>6808068</v>
       </c>
       <c r="S15" t="n">
         <v>20</v>
@@ -2133,10 +2138,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>123829275</v>
+        <v>123828739</v>
       </c>
       <c r="B16" t="n">
-        <v>78525</v>
+        <v>56700</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2145,41 +2150,46 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>228912</v>
+        <v>100138</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Andljusbäcken, Andljusbäcken, Dlr</t>
+          <t>Härkämäck, Dlr</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>459544</v>
+        <v>459636</v>
       </c>
       <c r="R16" t="n">
-        <v>6807989</v>
+        <v>6808042</v>
       </c>
       <c r="S16" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2223,22 +2233,22 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>123834966</v>
+        <v>123834567</v>
       </c>
       <c r="B17" t="n">
-        <v>57512</v>
+        <v>79377</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2247,33 +2257,28 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100110</v>
+        <v>229821</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Gråspett</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Picus canus</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>J.F. Gmelin, 1788</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="P17" t="inlineStr">
         <is>
           <t>Härkämäck, Dlr</t>
@@ -2320,7 +2325,7 @@
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>Förbiflygande.</t>
+          <t>Miljöbild.</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2347,7 +2352,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>123833814</v>
+        <v>123834650</v>
       </c>
       <c r="B18" t="n">
         <v>78525</v>
@@ -2383,17 +2388,17 @@
       <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Härkämäck, Härkämäck, Dlr</t>
+          <t>Härkämäck, Dlr</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>459293</v>
+        <v>459399</v>
       </c>
       <c r="R18" t="n">
-        <v>6808123</v>
+        <v>6808189</v>
       </c>
       <c r="S18" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2423,6 +2428,11 @@
       <c r="AA18" t="inlineStr">
         <is>
           <t>2025-04-07</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>Miljöbild</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2437,22 +2447,22 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>123829712</v>
+        <v>123829889</v>
       </c>
       <c r="B19" t="n">
-        <v>90990</v>
+        <v>78525</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2465,21 +2475,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>1202</v>
+        <v>228912</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2489,10 +2499,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>459573</v>
+        <v>459494</v>
       </c>
       <c r="R19" t="n">
-        <v>6808047</v>
+        <v>6807997</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2525,6 +2535,11 @@
       <c r="AA19" t="inlineStr">
         <is>
           <t>2025-04-07</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>Miljöbild.</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2551,10 +2566,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>123831578</v>
+        <v>123834006</v>
       </c>
       <c r="B20" t="n">
-        <v>74879</v>
+        <v>78525</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2567,37 +2582,37 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6440</v>
+        <v>228912</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Andljusbäcken, Andljusbäcken, Dlr</t>
+          <t>Härkämäck, Härkämäck, Dlr</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>459287</v>
+        <v>459326</v>
       </c>
       <c r="R20" t="n">
-        <v>6808008</v>
+        <v>6808188</v>
       </c>
       <c r="S20" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2641,22 +2656,22 @@
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>123829941</v>
+        <v>123829982</v>
       </c>
       <c r="B21" t="n">
-        <v>78525</v>
+        <v>77716</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2669,37 +2684,37 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>228912</v>
+        <v>6487</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Blågrå svartspik</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Chaenothecopsis fennica</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Laurila) Tibell</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Härkämäck, Dlr</t>
+          <t>Andljusbäcken, Andljusbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>459480</v>
+        <v>459432</v>
       </c>
       <c r="R21" t="n">
-        <v>6808013</v>
+        <v>6807989</v>
       </c>
       <c r="S21" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2729,11 +2744,6 @@
       <c r="AA21" t="inlineStr">
         <is>
           <t>2025-04-07</t>
-        </is>
-      </c>
-      <c r="AC21" t="inlineStr">
-        <is>
-          <t>Miljöbild.</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2748,22 +2758,22 @@
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>123834630</v>
+        <v>123829197</v>
       </c>
       <c r="B22" t="n">
-        <v>57512</v>
+        <v>78525</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2772,41 +2782,41 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>100110</v>
+        <v>228912</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Gråspett</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Picus canus</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>J.F. Gmelin, 1788</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Härkämäck, Härkämäck, Dlr</t>
+          <t>Andljusbäcken, Andljusbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>459408</v>
+        <v>459611</v>
       </c>
       <c r="R22" t="n">
-        <v>6808198</v>
+        <v>6807987</v>
       </c>
       <c r="S22" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -2836,11 +2846,6 @@
       <c r="AA22" t="inlineStr">
         <is>
           <t>2025-04-07</t>
-        </is>
-      </c>
-      <c r="AC22" t="inlineStr">
-        <is>
-          <t>Förbiflygande.</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2855,22 +2860,22 @@
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>123834034</v>
+        <v>123829879</v>
       </c>
       <c r="B23" t="n">
-        <v>57507</v>
+        <v>78788</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2883,42 +2888,37 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
-      <c r="M23" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Andljusen, Dlr</t>
+          <t>Andljusbäcken, Andljusbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>459325</v>
+        <v>459488</v>
       </c>
       <c r="R23" t="n">
-        <v>6808176</v>
+        <v>6807974</v>
       </c>
       <c r="S23" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -2948,11 +2948,6 @@
       <c r="AA23" t="inlineStr">
         <is>
           <t>2025-04-07</t>
-        </is>
-      </c>
-      <c r="AC23" t="inlineStr">
-        <is>
-          <t>Miljöbild.</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -2967,22 +2962,22 @@
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>123829879</v>
+        <v>123834998</v>
       </c>
       <c r="B24" t="n">
-        <v>78788</v>
+        <v>79377</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -2995,34 +2990,34 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6425</v>
+        <v>229821</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Andljusbäcken, Andljusbäcken, Dlr</t>
+          <t>Härkämäck, Härkämäck, Dlr</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>459488</v>
+        <v>459437</v>
       </c>
       <c r="R24" t="n">
-        <v>6807974</v>
+        <v>6808171</v>
       </c>
       <c r="S24" t="n">
         <v>20</v>
@@ -3081,10 +3076,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>123833917</v>
+        <v>123831065</v>
       </c>
       <c r="B25" t="n">
-        <v>78525</v>
+        <v>78788</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3097,21 +3092,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3121,13 +3116,13 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>459292</v>
+        <v>459425</v>
       </c>
       <c r="R25" t="n">
-        <v>6808184</v>
+        <v>6808084</v>
       </c>
       <c r="S25" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3183,10 +3178,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>123829889</v>
+        <v>123831467</v>
       </c>
       <c r="B26" t="n">
-        <v>78525</v>
+        <v>79377</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3199,34 +3194,34 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>228912</v>
+        <v>229821</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Härkämäck, Dlr</t>
+          <t>Härkämäck, Härkämäck, Dlr</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>459494</v>
+        <v>459290</v>
       </c>
       <c r="R26" t="n">
-        <v>6807997</v>
+        <v>6808098</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3261,11 +3256,6 @@
           <t>2025-04-07</t>
         </is>
       </c>
-      <c r="AC26" t="inlineStr">
-        <is>
-          <t>Miljöbild.</t>
-        </is>
-      </c>
       <c r="AD26" t="b">
         <v>0</v>
       </c>
@@ -3278,22 +3268,22 @@
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Niklas Rehn</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Niklas Rehn</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>123829632</v>
+        <v>123834183</v>
       </c>
       <c r="B27" t="n">
-        <v>91277</v>
+        <v>78788</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3306,37 +3296,37 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>658</v>
+        <v>6425</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Härkämäck, Dlr</t>
+          <t>Andljusbäcken, Andljusbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>459573</v>
+        <v>459373</v>
       </c>
       <c r="R27" t="n">
-        <v>6808047</v>
+        <v>6808222</v>
       </c>
       <c r="S27" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3380,22 +3370,22 @@
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>123834890</v>
+        <v>123834641</v>
       </c>
       <c r="B28" t="n">
-        <v>78867</v>
+        <v>78788</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3408,21 +3398,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>864</v>
+        <v>6425</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Knottrig blåslav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Hypogymnia bitteri</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Lynge) Ahti</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3432,10 +3422,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>459427</v>
+        <v>459405</v>
       </c>
       <c r="R28" t="n">
-        <v>6808130</v>
+        <v>6808172</v>
       </c>
       <c r="S28" t="n">
         <v>20</v>
@@ -3494,7 +3484,7 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>123831065</v>
+        <v>123829246</v>
       </c>
       <c r="B29" t="n">
         <v>78788</v>
@@ -3530,14 +3520,14 @@
       <c r="I29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Andljusbäcken, Andljusbäcken, Dlr</t>
+          <t>Härkämäck, Dlr</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>459425</v>
+        <v>459586</v>
       </c>
       <c r="R29" t="n">
-        <v>6808084</v>
+        <v>6807981</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3572,6 +3562,11 @@
           <t>2025-04-07</t>
         </is>
       </c>
+      <c r="AC29" t="inlineStr">
+        <is>
+          <t>Som vanligt garnlav i omgivningen. Miljöbilder.</t>
+        </is>
+      </c>
       <c r="AD29" t="b">
         <v>0</v>
       </c>
@@ -3584,22 +3579,22 @@
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>123835432</v>
+        <v>123834034</v>
       </c>
       <c r="B30" t="n">
-        <v>78788</v>
+        <v>57507</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3612,34 +3607,39 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Härkämäck, Dlr</t>
+          <t>Andljusen, Dlr</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>459524</v>
+        <v>459325</v>
       </c>
       <c r="R30" t="n">
-        <v>6808114</v>
+        <v>6808176</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3676,7 +3676,7 @@
       </c>
       <c r="AC30" t="inlineStr">
         <is>
-          <t>Garnlav i alla riktningar, ca 50 meter i radie. Miljöbild.</t>
+          <t>Miljöbild.</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3703,10 +3703,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>123830162</v>
+        <v>123835432</v>
       </c>
       <c r="B31" t="n">
-        <v>78172</v>
+        <v>78788</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3719,21 +3719,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6437</v>
+        <v>6425</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3743,10 +3743,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>459480</v>
+        <v>459524</v>
       </c>
       <c r="R31" t="n">
-        <v>6808013</v>
+        <v>6808114</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3783,7 +3783,7 @@
       </c>
       <c r="AC31" t="inlineStr">
         <is>
-          <t>Miljöbild.</t>
+          <t>Garnlav i alla riktningar, ca 50 meter i radie. Miljöbild.</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3810,7 +3810,7 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>123827957</v>
+        <v>123829918</v>
       </c>
       <c r="B32" t="n">
         <v>78524</v>
@@ -3850,10 +3850,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>459664</v>
+        <v>459424</v>
       </c>
       <c r="R32" t="n">
-        <v>6808079</v>
+        <v>6807998</v>
       </c>
       <c r="S32" t="n">
         <v>20</v>
@@ -3912,10 +3912,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>123834006</v>
+        <v>123831067</v>
       </c>
       <c r="B33" t="n">
-        <v>78525</v>
+        <v>78788</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -3928,37 +3928,37 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Härkämäck, Härkämäck, Dlr</t>
+          <t>Härkämäck, Dlr</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>459326</v>
+        <v>459439</v>
       </c>
       <c r="R33" t="n">
-        <v>6808188</v>
+        <v>6808067</v>
       </c>
       <c r="S33" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -3988,6 +3988,11 @@
       <c r="AA33" t="inlineStr">
         <is>
           <t>2025-04-07</t>
+        </is>
+      </c>
+      <c r="AC33" t="inlineStr">
+        <is>
+          <t>Synligt i en radie av ca 50 meter. Miljöbild.</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4002,12 +4007,12 @@
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
@@ -4116,10 +4121,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>123831097</v>
+        <v>123829102</v>
       </c>
       <c r="B35" t="n">
-        <v>79377</v>
+        <v>78788</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4132,21 +4137,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>229821</v>
+        <v>6425</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4156,10 +4161,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>459402</v>
+        <v>459666</v>
       </c>
       <c r="R35" t="n">
-        <v>6808072</v>
+        <v>6807990</v>
       </c>
       <c r="S35" t="n">
         <v>20</v>
@@ -4218,10 +4223,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>123828882</v>
+        <v>123833814</v>
       </c>
       <c r="B36" t="n">
-        <v>78820</v>
+        <v>78525</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4234,37 +4239,37 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>185</v>
+        <v>228912</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Andljusbäcken, Andljusbäcken, Dlr</t>
+          <t>Härkämäck, Härkämäck, Dlr</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>459600</v>
+        <v>459293</v>
       </c>
       <c r="R36" t="n">
-        <v>6808030</v>
+        <v>6808123</v>
       </c>
       <c r="S36" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -4308,22 +4313,22 @@
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>123828783</v>
+        <v>123833729</v>
       </c>
       <c r="B37" t="n">
-        <v>78788</v>
+        <v>78525</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4336,37 +4341,37 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
-          <t>Andljusbäcken, Andljusbäcken, Dlr</t>
+          <t>Andljusen, Dlr</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>459611</v>
+        <v>459286</v>
       </c>
       <c r="R37" t="n">
-        <v>6808048</v>
+        <v>6808090</v>
       </c>
       <c r="S37" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -4396,6 +4401,11 @@
       <c r="AA37" t="inlineStr">
         <is>
           <t>2025-04-07</t>
+        </is>
+      </c>
+      <c r="AC37" t="inlineStr">
+        <is>
+          <t>Miljöbild.</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4410,22 +4420,22 @@
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>123834567</v>
+        <v>123828044</v>
       </c>
       <c r="B38" t="n">
-        <v>79377</v>
+        <v>78788</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4438,21 +4448,21 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>229821</v>
+        <v>6425</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4462,10 +4472,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>459399</v>
+        <v>459681</v>
       </c>
       <c r="R38" t="n">
-        <v>6808189</v>
+        <v>6808072</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4502,7 +4512,7 @@
       </c>
       <c r="AC38" t="inlineStr">
         <is>
-          <t>Miljöbild.</t>
+          <t>Garnlav i synfältet i en radie av ca 50 meter. Miljöbild.</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4529,10 +4539,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>123829205</v>
+        <v>123829632</v>
       </c>
       <c r="B39" t="n">
-        <v>78524</v>
+        <v>91277</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4545,37 +4555,37 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6446</v>
+        <v>658</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
-          <t>Andljusbäcken, Andljusbäcken, Dlr</t>
+          <t>Härkämäck, Dlr</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>459611</v>
+        <v>459573</v>
       </c>
       <c r="R39" t="n">
-        <v>6807987</v>
+        <v>6808047</v>
       </c>
       <c r="S39" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
@@ -4619,22 +4629,22 @@
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>123829394</v>
+        <v>123828608</v>
       </c>
       <c r="B40" t="n">
-        <v>77716</v>
+        <v>78788</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -4647,21 +4657,21 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6487</v>
+        <v>6425</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Blågrå svartspik</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Chaenothecopsis fennica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Laurila) Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4671,10 +4681,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>459586</v>
+        <v>459636</v>
       </c>
       <c r="R40" t="n">
-        <v>6807981</v>
+        <v>6808042</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4707,6 +4717,11 @@
       <c r="AA40" t="inlineStr">
         <is>
           <t>2025-04-07</t>
+        </is>
+      </c>
+      <c r="AC40" t="inlineStr">
+        <is>
+          <t>Garnlav i synfältet i en radie av ca 50 meter. Miljöbilder.</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4733,7 +4748,7 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>123829102</v>
+        <v>123834220</v>
       </c>
       <c r="B41" t="n">
         <v>78788</v>
@@ -4769,17 +4784,17 @@
       <c r="I41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
-          <t>Andljusbäcken, Andljusbäcken, Dlr</t>
+          <t>Andljusen, Dlr</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>459666</v>
+        <v>459325</v>
       </c>
       <c r="R41" t="n">
-        <v>6807990</v>
+        <v>6808176</v>
       </c>
       <c r="S41" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -4809,6 +4824,11 @@
       <c r="AA41" t="inlineStr">
         <is>
           <t>2025-04-07</t>
+        </is>
+      </c>
+      <c r="AC41" t="inlineStr">
+        <is>
+          <t>I synfält, radie av ca 50 meter. Miljöbild.</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -4823,22 +4843,22 @@
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>123835135</v>
+        <v>123830162</v>
       </c>
       <c r="B42" t="n">
-        <v>78788</v>
+        <v>78172</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -4851,21 +4871,21 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6425</v>
+        <v>6437</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4875,10 +4895,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>459455</v>
+        <v>459480</v>
       </c>
       <c r="R42" t="n">
-        <v>6808164</v>
+        <v>6808013</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4915,7 +4935,7 @@
       </c>
       <c r="AC42" t="inlineStr">
         <is>
-          <t>Garnlav i en radie av ca 50 meter, synfältet. Miljöbild.</t>
+          <t>Miljöbild.</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -4942,10 +4962,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>123829310</v>
+        <v>123833917</v>
       </c>
       <c r="B43" t="n">
-        <v>57507</v>
+        <v>78525</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -4958,42 +4978,37 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>100049</v>
+        <v>228912</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
-      <c r="M43" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P43" t="inlineStr">
         <is>
-          <t>Härkämäck, Dlr</t>
+          <t>Andljusbäcken, Andljusbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>459586</v>
+        <v>459292</v>
       </c>
       <c r="R43" t="n">
-        <v>6807981</v>
+        <v>6808184</v>
       </c>
       <c r="S43" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T43" t="inlineStr">
         <is>
@@ -5037,22 +5052,22 @@
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>123831277</v>
+        <v>123831578</v>
       </c>
       <c r="B44" t="n">
-        <v>57507</v>
+        <v>74879</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5065,42 +5080,37 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>100049</v>
+        <v>6440</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
-      <c r="M44" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P44" t="inlineStr">
         <is>
-          <t>Härkämäck, Dlr</t>
+          <t>Andljusbäcken, Andljusbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>459389</v>
+        <v>459287</v>
       </c>
       <c r="R44" t="n">
-        <v>6808070</v>
+        <v>6808008</v>
       </c>
       <c r="S44" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T44" t="inlineStr">
         <is>
@@ -5130,11 +5140,6 @@
       <c r="AA44" t="inlineStr">
         <is>
           <t>2025-04-07</t>
-        </is>
-      </c>
-      <c r="AC44" t="inlineStr">
-        <is>
-          <t>Miljöbild.</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5149,22 +5154,22 @@
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>123829982</v>
+        <v>123828882</v>
       </c>
       <c r="B45" t="n">
-        <v>77716</v>
+        <v>78820</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5177,21 +5182,21 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6487</v>
+        <v>185</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Blågrå svartspik</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Chaenothecopsis fennica</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Laurila) Tibell</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5201,10 +5206,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>459432</v>
+        <v>459600</v>
       </c>
       <c r="R45" t="n">
-        <v>6807989</v>
+        <v>6808030</v>
       </c>
       <c r="S45" t="n">
         <v>20</v>
@@ -5263,10 +5268,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>123829918</v>
+        <v>123829310</v>
       </c>
       <c r="B46" t="n">
-        <v>78524</v>
+        <v>57507</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5279,37 +5284,42 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>6446</v>
+        <v>100049</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P46" t="inlineStr">
         <is>
-          <t>Andljusbäcken, Andljusbäcken, Dlr</t>
+          <t>Härkämäck, Dlr</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>459424</v>
+        <v>459586</v>
       </c>
       <c r="R46" t="n">
-        <v>6807998</v>
+        <v>6807981</v>
       </c>
       <c r="S46" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T46" t="inlineStr">
         <is>
@@ -5353,19 +5363,19 @@
       <c r="AT46" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX46" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>123834220</v>
+        <v>123828783</v>
       </c>
       <c r="B47" t="n">
         <v>78788</v>
@@ -5401,17 +5411,17 @@
       <c r="I47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
-          <t>Andljusen, Dlr</t>
+          <t>Andljusbäcken, Andljusbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>459325</v>
+        <v>459611</v>
       </c>
       <c r="R47" t="n">
-        <v>6808176</v>
+        <v>6808048</v>
       </c>
       <c r="S47" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T47" t="inlineStr">
         <is>
@@ -5441,11 +5451,6 @@
       <c r="AA47" t="inlineStr">
         <is>
           <t>2025-04-07</t>
-        </is>
-      </c>
-      <c r="AC47" t="inlineStr">
-        <is>
-          <t>I synfält, radie av ca 50 meter. Miljöbild.</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5460,22 +5465,22 @@
       <c r="AT47" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX47" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>123828826</v>
+        <v>123829712</v>
       </c>
       <c r="B48" t="n">
-        <v>56700</v>
+        <v>90990</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -5484,43 +5489,38 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>100138</v>
+        <v>1202</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
-      <c r="M48" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="P48" t="inlineStr">
         <is>
           <t>Härkämäck, Dlr</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>459636</v>
+        <v>459573</v>
       </c>
       <c r="R48" t="n">
-        <v>6808042</v>
+        <v>6808047</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5553,11 +5553,6 @@
       <c r="AA48" t="inlineStr">
         <is>
           <t>2025-04-07</t>
-        </is>
-      </c>
-      <c r="AC48" t="inlineStr">
-        <is>
-          <t>Garnlav i bakgrund. Miljöbild.</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5584,10 +5579,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>123833841</v>
+        <v>123830920</v>
       </c>
       <c r="B49" t="n">
-        <v>78788</v>
+        <v>78433</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -5600,37 +5595,37 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
-          <t>Härkämäck, Härkämäck, Dlr</t>
+          <t>Andljusbäcken, Andljusbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>459300</v>
+        <v>459462</v>
       </c>
       <c r="R49" t="n">
-        <v>6808144</v>
+        <v>6808078</v>
       </c>
       <c r="S49" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T49" t="inlineStr">
         <is>
@@ -5674,22 +5669,22 @@
       <c r="AT49" t="inlineStr"/>
       <c r="AW49" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX49" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>123833754</v>
+        <v>123831277</v>
       </c>
       <c r="B50" t="n">
-        <v>92271</v>
+        <v>57507</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -5698,41 +5693,46 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>4364</v>
+        <v>100049</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
+      <c r="M50" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P50" t="inlineStr">
         <is>
-          <t>Härkämäck, Härkämäck, Dlr</t>
+          <t>Härkämäck, Dlr</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>459290</v>
+        <v>459389</v>
       </c>
       <c r="R50" t="n">
-        <v>6808093</v>
+        <v>6808070</v>
       </c>
       <c r="S50" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T50" t="inlineStr">
         <is>
@@ -5762,6 +5762,11 @@
       <c r="AA50" t="inlineStr">
         <is>
           <t>2025-04-07</t>
+        </is>
+      </c>
+      <c r="AC50" t="inlineStr">
+        <is>
+          <t>Miljöbild.</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -5776,22 +5781,22 @@
       <c r="AT50" t="inlineStr"/>
       <c r="AW50" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX50" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>123828608</v>
+        <v>123829205</v>
       </c>
       <c r="B51" t="n">
-        <v>78788</v>
+        <v>78524</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -5804,37 +5809,37 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
-          <t>Härkämäck, Dlr</t>
+          <t>Andljusbäcken, Andljusbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>459636</v>
+        <v>459611</v>
       </c>
       <c r="R51" t="n">
-        <v>6808042</v>
+        <v>6807987</v>
       </c>
       <c r="S51" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T51" t="inlineStr">
         <is>
@@ -5864,11 +5869,6 @@
       <c r="AA51" t="inlineStr">
         <is>
           <t>2025-04-07</t>
-        </is>
-      </c>
-      <c r="AC51" t="inlineStr">
-        <is>
-          <t>Garnlav i synfältet i en radie av ca 50 meter. Miljöbilder.</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -5883,22 +5883,22 @@
       <c r="AT51" t="inlineStr"/>
       <c r="AW51" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX51" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>123830009</v>
+        <v>123831097</v>
       </c>
       <c r="B52" t="n">
-        <v>78524</v>
+        <v>79377</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -5911,37 +5911,37 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>6446</v>
+        <v>229821</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
-          <t>Härkämäck, Dlr</t>
+          <t>Andljusbäcken, Andljusbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>459480</v>
+        <v>459402</v>
       </c>
       <c r="R52" t="n">
-        <v>6808013</v>
+        <v>6808072</v>
       </c>
       <c r="S52" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T52" t="inlineStr">
         <is>
@@ -5971,11 +5971,6 @@
       <c r="AA52" t="inlineStr">
         <is>
           <t>2025-04-07</t>
-        </is>
-      </c>
-      <c r="AC52" t="inlineStr">
-        <is>
-          <t>Miljöbild.</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -5990,22 +5985,22 @@
       <c r="AT52" t="inlineStr"/>
       <c r="AW52" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX52" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>123920732</v>
+        <v>123920427</v>
       </c>
       <c r="B53" t="n">
-        <v>78788</v>
+        <v>57491</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -6018,34 +6013,39 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
+      <c r="M53" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="P53" t="inlineStr">
         <is>
           <t>Härkämäck, Dlr</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>459616</v>
+        <v>459571</v>
       </c>
       <c r="R53" t="n">
-        <v>6808044</v>
+        <v>6808057</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6097,14 +6097,14 @@
       </c>
       <c r="AX53" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Anders Heggestad, lennart karlsson, Håkan Thenander, Niklas Rehn</t>
+          <t>Philipp Weiss, Anders Heggestad, Håkan Thenander, lennart karlsson, Niklas Rehn</t>
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>123920727</v>
+        <v>123920729</v>
       </c>
       <c r="B54" t="n">
         <v>78788</v>
@@ -6144,10 +6144,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>459542</v>
+        <v>459566</v>
       </c>
       <c r="R54" t="n">
-        <v>6808123</v>
+        <v>6808068</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6206,7 +6206,7 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>123920728</v>
+        <v>123920731</v>
       </c>
       <c r="B55" t="n">
         <v>78788</v>
@@ -6246,10 +6246,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>459539</v>
+        <v>459608</v>
       </c>
       <c r="R55" t="n">
-        <v>6808073</v>
+        <v>6808066</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6308,10 +6308,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>123920540</v>
+        <v>123920930</v>
       </c>
       <c r="B56" t="n">
-        <v>78525</v>
+        <v>78433</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -6324,21 +6324,21 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>228912</v>
+        <v>353</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6348,10 +6348,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>459589</v>
+        <v>459600</v>
       </c>
       <c r="R56" t="n">
-        <v>6807980</v>
+        <v>6807961</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6410,10 +6410,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>123920442</v>
+        <v>123920540</v>
       </c>
       <c r="B57" t="n">
-        <v>56700</v>
+        <v>78525</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -6422,43 +6422,38 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>100138</v>
+        <v>228912</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
-      <c r="M57" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="P57" t="inlineStr">
         <is>
           <t>Härkämäck, Dlr</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>459593</v>
+        <v>459589</v>
       </c>
       <c r="R57" t="n">
-        <v>6807978</v>
+        <v>6807980</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6510,14 +6505,14 @@
       </c>
       <c r="AX57" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Anders Heggestad, Håkan Thenander, lennart karlsson, Niklas Rehn</t>
+          <t>Philipp Weiss, Anders Heggestad, lennart karlsson, Håkan Thenander, Niklas Rehn</t>
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>123920729</v>
+        <v>123920734</v>
       </c>
       <c r="B58" t="n">
         <v>78788</v>
@@ -6557,10 +6552,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>459566</v>
+        <v>459613</v>
       </c>
       <c r="R58" t="n">
-        <v>6808068</v>
+        <v>6807959</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6619,10 +6614,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>123920419</v>
+        <v>123920728</v>
       </c>
       <c r="B59" t="n">
-        <v>90990</v>
+        <v>78788</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
@@ -6635,21 +6630,21 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -6659,10 +6654,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>459603</v>
+        <v>459539</v>
       </c>
       <c r="R59" t="n">
-        <v>6807965</v>
+        <v>6808073</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6714,14 +6709,14 @@
       </c>
       <c r="AX59" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Anders Heggestad, Håkan Thenander, lennart karlsson, Niklas Rehn</t>
+          <t>Philipp Weiss, Anders Heggestad, lennart karlsson, Håkan Thenander, Niklas Rehn</t>
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>123920733</v>
+        <v>123920727</v>
       </c>
       <c r="B60" t="n">
         <v>78788</v>
@@ -6761,10 +6756,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>459589</v>
+        <v>459542</v>
       </c>
       <c r="R60" t="n">
-        <v>6807980</v>
+        <v>6808123</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6823,10 +6818,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>123920399</v>
+        <v>123920733</v>
       </c>
       <c r="B61" t="n">
-        <v>79377</v>
+        <v>78788</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
@@ -6839,21 +6834,21 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>229821</v>
+        <v>6425</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -6863,10 +6858,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>459591</v>
+        <v>459589</v>
       </c>
       <c r="R61" t="n">
-        <v>6808065</v>
+        <v>6807980</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -6918,17 +6913,17 @@
       </c>
       <c r="AX61" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Anders Heggestad, Håkan Thenander, lennart karlsson, Niklas Rehn</t>
+          <t>Philipp Weiss, Anders Heggestad, lennart karlsson, Håkan Thenander, Niklas Rehn</t>
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>123920731</v>
+        <v>123920419</v>
       </c>
       <c r="B62" t="n">
-        <v>78788</v>
+        <v>90990</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
@@ -6941,21 +6936,21 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -6965,10 +6960,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>459608</v>
+        <v>459603</v>
       </c>
       <c r="R62" t="n">
-        <v>6808066</v>
+        <v>6807965</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -7020,17 +7015,17 @@
       </c>
       <c r="AX62" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Anders Heggestad, lennart karlsson, Håkan Thenander, Niklas Rehn</t>
+          <t>Philipp Weiss, Anders Heggestad, Håkan Thenander, lennart karlsson, Niklas Rehn</t>
         </is>
       </c>
       <c r="AY62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>123920441</v>
+        <v>123920732</v>
       </c>
       <c r="B63" t="n">
-        <v>56700</v>
+        <v>78788</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
@@ -7039,43 +7034,38 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
-      <c r="M63" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="P63" t="inlineStr">
         <is>
           <t>Härkämäck, Dlr</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>459609</v>
+        <v>459616</v>
       </c>
       <c r="R63" t="n">
-        <v>6807987</v>
+        <v>6808044</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -7127,17 +7117,17 @@
       </c>
       <c r="AX63" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Anders Heggestad, Håkan Thenander, lennart karlsson, Niklas Rehn</t>
+          <t>Philipp Weiss, Anders Heggestad, lennart karlsson, Håkan Thenander, Niklas Rehn</t>
         </is>
       </c>
       <c r="AY63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>123920930</v>
+        <v>123920440</v>
       </c>
       <c r="B64" t="n">
-        <v>78433</v>
+        <v>56700</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
@@ -7146,38 +7136,43 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>353</v>
+        <v>100138</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
+      <c r="M64" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="P64" t="inlineStr">
         <is>
           <t>Härkämäck, Dlr</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>459600</v>
+        <v>459617</v>
       </c>
       <c r="R64" t="n">
-        <v>6807961</v>
+        <v>6808041</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7229,17 +7224,17 @@
       </c>
       <c r="AX64" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Anders Heggestad, lennart karlsson, Håkan Thenander, Niklas Rehn</t>
+          <t>Philipp Weiss, Anders Heggestad, Håkan Thenander, lennart karlsson, Niklas Rehn</t>
         </is>
       </c>
       <c r="AY64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>123920427</v>
+        <v>123920442</v>
       </c>
       <c r="B65" t="n">
-        <v>57491</v>
+        <v>56700</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
@@ -7248,31 +7243,31 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>100109</v>
+        <v>100138</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
       <c r="M65" t="inlineStr">
         <is>
-          <t>födosökande</t>
+          <t>färsk spillning</t>
         </is>
       </c>
       <c r="P65" t="inlineStr">
@@ -7281,10 +7276,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>459571</v>
+        <v>459593</v>
       </c>
       <c r="R65" t="n">
-        <v>6808057</v>
+        <v>6807978</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7343,10 +7338,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>123920734</v>
+        <v>123920441</v>
       </c>
       <c r="B66" t="n">
-        <v>78788</v>
+        <v>56700</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
@@ -7355,38 +7350,43 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
+      <c r="M66" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="P66" t="inlineStr">
         <is>
           <t>Härkämäck, Dlr</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>459613</v>
+        <v>459609</v>
       </c>
       <c r="R66" t="n">
-        <v>6807959</v>
+        <v>6807987</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7438,7 +7438,7 @@
       </c>
       <c r="AX66" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Anders Heggestad, lennart karlsson, Håkan Thenander, Niklas Rehn</t>
+          <t>Philipp Weiss, Anders Heggestad, Håkan Thenander, lennart karlsson, Niklas Rehn</t>
         </is>
       </c>
       <c r="AY66" t="inlineStr"/>
@@ -7547,10 +7547,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>123920440</v>
+        <v>123920399</v>
       </c>
       <c r="B68" t="n">
-        <v>56700</v>
+        <v>79377</v>
       </c>
       <c r="C68" t="inlineStr">
         <is>
@@ -7559,43 +7559,38 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>100138</v>
+        <v>229821</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
-      <c r="M68" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="P68" t="inlineStr">
         <is>
           <t>Härkämäck, Dlr</t>
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>459617</v>
+        <v>459591</v>
       </c>
       <c r="R68" t="n">
-        <v>6808041</v>
+        <v>6808065</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>

--- a/artfynd/A 61327-2022 artfynd.xlsx
+++ b/artfynd/A 61327-2022 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>123834641</v>
+        <v>123829712</v>
       </c>
       <c r="B2" t="n">
-        <v>78810</v>
+        <v>91012</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,37 +691,37 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Härkämäck, Härkämäck, Dlr</t>
+          <t>Härkämäck, Dlr</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>459405</v>
+        <v>459573</v>
       </c>
       <c r="R2" t="n">
-        <v>6808172</v>
+        <v>6808047</v>
       </c>
       <c r="S2" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -765,22 +765,22 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123829918</v>
+        <v>123829121</v>
       </c>
       <c r="B3" t="n">
-        <v>78546</v>
+        <v>78810</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -793,37 +793,37 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Andljusbäcken, Andljusbäcken, Dlr</t>
+          <t>Härkämäck, Dlr</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>459424</v>
+        <v>459641</v>
       </c>
       <c r="R3" t="n">
-        <v>6807998</v>
+        <v>6807971</v>
       </c>
       <c r="S3" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -853,6 +853,11 @@
       <c r="AA3" t="inlineStr">
         <is>
           <t>2025-04-07</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>I synfältet i en radie av ca 40 meter. Miljöbild.</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -867,22 +872,22 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123833814</v>
+        <v>123830009</v>
       </c>
       <c r="B4" t="n">
-        <v>78547</v>
+        <v>78546</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -895,37 +900,37 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>228912</v>
+        <v>6446</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Härkämäck, Härkämäck, Dlr</t>
+          <t>Härkämäck, Dlr</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>459293</v>
+        <v>459480</v>
       </c>
       <c r="R4" t="n">
-        <v>6808123</v>
+        <v>6808013</v>
       </c>
       <c r="S4" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -955,6 +960,11 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2025-04-07</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Miljöbild.</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -969,22 +979,22 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123829712</v>
+        <v>123834641</v>
       </c>
       <c r="B5" t="n">
-        <v>91012</v>
+        <v>78810</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -997,37 +1007,37 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Härkämäck, Dlr</t>
+          <t>Härkämäck, Härkämäck, Dlr</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>459573</v>
+        <v>459405</v>
       </c>
       <c r="R5" t="n">
-        <v>6808047</v>
+        <v>6808172</v>
       </c>
       <c r="S5" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1071,22 +1081,22 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>123831065</v>
+        <v>123833814</v>
       </c>
       <c r="B6" t="n">
-        <v>78810</v>
+        <v>78547</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1099,37 +1109,37 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Andljusbäcken, Andljusbäcken, Dlr</t>
+          <t>Härkämäck, Härkämäck, Dlr</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>459425</v>
+        <v>459293</v>
       </c>
       <c r="R6" t="n">
-        <v>6808084</v>
+        <v>6808123</v>
       </c>
       <c r="S6" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1173,22 +1183,22 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>123831467</v>
+        <v>123830920</v>
       </c>
       <c r="B7" t="n">
-        <v>79399</v>
+        <v>78455</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1201,37 +1211,37 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>229821</v>
+        <v>353</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Härkämäck, Härkämäck, Dlr</t>
+          <t>Andljusbäcken, Andljusbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>459290</v>
+        <v>459462</v>
       </c>
       <c r="R7" t="n">
-        <v>6808098</v>
+        <v>6808078</v>
       </c>
       <c r="S7" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1275,19 +1285,19 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Niklas Rehn</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Niklas Rehn</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>123835135</v>
+        <v>123831065</v>
       </c>
       <c r="B8" t="n">
         <v>78810</v>
@@ -1323,14 +1333,14 @@
       <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Härkämäck, Dlr</t>
+          <t>Andljusbäcken, Andljusbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>459455</v>
+        <v>459425</v>
       </c>
       <c r="R8" t="n">
-        <v>6808164</v>
+        <v>6808084</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1365,11 +1375,6 @@
           <t>2025-04-07</t>
         </is>
       </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>Garnlav i en radie av ca 50 meter, synfältet. Miljöbild.</t>
-        </is>
-      </c>
       <c r="AD8" t="b">
         <v>0</v>
       </c>
@@ -1382,22 +1387,22 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>123829197</v>
+        <v>123828044</v>
       </c>
       <c r="B9" t="n">
-        <v>78547</v>
+        <v>78810</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1410,37 +1415,37 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Andljusbäcken, Andljusbäcken, Dlr</t>
+          <t>Härkämäck, Dlr</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>459611</v>
+        <v>459681</v>
       </c>
       <c r="R9" t="n">
-        <v>6807987</v>
+        <v>6808072</v>
       </c>
       <c r="S9" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1470,6 +1475,11 @@
       <c r="AA9" t="inlineStr">
         <is>
           <t>2025-04-07</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Garnlav i synfältet i en radie av ca 50 meter. Miljöbild.</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1484,22 +1494,22 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>123834998</v>
+        <v>123831244</v>
       </c>
       <c r="B10" t="n">
-        <v>79399</v>
+        <v>78810</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1512,34 +1522,34 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>229821</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Härkämäck, Härkämäck, Dlr</t>
+          <t>Andljusbäcken, Andljusbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>459437</v>
+        <v>459393</v>
       </c>
       <c r="R10" t="n">
-        <v>6808171</v>
+        <v>6808027</v>
       </c>
       <c r="S10" t="n">
         <v>20</v>
@@ -1598,10 +1608,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>123835432</v>
+        <v>123834195</v>
       </c>
       <c r="B11" t="n">
-        <v>78810</v>
+        <v>78547</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1614,34 +1624,34 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Härkämäck, Dlr</t>
+          <t>Härkämäck, Härkämäck, Dlr</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>459524</v>
+        <v>459365</v>
       </c>
       <c r="R11" t="n">
-        <v>6808114</v>
+        <v>6808224</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1676,11 +1686,6 @@
           <t>2025-04-07</t>
         </is>
       </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>Garnlav i alla riktningar, ca 50 meter i radie. Miljöbild.</t>
-        </is>
-      </c>
       <c r="AD11" t="b">
         <v>0</v>
       </c>
@@ -1693,22 +1698,22 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>123828608</v>
+        <v>123829918</v>
       </c>
       <c r="B12" t="n">
-        <v>78810</v>
+        <v>78546</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1721,37 +1726,37 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Härkämäck, Dlr</t>
+          <t>Andljusbäcken, Andljusbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>459636</v>
+        <v>459424</v>
       </c>
       <c r="R12" t="n">
-        <v>6808042</v>
+        <v>6807998</v>
       </c>
       <c r="S12" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1781,11 +1786,6 @@
       <c r="AA12" t="inlineStr">
         <is>
           <t>2025-04-07</t>
-        </is>
-      </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>Garnlav i synfältet i en radie av ca 50 meter. Miljöbilder.</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1800,22 +1800,22 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>123834183</v>
+        <v>123831578</v>
       </c>
       <c r="B13" t="n">
-        <v>78810</v>
+        <v>74901</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1828,21 +1828,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1852,10 +1852,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>459373</v>
+        <v>459287</v>
       </c>
       <c r="R13" t="n">
-        <v>6808222</v>
+        <v>6808008</v>
       </c>
       <c r="S13" t="n">
         <v>20</v>
@@ -1914,10 +1914,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>123831067</v>
+        <v>123834630</v>
       </c>
       <c r="B14" t="n">
-        <v>78810</v>
+        <v>57534</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1926,38 +1926,38 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6425</v>
+        <v>100110</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gråspett</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picus canus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>J.F. Gmelin, 1788</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Härkämäck, Dlr</t>
+          <t>Härkämäck, Härkämäck, Dlr</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>459439</v>
+        <v>459408</v>
       </c>
       <c r="R14" t="n">
-        <v>6808067</v>
+        <v>6808198</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1994,7 +1994,7 @@
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>Synligt i en radie av ca 50 meter. Miljöbild.</t>
+          <t>Förbiflygande.</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2009,22 +2009,22 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>123830009</v>
+        <v>123828608</v>
       </c>
       <c r="B15" t="n">
-        <v>78546</v>
+        <v>78810</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2037,21 +2037,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2061,10 +2061,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>459480</v>
+        <v>459636</v>
       </c>
       <c r="R15" t="n">
-        <v>6808013</v>
+        <v>6808042</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2101,7 +2101,7 @@
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>Miljöbild.</t>
+          <t>Garnlav i synfältet i en radie av ca 50 meter. Miljöbilder.</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2128,7 +2128,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>123831244</v>
+        <v>123833841</v>
       </c>
       <c r="B16" t="n">
         <v>78810</v>
@@ -2164,17 +2164,17 @@
       <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Andljusbäcken, Andljusbäcken, Dlr</t>
+          <t>Härkämäck, Härkämäck, Dlr</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>459393</v>
+        <v>459300</v>
       </c>
       <c r="R16" t="n">
-        <v>6808027</v>
+        <v>6808144</v>
       </c>
       <c r="S16" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2218,22 +2218,22 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>123827957</v>
+        <v>123830162</v>
       </c>
       <c r="B17" t="n">
-        <v>78546</v>
+        <v>78194</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2246,37 +2246,37 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6446</v>
+        <v>6437</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Andljusbäcken, Andljusbäcken, Dlr</t>
+          <t>Härkämäck, Dlr</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>459664</v>
+        <v>459480</v>
       </c>
       <c r="R17" t="n">
-        <v>6808079</v>
+        <v>6808013</v>
       </c>
       <c r="S17" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2306,6 +2306,11 @@
       <c r="AA17" t="inlineStr">
         <is>
           <t>2025-04-07</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>Miljöbild.</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2320,22 +2325,22 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>123828739</v>
+        <v>123834650</v>
       </c>
       <c r="B18" t="n">
-        <v>56722</v>
+        <v>78547</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2344,43 +2349,38 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100138</v>
+        <v>228912</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="P18" t="inlineStr">
         <is>
           <t>Härkämäck, Dlr</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>459636</v>
+        <v>459399</v>
       </c>
       <c r="R18" t="n">
-        <v>6808042</v>
+        <v>6808189</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2413,6 +2413,11 @@
       <c r="AA18" t="inlineStr">
         <is>
           <t>2025-04-07</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>Miljöbild</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2439,7 +2444,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>123829941</v>
+        <v>123834006</v>
       </c>
       <c r="B19" t="n">
         <v>78547</v>
@@ -2475,17 +2480,17 @@
       <c r="I19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Härkämäck, Dlr</t>
+          <t>Härkämäck, Härkämäck, Dlr</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>459480</v>
+        <v>459326</v>
       </c>
       <c r="R19" t="n">
-        <v>6808013</v>
+        <v>6808188</v>
       </c>
       <c r="S19" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2515,11 +2520,6 @@
       <c r="AA19" t="inlineStr">
         <is>
           <t>2025-04-07</t>
-        </is>
-      </c>
-      <c r="AC19" t="inlineStr">
-        <is>
-          <t>Miljöbild.</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2534,22 +2534,22 @@
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>123834006</v>
+        <v>123828742</v>
       </c>
       <c r="B20" t="n">
-        <v>78547</v>
+        <v>78810</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2562,37 +2562,37 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Härkämäck, Härkämäck, Dlr</t>
+          <t>Andljusbäcken, Andljusbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>459326</v>
+        <v>459612</v>
       </c>
       <c r="R20" t="n">
-        <v>6808188</v>
+        <v>6808068</v>
       </c>
       <c r="S20" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2636,22 +2636,22 @@
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>123829982</v>
+        <v>123828783</v>
       </c>
       <c r="B21" t="n">
-        <v>77738</v>
+        <v>78810</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2664,21 +2664,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6487</v>
+        <v>6425</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Blågrå svartspik</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Chaenothecopsis fennica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Laurila) Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2688,10 +2688,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>459432</v>
+        <v>459611</v>
       </c>
       <c r="R21" t="n">
-        <v>6807989</v>
+        <v>6808048</v>
       </c>
       <c r="S21" t="n">
         <v>20</v>
@@ -2750,10 +2750,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>123834966</v>
+        <v>123829310</v>
       </c>
       <c r="B22" t="n">
-        <v>57534</v>
+        <v>57529</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2762,31 +2762,31 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>100110</v>
+        <v>100049</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Gråspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Picus canus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>J.F. Gmelin, 1788</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
       <c r="M22" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P22" t="inlineStr">
@@ -2795,10 +2795,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>459399</v>
+        <v>459586</v>
       </c>
       <c r="R22" t="n">
-        <v>6808189</v>
+        <v>6807981</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2831,11 +2831,6 @@
       <c r="AA22" t="inlineStr">
         <is>
           <t>2025-04-07</t>
-        </is>
-      </c>
-      <c r="AC22" t="inlineStr">
-        <is>
-          <t>Förbiflygande.</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2862,10 +2857,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>123833729</v>
+        <v>123829394</v>
       </c>
       <c r="B23" t="n">
-        <v>78547</v>
+        <v>77738</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2878,34 +2873,34 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>228912</v>
+        <v>6487</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Blågrå svartspik</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Chaenothecopsis fennica</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Laurila) Tibell</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Andljusen, Dlr</t>
+          <t>Härkämäck, Dlr</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>459286</v>
+        <v>459586</v>
       </c>
       <c r="R23" t="n">
-        <v>6808090</v>
+        <v>6807981</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2938,11 +2933,6 @@
       <c r="AA23" t="inlineStr">
         <is>
           <t>2025-04-07</t>
-        </is>
-      </c>
-      <c r="AC23" t="inlineStr">
-        <is>
-          <t>Miljöbild.</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -2969,10 +2959,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>123829879</v>
+        <v>123829205</v>
       </c>
       <c r="B24" t="n">
-        <v>78810</v>
+        <v>78546</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -2985,21 +2975,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3009,10 +2999,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>459488</v>
+        <v>459611</v>
       </c>
       <c r="R24" t="n">
-        <v>6807974</v>
+        <v>6807987</v>
       </c>
       <c r="S24" t="n">
         <v>20</v>
@@ -3071,10 +3061,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>123829121</v>
+        <v>123833917</v>
       </c>
       <c r="B25" t="n">
-        <v>78810</v>
+        <v>78547</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3087,37 +3077,37 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Härkämäck, Dlr</t>
+          <t>Andljusbäcken, Andljusbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>459641</v>
+        <v>459292</v>
       </c>
       <c r="R25" t="n">
-        <v>6807971</v>
+        <v>6808184</v>
       </c>
       <c r="S25" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3147,11 +3137,6 @@
       <c r="AA25" t="inlineStr">
         <is>
           <t>2025-04-07</t>
-        </is>
-      </c>
-      <c r="AC25" t="inlineStr">
-        <is>
-          <t>I synfältet i en radie av ca 40 meter. Miljöbild.</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3166,19 +3151,19 @@
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>123829102</v>
+        <v>123831067</v>
       </c>
       <c r="B26" t="n">
         <v>78810</v>
@@ -3214,17 +3199,17 @@
       <c r="I26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Andljusbäcken, Andljusbäcken, Dlr</t>
+          <t>Härkämäck, Dlr</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>459666</v>
+        <v>459439</v>
       </c>
       <c r="R26" t="n">
-        <v>6807990</v>
+        <v>6808067</v>
       </c>
       <c r="S26" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3254,6 +3239,11 @@
       <c r="AA26" t="inlineStr">
         <is>
           <t>2025-04-07</t>
+        </is>
+      </c>
+      <c r="AC26" t="inlineStr">
+        <is>
+          <t>Synligt i en radie av ca 50 meter. Miljöbild.</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3268,22 +3258,22 @@
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>123829394</v>
+        <v>123828739</v>
       </c>
       <c r="B27" t="n">
-        <v>77738</v>
+        <v>56722</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3292,38 +3282,43 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6487</v>
+        <v>100138</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Blågrå svartspik</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Chaenothecopsis fennica</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Laurila) Tibell</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="P27" t="inlineStr">
         <is>
           <t>Härkämäck, Dlr</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>459586</v>
+        <v>459636</v>
       </c>
       <c r="R27" t="n">
-        <v>6807981</v>
+        <v>6808042</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3382,10 +3377,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>123834630</v>
+        <v>123829982</v>
       </c>
       <c r="B28" t="n">
-        <v>57534</v>
+        <v>77738</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3394,41 +3389,41 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>100110</v>
+        <v>6487</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Gråspett</t>
+          <t>Blågrå svartspik</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Picus canus</t>
+          <t>Chaenothecopsis fennica</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>J.F. Gmelin, 1788</t>
+          <t>(Laurila) Tibell</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Härkämäck, Härkämäck, Dlr</t>
+          <t>Andljusbäcken, Andljusbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>459408</v>
+        <v>459432</v>
       </c>
       <c r="R28" t="n">
-        <v>6808198</v>
+        <v>6807989</v>
       </c>
       <c r="S28" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3458,11 +3453,6 @@
       <c r="AA28" t="inlineStr">
         <is>
           <t>2025-04-07</t>
-        </is>
-      </c>
-      <c r="AC28" t="inlineStr">
-        <is>
-          <t>Förbiflygande.</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3477,19 +3467,19 @@
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>123833917</v>
+        <v>123829197</v>
       </c>
       <c r="B29" t="n">
         <v>78547</v>
@@ -3529,10 +3519,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>459292</v>
+        <v>459611</v>
       </c>
       <c r="R29" t="n">
-        <v>6808184</v>
+        <v>6807987</v>
       </c>
       <c r="S29" t="n">
         <v>20</v>
@@ -3591,10 +3581,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>123831578</v>
+        <v>123829941</v>
       </c>
       <c r="B30" t="n">
-        <v>74901</v>
+        <v>78547</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3607,37 +3597,37 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6440</v>
+        <v>228912</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Andljusbäcken, Andljusbäcken, Dlr</t>
+          <t>Härkämäck, Dlr</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>459287</v>
+        <v>459480</v>
       </c>
       <c r="R30" t="n">
-        <v>6808008</v>
+        <v>6808013</v>
       </c>
       <c r="S30" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -3667,6 +3657,11 @@
       <c r="AA30" t="inlineStr">
         <is>
           <t>2025-04-07</t>
+        </is>
+      </c>
+      <c r="AC30" t="inlineStr">
+        <is>
+          <t>Miljöbild.</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3681,19 +3676,19 @@
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>123833841</v>
+        <v>123829879</v>
       </c>
       <c r="B31" t="n">
         <v>78810</v>
@@ -3729,17 +3724,17 @@
       <c r="I31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Härkämäck, Härkämäck, Dlr</t>
+          <t>Andljusbäcken, Andljusbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>459300</v>
+        <v>459488</v>
       </c>
       <c r="R31" t="n">
-        <v>6808144</v>
+        <v>6807974</v>
       </c>
       <c r="S31" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -3783,22 +3778,22 @@
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>123830162</v>
+        <v>123834998</v>
       </c>
       <c r="B32" t="n">
-        <v>78194</v>
+        <v>79399</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -3811,37 +3806,37 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6437</v>
+        <v>229821</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Härkämäck, Dlr</t>
+          <t>Härkämäck, Härkämäck, Dlr</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>459480</v>
+        <v>459437</v>
       </c>
       <c r="R32" t="n">
-        <v>6808013</v>
+        <v>6808171</v>
       </c>
       <c r="S32" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -3871,11 +3866,6 @@
       <c r="AA32" t="inlineStr">
         <is>
           <t>2025-04-07</t>
-        </is>
-      </c>
-      <c r="AC32" t="inlineStr">
-        <is>
-          <t>Miljöbild.</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -3890,22 +3880,22 @@
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>123829275</v>
+        <v>123833754</v>
       </c>
       <c r="B33" t="n">
-        <v>78547</v>
+        <v>92293</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -3914,41 +3904,41 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>228912</v>
+        <v>4364</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Andljusbäcken, Andljusbäcken, Dlr</t>
+          <t>Härkämäck, Härkämäck, Dlr</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>459544</v>
+        <v>459290</v>
       </c>
       <c r="R33" t="n">
-        <v>6807989</v>
+        <v>6808093</v>
       </c>
       <c r="S33" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -3992,22 +3982,22 @@
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>123830920</v>
+        <v>123829632</v>
       </c>
       <c r="B34" t="n">
-        <v>78455</v>
+        <v>91299</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4020,37 +4010,37 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>353</v>
+        <v>658</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Andljusbäcken, Andljusbäcken, Dlr</t>
+          <t>Härkämäck, Dlr</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>459462</v>
+        <v>459573</v>
       </c>
       <c r="R34" t="n">
-        <v>6808078</v>
+        <v>6808047</v>
       </c>
       <c r="S34" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -4094,22 +4084,22 @@
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>123828882</v>
+        <v>123834034</v>
       </c>
       <c r="B35" t="n">
-        <v>78842</v>
+        <v>57529</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4122,37 +4112,42 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>185</v>
+        <v>100049</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Andljusbäcken, Andljusbäcken, Dlr</t>
+          <t>Andljusen, Dlr</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>459600</v>
+        <v>459325</v>
       </c>
       <c r="R35" t="n">
-        <v>6808030</v>
+        <v>6808176</v>
       </c>
       <c r="S35" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -4182,6 +4177,11 @@
       <c r="AA35" t="inlineStr">
         <is>
           <t>2025-04-07</t>
+        </is>
+      </c>
+      <c r="AC35" t="inlineStr">
+        <is>
+          <t>Miljöbild.</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4196,22 +4196,22 @@
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>123828742</v>
+        <v>123827957</v>
       </c>
       <c r="B36" t="n">
-        <v>78810</v>
+        <v>78546</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4224,21 +4224,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4248,10 +4248,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>459612</v>
+        <v>459664</v>
       </c>
       <c r="R36" t="n">
-        <v>6808068</v>
+        <v>6808079</v>
       </c>
       <c r="S36" t="n">
         <v>20</v>
@@ -4310,10 +4310,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>123831097</v>
+        <v>123834220</v>
       </c>
       <c r="B37" t="n">
-        <v>79399</v>
+        <v>78810</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4326,37 +4326,37 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>229821</v>
+        <v>6425</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
-          <t>Andljusbäcken, Andljusbäcken, Dlr</t>
+          <t>Andljusen, Dlr</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>459402</v>
+        <v>459325</v>
       </c>
       <c r="R37" t="n">
-        <v>6808072</v>
+        <v>6808176</v>
       </c>
       <c r="S37" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -4386,6 +4386,11 @@
       <c r="AA37" t="inlineStr">
         <is>
           <t>2025-04-07</t>
+        </is>
+      </c>
+      <c r="AC37" t="inlineStr">
+        <is>
+          <t>I synfält, radie av ca 50 meter. Miljöbild.</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4400,22 +4405,22 @@
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>123834890</v>
+        <v>123828882</v>
       </c>
       <c r="B38" t="n">
-        <v>78889</v>
+        <v>78842</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4428,34 +4433,34 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>864</v>
+        <v>185</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Knottrig blåslav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Hypogymnia bitteri</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Lynge) Ahti</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
-          <t>Härkämäck, Härkämäck, Dlr</t>
+          <t>Andljusbäcken, Andljusbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>459427</v>
+        <v>459600</v>
       </c>
       <c r="R38" t="n">
-        <v>6808130</v>
+        <v>6808030</v>
       </c>
       <c r="S38" t="n">
         <v>20</v>
@@ -4514,7 +4519,7 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>123834220</v>
+        <v>123829246</v>
       </c>
       <c r="B39" t="n">
         <v>78810</v>
@@ -4550,14 +4555,14 @@
       <c r="I39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
-          <t>Andljusen, Dlr</t>
+          <t>Härkämäck, Dlr</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>459325</v>
+        <v>459586</v>
       </c>
       <c r="R39" t="n">
-        <v>6808176</v>
+        <v>6807981</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4594,7 +4599,7 @@
       </c>
       <c r="AC39" t="inlineStr">
         <is>
-          <t>I synfält, radie av ca 50 meter. Miljöbild.</t>
+          <t>Som vanligt garnlav i omgivningen. Miljöbilder.</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4621,10 +4626,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>123834567</v>
+        <v>123831277</v>
       </c>
       <c r="B40" t="n">
-        <v>79399</v>
+        <v>57529</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -4637,34 +4642,39 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>229821</v>
+        <v>100049</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P40" t="inlineStr">
         <is>
           <t>Härkämäck, Dlr</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>459399</v>
+        <v>459389</v>
       </c>
       <c r="R40" t="n">
-        <v>6808189</v>
+        <v>6808070</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4728,10 +4738,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>123831277</v>
+        <v>123831097</v>
       </c>
       <c r="B41" t="n">
-        <v>57529</v>
+        <v>79399</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -4744,42 +4754,37 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>100049</v>
+        <v>229821</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
-      <c r="M41" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P41" t="inlineStr">
         <is>
-          <t>Härkämäck, Dlr</t>
+          <t>Andljusbäcken, Andljusbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>459389</v>
+        <v>459402</v>
       </c>
       <c r="R41" t="n">
-        <v>6808070</v>
+        <v>6808072</v>
       </c>
       <c r="S41" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -4809,11 +4814,6 @@
       <c r="AA41" t="inlineStr">
         <is>
           <t>2025-04-07</t>
-        </is>
-      </c>
-      <c r="AC41" t="inlineStr">
-        <is>
-          <t>Miljöbild.</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -4828,19 +4828,19 @@
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>123829246</v>
+        <v>123835432</v>
       </c>
       <c r="B42" t="n">
         <v>78810</v>
@@ -4880,10 +4880,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>459586</v>
+        <v>459524</v>
       </c>
       <c r="R42" t="n">
-        <v>6807981</v>
+        <v>6808114</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4920,7 +4920,7 @@
       </c>
       <c r="AC42" t="inlineStr">
         <is>
-          <t>Som vanligt garnlav i omgivningen. Miljöbilder.</t>
+          <t>Garnlav i alla riktningar, ca 50 meter i radie. Miljöbild.</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -4947,10 +4947,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>123834650</v>
+        <v>123834966</v>
       </c>
       <c r="B43" t="n">
-        <v>78547</v>
+        <v>57534</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -4959,28 +4959,33 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>228912</v>
+        <v>100110</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Gråspett</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Picus canus</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>J.F. Gmelin, 1788</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P43" t="inlineStr">
         <is>
           <t>Härkämäck, Dlr</t>
@@ -5027,7 +5032,7 @@
       </c>
       <c r="AC43" t="inlineStr">
         <is>
-          <t>Miljöbild</t>
+          <t>Förbiflygande.</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5054,10 +5059,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>123829310</v>
+        <v>123833729</v>
       </c>
       <c r="B44" t="n">
-        <v>57529</v>
+        <v>78547</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5070,39 +5075,34 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>100049</v>
+        <v>228912</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
-      <c r="M44" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P44" t="inlineStr">
         <is>
-          <t>Härkämäck, Dlr</t>
+          <t>Andljusen, Dlr</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>459586</v>
+        <v>459286</v>
       </c>
       <c r="R44" t="n">
-        <v>6807981</v>
+        <v>6808090</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5135,6 +5135,11 @@
       <c r="AA44" t="inlineStr">
         <is>
           <t>2025-04-07</t>
+        </is>
+      </c>
+      <c r="AC44" t="inlineStr">
+        <is>
+          <t>Miljöbild.</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5161,10 +5166,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>123828044</v>
+        <v>123831467</v>
       </c>
       <c r="B45" t="n">
-        <v>78810</v>
+        <v>79399</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5177,34 +5182,34 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6425</v>
+        <v>229821</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
-          <t>Härkämäck, Dlr</t>
+          <t>Härkämäck, Härkämäck, Dlr</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>459681</v>
+        <v>459290</v>
       </c>
       <c r="R45" t="n">
-        <v>6808072</v>
+        <v>6808098</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5239,11 +5244,6 @@
           <t>2025-04-07</t>
         </is>
       </c>
-      <c r="AC45" t="inlineStr">
-        <is>
-          <t>Garnlav i synfältet i en radie av ca 50 meter. Miljöbild.</t>
-        </is>
-      </c>
       <c r="AD45" t="b">
         <v>0</v>
       </c>
@@ -5256,22 +5256,22 @@
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Niklas Rehn</t>
         </is>
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Niklas Rehn</t>
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>123834034</v>
+        <v>123835135</v>
       </c>
       <c r="B46" t="n">
-        <v>57529</v>
+        <v>78810</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5284,39 +5284,34 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
-      <c r="M46" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P46" t="inlineStr">
         <is>
-          <t>Andljusen, Dlr</t>
+          <t>Härkämäck, Dlr</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>459325</v>
+        <v>459455</v>
       </c>
       <c r="R46" t="n">
-        <v>6808176</v>
+        <v>6808164</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5353,7 +5348,7 @@
       </c>
       <c r="AC46" t="inlineStr">
         <is>
-          <t>Miljöbild.</t>
+          <t>Garnlav i en radie av ca 50 meter, synfältet. Miljöbild.</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5380,10 +5375,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>123833754</v>
+        <v>123834567</v>
       </c>
       <c r="B47" t="n">
-        <v>92293</v>
+        <v>79399</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5392,41 +5387,41 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>4364</v>
+        <v>229821</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
-          <t>Härkämäck, Härkämäck, Dlr</t>
+          <t>Härkämäck, Dlr</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>459290</v>
+        <v>459399</v>
       </c>
       <c r="R47" t="n">
-        <v>6808093</v>
+        <v>6808189</v>
       </c>
       <c r="S47" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T47" t="inlineStr">
         <is>
@@ -5456,6 +5451,11 @@
       <c r="AA47" t="inlineStr">
         <is>
           <t>2025-04-07</t>
+        </is>
+      </c>
+      <c r="AC47" t="inlineStr">
+        <is>
+          <t>Miljöbild.</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5470,22 +5470,22 @@
       <c r="AT47" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX47" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>123829632</v>
+        <v>123829275</v>
       </c>
       <c r="B48" t="n">
-        <v>91299</v>
+        <v>78547</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -5498,37 +5498,37 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>658</v>
+        <v>228912</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
-          <t>Härkämäck, Dlr</t>
+          <t>Andljusbäcken, Andljusbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>459573</v>
+        <v>459544</v>
       </c>
       <c r="R48" t="n">
-        <v>6808047</v>
+        <v>6807989</v>
       </c>
       <c r="S48" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T48" t="inlineStr">
         <is>
@@ -5572,22 +5572,22 @@
       <c r="AT48" t="inlineStr"/>
       <c r="AW48" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX48" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>123834195</v>
+        <v>123834890</v>
       </c>
       <c r="B49" t="n">
-        <v>78547</v>
+        <v>78889</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -5600,21 +5600,21 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>228912</v>
+        <v>864</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Lynge) Ahti</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5624,13 +5624,13 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>459365</v>
+        <v>459427</v>
       </c>
       <c r="R49" t="n">
-        <v>6808224</v>
+        <v>6808130</v>
       </c>
       <c r="S49" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T49" t="inlineStr">
         <is>
@@ -5674,22 +5674,22 @@
       <c r="AT49" t="inlineStr"/>
       <c r="AW49" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX49" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>123829205</v>
+        <v>123829889</v>
       </c>
       <c r="B50" t="n">
-        <v>78546</v>
+        <v>78547</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -5702,37 +5702,37 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>6446</v>
+        <v>228912</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
-          <t>Andljusbäcken, Andljusbäcken, Dlr</t>
+          <t>Härkämäck, Dlr</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>459611</v>
+        <v>459494</v>
       </c>
       <c r="R50" t="n">
-        <v>6807987</v>
+        <v>6807997</v>
       </c>
       <c r="S50" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T50" t="inlineStr">
         <is>
@@ -5762,6 +5762,11 @@
       <c r="AA50" t="inlineStr">
         <is>
           <t>2025-04-07</t>
+        </is>
+      </c>
+      <c r="AC50" t="inlineStr">
+        <is>
+          <t>Miljöbild.</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -5776,19 +5781,19 @@
       <c r="AT50" t="inlineStr"/>
       <c r="AW50" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX50" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>123828783</v>
+        <v>123834183</v>
       </c>
       <c r="B51" t="n">
         <v>78810</v>
@@ -5828,10 +5833,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>459611</v>
+        <v>459373</v>
       </c>
       <c r="R51" t="n">
-        <v>6808048</v>
+        <v>6808222</v>
       </c>
       <c r="S51" t="n">
         <v>20</v>
@@ -5890,10 +5895,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>123829889</v>
+        <v>123829102</v>
       </c>
       <c r="B52" t="n">
-        <v>78547</v>
+        <v>78810</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -5906,37 +5911,37 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
-          <t>Härkämäck, Dlr</t>
+          <t>Andljusbäcken, Andljusbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>459494</v>
+        <v>459666</v>
       </c>
       <c r="R52" t="n">
-        <v>6807997</v>
+        <v>6807990</v>
       </c>
       <c r="S52" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T52" t="inlineStr">
         <is>
@@ -5966,11 +5971,6 @@
       <c r="AA52" t="inlineStr">
         <is>
           <t>2025-04-07</t>
-        </is>
-      </c>
-      <c r="AC52" t="inlineStr">
-        <is>
-          <t>Miljöbild.</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -5985,19 +5985,19 @@
       <c r="AT52" t="inlineStr"/>
       <c r="AW52" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX52" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>123920734</v>
+        <v>123920731</v>
       </c>
       <c r="B53" t="n">
         <v>78810</v>
@@ -6037,10 +6037,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>459613</v>
+        <v>459608</v>
       </c>
       <c r="R53" t="n">
-        <v>6807959</v>
+        <v>6808066</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6092,17 +6092,17 @@
       </c>
       <c r="AX53" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Niklas Rehn, Håkan Thenander, lennart karlsson, Anders Heggestad</t>
+          <t>Philipp Weiss, Anders Heggestad, lennart karlsson, Håkan Thenander, Niklas Rehn</t>
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>123920730</v>
+        <v>123920930</v>
       </c>
       <c r="B54" t="n">
-        <v>78810</v>
+        <v>78455</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -6115,21 +6115,21 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -6139,10 +6139,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>459590</v>
+        <v>459600</v>
       </c>
       <c r="R54" t="n">
-        <v>6808062</v>
+        <v>6807961</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6194,17 +6194,17 @@
       </c>
       <c r="AX54" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Niklas Rehn, Håkan Thenander, lennart karlsson, Anders Heggestad</t>
+          <t>Philipp Weiss, Anders Heggestad, lennart karlsson, Håkan Thenander, Niklas Rehn</t>
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>123920442</v>
+        <v>123920399</v>
       </c>
       <c r="B55" t="n">
-        <v>56722</v>
+        <v>79399</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -6213,43 +6213,38 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>100138</v>
+        <v>229821</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
-      <c r="M55" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="P55" t="inlineStr">
         <is>
           <t>Härkämäck, Dlr</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>459593</v>
+        <v>459591</v>
       </c>
       <c r="R55" t="n">
-        <v>6807978</v>
+        <v>6808065</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6308,10 +6303,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>123920399</v>
+        <v>123920732</v>
       </c>
       <c r="B56" t="n">
-        <v>79399</v>
+        <v>78810</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -6324,21 +6319,21 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>229821</v>
+        <v>6425</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6348,10 +6343,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>459591</v>
+        <v>459616</v>
       </c>
       <c r="R56" t="n">
-        <v>6808065</v>
+        <v>6808044</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6403,14 +6398,14 @@
       </c>
       <c r="AX56" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Anders Heggestad, Håkan Thenander, lennart karlsson, Niklas Rehn</t>
+          <t>Philipp Weiss, Anders Heggestad, lennart karlsson, Håkan Thenander, Niklas Rehn</t>
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>123920731</v>
+        <v>123920733</v>
       </c>
       <c r="B57" t="n">
         <v>78810</v>
@@ -6450,10 +6445,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>459608</v>
+        <v>459589</v>
       </c>
       <c r="R57" t="n">
-        <v>6808066</v>
+        <v>6807980</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6505,14 +6500,14 @@
       </c>
       <c r="AX57" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Niklas Rehn, Håkan Thenander, lennart karlsson, Anders Heggestad</t>
+          <t>Philipp Weiss, Anders Heggestad, lennart karlsson, Håkan Thenander, Niklas Rehn</t>
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>123920733</v>
+        <v>123920734</v>
       </c>
       <c r="B58" t="n">
         <v>78810</v>
@@ -6552,10 +6547,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>459589</v>
+        <v>459613</v>
       </c>
       <c r="R58" t="n">
-        <v>6807980</v>
+        <v>6807959</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6607,14 +6602,14 @@
       </c>
       <c r="AX58" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Niklas Rehn, Håkan Thenander, lennart karlsson, Anders Heggestad</t>
+          <t>Philipp Weiss, Anders Heggestad, lennart karlsson, Håkan Thenander, Niklas Rehn</t>
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>123920440</v>
+        <v>123920441</v>
       </c>
       <c r="B59" t="n">
         <v>56722</v>
@@ -6659,10 +6654,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>459617</v>
+        <v>459609</v>
       </c>
       <c r="R59" t="n">
-        <v>6808041</v>
+        <v>6807987</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6714,17 +6709,17 @@
       </c>
       <c r="AX59" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Anders Heggestad, Håkan Thenander, lennart karlsson, Niklas Rehn</t>
+          <t>Philipp Weiss, Niklas Rehn, lennart karlsson, Håkan Thenander, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>123920728</v>
+        <v>123920540</v>
       </c>
       <c r="B60" t="n">
-        <v>78810</v>
+        <v>78547</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
@@ -6737,21 +6732,21 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -6761,10 +6756,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>459539</v>
+        <v>459589</v>
       </c>
       <c r="R60" t="n">
-        <v>6808073</v>
+        <v>6807980</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6823,10 +6818,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>123920930</v>
+        <v>123920729</v>
       </c>
       <c r="B61" t="n">
-        <v>78455</v>
+        <v>78810</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
@@ -6839,21 +6834,21 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -6863,10 +6858,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>459600</v>
+        <v>459566</v>
       </c>
       <c r="R61" t="n">
-        <v>6807961</v>
+        <v>6808068</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -6925,10 +6920,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>123920540</v>
+        <v>123920442</v>
       </c>
       <c r="B62" t="n">
-        <v>78547</v>
+        <v>56722</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
@@ -6937,38 +6932,43 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>228912</v>
+        <v>100138</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
+      <c r="M62" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="P62" t="inlineStr">
         <is>
           <t>Härkämäck, Dlr</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>459589</v>
+        <v>459593</v>
       </c>
       <c r="R62" t="n">
-        <v>6807980</v>
+        <v>6807978</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -7020,17 +7020,17 @@
       </c>
       <c r="AX62" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Anders Heggestad, lennart karlsson, Håkan Thenander, Niklas Rehn</t>
+          <t>Philipp Weiss, Anders Heggestad, Håkan Thenander, lennart karlsson, Niklas Rehn</t>
         </is>
       </c>
       <c r="AY62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>123920732</v>
+        <v>123920440</v>
       </c>
       <c r="B63" t="n">
-        <v>78810</v>
+        <v>56722</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
@@ -7039,38 +7039,43 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
+      <c r="M63" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="P63" t="inlineStr">
         <is>
           <t>Härkämäck, Dlr</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>459616</v>
+        <v>459617</v>
       </c>
       <c r="R63" t="n">
-        <v>6808044</v>
+        <v>6808041</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -7122,17 +7127,17 @@
       </c>
       <c r="AX63" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Niklas Rehn, Håkan Thenander, lennart karlsson, Anders Heggestad</t>
+          <t>Philipp Weiss, Niklas Rehn, lennart karlsson, Håkan Thenander, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>123920419</v>
+        <v>123920727</v>
       </c>
       <c r="B64" t="n">
-        <v>91012</v>
+        <v>78810</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
@@ -7145,21 +7150,21 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -7169,10 +7174,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>459603</v>
+        <v>459542</v>
       </c>
       <c r="R64" t="n">
-        <v>6807965</v>
+        <v>6808123</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7224,17 +7229,17 @@
       </c>
       <c r="AX64" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Anders Heggestad, Håkan Thenander, lennart karlsson, Niklas Rehn</t>
+          <t>Philipp Weiss, Anders Heggestad, lennart karlsson, Håkan Thenander, Niklas Rehn</t>
         </is>
       </c>
       <c r="AY64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>123920441</v>
+        <v>123920419</v>
       </c>
       <c r="B65" t="n">
-        <v>56722</v>
+        <v>91012</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
@@ -7243,43 +7248,38 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>100138</v>
+        <v>1202</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
-      <c r="M65" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="P65" t="inlineStr">
         <is>
           <t>Härkämäck, Dlr</t>
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>459609</v>
+        <v>459603</v>
       </c>
       <c r="R65" t="n">
-        <v>6807987</v>
+        <v>6807965</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7338,7 +7338,7 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>123920729</v>
+        <v>123920728</v>
       </c>
       <c r="B66" t="n">
         <v>78810</v>
@@ -7378,10 +7378,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>459566</v>
+        <v>459539</v>
       </c>
       <c r="R66" t="n">
-        <v>6808068</v>
+        <v>6808073</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7433,14 +7433,14 @@
       </c>
       <c r="AX66" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Niklas Rehn, Håkan Thenander, lennart karlsson, Anders Heggestad</t>
+          <t>Philipp Weiss, Anders Heggestad, lennart karlsson, Håkan Thenander, Niklas Rehn</t>
         </is>
       </c>
       <c r="AY66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>123920727</v>
+        <v>123920730</v>
       </c>
       <c r="B67" t="n">
         <v>78810</v>
@@ -7480,10 +7480,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>459542</v>
+        <v>459590</v>
       </c>
       <c r="R67" t="n">
-        <v>6808123</v>
+        <v>6808062</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7535,7 +7535,7 @@
       </c>
       <c r="AX67" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Niklas Rehn, Håkan Thenander, lennart karlsson, Anders Heggestad</t>
+          <t>Philipp Weiss, Anders Heggestad, lennart karlsson, Håkan Thenander, Niklas Rehn</t>
         </is>
       </c>
       <c r="AY67" t="inlineStr"/>
@@ -7642,7 +7642,7 @@
       </c>
       <c r="AX68" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Anders Heggestad, Håkan Thenander, lennart karlsson, Niklas Rehn</t>
+          <t>Philipp Weiss, Niklas Rehn, lennart karlsson, Håkan Thenander, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY68" t="inlineStr"/>

--- a/artfynd/A 61327-2022 artfynd.xlsx
+++ b/artfynd/A 61327-2022 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>123829712</v>
+        <v>123831065</v>
       </c>
       <c r="B2" t="n">
-        <v>91012</v>
+        <v>78810</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,34 +691,34 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Härkämäck, Dlr</t>
+          <t>Andljusbäcken, Andljusbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>459573</v>
+        <v>459425</v>
       </c>
       <c r="R2" t="n">
-        <v>6808047</v>
+        <v>6808084</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -765,22 +765,22 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123829121</v>
+        <v>123833917</v>
       </c>
       <c r="B3" t="n">
-        <v>78810</v>
+        <v>78547</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -793,37 +793,37 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Härkämäck, Dlr</t>
+          <t>Andljusbäcken, Andljusbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>459641</v>
+        <v>459292</v>
       </c>
       <c r="R3" t="n">
-        <v>6807971</v>
+        <v>6808184</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -853,11 +853,6 @@
       <c r="AA3" t="inlineStr">
         <is>
           <t>2025-04-07</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>I synfältet i en radie av ca 40 meter. Miljöbild.</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -872,22 +867,22 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123830009</v>
+        <v>123831097</v>
       </c>
       <c r="B4" t="n">
-        <v>78546</v>
+        <v>79399</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -900,37 +895,37 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6446</v>
+        <v>229821</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Härkämäck, Dlr</t>
+          <t>Andljusbäcken, Andljusbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>459480</v>
+        <v>459402</v>
       </c>
       <c r="R4" t="n">
-        <v>6808013</v>
+        <v>6808072</v>
       </c>
       <c r="S4" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -960,11 +955,6 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2025-04-07</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Miljöbild.</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -979,22 +969,22 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123834641</v>
+        <v>123833754</v>
       </c>
       <c r="B5" t="n">
-        <v>78810</v>
+        <v>92293</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1003,25 +993,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1031,13 +1021,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>459405</v>
+        <v>459290</v>
       </c>
       <c r="R5" t="n">
-        <v>6808172</v>
+        <v>6808093</v>
       </c>
       <c r="S5" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1081,22 +1071,22 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>123833814</v>
+        <v>123829918</v>
       </c>
       <c r="B6" t="n">
-        <v>78547</v>
+        <v>78546</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1109,37 +1099,37 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>228912</v>
+        <v>6446</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Härkämäck, Härkämäck, Dlr</t>
+          <t>Andljusbäcken, Andljusbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>459293</v>
+        <v>459424</v>
       </c>
       <c r="R6" t="n">
-        <v>6808123</v>
+        <v>6807998</v>
       </c>
       <c r="S6" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1183,22 +1173,22 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>123830920</v>
+        <v>123829982</v>
       </c>
       <c r="B7" t="n">
-        <v>78455</v>
+        <v>77738</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1211,21 +1201,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>353</v>
+        <v>6487</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Blågrå svartspik</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Chaenothecopsis fennica</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Laurila) Tibell</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1235,10 +1225,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>459462</v>
+        <v>459432</v>
       </c>
       <c r="R7" t="n">
-        <v>6808078</v>
+        <v>6807989</v>
       </c>
       <c r="S7" t="n">
         <v>20</v>
@@ -1297,7 +1287,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>123831065</v>
+        <v>123833841</v>
       </c>
       <c r="B8" t="n">
         <v>78810</v>
@@ -1333,17 +1323,17 @@
       <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Andljusbäcken, Andljusbäcken, Dlr</t>
+          <t>Härkämäck, Härkämäck, Dlr</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>459425</v>
+        <v>459300</v>
       </c>
       <c r="R8" t="n">
-        <v>6808084</v>
+        <v>6808144</v>
       </c>
       <c r="S8" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1387,22 +1377,22 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>123828044</v>
+        <v>123827957</v>
       </c>
       <c r="B9" t="n">
-        <v>78810</v>
+        <v>78546</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1415,37 +1405,37 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Härkämäck, Dlr</t>
+          <t>Andljusbäcken, Andljusbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>459681</v>
+        <v>459664</v>
       </c>
       <c r="R9" t="n">
-        <v>6808072</v>
+        <v>6808079</v>
       </c>
       <c r="S9" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1475,11 +1465,6 @@
       <c r="AA9" t="inlineStr">
         <is>
           <t>2025-04-07</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>Garnlav i synfältet i en radie av ca 50 meter. Miljöbild.</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1494,22 +1479,22 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>123831244</v>
+        <v>123829310</v>
       </c>
       <c r="B10" t="n">
-        <v>78810</v>
+        <v>57529</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1522,37 +1507,42 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Andljusbäcken, Andljusbäcken, Dlr</t>
+          <t>Härkämäck, Dlr</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>459393</v>
+        <v>459586</v>
       </c>
       <c r="R10" t="n">
-        <v>6808027</v>
+        <v>6807981</v>
       </c>
       <c r="S10" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1596,22 +1586,22 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>123834195</v>
+        <v>123830162</v>
       </c>
       <c r="B11" t="n">
-        <v>78547</v>
+        <v>78194</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1624,34 +1614,34 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>228912</v>
+        <v>6437</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Härkämäck, Härkämäck, Dlr</t>
+          <t>Härkämäck, Dlr</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>459365</v>
+        <v>459480</v>
       </c>
       <c r="R11" t="n">
-        <v>6808224</v>
+        <v>6808013</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1686,6 +1676,11 @@
           <t>2025-04-07</t>
         </is>
       </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Miljöbild.</t>
+        </is>
+      </c>
       <c r="AD11" t="b">
         <v>0</v>
       </c>
@@ -1698,22 +1693,22 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>123829918</v>
+        <v>123829275</v>
       </c>
       <c r="B12" t="n">
-        <v>78546</v>
+        <v>78547</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1726,21 +1721,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6446</v>
+        <v>228912</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1750,10 +1745,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>459424</v>
+        <v>459544</v>
       </c>
       <c r="R12" t="n">
-        <v>6807998</v>
+        <v>6807989</v>
       </c>
       <c r="S12" t="n">
         <v>20</v>
@@ -1812,10 +1807,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>123831578</v>
+        <v>123829394</v>
       </c>
       <c r="B13" t="n">
-        <v>74901</v>
+        <v>77738</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1828,37 +1823,37 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6440</v>
+        <v>6487</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Blågrå svartspik</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Chaenothecopsis fennica</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Laurila) Tibell</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Andljusbäcken, Andljusbäcken, Dlr</t>
+          <t>Härkämäck, Dlr</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>459287</v>
+        <v>459586</v>
       </c>
       <c r="R13" t="n">
-        <v>6808008</v>
+        <v>6807981</v>
       </c>
       <c r="S13" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1902,22 +1897,22 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>123834630</v>
+        <v>123831277</v>
       </c>
       <c r="B14" t="n">
-        <v>57534</v>
+        <v>57529</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1926,38 +1921,43 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100110</v>
+        <v>100049</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Gråspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Picus canus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>J.F. Gmelin, 1788</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Härkämäck, Härkämäck, Dlr</t>
+          <t>Härkämäck, Dlr</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>459408</v>
+        <v>459389</v>
       </c>
       <c r="R14" t="n">
-        <v>6808198</v>
+        <v>6808070</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1994,7 +1994,7 @@
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>Förbiflygande.</t>
+          <t>Miljöbild.</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2009,22 +2009,22 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>123828608</v>
+        <v>123829889</v>
       </c>
       <c r="B15" t="n">
-        <v>78810</v>
+        <v>78547</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2037,21 +2037,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2061,10 +2061,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>459636</v>
+        <v>459494</v>
       </c>
       <c r="R15" t="n">
-        <v>6808042</v>
+        <v>6807997</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2101,7 +2101,7 @@
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>Garnlav i synfältet i en radie av ca 50 meter. Miljöbilder.</t>
+          <t>Miljöbild.</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2128,7 +2128,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>123833841</v>
+        <v>123829121</v>
       </c>
       <c r="B16" t="n">
         <v>78810</v>
@@ -2164,17 +2164,17 @@
       <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Härkämäck, Härkämäck, Dlr</t>
+          <t>Härkämäck, Dlr</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>459300</v>
+        <v>459641</v>
       </c>
       <c r="R16" t="n">
-        <v>6808144</v>
+        <v>6807971</v>
       </c>
       <c r="S16" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2204,6 +2204,11 @@
       <c r="AA16" t="inlineStr">
         <is>
           <t>2025-04-07</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>I synfältet i en radie av ca 40 meter. Miljöbild.</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2218,22 +2223,22 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>123830162</v>
+        <v>123834183</v>
       </c>
       <c r="B17" t="n">
-        <v>78194</v>
+        <v>78810</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2246,37 +2251,37 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6437</v>
+        <v>6425</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Härkämäck, Dlr</t>
+          <t>Andljusbäcken, Andljusbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>459480</v>
+        <v>459373</v>
       </c>
       <c r="R17" t="n">
-        <v>6808013</v>
+        <v>6808222</v>
       </c>
       <c r="S17" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2306,11 +2311,6 @@
       <c r="AA17" t="inlineStr">
         <is>
           <t>2025-04-07</t>
-        </is>
-      </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>Miljöbild.</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2325,19 +2325,19 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>123834650</v>
+        <v>123833814</v>
       </c>
       <c r="B18" t="n">
         <v>78547</v>
@@ -2373,17 +2373,17 @@
       <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Härkämäck, Dlr</t>
+          <t>Härkämäck, Härkämäck, Dlr</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>459399</v>
+        <v>459293</v>
       </c>
       <c r="R18" t="n">
-        <v>6808189</v>
+        <v>6808123</v>
       </c>
       <c r="S18" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2413,11 +2413,6 @@
       <c r="AA18" t="inlineStr">
         <is>
           <t>2025-04-07</t>
-        </is>
-      </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>Miljöbild</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2432,19 +2427,19 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>123834006</v>
+        <v>123829197</v>
       </c>
       <c r="B19" t="n">
         <v>78547</v>
@@ -2480,17 +2475,17 @@
       <c r="I19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Härkämäck, Härkämäck, Dlr</t>
+          <t>Andljusbäcken, Andljusbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>459326</v>
+        <v>459611</v>
       </c>
       <c r="R19" t="n">
-        <v>6808188</v>
+        <v>6807987</v>
       </c>
       <c r="S19" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2534,22 +2529,22 @@
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>123828742</v>
+        <v>123830009</v>
       </c>
       <c r="B20" t="n">
-        <v>78810</v>
+        <v>78546</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2562,37 +2557,37 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Andljusbäcken, Andljusbäcken, Dlr</t>
+          <t>Härkämäck, Dlr</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>459612</v>
+        <v>459480</v>
       </c>
       <c r="R20" t="n">
-        <v>6808068</v>
+        <v>6808013</v>
       </c>
       <c r="S20" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2622,6 +2617,11 @@
       <c r="AA20" t="inlineStr">
         <is>
           <t>2025-04-07</t>
+        </is>
+      </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>Miljöbild.</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2636,19 +2636,19 @@
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>123828783</v>
+        <v>123834641</v>
       </c>
       <c r="B21" t="n">
         <v>78810</v>
@@ -2684,14 +2684,14 @@
       <c r="I21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Andljusbäcken, Andljusbäcken, Dlr</t>
+          <t>Härkämäck, Härkämäck, Dlr</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>459611</v>
+        <v>459405</v>
       </c>
       <c r="R21" t="n">
-        <v>6808048</v>
+        <v>6808172</v>
       </c>
       <c r="S21" t="n">
         <v>20</v>
@@ -2750,10 +2750,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>123829310</v>
+        <v>123828739</v>
       </c>
       <c r="B22" t="n">
-        <v>57529</v>
+        <v>56722</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2762,31 +2762,31 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>100049</v>
+        <v>100138</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
       <c r="M22" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färsk spillning</t>
         </is>
       </c>
       <c r="P22" t="inlineStr">
@@ -2795,10 +2795,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>459586</v>
+        <v>459636</v>
       </c>
       <c r="R22" t="n">
-        <v>6807981</v>
+        <v>6808042</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2857,10 +2857,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>123829394</v>
+        <v>123829941</v>
       </c>
       <c r="B23" t="n">
-        <v>77738</v>
+        <v>78547</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2873,21 +2873,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6487</v>
+        <v>228912</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Blågrå svartspik</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Chaenothecopsis fennica</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Laurila) Tibell</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2897,10 +2897,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>459586</v>
+        <v>459480</v>
       </c>
       <c r="R23" t="n">
-        <v>6807981</v>
+        <v>6808013</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2933,6 +2933,11 @@
       <c r="AA23" t="inlineStr">
         <is>
           <t>2025-04-07</t>
+        </is>
+      </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>Miljöbild.</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -2959,10 +2964,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>123829205</v>
+        <v>123831467</v>
       </c>
       <c r="B24" t="n">
-        <v>78546</v>
+        <v>79399</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -2975,37 +2980,37 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6446</v>
+        <v>229821</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Andljusbäcken, Andljusbäcken, Dlr</t>
+          <t>Härkämäck, Härkämäck, Dlr</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>459611</v>
+        <v>459290</v>
       </c>
       <c r="R24" t="n">
-        <v>6807987</v>
+        <v>6808098</v>
       </c>
       <c r="S24" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3049,22 +3054,22 @@
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Niklas Rehn</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Niklas Rehn</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>123833917</v>
+        <v>123828742</v>
       </c>
       <c r="B25" t="n">
-        <v>78547</v>
+        <v>78810</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3077,21 +3082,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3101,10 +3106,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>459292</v>
+        <v>459612</v>
       </c>
       <c r="R25" t="n">
-        <v>6808184</v>
+        <v>6808068</v>
       </c>
       <c r="S25" t="n">
         <v>20</v>
@@ -3163,10 +3168,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>123831067</v>
+        <v>123834630</v>
       </c>
       <c r="B26" t="n">
-        <v>78810</v>
+        <v>57534</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3175,38 +3180,38 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6425</v>
+        <v>100110</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gråspett</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picus canus</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>J.F. Gmelin, 1788</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Härkämäck, Dlr</t>
+          <t>Härkämäck, Härkämäck, Dlr</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>459439</v>
+        <v>459408</v>
       </c>
       <c r="R26" t="n">
-        <v>6808067</v>
+        <v>6808198</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3243,7 +3248,7 @@
       </c>
       <c r="AC26" t="inlineStr">
         <is>
-          <t>Synligt i en radie av ca 50 meter. Miljöbild.</t>
+          <t>Förbiflygande.</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3258,22 +3263,22 @@
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>123828739</v>
+        <v>123834966</v>
       </c>
       <c r="B27" t="n">
-        <v>56722</v>
+        <v>57534</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3286,27 +3291,27 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>100138</v>
+        <v>100110</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Gråspett</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Picus canus</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>J.F. Gmelin, 1788</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
       <c r="M27" t="inlineStr">
         <is>
-          <t>färsk spillning</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="P27" t="inlineStr">
@@ -3315,10 +3320,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>459636</v>
+        <v>459399</v>
       </c>
       <c r="R27" t="n">
-        <v>6808042</v>
+        <v>6808189</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3351,6 +3356,11 @@
       <c r="AA27" t="inlineStr">
         <is>
           <t>2025-04-07</t>
+        </is>
+      </c>
+      <c r="AC27" t="inlineStr">
+        <is>
+          <t>Förbiflygande.</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3377,10 +3387,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>123829982</v>
+        <v>123831244</v>
       </c>
       <c r="B28" t="n">
-        <v>77738</v>
+        <v>78810</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3393,21 +3403,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6487</v>
+        <v>6425</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Blågrå svartspik</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Chaenothecopsis fennica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Laurila) Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3417,10 +3427,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>459432</v>
+        <v>459393</v>
       </c>
       <c r="R28" t="n">
-        <v>6807989</v>
+        <v>6808027</v>
       </c>
       <c r="S28" t="n">
         <v>20</v>
@@ -3479,10 +3489,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>123829197</v>
+        <v>123834034</v>
       </c>
       <c r="B29" t="n">
-        <v>78547</v>
+        <v>57529</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3495,37 +3505,42 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>228912</v>
+        <v>100049</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Andljusbäcken, Andljusbäcken, Dlr</t>
+          <t>Andljusen, Dlr</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>459611</v>
+        <v>459325</v>
       </c>
       <c r="R29" t="n">
-        <v>6807987</v>
+        <v>6808176</v>
       </c>
       <c r="S29" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3555,6 +3570,11 @@
       <c r="AA29" t="inlineStr">
         <is>
           <t>2025-04-07</t>
+        </is>
+      </c>
+      <c r="AC29" t="inlineStr">
+        <is>
+          <t>Miljöbild.</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3569,22 +3589,22 @@
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>123829941</v>
+        <v>123828608</v>
       </c>
       <c r="B30" t="n">
-        <v>78547</v>
+        <v>78810</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3597,21 +3617,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3621,10 +3641,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>459480</v>
+        <v>459636</v>
       </c>
       <c r="R30" t="n">
-        <v>6808013</v>
+        <v>6808042</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3661,7 +3681,7 @@
       </c>
       <c r="AC30" t="inlineStr">
         <is>
-          <t>Miljöbild.</t>
+          <t>Garnlav i synfältet i en radie av ca 50 meter. Miljöbilder.</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3688,10 +3708,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>123829879</v>
+        <v>123828882</v>
       </c>
       <c r="B31" t="n">
-        <v>78810</v>
+        <v>78842</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3704,21 +3724,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3728,10 +3748,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>459488</v>
+        <v>459600</v>
       </c>
       <c r="R31" t="n">
-        <v>6807974</v>
+        <v>6808030</v>
       </c>
       <c r="S31" t="n">
         <v>20</v>
@@ -3790,7 +3810,7 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>123834998</v>
+        <v>123834567</v>
       </c>
       <c r="B32" t="n">
         <v>79399</v>
@@ -3826,17 +3846,17 @@
       <c r="I32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Härkämäck, Härkämäck, Dlr</t>
+          <t>Härkämäck, Dlr</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>459437</v>
+        <v>459399</v>
       </c>
       <c r="R32" t="n">
-        <v>6808171</v>
+        <v>6808189</v>
       </c>
       <c r="S32" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -3866,6 +3886,11 @@
       <c r="AA32" t="inlineStr">
         <is>
           <t>2025-04-07</t>
+        </is>
+      </c>
+      <c r="AC32" t="inlineStr">
+        <is>
+          <t>Miljöbild.</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -3880,22 +3905,22 @@
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>123833754</v>
+        <v>123835432</v>
       </c>
       <c r="B33" t="n">
-        <v>92293</v>
+        <v>78810</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -3904,41 +3929,41 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Härkämäck, Härkämäck, Dlr</t>
+          <t>Härkämäck, Dlr</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>459290</v>
+        <v>459524</v>
       </c>
       <c r="R33" t="n">
-        <v>6808093</v>
+        <v>6808114</v>
       </c>
       <c r="S33" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -3968,6 +3993,11 @@
       <c r="AA33" t="inlineStr">
         <is>
           <t>2025-04-07</t>
+        </is>
+      </c>
+      <c r="AC33" t="inlineStr">
+        <is>
+          <t>Garnlav i alla riktningar, ca 50 meter i radie. Miljöbild.</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -3982,22 +4012,22 @@
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>123829632</v>
+        <v>123829102</v>
       </c>
       <c r="B34" t="n">
-        <v>91299</v>
+        <v>78810</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4010,37 +4040,37 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>658</v>
+        <v>6425</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Härkämäck, Dlr</t>
+          <t>Andljusbäcken, Andljusbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>459573</v>
+        <v>459666</v>
       </c>
       <c r="R34" t="n">
-        <v>6808047</v>
+        <v>6807990</v>
       </c>
       <c r="S34" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -4084,22 +4114,22 @@
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>123834034</v>
+        <v>123829632</v>
       </c>
       <c r="B35" t="n">
-        <v>57529</v>
+        <v>91299</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4112,39 +4142,34 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>100049</v>
+        <v>658</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
-      <c r="M35" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Andljusen, Dlr</t>
+          <t>Härkämäck, Dlr</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>459325</v>
+        <v>459573</v>
       </c>
       <c r="R35" t="n">
-        <v>6808176</v>
+        <v>6808047</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4177,11 +4202,6 @@
       <c r="AA35" t="inlineStr">
         <is>
           <t>2025-04-07</t>
-        </is>
-      </c>
-      <c r="AC35" t="inlineStr">
-        <is>
-          <t>Miljöbild.</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4208,10 +4228,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>123827957</v>
+        <v>123834195</v>
       </c>
       <c r="B36" t="n">
-        <v>78546</v>
+        <v>78547</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4224,37 +4244,37 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6446</v>
+        <v>228912</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Andljusbäcken, Andljusbäcken, Dlr</t>
+          <t>Härkämäck, Härkämäck, Dlr</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>459664</v>
+        <v>459365</v>
       </c>
       <c r="R36" t="n">
-        <v>6808079</v>
+        <v>6808224</v>
       </c>
       <c r="S36" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -4298,22 +4318,22 @@
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>123834220</v>
+        <v>123834890</v>
       </c>
       <c r="B37" t="n">
-        <v>78810</v>
+        <v>78889</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4326,37 +4346,37 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6425</v>
+        <v>864</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Lynge) Ahti</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
-          <t>Andljusen, Dlr</t>
+          <t>Härkämäck, Härkämäck, Dlr</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>459325</v>
+        <v>459427</v>
       </c>
       <c r="R37" t="n">
-        <v>6808176</v>
+        <v>6808130</v>
       </c>
       <c r="S37" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -4386,11 +4406,6 @@
       <c r="AA37" t="inlineStr">
         <is>
           <t>2025-04-07</t>
-        </is>
-      </c>
-      <c r="AC37" t="inlineStr">
-        <is>
-          <t>I synfält, radie av ca 50 meter. Miljöbild.</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4405,22 +4420,22 @@
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>123828882</v>
+        <v>123831067</v>
       </c>
       <c r="B38" t="n">
-        <v>78842</v>
+        <v>78810</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4433,37 +4448,37 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
-          <t>Andljusbäcken, Andljusbäcken, Dlr</t>
+          <t>Härkämäck, Dlr</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>459600</v>
+        <v>459439</v>
       </c>
       <c r="R38" t="n">
-        <v>6808030</v>
+        <v>6808067</v>
       </c>
       <c r="S38" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -4493,6 +4508,11 @@
       <c r="AA38" t="inlineStr">
         <is>
           <t>2025-04-07</t>
+        </is>
+      </c>
+      <c r="AC38" t="inlineStr">
+        <is>
+          <t>Synligt i en radie av ca 50 meter. Miljöbild.</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4507,19 +4527,19 @@
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>123829246</v>
+        <v>123834220</v>
       </c>
       <c r="B39" t="n">
         <v>78810</v>
@@ -4555,14 +4575,14 @@
       <c r="I39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
-          <t>Härkämäck, Dlr</t>
+          <t>Andljusen, Dlr</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>459586</v>
+        <v>459325</v>
       </c>
       <c r="R39" t="n">
-        <v>6807981</v>
+        <v>6808176</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4599,7 +4619,7 @@
       </c>
       <c r="AC39" t="inlineStr">
         <is>
-          <t>Som vanligt garnlav i omgivningen. Miljöbilder.</t>
+          <t>I synfält, radie av ca 50 meter. Miljöbild.</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4626,10 +4646,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>123831277</v>
+        <v>123828783</v>
       </c>
       <c r="B40" t="n">
-        <v>57529</v>
+        <v>78810</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -4642,42 +4662,37 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
-      <c r="M40" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P40" t="inlineStr">
         <is>
-          <t>Härkämäck, Dlr</t>
+          <t>Andljusbäcken, Andljusbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>459389</v>
+        <v>459611</v>
       </c>
       <c r="R40" t="n">
-        <v>6808070</v>
+        <v>6808048</v>
       </c>
       <c r="S40" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T40" t="inlineStr">
         <is>
@@ -4707,11 +4722,6 @@
       <c r="AA40" t="inlineStr">
         <is>
           <t>2025-04-07</t>
-        </is>
-      </c>
-      <c r="AC40" t="inlineStr">
-        <is>
-          <t>Miljöbild.</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4726,22 +4736,22 @@
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>123831097</v>
+        <v>123833729</v>
       </c>
       <c r="B41" t="n">
-        <v>79399</v>
+        <v>78547</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -4754,37 +4764,37 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>229821</v>
+        <v>228912</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
-          <t>Andljusbäcken, Andljusbäcken, Dlr</t>
+          <t>Andljusen, Dlr</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>459402</v>
+        <v>459286</v>
       </c>
       <c r="R41" t="n">
-        <v>6808072</v>
+        <v>6808090</v>
       </c>
       <c r="S41" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -4814,6 +4824,11 @@
       <c r="AA41" t="inlineStr">
         <is>
           <t>2025-04-07</t>
+        </is>
+      </c>
+      <c r="AC41" t="inlineStr">
+        <is>
+          <t>Miljöbild.</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -4828,22 +4843,22 @@
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>123835432</v>
+        <v>123834998</v>
       </c>
       <c r="B42" t="n">
-        <v>78810</v>
+        <v>79399</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -4856,37 +4871,37 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6425</v>
+        <v>229821</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
-          <t>Härkämäck, Dlr</t>
+          <t>Härkämäck, Härkämäck, Dlr</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>459524</v>
+        <v>459437</v>
       </c>
       <c r="R42" t="n">
-        <v>6808114</v>
+        <v>6808171</v>
       </c>
       <c r="S42" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -4916,11 +4931,6 @@
       <c r="AA42" t="inlineStr">
         <is>
           <t>2025-04-07</t>
-        </is>
-      </c>
-      <c r="AC42" t="inlineStr">
-        <is>
-          <t>Garnlav i alla riktningar, ca 50 meter i radie. Miljöbild.</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -4935,22 +4945,22 @@
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>123834966</v>
+        <v>123829246</v>
       </c>
       <c r="B43" t="n">
-        <v>57534</v>
+        <v>78810</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -4959,43 +4969,38 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>100110</v>
+        <v>6425</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Gråspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Picus canus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>J.F. Gmelin, 1788</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
-      <c r="M43" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="P43" t="inlineStr">
         <is>
           <t>Härkämäck, Dlr</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>459399</v>
+        <v>459586</v>
       </c>
       <c r="R43" t="n">
-        <v>6808189</v>
+        <v>6807981</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5032,7 +5037,7 @@
       </c>
       <c r="AC43" t="inlineStr">
         <is>
-          <t>Förbiflygande.</t>
+          <t>Som vanligt garnlav i omgivningen. Miljöbilder.</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5059,10 +5064,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>123833729</v>
+        <v>123828044</v>
       </c>
       <c r="B44" t="n">
-        <v>78547</v>
+        <v>78810</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5075,34 +5080,34 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
-          <t>Andljusen, Dlr</t>
+          <t>Härkämäck, Dlr</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>459286</v>
+        <v>459681</v>
       </c>
       <c r="R44" t="n">
-        <v>6808090</v>
+        <v>6808072</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5139,7 +5144,7 @@
       </c>
       <c r="AC44" t="inlineStr">
         <is>
-          <t>Miljöbild.</t>
+          <t>Garnlav i synfältet i en radie av ca 50 meter. Miljöbild.</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5166,10 +5171,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>123831467</v>
+        <v>123835135</v>
       </c>
       <c r="B45" t="n">
-        <v>79399</v>
+        <v>78810</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5182,34 +5187,34 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>229821</v>
+        <v>6425</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
-          <t>Härkämäck, Härkämäck, Dlr</t>
+          <t>Härkämäck, Dlr</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>459290</v>
+        <v>459455</v>
       </c>
       <c r="R45" t="n">
-        <v>6808098</v>
+        <v>6808164</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5244,6 +5249,11 @@
           <t>2025-04-07</t>
         </is>
       </c>
+      <c r="AC45" t="inlineStr">
+        <is>
+          <t>Garnlav i en radie av ca 50 meter, synfältet. Miljöbild.</t>
+        </is>
+      </c>
       <c r="AD45" t="b">
         <v>0</v>
       </c>
@@ -5256,22 +5266,22 @@
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
         <is>
-          <t>Niklas Rehn</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>Niklas Rehn</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>123835135</v>
+        <v>123829712</v>
       </c>
       <c r="B46" t="n">
-        <v>78810</v>
+        <v>91012</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5284,21 +5294,21 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5308,10 +5318,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>459455</v>
+        <v>459573</v>
       </c>
       <c r="R46" t="n">
-        <v>6808164</v>
+        <v>6808047</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5344,11 +5354,6 @@
       <c r="AA46" t="inlineStr">
         <is>
           <t>2025-04-07</t>
-        </is>
-      </c>
-      <c r="AC46" t="inlineStr">
-        <is>
-          <t>Garnlav i en radie av ca 50 meter, synfältet. Miljöbild.</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5375,10 +5380,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>123834567</v>
+        <v>123830920</v>
       </c>
       <c r="B47" t="n">
-        <v>79399</v>
+        <v>78455</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5391,37 +5396,37 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>229821</v>
+        <v>353</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
-          <t>Härkämäck, Dlr</t>
+          <t>Andljusbäcken, Andljusbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>459399</v>
+        <v>459462</v>
       </c>
       <c r="R47" t="n">
-        <v>6808189</v>
+        <v>6808078</v>
       </c>
       <c r="S47" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T47" t="inlineStr">
         <is>
@@ -5451,11 +5456,6 @@
       <c r="AA47" t="inlineStr">
         <is>
           <t>2025-04-07</t>
-        </is>
-      </c>
-      <c r="AC47" t="inlineStr">
-        <is>
-          <t>Miljöbild.</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5470,22 +5470,22 @@
       <c r="AT47" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX47" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>123829275</v>
+        <v>123829205</v>
       </c>
       <c r="B48" t="n">
-        <v>78547</v>
+        <v>78546</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -5498,21 +5498,21 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>228912</v>
+        <v>6446</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5522,10 +5522,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>459544</v>
+        <v>459611</v>
       </c>
       <c r="R48" t="n">
-        <v>6807989</v>
+        <v>6807987</v>
       </c>
       <c r="S48" t="n">
         <v>20</v>
@@ -5584,10 +5584,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>123834890</v>
+        <v>123829879</v>
       </c>
       <c r="B49" t="n">
-        <v>78889</v>
+        <v>78810</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -5600,34 +5600,34 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>864</v>
+        <v>6425</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Knottrig blåslav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Hypogymnia bitteri</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Lynge) Ahti</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
-          <t>Härkämäck, Härkämäck, Dlr</t>
+          <t>Andljusbäcken, Andljusbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>459427</v>
+        <v>459488</v>
       </c>
       <c r="R49" t="n">
-        <v>6808130</v>
+        <v>6807974</v>
       </c>
       <c r="S49" t="n">
         <v>20</v>
@@ -5686,10 +5686,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>123829889</v>
+        <v>123831578</v>
       </c>
       <c r="B50" t="n">
-        <v>78547</v>
+        <v>74901</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -5702,37 +5702,37 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>228912</v>
+        <v>6440</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
-          <t>Härkämäck, Dlr</t>
+          <t>Andljusbäcken, Andljusbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>459494</v>
+        <v>459287</v>
       </c>
       <c r="R50" t="n">
-        <v>6807997</v>
+        <v>6808008</v>
       </c>
       <c r="S50" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T50" t="inlineStr">
         <is>
@@ -5762,11 +5762,6 @@
       <c r="AA50" t="inlineStr">
         <is>
           <t>2025-04-07</t>
-        </is>
-      </c>
-      <c r="AC50" t="inlineStr">
-        <is>
-          <t>Miljöbild.</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -5781,22 +5776,22 @@
       <c r="AT50" t="inlineStr"/>
       <c r="AW50" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX50" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>123834183</v>
+        <v>123834650</v>
       </c>
       <c r="B51" t="n">
-        <v>78810</v>
+        <v>78547</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -5809,37 +5804,37 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
-          <t>Andljusbäcken, Andljusbäcken, Dlr</t>
+          <t>Härkämäck, Dlr</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>459373</v>
+        <v>459399</v>
       </c>
       <c r="R51" t="n">
-        <v>6808222</v>
+        <v>6808189</v>
       </c>
       <c r="S51" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T51" t="inlineStr">
         <is>
@@ -5869,6 +5864,11 @@
       <c r="AA51" t="inlineStr">
         <is>
           <t>2025-04-07</t>
+        </is>
+      </c>
+      <c r="AC51" t="inlineStr">
+        <is>
+          <t>Miljöbild</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -5883,22 +5883,22 @@
       <c r="AT51" t="inlineStr"/>
       <c r="AW51" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX51" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>123829102</v>
+        <v>123834006</v>
       </c>
       <c r="B52" t="n">
-        <v>78810</v>
+        <v>78547</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -5911,37 +5911,37 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
-          <t>Andljusbäcken, Andljusbäcken, Dlr</t>
+          <t>Härkämäck, Härkämäck, Dlr</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>459666</v>
+        <v>459326</v>
       </c>
       <c r="R52" t="n">
-        <v>6807990</v>
+        <v>6808188</v>
       </c>
       <c r="S52" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T52" t="inlineStr">
         <is>
@@ -5985,19 +5985,19 @@
       <c r="AT52" t="inlineStr"/>
       <c r="AW52" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX52" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>123920731</v>
+        <v>123920732</v>
       </c>
       <c r="B53" t="n">
         <v>78810</v>
@@ -6037,10 +6037,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>459608</v>
+        <v>459616</v>
       </c>
       <c r="R53" t="n">
-        <v>6808066</v>
+        <v>6808044</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6099,10 +6099,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>123920930</v>
+        <v>123920728</v>
       </c>
       <c r="B54" t="n">
-        <v>78455</v>
+        <v>78810</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -6115,21 +6115,21 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -6139,10 +6139,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>459600</v>
+        <v>459539</v>
       </c>
       <c r="R54" t="n">
-        <v>6807961</v>
+        <v>6808073</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6201,10 +6201,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>123920399</v>
+        <v>123920730</v>
       </c>
       <c r="B55" t="n">
-        <v>79399</v>
+        <v>78810</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -6217,21 +6217,21 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>229821</v>
+        <v>6425</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -6241,10 +6241,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>459591</v>
+        <v>459590</v>
       </c>
       <c r="R55" t="n">
-        <v>6808065</v>
+        <v>6808062</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6296,17 +6296,17 @@
       </c>
       <c r="AX55" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Anders Heggestad, Håkan Thenander, lennart karlsson, Niklas Rehn</t>
+          <t>Philipp Weiss, Anders Heggestad, lennart karlsson, Håkan Thenander, Niklas Rehn</t>
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>123920732</v>
+        <v>123920440</v>
       </c>
       <c r="B56" t="n">
-        <v>78810</v>
+        <v>56722</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -6315,38 +6315,43 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
+      <c r="M56" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="P56" t="inlineStr">
         <is>
           <t>Härkämäck, Dlr</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>459616</v>
+        <v>459617</v>
       </c>
       <c r="R56" t="n">
-        <v>6808044</v>
+        <v>6808041</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6398,17 +6403,17 @@
       </c>
       <c r="AX56" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Anders Heggestad, lennart karlsson, Håkan Thenander, Niklas Rehn</t>
+          <t>Philipp Weiss, Anders Heggestad, Håkan Thenander, lennart karlsson, Niklas Rehn</t>
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>123920733</v>
+        <v>123920540</v>
       </c>
       <c r="B57" t="n">
-        <v>78810</v>
+        <v>78547</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -6421,21 +6426,21 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6507,10 +6512,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>123920734</v>
+        <v>123920419</v>
       </c>
       <c r="B58" t="n">
-        <v>78810</v>
+        <v>91012</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
@@ -6523,21 +6528,21 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -6547,10 +6552,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>459613</v>
+        <v>459603</v>
       </c>
       <c r="R58" t="n">
-        <v>6807959</v>
+        <v>6807965</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6602,14 +6607,14 @@
       </c>
       <c r="AX58" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Anders Heggestad, lennart karlsson, Håkan Thenander, Niklas Rehn</t>
+          <t>Philipp Weiss, Anders Heggestad, Håkan Thenander, lennart karlsson, Niklas Rehn</t>
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>123920441</v>
+        <v>123920442</v>
       </c>
       <c r="B59" t="n">
         <v>56722</v>
@@ -6654,10 +6659,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>459609</v>
+        <v>459593</v>
       </c>
       <c r="R59" t="n">
-        <v>6807987</v>
+        <v>6807978</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6709,17 +6714,17 @@
       </c>
       <c r="AX59" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Niklas Rehn, lennart karlsson, Håkan Thenander, Anders Heggestad</t>
+          <t>Philipp Weiss, Anders Heggestad, Håkan Thenander, lennart karlsson, Niklas Rehn</t>
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>123920540</v>
+        <v>123920930</v>
       </c>
       <c r="B60" t="n">
-        <v>78547</v>
+        <v>78455</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
@@ -6732,21 +6737,21 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>228912</v>
+        <v>353</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -6756,10 +6761,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>459589</v>
+        <v>459600</v>
       </c>
       <c r="R60" t="n">
-        <v>6807980</v>
+        <v>6807961</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6811,7 +6816,7 @@
       </c>
       <c r="AX60" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Niklas Rehn, Håkan Thenander, lennart karlsson, Anders Heggestad</t>
+          <t>Philipp Weiss, Anders Heggestad, lennart karlsson, Håkan Thenander, Niklas Rehn</t>
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
@@ -6920,10 +6925,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>123920442</v>
+        <v>123920733</v>
       </c>
       <c r="B62" t="n">
-        <v>56722</v>
+        <v>78810</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
@@ -6932,43 +6937,38 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
-      <c r="M62" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="P62" t="inlineStr">
         <is>
           <t>Härkämäck, Dlr</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>459593</v>
+        <v>459589</v>
       </c>
       <c r="R62" t="n">
-        <v>6807978</v>
+        <v>6807980</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -7020,17 +7020,17 @@
       </c>
       <c r="AX62" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Anders Heggestad, Håkan Thenander, lennart karlsson, Niklas Rehn</t>
+          <t>Philipp Weiss, Anders Heggestad, lennart karlsson, Håkan Thenander, Niklas Rehn</t>
         </is>
       </c>
       <c r="AY62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>123920440</v>
+        <v>123920734</v>
       </c>
       <c r="B63" t="n">
-        <v>56722</v>
+        <v>78810</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
@@ -7039,43 +7039,38 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
-      <c r="M63" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="P63" t="inlineStr">
         <is>
           <t>Härkämäck, Dlr</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>459617</v>
+        <v>459613</v>
       </c>
       <c r="R63" t="n">
-        <v>6808041</v>
+        <v>6807959</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -7127,17 +7122,17 @@
       </c>
       <c r="AX63" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Niklas Rehn, lennart karlsson, Håkan Thenander, Anders Heggestad</t>
+          <t>Philipp Weiss, Anders Heggestad, lennart karlsson, Håkan Thenander, Niklas Rehn</t>
         </is>
       </c>
       <c r="AY63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>123920727</v>
+        <v>123920427</v>
       </c>
       <c r="B64" t="n">
-        <v>78810</v>
+        <v>57513</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
@@ -7150,34 +7145,39 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
+      <c r="M64" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="P64" t="inlineStr">
         <is>
           <t>Härkämäck, Dlr</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>459542</v>
+        <v>459571</v>
       </c>
       <c r="R64" t="n">
-        <v>6808123</v>
+        <v>6808057</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7229,17 +7229,17 @@
       </c>
       <c r="AX64" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Anders Heggestad, lennart karlsson, Håkan Thenander, Niklas Rehn</t>
+          <t>Philipp Weiss, Anders Heggestad, Håkan Thenander, lennart karlsson, Niklas Rehn</t>
         </is>
       </c>
       <c r="AY64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>123920419</v>
+        <v>123920441</v>
       </c>
       <c r="B65" t="n">
-        <v>91012</v>
+        <v>56722</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
@@ -7248,38 +7248,43 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>1202</v>
+        <v>100138</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
+      <c r="M65" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="P65" t="inlineStr">
         <is>
           <t>Härkämäck, Dlr</t>
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>459603</v>
+        <v>459609</v>
       </c>
       <c r="R65" t="n">
-        <v>6807965</v>
+        <v>6807987</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7338,10 +7343,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>123920728</v>
+        <v>123920399</v>
       </c>
       <c r="B66" t="n">
-        <v>78810</v>
+        <v>79399</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
@@ -7354,21 +7359,21 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>6425</v>
+        <v>229821</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
@@ -7378,10 +7383,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>459539</v>
+        <v>459591</v>
       </c>
       <c r="R66" t="n">
-        <v>6808073</v>
+        <v>6808065</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7433,14 +7438,14 @@
       </c>
       <c r="AX66" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Anders Heggestad, lennart karlsson, Håkan Thenander, Niklas Rehn</t>
+          <t>Philipp Weiss, Anders Heggestad, Håkan Thenander, lennart karlsson, Niklas Rehn</t>
         </is>
       </c>
       <c r="AY66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>123920730</v>
+        <v>123920731</v>
       </c>
       <c r="B67" t="n">
         <v>78810</v>
@@ -7480,10 +7485,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>459590</v>
+        <v>459608</v>
       </c>
       <c r="R67" t="n">
-        <v>6808062</v>
+        <v>6808066</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7542,10 +7547,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>123920427</v>
+        <v>123920727</v>
       </c>
       <c r="B68" t="n">
-        <v>57513</v>
+        <v>78810</v>
       </c>
       <c r="C68" t="inlineStr">
         <is>
@@ -7558,39 +7563,34 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
-      <c r="M68" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
       <c r="P68" t="inlineStr">
         <is>
           <t>Härkämäck, Dlr</t>
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>459571</v>
+        <v>459542</v>
       </c>
       <c r="R68" t="n">
-        <v>6808057</v>
+        <v>6808123</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7642,7 +7642,7 @@
       </c>
       <c r="AX68" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Niklas Rehn, lennart karlsson, Håkan Thenander, Anders Heggestad</t>
+          <t>Philipp Weiss, Anders Heggestad, lennart karlsson, Håkan Thenander, Niklas Rehn</t>
         </is>
       </c>
       <c r="AY68" t="inlineStr"/>

--- a/artfynd/A 61327-2022 artfynd.xlsx
+++ b/artfynd/A 61327-2022 artfynd.xlsx
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123833917</v>
+        <v>123829246</v>
       </c>
       <c r="B3" t="n">
-        <v>78547</v>
+        <v>78810</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -793,37 +793,37 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Andljusbäcken, Andljusbäcken, Dlr</t>
+          <t>Härkämäck, Dlr</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>459292</v>
+        <v>459586</v>
       </c>
       <c r="R3" t="n">
-        <v>6808184</v>
+        <v>6807981</v>
       </c>
       <c r="S3" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -853,6 +853,11 @@
       <c r="AA3" t="inlineStr">
         <is>
           <t>2025-04-07</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Som vanligt garnlav i omgivningen. Miljöbilder.</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -867,22 +872,22 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123831097</v>
+        <v>123833814</v>
       </c>
       <c r="B4" t="n">
-        <v>79399</v>
+        <v>78547</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -895,37 +900,37 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>229821</v>
+        <v>228912</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Andljusbäcken, Andljusbäcken, Dlr</t>
+          <t>Härkämäck, Härkämäck, Dlr</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>459402</v>
+        <v>459293</v>
       </c>
       <c r="R4" t="n">
-        <v>6808072</v>
+        <v>6808123</v>
       </c>
       <c r="S4" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -969,22 +974,22 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123833754</v>
+        <v>123834650</v>
       </c>
       <c r="B5" t="n">
-        <v>92293</v>
+        <v>78547</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -993,41 +998,41 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>4364</v>
+        <v>228912</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Härkämäck, Härkämäck, Dlr</t>
+          <t>Härkämäck, Dlr</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>459290</v>
+        <v>459399</v>
       </c>
       <c r="R5" t="n">
-        <v>6808093</v>
+        <v>6808189</v>
       </c>
       <c r="S5" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1057,6 +1062,11 @@
       <c r="AA5" t="inlineStr">
         <is>
           <t>2025-04-07</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Miljöbild</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1071,22 +1081,22 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>123829918</v>
+        <v>123829941</v>
       </c>
       <c r="B6" t="n">
-        <v>78546</v>
+        <v>78547</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1099,37 +1109,37 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6446</v>
+        <v>228912</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Andljusbäcken, Andljusbäcken, Dlr</t>
+          <t>Härkämäck, Dlr</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>459424</v>
+        <v>459480</v>
       </c>
       <c r="R6" t="n">
-        <v>6807998</v>
+        <v>6808013</v>
       </c>
       <c r="S6" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1159,6 +1169,11 @@
       <c r="AA6" t="inlineStr">
         <is>
           <t>2025-04-07</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Miljöbild.</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1173,22 +1188,22 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>123829982</v>
+        <v>123829889</v>
       </c>
       <c r="B7" t="n">
-        <v>77738</v>
+        <v>78547</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1201,37 +1216,37 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6487</v>
+        <v>228912</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Blågrå svartspik</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Chaenothecopsis fennica</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Laurila) Tibell</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Andljusbäcken, Andljusbäcken, Dlr</t>
+          <t>Härkämäck, Dlr</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>459432</v>
+        <v>459494</v>
       </c>
       <c r="R7" t="n">
-        <v>6807989</v>
+        <v>6807997</v>
       </c>
       <c r="S7" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1261,6 +1276,11 @@
       <c r="AA7" t="inlineStr">
         <is>
           <t>2025-04-07</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Miljöbild.</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1275,22 +1295,22 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>123833841</v>
+        <v>123833729</v>
       </c>
       <c r="B8" t="n">
-        <v>78810</v>
+        <v>78547</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1303,37 +1323,37 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Härkämäck, Härkämäck, Dlr</t>
+          <t>Andljusen, Dlr</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>459300</v>
+        <v>459286</v>
       </c>
       <c r="R8" t="n">
-        <v>6808144</v>
+        <v>6808090</v>
       </c>
       <c r="S8" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1363,6 +1383,11 @@
       <c r="AA8" t="inlineStr">
         <is>
           <t>2025-04-07</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Miljöbild.</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1377,22 +1402,22 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>123827957</v>
+        <v>123831467</v>
       </c>
       <c r="B9" t="n">
-        <v>78546</v>
+        <v>79399</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1405,37 +1430,37 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6446</v>
+        <v>229821</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Andljusbäcken, Andljusbäcken, Dlr</t>
+          <t>Härkämäck, Härkämäck, Dlr</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>459664</v>
+        <v>459290</v>
       </c>
       <c r="R9" t="n">
-        <v>6808079</v>
+        <v>6808098</v>
       </c>
       <c r="S9" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1479,22 +1504,22 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Niklas Rehn</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Niklas Rehn</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>123829310</v>
+        <v>123834183</v>
       </c>
       <c r="B10" t="n">
-        <v>57529</v>
+        <v>78810</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1507,42 +1532,37 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Härkämäck, Dlr</t>
+          <t>Andljusbäcken, Andljusbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>459586</v>
+        <v>459373</v>
       </c>
       <c r="R10" t="n">
-        <v>6807981</v>
+        <v>6808222</v>
       </c>
       <c r="S10" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1586,22 +1606,22 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>123830162</v>
+        <v>123834641</v>
       </c>
       <c r="B11" t="n">
-        <v>78194</v>
+        <v>78810</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1614,37 +1634,37 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6437</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Härkämäck, Dlr</t>
+          <t>Härkämäck, Härkämäck, Dlr</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>459480</v>
+        <v>459405</v>
       </c>
       <c r="R11" t="n">
-        <v>6808013</v>
+        <v>6808172</v>
       </c>
       <c r="S11" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1674,11 +1694,6 @@
       <c r="AA11" t="inlineStr">
         <is>
           <t>2025-04-07</t>
-        </is>
-      </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>Miljöbild.</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1693,22 +1708,22 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>123829275</v>
+        <v>123834220</v>
       </c>
       <c r="B12" t="n">
-        <v>78547</v>
+        <v>78810</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1721,37 +1736,37 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Andljusbäcken, Andljusbäcken, Dlr</t>
+          <t>Andljusen, Dlr</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>459544</v>
+        <v>459325</v>
       </c>
       <c r="R12" t="n">
-        <v>6807989</v>
+        <v>6808176</v>
       </c>
       <c r="S12" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1781,6 +1796,11 @@
       <c r="AA12" t="inlineStr">
         <is>
           <t>2025-04-07</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>I synfält, radie av ca 50 meter. Miljöbild.</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1795,22 +1815,22 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>123829394</v>
+        <v>123828742</v>
       </c>
       <c r="B13" t="n">
-        <v>77738</v>
+        <v>78810</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1823,37 +1843,37 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6487</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Blågrå svartspik</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Chaenothecopsis fennica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Laurila) Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Härkämäck, Dlr</t>
+          <t>Andljusbäcken, Andljusbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>459586</v>
+        <v>459612</v>
       </c>
       <c r="R13" t="n">
-        <v>6807981</v>
+        <v>6808068</v>
       </c>
       <c r="S13" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1897,22 +1917,22 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>123831277</v>
+        <v>123831067</v>
       </c>
       <c r="B14" t="n">
-        <v>57529</v>
+        <v>78810</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1925,39 +1945,34 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P14" t="inlineStr">
         <is>
           <t>Härkämäck, Dlr</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>459389</v>
+        <v>459439</v>
       </c>
       <c r="R14" t="n">
-        <v>6808070</v>
+        <v>6808067</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1994,7 +2009,7 @@
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>Miljöbild.</t>
+          <t>Synligt i en radie av ca 50 meter. Miljöbild.</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2021,10 +2036,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>123829889</v>
+        <v>123828882</v>
       </c>
       <c r="B15" t="n">
-        <v>78547</v>
+        <v>78842</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2037,37 +2052,37 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>228912</v>
+        <v>185</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Härkämäck, Dlr</t>
+          <t>Andljusbäcken, Andljusbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>459494</v>
+        <v>459600</v>
       </c>
       <c r="R15" t="n">
-        <v>6807997</v>
+        <v>6808030</v>
       </c>
       <c r="S15" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2097,11 +2112,6 @@
       <c r="AA15" t="inlineStr">
         <is>
           <t>2025-04-07</t>
-        </is>
-      </c>
-      <c r="AC15" t="inlineStr">
-        <is>
-          <t>Miljöbild.</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2116,22 +2126,22 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>123829121</v>
+        <v>123834034</v>
       </c>
       <c r="B16" t="n">
-        <v>78810</v>
+        <v>57529</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2144,34 +2154,39 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Härkämäck, Dlr</t>
+          <t>Andljusen, Dlr</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>459641</v>
+        <v>459325</v>
       </c>
       <c r="R16" t="n">
-        <v>6807971</v>
+        <v>6808176</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2208,7 +2223,7 @@
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>I synfältet i en radie av ca 40 meter. Miljöbild.</t>
+          <t>Miljöbild.</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2235,10 +2250,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>123834183</v>
+        <v>123829310</v>
       </c>
       <c r="B17" t="n">
-        <v>78810</v>
+        <v>57529</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2251,37 +2266,42 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Andljusbäcken, Andljusbäcken, Dlr</t>
+          <t>Härkämäck, Dlr</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>459373</v>
+        <v>459586</v>
       </c>
       <c r="R17" t="n">
-        <v>6808222</v>
+        <v>6807981</v>
       </c>
       <c r="S17" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2325,19 +2345,19 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>123833814</v>
+        <v>123829197</v>
       </c>
       <c r="B18" t="n">
         <v>78547</v>
@@ -2373,17 +2393,17 @@
       <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Härkämäck, Härkämäck, Dlr</t>
+          <t>Andljusbäcken, Andljusbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>459293</v>
+        <v>459611</v>
       </c>
       <c r="R18" t="n">
-        <v>6808123</v>
+        <v>6807987</v>
       </c>
       <c r="S18" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2427,19 +2447,19 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>123829197</v>
+        <v>123829275</v>
       </c>
       <c r="B19" t="n">
         <v>78547</v>
@@ -2479,10 +2499,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>459611</v>
+        <v>459544</v>
       </c>
       <c r="R19" t="n">
-        <v>6807987</v>
+        <v>6807989</v>
       </c>
       <c r="S19" t="n">
         <v>20</v>
@@ -2541,10 +2561,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>123830009</v>
+        <v>123833754</v>
       </c>
       <c r="B20" t="n">
-        <v>78546</v>
+        <v>92293</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2553,41 +2573,41 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6446</v>
+        <v>4364</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Härkämäck, Dlr</t>
+          <t>Härkämäck, Härkämäck, Dlr</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>459480</v>
+        <v>459290</v>
       </c>
       <c r="R20" t="n">
-        <v>6808013</v>
+        <v>6808093</v>
       </c>
       <c r="S20" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2617,11 +2637,6 @@
       <c r="AA20" t="inlineStr">
         <is>
           <t>2025-04-07</t>
-        </is>
-      </c>
-      <c r="AC20" t="inlineStr">
-        <is>
-          <t>Miljöbild.</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2636,22 +2651,22 @@
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>123834641</v>
+        <v>123829712</v>
       </c>
       <c r="B21" t="n">
-        <v>78810</v>
+        <v>91012</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2664,37 +2679,37 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Härkämäck, Härkämäck, Dlr</t>
+          <t>Härkämäck, Dlr</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>459405</v>
+        <v>459573</v>
       </c>
       <c r="R21" t="n">
-        <v>6808172</v>
+        <v>6808047</v>
       </c>
       <c r="S21" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2738,22 +2753,22 @@
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>123828739</v>
+        <v>123829102</v>
       </c>
       <c r="B22" t="n">
-        <v>56722</v>
+        <v>78810</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2762,46 +2777,41 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
-      <c r="M22" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Härkämäck, Dlr</t>
+          <t>Andljusbäcken, Andljusbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>459636</v>
+        <v>459666</v>
       </c>
       <c r="R22" t="n">
-        <v>6808042</v>
+        <v>6807990</v>
       </c>
       <c r="S22" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -2845,22 +2855,22 @@
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>123829941</v>
+        <v>123831277</v>
       </c>
       <c r="B23" t="n">
-        <v>78547</v>
+        <v>57529</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2873,34 +2883,39 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>228912</v>
+        <v>100049</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P23" t="inlineStr">
         <is>
           <t>Härkämäck, Dlr</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>459480</v>
+        <v>459389</v>
       </c>
       <c r="R23" t="n">
-        <v>6808013</v>
+        <v>6808070</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2964,10 +2979,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>123831467</v>
+        <v>123828739</v>
       </c>
       <c r="B24" t="n">
-        <v>79399</v>
+        <v>56722</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -2976,38 +2991,43 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>229821</v>
+        <v>100138</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Härkämäck, Härkämäck, Dlr</t>
+          <t>Härkämäck, Dlr</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>459290</v>
+        <v>459636</v>
       </c>
       <c r="R24" t="n">
-        <v>6808098</v>
+        <v>6808042</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3054,19 +3074,19 @@
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Niklas Rehn</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Niklas Rehn</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>123828742</v>
+        <v>123835432</v>
       </c>
       <c r="B25" t="n">
         <v>78810</v>
@@ -3102,17 +3122,17 @@
       <c r="I25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Andljusbäcken, Andljusbäcken, Dlr</t>
+          <t>Härkämäck, Dlr</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>459612</v>
+        <v>459524</v>
       </c>
       <c r="R25" t="n">
-        <v>6808068</v>
+        <v>6808114</v>
       </c>
       <c r="S25" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3142,6 +3162,11 @@
       <c r="AA25" t="inlineStr">
         <is>
           <t>2025-04-07</t>
+        </is>
+      </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>Garnlav i alla riktningar, ca 50 meter i radie. Miljöbild.</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3156,22 +3181,22 @@
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>123834630</v>
+        <v>123830009</v>
       </c>
       <c r="B26" t="n">
-        <v>57534</v>
+        <v>78546</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3180,38 +3205,38 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>100110</v>
+        <v>6446</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Gråspett</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Picus canus</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>J.F. Gmelin, 1788</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Härkämäck, Härkämäck, Dlr</t>
+          <t>Härkämäck, Dlr</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>459408</v>
+        <v>459480</v>
       </c>
       <c r="R26" t="n">
-        <v>6808198</v>
+        <v>6808013</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3248,7 +3273,7 @@
       </c>
       <c r="AC26" t="inlineStr">
         <is>
-          <t>Förbiflygande.</t>
+          <t>Miljöbild.</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3263,22 +3288,22 @@
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>123834966</v>
+        <v>123833841</v>
       </c>
       <c r="B27" t="n">
-        <v>57534</v>
+        <v>78810</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3287,46 +3312,41 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>100110</v>
+        <v>6425</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Gråspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Picus canus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>J.F. Gmelin, 1788</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
-      <c r="M27" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Härkämäck, Dlr</t>
+          <t>Härkämäck, Härkämäck, Dlr</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>459399</v>
+        <v>459300</v>
       </c>
       <c r="R27" t="n">
-        <v>6808189</v>
+        <v>6808144</v>
       </c>
       <c r="S27" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3356,11 +3376,6 @@
       <c r="AA27" t="inlineStr">
         <is>
           <t>2025-04-07</t>
-        </is>
-      </c>
-      <c r="AC27" t="inlineStr">
-        <is>
-          <t>Förbiflygande.</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3375,22 +3390,22 @@
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>123831244</v>
+        <v>123834966</v>
       </c>
       <c r="B28" t="n">
-        <v>78810</v>
+        <v>57534</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3399,41 +3414,46 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6425</v>
+        <v>100110</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gråspett</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picus canus</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>J.F. Gmelin, 1788</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Andljusbäcken, Andljusbäcken, Dlr</t>
+          <t>Härkämäck, Dlr</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>459393</v>
+        <v>459399</v>
       </c>
       <c r="R28" t="n">
-        <v>6808027</v>
+        <v>6808189</v>
       </c>
       <c r="S28" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3463,6 +3483,11 @@
       <c r="AA28" t="inlineStr">
         <is>
           <t>2025-04-07</t>
+        </is>
+      </c>
+      <c r="AC28" t="inlineStr">
+        <is>
+          <t>Förbiflygande.</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3477,22 +3502,22 @@
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>123834034</v>
+        <v>123829205</v>
       </c>
       <c r="B29" t="n">
-        <v>57529</v>
+        <v>78546</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3505,42 +3530,37 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>100049</v>
+        <v>6446</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
-      <c r="M29" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Andljusen, Dlr</t>
+          <t>Andljusbäcken, Andljusbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>459325</v>
+        <v>459611</v>
       </c>
       <c r="R29" t="n">
-        <v>6808176</v>
+        <v>6807987</v>
       </c>
       <c r="S29" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3570,11 +3590,6 @@
       <c r="AA29" t="inlineStr">
         <is>
           <t>2025-04-07</t>
-        </is>
-      </c>
-      <c r="AC29" t="inlineStr">
-        <is>
-          <t>Miljöbild.</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3589,22 +3604,22 @@
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>123828608</v>
+        <v>123829394</v>
       </c>
       <c r="B30" t="n">
-        <v>78810</v>
+        <v>77738</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3617,21 +3632,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6425</v>
+        <v>6487</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Blågrå svartspik</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenothecopsis fennica</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Laurila) Tibell</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3641,10 +3656,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>459636</v>
+        <v>459586</v>
       </c>
       <c r="R30" t="n">
-        <v>6808042</v>
+        <v>6807981</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3677,11 +3692,6 @@
       <c r="AA30" t="inlineStr">
         <is>
           <t>2025-04-07</t>
-        </is>
-      </c>
-      <c r="AC30" t="inlineStr">
-        <is>
-          <t>Garnlav i synfältet i en radie av ca 50 meter. Miljöbilder.</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3708,10 +3718,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>123828882</v>
+        <v>123828783</v>
       </c>
       <c r="B31" t="n">
-        <v>78842</v>
+        <v>78810</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3724,21 +3734,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3748,10 +3758,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>459600</v>
+        <v>459611</v>
       </c>
       <c r="R31" t="n">
-        <v>6808030</v>
+        <v>6808048</v>
       </c>
       <c r="S31" t="n">
         <v>20</v>
@@ -3917,7 +3927,7 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>123835432</v>
+        <v>123828044</v>
       </c>
       <c r="B33" t="n">
         <v>78810</v>
@@ -3957,10 +3967,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>459524</v>
+        <v>459681</v>
       </c>
       <c r="R33" t="n">
-        <v>6808114</v>
+        <v>6808072</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3997,7 +4007,7 @@
       </c>
       <c r="AC33" t="inlineStr">
         <is>
-          <t>Garnlav i alla riktningar, ca 50 meter i radie. Miljöbild.</t>
+          <t>Garnlav i synfältet i en radie av ca 50 meter. Miljöbild.</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4024,10 +4034,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>123829102</v>
+        <v>123830162</v>
       </c>
       <c r="B34" t="n">
-        <v>78810</v>
+        <v>78194</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4040,37 +4050,37 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6425</v>
+        <v>6437</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Andljusbäcken, Andljusbäcken, Dlr</t>
+          <t>Härkämäck, Dlr</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>459666</v>
+        <v>459480</v>
       </c>
       <c r="R34" t="n">
-        <v>6807990</v>
+        <v>6808013</v>
       </c>
       <c r="S34" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -4100,6 +4110,11 @@
       <c r="AA34" t="inlineStr">
         <is>
           <t>2025-04-07</t>
+        </is>
+      </c>
+      <c r="AC34" t="inlineStr">
+        <is>
+          <t>Miljöbild.</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4114,22 +4129,22 @@
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>123829632</v>
+        <v>123830920</v>
       </c>
       <c r="B35" t="n">
-        <v>91299</v>
+        <v>78455</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4142,37 +4157,37 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>658</v>
+        <v>353</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Härkämäck, Dlr</t>
+          <t>Andljusbäcken, Andljusbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>459573</v>
+        <v>459462</v>
       </c>
       <c r="R35" t="n">
-        <v>6808047</v>
+        <v>6808078</v>
       </c>
       <c r="S35" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -4216,19 +4231,19 @@
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>123834195</v>
+        <v>123833917</v>
       </c>
       <c r="B36" t="n">
         <v>78547</v>
@@ -4264,17 +4279,17 @@
       <c r="I36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Härkämäck, Härkämäck, Dlr</t>
+          <t>Andljusbäcken, Andljusbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>459365</v>
+        <v>459292</v>
       </c>
       <c r="R36" t="n">
-        <v>6808224</v>
+        <v>6808184</v>
       </c>
       <c r="S36" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -4318,22 +4333,22 @@
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>123834890</v>
+        <v>123829121</v>
       </c>
       <c r="B37" t="n">
-        <v>78889</v>
+        <v>78810</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4346,37 +4361,37 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>864</v>
+        <v>6425</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Knottrig blåslav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Hypogymnia bitteri</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Lynge) Ahti</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
-          <t>Härkämäck, Härkämäck, Dlr</t>
+          <t>Härkämäck, Dlr</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>459427</v>
+        <v>459641</v>
       </c>
       <c r="R37" t="n">
-        <v>6808130</v>
+        <v>6807971</v>
       </c>
       <c r="S37" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -4406,6 +4421,11 @@
       <c r="AA37" t="inlineStr">
         <is>
           <t>2025-04-07</t>
+        </is>
+      </c>
+      <c r="AC37" t="inlineStr">
+        <is>
+          <t>I synfältet i en radie av ca 40 meter. Miljöbild.</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4420,22 +4440,22 @@
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>123831067</v>
+        <v>123829632</v>
       </c>
       <c r="B38" t="n">
-        <v>78810</v>
+        <v>91299</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4448,21 +4468,21 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6425</v>
+        <v>658</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4472,10 +4492,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>459439</v>
+        <v>459573</v>
       </c>
       <c r="R38" t="n">
-        <v>6808067</v>
+        <v>6808047</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4508,11 +4528,6 @@
       <c r="AA38" t="inlineStr">
         <is>
           <t>2025-04-07</t>
-        </is>
-      </c>
-      <c r="AC38" t="inlineStr">
-        <is>
-          <t>Synligt i en radie av ca 50 meter. Miljöbild.</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4539,10 +4554,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>123834220</v>
+        <v>123834998</v>
       </c>
       <c r="B39" t="n">
-        <v>78810</v>
+        <v>79399</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4555,37 +4570,37 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6425</v>
+        <v>229821</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
-          <t>Andljusen, Dlr</t>
+          <t>Härkämäck, Härkämäck, Dlr</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>459325</v>
+        <v>459437</v>
       </c>
       <c r="R39" t="n">
-        <v>6808176</v>
+        <v>6808171</v>
       </c>
       <c r="S39" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
@@ -4615,11 +4630,6 @@
       <c r="AA39" t="inlineStr">
         <is>
           <t>2025-04-07</t>
-        </is>
-      </c>
-      <c r="AC39" t="inlineStr">
-        <is>
-          <t>I synfält, radie av ca 50 meter. Miljöbild.</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4634,19 +4644,19 @@
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>123828783</v>
+        <v>123828608</v>
       </c>
       <c r="B40" t="n">
         <v>78810</v>
@@ -4682,17 +4692,17 @@
       <c r="I40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
-          <t>Andljusbäcken, Andljusbäcken, Dlr</t>
+          <t>Härkämäck, Dlr</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>459611</v>
+        <v>459636</v>
       </c>
       <c r="R40" t="n">
-        <v>6808048</v>
+        <v>6808042</v>
       </c>
       <c r="S40" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T40" t="inlineStr">
         <is>
@@ -4722,6 +4732,11 @@
       <c r="AA40" t="inlineStr">
         <is>
           <t>2025-04-07</t>
+        </is>
+      </c>
+      <c r="AC40" t="inlineStr">
+        <is>
+          <t>Garnlav i synfältet i en radie av ca 50 meter. Miljöbilder.</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4736,22 +4751,22 @@
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>123833729</v>
+        <v>123827957</v>
       </c>
       <c r="B41" t="n">
-        <v>78547</v>
+        <v>78546</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -4764,37 +4779,37 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>228912</v>
+        <v>6446</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
-          <t>Andljusen, Dlr</t>
+          <t>Andljusbäcken, Andljusbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>459286</v>
+        <v>459664</v>
       </c>
       <c r="R41" t="n">
-        <v>6808090</v>
+        <v>6808079</v>
       </c>
       <c r="S41" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -4824,11 +4839,6 @@
       <c r="AA41" t="inlineStr">
         <is>
           <t>2025-04-07</t>
-        </is>
-      </c>
-      <c r="AC41" t="inlineStr">
-        <is>
-          <t>Miljöbild.</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -4843,22 +4853,22 @@
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>123834998</v>
+        <v>123829879</v>
       </c>
       <c r="B42" t="n">
-        <v>79399</v>
+        <v>78810</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -4871,34 +4881,34 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>229821</v>
+        <v>6425</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
-          <t>Härkämäck, Härkämäck, Dlr</t>
+          <t>Andljusbäcken, Andljusbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>459437</v>
+        <v>459488</v>
       </c>
       <c r="R42" t="n">
-        <v>6808171</v>
+        <v>6807974</v>
       </c>
       <c r="S42" t="n">
         <v>20</v>
@@ -4957,10 +4967,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>123829246</v>
+        <v>123831097</v>
       </c>
       <c r="B43" t="n">
-        <v>78810</v>
+        <v>79399</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -4973,37 +4983,37 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6425</v>
+        <v>229821</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
-          <t>Härkämäck, Dlr</t>
+          <t>Andljusbäcken, Andljusbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>459586</v>
+        <v>459402</v>
       </c>
       <c r="R43" t="n">
-        <v>6807981</v>
+        <v>6808072</v>
       </c>
       <c r="S43" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T43" t="inlineStr">
         <is>
@@ -5033,11 +5043,6 @@
       <c r="AA43" t="inlineStr">
         <is>
           <t>2025-04-07</t>
-        </is>
-      </c>
-      <c r="AC43" t="inlineStr">
-        <is>
-          <t>Som vanligt garnlav i omgivningen. Miljöbilder.</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5052,22 +5057,22 @@
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>123828044</v>
+        <v>123834006</v>
       </c>
       <c r="B44" t="n">
-        <v>78810</v>
+        <v>78547</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5080,37 +5085,37 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
-          <t>Härkämäck, Dlr</t>
+          <t>Härkämäck, Härkämäck, Dlr</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>459681</v>
+        <v>459326</v>
       </c>
       <c r="R44" t="n">
-        <v>6808072</v>
+        <v>6808188</v>
       </c>
       <c r="S44" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T44" t="inlineStr">
         <is>
@@ -5140,11 +5145,6 @@
       <c r="AA44" t="inlineStr">
         <is>
           <t>2025-04-07</t>
-        </is>
-      </c>
-      <c r="AC44" t="inlineStr">
-        <is>
-          <t>Garnlav i synfältet i en radie av ca 50 meter. Miljöbild.</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5159,12 +5159,12 @@
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
@@ -5278,10 +5278,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>123829712</v>
+        <v>123829918</v>
       </c>
       <c r="B46" t="n">
-        <v>91012</v>
+        <v>78546</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5294,37 +5294,37 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>1202</v>
+        <v>6446</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
-          <t>Härkämäck, Dlr</t>
+          <t>Andljusbäcken, Andljusbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>459573</v>
+        <v>459424</v>
       </c>
       <c r="R46" t="n">
-        <v>6808047</v>
+        <v>6807998</v>
       </c>
       <c r="S46" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T46" t="inlineStr">
         <is>
@@ -5368,22 +5368,22 @@
       <c r="AT46" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX46" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>123830920</v>
+        <v>123829982</v>
       </c>
       <c r="B47" t="n">
-        <v>78455</v>
+        <v>77738</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5396,21 +5396,21 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>353</v>
+        <v>6487</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Blågrå svartspik</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Chaenothecopsis fennica</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Laurila) Tibell</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5420,10 +5420,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>459462</v>
+        <v>459432</v>
       </c>
       <c r="R47" t="n">
-        <v>6808078</v>
+        <v>6807989</v>
       </c>
       <c r="S47" t="n">
         <v>20</v>
@@ -5482,10 +5482,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>123829205</v>
+        <v>123834195</v>
       </c>
       <c r="B48" t="n">
-        <v>78546</v>
+        <v>78547</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -5498,37 +5498,37 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>6446</v>
+        <v>228912</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
-          <t>Andljusbäcken, Andljusbäcken, Dlr</t>
+          <t>Härkämäck, Härkämäck, Dlr</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>459611</v>
+        <v>459365</v>
       </c>
       <c r="R48" t="n">
-        <v>6807987</v>
+        <v>6808224</v>
       </c>
       <c r="S48" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T48" t="inlineStr">
         <is>
@@ -5572,22 +5572,22 @@
       <c r="AT48" t="inlineStr"/>
       <c r="AW48" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX48" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>123829879</v>
+        <v>123834630</v>
       </c>
       <c r="B49" t="n">
-        <v>78810</v>
+        <v>57534</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -5596,41 +5596,41 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>6425</v>
+        <v>100110</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gråspett</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picus canus</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>J.F. Gmelin, 1788</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
-          <t>Andljusbäcken, Andljusbäcken, Dlr</t>
+          <t>Härkämäck, Härkämäck, Dlr</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>459488</v>
+        <v>459408</v>
       </c>
       <c r="R49" t="n">
-        <v>6807974</v>
+        <v>6808198</v>
       </c>
       <c r="S49" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T49" t="inlineStr">
         <is>
@@ -5660,6 +5660,11 @@
       <c r="AA49" t="inlineStr">
         <is>
           <t>2025-04-07</t>
+        </is>
+      </c>
+      <c r="AC49" t="inlineStr">
+        <is>
+          <t>Förbiflygande.</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -5674,22 +5679,22 @@
       <c r="AT49" t="inlineStr"/>
       <c r="AW49" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX49" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>123831578</v>
+        <v>123831244</v>
       </c>
       <c r="B50" t="n">
-        <v>74901</v>
+        <v>78810</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -5702,21 +5707,21 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5726,10 +5731,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>459287</v>
+        <v>459393</v>
       </c>
       <c r="R50" t="n">
-        <v>6808008</v>
+        <v>6808027</v>
       </c>
       <c r="S50" t="n">
         <v>20</v>
@@ -5788,10 +5793,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>123834650</v>
+        <v>123831578</v>
       </c>
       <c r="B51" t="n">
-        <v>78547</v>
+        <v>74901</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -5804,37 +5809,37 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>228912</v>
+        <v>6440</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
-          <t>Härkämäck, Dlr</t>
+          <t>Andljusbäcken, Andljusbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>459399</v>
+        <v>459287</v>
       </c>
       <c r="R51" t="n">
-        <v>6808189</v>
+        <v>6808008</v>
       </c>
       <c r="S51" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T51" t="inlineStr">
         <is>
@@ -5864,11 +5869,6 @@
       <c r="AA51" t="inlineStr">
         <is>
           <t>2025-04-07</t>
-        </is>
-      </c>
-      <c r="AC51" t="inlineStr">
-        <is>
-          <t>Miljöbild</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -5883,22 +5883,22 @@
       <c r="AT51" t="inlineStr"/>
       <c r="AW51" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX51" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>123834006</v>
+        <v>123834890</v>
       </c>
       <c r="B52" t="n">
-        <v>78547</v>
+        <v>78889</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -5911,21 +5911,21 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>228912</v>
+        <v>864</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Lynge) Ahti</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -5935,13 +5935,13 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>459326</v>
+        <v>459427</v>
       </c>
       <c r="R52" t="n">
-        <v>6808188</v>
+        <v>6808130</v>
       </c>
       <c r="S52" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T52" t="inlineStr">
         <is>
@@ -5985,22 +5985,22 @@
       <c r="AT52" t="inlineStr"/>
       <c r="AW52" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX52" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>123920732</v>
+        <v>123920441</v>
       </c>
       <c r="B53" t="n">
-        <v>78810</v>
+        <v>56722</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -6009,38 +6009,43 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
+      <c r="M53" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="P53" t="inlineStr">
         <is>
           <t>Härkämäck, Dlr</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>459616</v>
+        <v>459609</v>
       </c>
       <c r="R53" t="n">
-        <v>6808044</v>
+        <v>6807987</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6092,17 +6097,17 @@
       </c>
       <c r="AX53" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Anders Heggestad, lennart karlsson, Håkan Thenander, Niklas Rehn</t>
+          <t>Philipp Weiss, Anders Heggestad, Håkan Thenander, lennart karlsson, Niklas Rehn</t>
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>123920728</v>
+        <v>123920440</v>
       </c>
       <c r="B54" t="n">
-        <v>78810</v>
+        <v>56722</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -6111,38 +6116,43 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
+      <c r="M54" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="P54" t="inlineStr">
         <is>
           <t>Härkämäck, Dlr</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>459539</v>
+        <v>459617</v>
       </c>
       <c r="R54" t="n">
-        <v>6808073</v>
+        <v>6808041</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6194,14 +6204,14 @@
       </c>
       <c r="AX54" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Anders Heggestad, lennart karlsson, Håkan Thenander, Niklas Rehn</t>
+          <t>Philipp Weiss, Anders Heggestad, Håkan Thenander, lennart karlsson, Niklas Rehn</t>
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>123920730</v>
+        <v>123920729</v>
       </c>
       <c r="B55" t="n">
         <v>78810</v>
@@ -6241,10 +6251,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>459590</v>
+        <v>459566</v>
       </c>
       <c r="R55" t="n">
-        <v>6808062</v>
+        <v>6808068</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6303,10 +6313,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>123920440</v>
+        <v>123920731</v>
       </c>
       <c r="B56" t="n">
-        <v>56722</v>
+        <v>78810</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -6315,43 +6325,38 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
-      <c r="M56" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="P56" t="inlineStr">
         <is>
           <t>Härkämäck, Dlr</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>459617</v>
+        <v>459608</v>
       </c>
       <c r="R56" t="n">
-        <v>6808041</v>
+        <v>6808066</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6403,17 +6408,17 @@
       </c>
       <c r="AX56" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Anders Heggestad, Håkan Thenander, lennart karlsson, Niklas Rehn</t>
+          <t>Philipp Weiss, Anders Heggestad, lennart karlsson, Håkan Thenander, Niklas Rehn</t>
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>123920540</v>
+        <v>123920442</v>
       </c>
       <c r="B57" t="n">
-        <v>78547</v>
+        <v>56722</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -6422,38 +6427,43 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>228912</v>
+        <v>100138</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
+      <c r="M57" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="P57" t="inlineStr">
         <is>
           <t>Härkämäck, Dlr</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>459589</v>
+        <v>459593</v>
       </c>
       <c r="R57" t="n">
-        <v>6807980</v>
+        <v>6807978</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6505,17 +6515,17 @@
       </c>
       <c r="AX57" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Anders Heggestad, lennart karlsson, Håkan Thenander, Niklas Rehn</t>
+          <t>Philipp Weiss, Anders Heggestad, Håkan Thenander, lennart karlsson, Niklas Rehn</t>
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>123920419</v>
+        <v>123920733</v>
       </c>
       <c r="B58" t="n">
-        <v>91012</v>
+        <v>78810</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
@@ -6528,21 +6538,21 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -6552,10 +6562,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>459603</v>
+        <v>459589</v>
       </c>
       <c r="R58" t="n">
-        <v>6807965</v>
+        <v>6807980</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6607,17 +6617,17 @@
       </c>
       <c r="AX58" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Anders Heggestad, Håkan Thenander, lennart karlsson, Niklas Rehn</t>
+          <t>Philipp Weiss, Anders Heggestad, lennart karlsson, Håkan Thenander, Niklas Rehn</t>
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>123920442</v>
+        <v>123920732</v>
       </c>
       <c r="B59" t="n">
-        <v>56722</v>
+        <v>78810</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
@@ -6626,43 +6636,38 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
-      <c r="M59" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="P59" t="inlineStr">
         <is>
           <t>Härkämäck, Dlr</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>459593</v>
+        <v>459616</v>
       </c>
       <c r="R59" t="n">
-        <v>6807978</v>
+        <v>6808044</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6714,17 +6719,17 @@
       </c>
       <c r="AX59" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Anders Heggestad, Håkan Thenander, lennart karlsson, Niklas Rehn</t>
+          <t>Philipp Weiss, Anders Heggestad, lennart karlsson, Håkan Thenander, Niklas Rehn</t>
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>123920930</v>
+        <v>123920540</v>
       </c>
       <c r="B60" t="n">
-        <v>78455</v>
+        <v>78547</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
@@ -6737,21 +6742,21 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>353</v>
+        <v>228912</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -6761,10 +6766,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>459600</v>
+        <v>459589</v>
       </c>
       <c r="R60" t="n">
-        <v>6807961</v>
+        <v>6807980</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6823,7 +6828,7 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>123920729</v>
+        <v>123920734</v>
       </c>
       <c r="B61" t="n">
         <v>78810</v>
@@ -6863,10 +6868,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>459566</v>
+        <v>459613</v>
       </c>
       <c r="R61" t="n">
-        <v>6808068</v>
+        <v>6807959</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -6925,10 +6930,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>123920733</v>
+        <v>123920419</v>
       </c>
       <c r="B62" t="n">
-        <v>78810</v>
+        <v>91012</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
@@ -6941,21 +6946,21 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -6965,10 +6970,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>459589</v>
+        <v>459603</v>
       </c>
       <c r="R62" t="n">
-        <v>6807980</v>
+        <v>6807965</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -7020,17 +7025,17 @@
       </c>
       <c r="AX62" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Anders Heggestad, lennart karlsson, Håkan Thenander, Niklas Rehn</t>
+          <t>Philipp Weiss, Anders Heggestad, Håkan Thenander, lennart karlsson, Niklas Rehn</t>
         </is>
       </c>
       <c r="AY62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>123920734</v>
+        <v>123920930</v>
       </c>
       <c r="B63" t="n">
-        <v>78810</v>
+        <v>78455</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
@@ -7043,21 +7048,21 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -7067,10 +7072,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>459613</v>
+        <v>459600</v>
       </c>
       <c r="R63" t="n">
-        <v>6807959</v>
+        <v>6807961</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -7129,10 +7134,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>123920427</v>
+        <v>123920727</v>
       </c>
       <c r="B64" t="n">
-        <v>57513</v>
+        <v>78810</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
@@ -7145,39 +7150,34 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
-      <c r="M64" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
       <c r="P64" t="inlineStr">
         <is>
           <t>Härkämäck, Dlr</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>459571</v>
+        <v>459542</v>
       </c>
       <c r="R64" t="n">
-        <v>6808057</v>
+        <v>6808123</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7229,17 +7229,17 @@
       </c>
       <c r="AX64" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Anders Heggestad, Håkan Thenander, lennart karlsson, Niklas Rehn</t>
+          <t>Philipp Weiss, Anders Heggestad, lennart karlsson, Håkan Thenander, Niklas Rehn</t>
         </is>
       </c>
       <c r="AY64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>123920441</v>
+        <v>123920730</v>
       </c>
       <c r="B65" t="n">
-        <v>56722</v>
+        <v>78810</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
@@ -7248,43 +7248,38 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
-      <c r="M65" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="P65" t="inlineStr">
         <is>
           <t>Härkämäck, Dlr</t>
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>459609</v>
+        <v>459590</v>
       </c>
       <c r="R65" t="n">
-        <v>6807987</v>
+        <v>6808062</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7336,17 +7331,17 @@
       </c>
       <c r="AX65" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Anders Heggestad, Håkan Thenander, lennart karlsson, Niklas Rehn</t>
+          <t>Philipp Weiss, Anders Heggestad, lennart karlsson, Håkan Thenander, Niklas Rehn</t>
         </is>
       </c>
       <c r="AY65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>123920399</v>
+        <v>123920427</v>
       </c>
       <c r="B66" t="n">
-        <v>79399</v>
+        <v>57513</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
@@ -7359,34 +7354,39 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>229821</v>
+        <v>100109</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
+      <c r="M66" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="P66" t="inlineStr">
         <is>
           <t>Härkämäck, Dlr</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>459591</v>
+        <v>459571</v>
       </c>
       <c r="R66" t="n">
-        <v>6808065</v>
+        <v>6808057</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7445,7 +7445,7 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>123920731</v>
+        <v>123920728</v>
       </c>
       <c r="B67" t="n">
         <v>78810</v>
@@ -7485,10 +7485,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>459608</v>
+        <v>459539</v>
       </c>
       <c r="R67" t="n">
-        <v>6808066</v>
+        <v>6808073</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7547,10 +7547,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>123920727</v>
+        <v>123920399</v>
       </c>
       <c r="B68" t="n">
-        <v>78810</v>
+        <v>79399</v>
       </c>
       <c r="C68" t="inlineStr">
         <is>
@@ -7563,21 +7563,21 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>6425</v>
+        <v>229821</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
@@ -7587,10 +7587,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>459542</v>
+        <v>459591</v>
       </c>
       <c r="R68" t="n">
-        <v>6808123</v>
+        <v>6808065</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7642,7 +7642,7 @@
       </c>
       <c r="AX68" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Anders Heggestad, lennart karlsson, Håkan Thenander, Niklas Rehn</t>
+          <t>Philipp Weiss, Anders Heggestad, Håkan Thenander, lennart karlsson, Niklas Rehn</t>
         </is>
       </c>
       <c r="AY68" t="inlineStr"/>

--- a/artfynd/A 61327-2022 artfynd.xlsx
+++ b/artfynd/A 61327-2022 artfynd.xlsx
@@ -5997,7 +5997,7 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>123920441</v>
+        <v>123920440</v>
       </c>
       <c r="B53" t="n">
         <v>56722</v>
@@ -6042,10 +6042,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>459609</v>
+        <v>459617</v>
       </c>
       <c r="R53" t="n">
-        <v>6807987</v>
+        <v>6808041</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6104,10 +6104,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>123920440</v>
+        <v>123920734</v>
       </c>
       <c r="B54" t="n">
-        <v>56722</v>
+        <v>78810</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -6116,43 +6116,38 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
-      <c r="M54" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="P54" t="inlineStr">
         <is>
           <t>Härkämäck, Dlr</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>459617</v>
+        <v>459613</v>
       </c>
       <c r="R54" t="n">
-        <v>6808041</v>
+        <v>6807959</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6204,14 +6199,14 @@
       </c>
       <c r="AX54" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Anders Heggestad, Håkan Thenander, lennart karlsson, Niklas Rehn</t>
+          <t>Philipp Weiss, Anders Heggestad, lennart karlsson, Håkan Thenander, Niklas Rehn</t>
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>123920729</v>
+        <v>123920731</v>
       </c>
       <c r="B55" t="n">
         <v>78810</v>
@@ -6251,10 +6246,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>459566</v>
+        <v>459608</v>
       </c>
       <c r="R55" t="n">
-        <v>6808068</v>
+        <v>6808066</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6313,10 +6308,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>123920731</v>
+        <v>123920399</v>
       </c>
       <c r="B56" t="n">
-        <v>78810</v>
+        <v>79399</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -6329,21 +6324,21 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>6425</v>
+        <v>229821</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6353,10 +6348,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>459608</v>
+        <v>459591</v>
       </c>
       <c r="R56" t="n">
-        <v>6808066</v>
+        <v>6808065</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6408,17 +6403,17 @@
       </c>
       <c r="AX56" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Anders Heggestad, lennart karlsson, Håkan Thenander, Niklas Rehn</t>
+          <t>Philipp Weiss, Anders Heggestad, Håkan Thenander, lennart karlsson, Niklas Rehn</t>
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>123920442</v>
+        <v>123920730</v>
       </c>
       <c r="B57" t="n">
-        <v>56722</v>
+        <v>78810</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -6427,43 +6422,38 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
-      <c r="M57" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="P57" t="inlineStr">
         <is>
           <t>Härkämäck, Dlr</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>459593</v>
+        <v>459590</v>
       </c>
       <c r="R57" t="n">
-        <v>6807978</v>
+        <v>6808062</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6515,14 +6505,14 @@
       </c>
       <c r="AX57" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Anders Heggestad, Håkan Thenander, lennart karlsson, Niklas Rehn</t>
+          <t>Philipp Weiss, Anders Heggestad, lennart karlsson, Håkan Thenander, Niklas Rehn</t>
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>123920733</v>
+        <v>123920727</v>
       </c>
       <c r="B58" t="n">
         <v>78810</v>
@@ -6562,10 +6552,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>459589</v>
+        <v>459542</v>
       </c>
       <c r="R58" t="n">
-        <v>6807980</v>
+        <v>6808123</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6624,10 +6614,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>123920732</v>
+        <v>123920442</v>
       </c>
       <c r="B59" t="n">
-        <v>78810</v>
+        <v>56722</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
@@ -6636,38 +6626,43 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
+      <c r="M59" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="P59" t="inlineStr">
         <is>
           <t>Härkämäck, Dlr</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>459616</v>
+        <v>459593</v>
       </c>
       <c r="R59" t="n">
-        <v>6808044</v>
+        <v>6807978</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6719,17 +6714,17 @@
       </c>
       <c r="AX59" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Anders Heggestad, lennart karlsson, Håkan Thenander, Niklas Rehn</t>
+          <t>Philipp Weiss, Anders Heggestad, Håkan Thenander, lennart karlsson, Niklas Rehn</t>
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>123920540</v>
+        <v>123920419</v>
       </c>
       <c r="B60" t="n">
-        <v>78547</v>
+        <v>91012</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
@@ -6742,21 +6737,21 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>228912</v>
+        <v>1202</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -6766,10 +6761,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>459589</v>
+        <v>459603</v>
       </c>
       <c r="R60" t="n">
-        <v>6807980</v>
+        <v>6807965</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6821,17 +6816,17 @@
       </c>
       <c r="AX60" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Anders Heggestad, lennart karlsson, Håkan Thenander, Niklas Rehn</t>
+          <t>Philipp Weiss, Anders Heggestad, Håkan Thenander, lennart karlsson, Niklas Rehn</t>
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>123920734</v>
+        <v>123920441</v>
       </c>
       <c r="B61" t="n">
-        <v>78810</v>
+        <v>56722</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
@@ -6840,38 +6835,43 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
+      <c r="M61" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="P61" t="inlineStr">
         <is>
           <t>Härkämäck, Dlr</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>459613</v>
+        <v>459609</v>
       </c>
       <c r="R61" t="n">
-        <v>6807959</v>
+        <v>6807987</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -6923,17 +6923,17 @@
       </c>
       <c r="AX61" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Anders Heggestad, lennart karlsson, Håkan Thenander, Niklas Rehn</t>
+          <t>Philipp Weiss, Anders Heggestad, Håkan Thenander, lennart karlsson, Niklas Rehn</t>
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>123920419</v>
+        <v>123920930</v>
       </c>
       <c r="B62" t="n">
-        <v>91012</v>
+        <v>78455</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
@@ -6946,21 +6946,21 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>1202</v>
+        <v>353</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -6970,10 +6970,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>459603</v>
+        <v>459600</v>
       </c>
       <c r="R62" t="n">
-        <v>6807965</v>
+        <v>6807961</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -7025,17 +7025,17 @@
       </c>
       <c r="AX62" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Anders Heggestad, Håkan Thenander, lennart karlsson, Niklas Rehn</t>
+          <t>Philipp Weiss, Niklas Rehn, Håkan Thenander, lennart karlsson, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>123920930</v>
+        <v>123920540</v>
       </c>
       <c r="B63" t="n">
-        <v>78455</v>
+        <v>78547</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
@@ -7048,21 +7048,21 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>353</v>
+        <v>228912</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -7072,10 +7072,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>459600</v>
+        <v>459589</v>
       </c>
       <c r="R63" t="n">
-        <v>6807961</v>
+        <v>6807980</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -7134,10 +7134,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>123920727</v>
+        <v>123920427</v>
       </c>
       <c r="B64" t="n">
-        <v>78810</v>
+        <v>57513</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
@@ -7150,34 +7150,39 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
+      <c r="M64" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="P64" t="inlineStr">
         <is>
           <t>Härkämäck, Dlr</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>459542</v>
+        <v>459571</v>
       </c>
       <c r="R64" t="n">
-        <v>6808123</v>
+        <v>6808057</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7229,14 +7234,14 @@
       </c>
       <c r="AX64" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Anders Heggestad, lennart karlsson, Håkan Thenander, Niklas Rehn</t>
+          <t>Philipp Weiss, Anders Heggestad, Håkan Thenander, lennart karlsson, Niklas Rehn</t>
         </is>
       </c>
       <c r="AY64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>123920730</v>
+        <v>123920732</v>
       </c>
       <c r="B65" t="n">
         <v>78810</v>
@@ -7276,10 +7281,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>459590</v>
+        <v>459616</v>
       </c>
       <c r="R65" t="n">
-        <v>6808062</v>
+        <v>6808044</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7338,10 +7343,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>123920427</v>
+        <v>123920729</v>
       </c>
       <c r="B66" t="n">
-        <v>57513</v>
+        <v>78810</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
@@ -7354,39 +7359,34 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
-      <c r="M66" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
       <c r="P66" t="inlineStr">
         <is>
           <t>Härkämäck, Dlr</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>459571</v>
+        <v>459566</v>
       </c>
       <c r="R66" t="n">
-        <v>6808057</v>
+        <v>6808068</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7438,7 +7438,7 @@
       </c>
       <c r="AX66" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Anders Heggestad, Håkan Thenander, lennart karlsson, Niklas Rehn</t>
+          <t>Philipp Weiss, Anders Heggestad, lennart karlsson, Håkan Thenander, Niklas Rehn</t>
         </is>
       </c>
       <c r="AY66" t="inlineStr"/>
@@ -7547,10 +7547,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>123920399</v>
+        <v>123920733</v>
       </c>
       <c r="B68" t="n">
-        <v>79399</v>
+        <v>78810</v>
       </c>
       <c r="C68" t="inlineStr">
         <is>
@@ -7563,21 +7563,21 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>229821</v>
+        <v>6425</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
@@ -7587,10 +7587,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>459591</v>
+        <v>459589</v>
       </c>
       <c r="R68" t="n">
-        <v>6808065</v>
+        <v>6807980</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7642,7 +7642,7 @@
       </c>
       <c r="AX68" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Anders Heggestad, Håkan Thenander, lennart karlsson, Niklas Rehn</t>
+          <t>Philipp Weiss, Anders Heggestad, lennart karlsson, Håkan Thenander, Niklas Rehn</t>
         </is>
       </c>
       <c r="AY68" t="inlineStr"/>

--- a/artfynd/A 61327-2022 artfynd.xlsx
+++ b/artfynd/A 61327-2022 artfynd.xlsx
@@ -6823,10 +6823,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>123920441</v>
+        <v>123920540</v>
       </c>
       <c r="B61" t="n">
-        <v>56722</v>
+        <v>78547</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
@@ -6835,43 +6835,38 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>100138</v>
+        <v>228912</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
-      <c r="M61" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="P61" t="inlineStr">
         <is>
           <t>Härkämäck, Dlr</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>459609</v>
+        <v>459589</v>
       </c>
       <c r="R61" t="n">
-        <v>6807987</v>
+        <v>6807980</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -6923,7 +6918,7 @@
       </c>
       <c r="AX61" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Anders Heggestad, Håkan Thenander, lennart karlsson, Niklas Rehn</t>
+          <t>Philipp Weiss, Anders Heggestad, lennart karlsson, Håkan Thenander, Niklas Rehn</t>
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
@@ -7032,10 +7027,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>123920540</v>
+        <v>123920441</v>
       </c>
       <c r="B63" t="n">
-        <v>78547</v>
+        <v>56722</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
@@ -7044,38 +7039,43 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>228912</v>
+        <v>100138</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
+      <c r="M63" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="P63" t="inlineStr">
         <is>
           <t>Härkämäck, Dlr</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>459589</v>
+        <v>459609</v>
       </c>
       <c r="R63" t="n">
-        <v>6807980</v>
+        <v>6807987</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -7127,7 +7127,7 @@
       </c>
       <c r="AX63" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Anders Heggestad, lennart karlsson, Håkan Thenander, Niklas Rehn</t>
+          <t>Philipp Weiss, Anders Heggestad, Håkan Thenander, lennart karlsson, Niklas Rehn</t>
         </is>
       </c>
       <c r="AY63" t="inlineStr"/>
